--- a/2_Johto_Data.xlsx
+++ b/2_Johto_Data.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G263"/>
+  <dimension ref="A1:G274"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1086,7 +1086,7 @@
         <v>9-13</v>
       </c>
       <c r="F30" t="str">
-        <v>20%</v>
+        <v>17%</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -1109,7 +1109,7 @@
         <v>9-13</v>
       </c>
       <c r="F31" t="str">
-        <v>30%</v>
+        <v>25%</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -1132,7 +1132,7 @@
         <v>9-13</v>
       </c>
       <c r="F32" t="str">
-        <v>20%</v>
+        <v>16%</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>9-13</v>
       </c>
       <c r="F33" t="str">
-        <v>30%</v>
+        <v>25%</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -1163,22 +1163,22 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Challenge 9</v>
+        <v>Challenge 7</v>
       </c>
       <c r="B34" t="str">
-        <v>Ilex Forest</v>
+        <v>Route 33</v>
       </c>
       <c r="C34" t="str">
         <v/>
       </c>
       <c r="D34" t="str">
-        <v>Paras</v>
+        <v>Skiploom</v>
       </c>
       <c r="E34" t="str">
-        <v>13-17</v>
+        <v>9-13</v>
       </c>
       <c r="F34" t="str">
-        <v>30%</v>
+        <v>8%</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -1186,22 +1186,22 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Challenge 9</v>
+        <v>Challenge 7</v>
       </c>
       <c r="B35" t="str">
-        <v>Ilex Forest</v>
+        <v>Route 33</v>
       </c>
       <c r="C35" t="str">
         <v/>
       </c>
       <c r="D35" t="str">
-        <v>Caterpie</v>
+        <v>Aipom</v>
       </c>
       <c r="E35" t="str">
-        <v>12-16</v>
+        <v>9-13</v>
       </c>
       <c r="F35" t="str">
-        <v>20%</v>
+        <v>9%</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -1218,13 +1218,13 @@
         <v/>
       </c>
       <c r="D36" t="str">
-        <v>Weedle</v>
+        <v>Paras</v>
       </c>
       <c r="E36" t="str">
-        <v>12-16</v>
+        <v>13-17</v>
       </c>
       <c r="F36" t="str">
-        <v>20%</v>
+        <v>30%</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -1241,13 +1241,13 @@
         <v/>
       </c>
       <c r="D37" t="str">
-        <v>Metapod</v>
+        <v>Caterpie</v>
       </c>
       <c r="E37" t="str">
-        <v>13-17</v>
+        <v>12-16</v>
       </c>
       <c r="F37" t="str">
-        <v>15%</v>
+        <v>20%</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -1264,13 +1264,13 @@
         <v/>
       </c>
       <c r="D38" t="str">
-        <v>Kakuna</v>
+        <v>Weedle</v>
       </c>
       <c r="E38" t="str">
-        <v>13-17</v>
+        <v>12-16</v>
       </c>
       <c r="F38" t="str">
-        <v>15%</v>
+        <v>20%</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -1278,22 +1278,22 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Challenge 10</v>
+        <v>Challenge 9</v>
       </c>
       <c r="B39" t="str">
-        <v>Route 34</v>
+        <v>Ilex Forest</v>
       </c>
       <c r="C39" t="str">
         <v/>
       </c>
       <c r="D39" t="str">
-        <v>Drowzee</v>
+        <v>Metapod</v>
       </c>
       <c r="E39" t="str">
-        <v>15-19</v>
+        <v>13-17</v>
       </c>
       <c r="F39" t="str">
-        <v>20%</v>
+        <v>15%</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Challenge 10</v>
+        <v>Challenge 9</v>
       </c>
       <c r="B40" t="str">
-        <v>Route 34</v>
+        <v>Ilex Forest</v>
       </c>
       <c r="C40" t="str">
         <v/>
       </c>
       <c r="D40" t="str">
-        <v>Snubbull</v>
+        <v>Kakuna</v>
       </c>
       <c r="E40" t="str">
-        <v>15-19</v>
+        <v>13-17</v>
       </c>
       <c r="F40" t="str">
-        <v>35%</v>
+        <v>15%</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -1333,13 +1333,13 @@
         <v/>
       </c>
       <c r="D41" t="str">
-        <v>Jigglypuff</v>
+        <v>Drowzee</v>
       </c>
       <c r="E41" t="str">
-        <v>14-18</v>
+        <v>15-19</v>
       </c>
       <c r="F41" t="str">
-        <v>35%</v>
+        <v>20%</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -1356,13 +1356,13 @@
         <v/>
       </c>
       <c r="D42" t="str">
-        <v>Ditto</v>
+        <v>Snubbull</v>
       </c>
       <c r="E42" t="str">
-        <v>15-20</v>
+        <v>15-19</v>
       </c>
       <c r="F42" t="str">
-        <v>10%</v>
+        <v>35%</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -1370,19 +1370,19 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Challenge 12</v>
+        <v>Challenge 10</v>
       </c>
       <c r="B43" t="str">
-        <v>Route 35</v>
+        <v>Route 34</v>
       </c>
       <c r="C43" t="str">
         <v/>
       </c>
       <c r="D43" t="str">
-        <v>Yanma</v>
+        <v>Jigglypuff</v>
       </c>
       <c r="E43" t="str">
-        <v>20-25</v>
+        <v>14-18</v>
       </c>
       <c r="F43" t="str">
         <v>35%</v>
@@ -1393,22 +1393,22 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Challenge 12</v>
+        <v>Challenge 10</v>
       </c>
       <c r="B44" t="str">
-        <v>Route 35</v>
+        <v>Route 34</v>
       </c>
       <c r="C44" t="str">
         <v/>
       </c>
       <c r="D44" t="str">
-        <v>Growlithe</v>
+        <v>Ditto</v>
       </c>
       <c r="E44" t="str">
-        <v>20-25</v>
+        <v>15-20</v>
       </c>
       <c r="F44" t="str">
-        <v>25%</v>
+        <v>10%</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -1425,13 +1425,13 @@
         <v/>
       </c>
       <c r="D45" t="str">
-        <v>Nidoran♀</v>
+        <v>Yanma</v>
       </c>
       <c r="E45" t="str">
-        <v>19-24</v>
+        <v>20-25</v>
       </c>
       <c r="F45" t="str">
-        <v>20%</v>
+        <v>35%</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -1448,13 +1448,13 @@
         <v/>
       </c>
       <c r="D46" t="str">
-        <v>Nidoran♂</v>
+        <v>Growlithe</v>
       </c>
       <c r="E46" t="str">
-        <v>19-24</v>
+        <v>20-25</v>
       </c>
       <c r="F46" t="str">
-        <v>20%</v>
+        <v>25%</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -1462,22 +1462,22 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Challenge 13</v>
+        <v>Challenge 12</v>
       </c>
       <c r="B47" t="str">
-        <v>National Park</v>
+        <v>Route 35</v>
       </c>
       <c r="C47" t="str">
         <v/>
       </c>
       <c r="D47" t="str">
-        <v>Sunkern</v>
+        <v>Nidoran♀</v>
       </c>
       <c r="E47" t="str">
-        <v>22-27</v>
+        <v>19-24</v>
       </c>
       <c r="F47" t="str">
-        <v>30%</v>
+        <v>20%</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -1485,19 +1485,19 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Challenge 13</v>
+        <v>Challenge 12</v>
       </c>
       <c r="B48" t="str">
-        <v>National Park</v>
+        <v>Route 35</v>
       </c>
       <c r="C48" t="str">
         <v/>
       </c>
       <c r="D48" t="str">
-        <v>Caterpie</v>
+        <v>Nidoran♂</v>
       </c>
       <c r="E48" t="str">
-        <v>20-25</v>
+        <v>19-24</v>
       </c>
       <c r="F48" t="str">
         <v>20%</v>
@@ -1517,13 +1517,13 @@
         <v/>
       </c>
       <c r="D49" t="str">
-        <v>Weedle</v>
+        <v>Sunkern</v>
       </c>
       <c r="E49" t="str">
-        <v>20-25</v>
+        <v>22-27</v>
       </c>
       <c r="F49" t="str">
-        <v>20%</v>
+        <v>27%</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -1540,13 +1540,13 @@
         <v/>
       </c>
       <c r="D50" t="str">
-        <v>Scyther</v>
+        <v>Caterpie</v>
       </c>
       <c r="E50" t="str">
-        <v>24-28</v>
+        <v>20-25</v>
       </c>
       <c r="F50" t="str">
-        <v>15%</v>
+        <v>18%</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -1563,13 +1563,13 @@
         <v/>
       </c>
       <c r="D51" t="str">
-        <v>Pinsir</v>
+        <v>Weedle</v>
       </c>
       <c r="E51" t="str">
-        <v>24-28</v>
+        <v>20-25</v>
       </c>
       <c r="F51" t="str">
-        <v>15%</v>
+        <v>18%</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -1577,22 +1577,22 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Challenge 14</v>
+        <v>Challenge 13</v>
       </c>
       <c r="B52" t="str">
-        <v>Route 36</v>
+        <v>National Park</v>
       </c>
       <c r="C52" t="str">
         <v/>
       </c>
       <c r="D52" t="str">
-        <v>Stantler</v>
+        <v>Scyther</v>
       </c>
       <c r="E52" t="str">
-        <v>24-29</v>
+        <v>24-28</v>
       </c>
       <c r="F52" t="str">
-        <v>30%</v>
+        <v>14%</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -1600,22 +1600,22 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Challenge 14</v>
+        <v>Challenge 13</v>
       </c>
       <c r="B53" t="str">
-        <v>Route 36</v>
+        <v>National Park</v>
       </c>
       <c r="C53" t="str">
         <v/>
       </c>
       <c r="D53" t="str">
-        <v>Vulpix</v>
+        <v>Pinsir</v>
       </c>
       <c r="E53" t="str">
-        <v>24-29</v>
+        <v>24-28</v>
       </c>
       <c r="F53" t="str">
-        <v>25%</v>
+        <v>14%</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -1623,22 +1623,22 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Challenge 14</v>
+        <v>Challenge 13</v>
       </c>
       <c r="B54" t="str">
-        <v>Route 36</v>
+        <v>National Park</v>
       </c>
       <c r="C54" t="str">
         <v/>
       </c>
       <c r="D54" t="str">
-        <v>Growlithe</v>
+        <v>Venonat</v>
       </c>
       <c r="E54" t="str">
-        <v>24-29</v>
+        <v>20-28</v>
       </c>
       <c r="F54" t="str">
-        <v>25%</v>
+        <v>9%</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -1655,13 +1655,13 @@
         <v/>
       </c>
       <c r="D55" t="str">
-        <v>Gastly</v>
+        <v>Stantler</v>
       </c>
       <c r="E55" t="str">
-        <v>23-28</v>
+        <v>24-29</v>
       </c>
       <c r="F55" t="str">
-        <v>10%</v>
+        <v>30%</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -1678,13 +1678,13 @@
         <v/>
       </c>
       <c r="D56" t="str">
-        <v>Sudowoodo</v>
+        <v>Vulpix</v>
       </c>
       <c r="E56" t="str">
-        <v>26-30</v>
+        <v>24-29</v>
       </c>
       <c r="F56" t="str">
-        <v>10%</v>
+        <v>25%</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -1692,22 +1692,22 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Challenge 15</v>
+        <v>Challenge 14</v>
       </c>
       <c r="B57" t="str">
-        <v>Route 37</v>
+        <v>Route 36</v>
       </c>
       <c r="C57" t="str">
         <v/>
       </c>
       <c r="D57" t="str">
-        <v>Pidgeotto</v>
+        <v>Growlithe</v>
       </c>
       <c r="E57" t="str">
-        <v>26-31</v>
+        <v>24-29</v>
       </c>
       <c r="F57" t="str">
-        <v>30%</v>
+        <v>25%</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -1715,22 +1715,22 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Challenge 15</v>
+        <v>Challenge 14</v>
       </c>
       <c r="B58" t="str">
-        <v>Route 37</v>
+        <v>Route 36</v>
       </c>
       <c r="C58" t="str">
         <v/>
       </c>
       <c r="D58" t="str">
-        <v>Noctowl</v>
+        <v>Gastly</v>
       </c>
       <c r="E58" t="str">
-        <v>26-31</v>
+        <v>23-28</v>
       </c>
       <c r="F58" t="str">
-        <v>30%</v>
+        <v>10%</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -1738,22 +1738,22 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Challenge 15</v>
+        <v>Challenge 14</v>
       </c>
       <c r="B59" t="str">
-        <v>Route 37</v>
+        <v>Route 36</v>
       </c>
       <c r="C59" t="str">
         <v/>
       </c>
       <c r="D59" t="str">
-        <v>Ledian</v>
+        <v>Sudowoodo</v>
       </c>
       <c r="E59" t="str">
-        <v>27-32</v>
+        <v>26-30</v>
       </c>
       <c r="F59" t="str">
-        <v>20%</v>
+        <v>10%</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -1770,13 +1770,13 @@
         <v/>
       </c>
       <c r="D60" t="str">
-        <v>Ariados</v>
+        <v>Pidgeotto</v>
       </c>
       <c r="E60" t="str">
-        <v>27-32</v>
+        <v>26-31</v>
       </c>
       <c r="F60" t="str">
-        <v>20%</v>
+        <v>28%</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -1784,22 +1784,22 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Challenge 16</v>
+        <v>Challenge 15</v>
       </c>
       <c r="B61" t="str">
-        <v>Burned Tower</v>
+        <v>Route 37</v>
       </c>
       <c r="C61" t="str">
         <v/>
       </c>
       <c r="D61" t="str">
-        <v>Koffing</v>
+        <v>Noctowl</v>
       </c>
       <c r="E61" t="str">
-        <v>28-33</v>
+        <v>26-31</v>
       </c>
       <c r="F61" t="str">
-        <v>25%</v>
+        <v>29%</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Challenge 16</v>
+        <v>Challenge 15</v>
       </c>
       <c r="B62" t="str">
-        <v>Burned Tower</v>
+        <v>Route 37</v>
       </c>
       <c r="C62" t="str">
         <v/>
       </c>
       <c r="D62" t="str">
-        <v>Zubat</v>
+        <v>Ledian</v>
       </c>
       <c r="E62" t="str">
         <v>27-32</v>
       </c>
       <c r="F62" t="str">
-        <v>25%</v>
+        <v>19%</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -1830,22 +1830,22 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Challenge 16</v>
+        <v>Challenge 15</v>
       </c>
       <c r="B63" t="str">
-        <v>Burned Tower</v>
+        <v>Route 37</v>
       </c>
       <c r="C63" t="str">
         <v/>
       </c>
       <c r="D63" t="str">
-        <v>Krabby</v>
+        <v>Ariados</v>
       </c>
       <c r="E63" t="str">
         <v>27-32</v>
       </c>
       <c r="F63" t="str">
-        <v>15%</v>
+        <v>19%</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -1853,22 +1853,22 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Challenge 16</v>
+        <v>Challenge 15</v>
       </c>
       <c r="B64" t="str">
-        <v>Burned Tower</v>
+        <v>Route 37</v>
       </c>
       <c r="C64" t="str">
         <v/>
       </c>
       <c r="D64" t="str">
-        <v>Shuckle</v>
+        <v>Heracross</v>
       </c>
       <c r="E64" t="str">
-        <v>28-33</v>
+        <v>26-32</v>
       </c>
       <c r="F64" t="str">
-        <v>15%</v>
+        <v>5%</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -1885,13 +1885,13 @@
         <v/>
       </c>
       <c r="D65" t="str">
-        <v>Weezing</v>
+        <v>Koffing</v>
       </c>
       <c r="E65" t="str">
-        <v>32-36</v>
+        <v>28-33</v>
       </c>
       <c r="F65" t="str">
-        <v>10%</v>
+        <v>25%</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -1908,13 +1908,13 @@
         <v/>
       </c>
       <c r="D66" t="str">
-        <v>Magmar</v>
+        <v>Zubat</v>
       </c>
       <c r="E66" t="str">
-        <v>32-37</v>
+        <v>27-32</v>
       </c>
       <c r="F66" t="str">
-        <v>10%</v>
+        <v>25%</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -1922,22 +1922,22 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Challenge 18</v>
+        <v>Challenge 16</v>
       </c>
       <c r="B67" t="str">
-        <v>Route 38</v>
+        <v>Burned Tower</v>
       </c>
       <c r="C67" t="str">
         <v/>
       </c>
       <c r="D67" t="str">
-        <v>Raticate</v>
+        <v>Krabby</v>
       </c>
       <c r="E67" t="str">
-        <v>31-36</v>
+        <v>27-32</v>
       </c>
       <c r="F67" t="str">
-        <v>30%</v>
+        <v>15%</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -1945,22 +1945,22 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Challenge 18</v>
+        <v>Challenge 16</v>
       </c>
       <c r="B68" t="str">
-        <v>Route 38</v>
+        <v>Burned Tower</v>
       </c>
       <c r="C68" t="str">
         <v/>
       </c>
       <c r="D68" t="str">
-        <v>Pidgeotto</v>
+        <v>Shuckle</v>
       </c>
       <c r="E68" t="str">
-        <v>31-36</v>
+        <v>28-33</v>
       </c>
       <c r="F68" t="str">
-        <v>25%</v>
+        <v>15%</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -1968,22 +1968,22 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Challenge 18</v>
+        <v>Challenge 16</v>
       </c>
       <c r="B69" t="str">
-        <v>Route 38</v>
+        <v>Burned Tower</v>
       </c>
       <c r="C69" t="str">
         <v/>
       </c>
       <c r="D69" t="str">
-        <v>Snubbull</v>
+        <v>Weezing</v>
       </c>
       <c r="E69" t="str">
-        <v>30-35</v>
+        <v>32-36</v>
       </c>
       <c r="F69" t="str">
-        <v>15%</v>
+        <v>10%</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -1991,22 +1991,22 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Challenge 18</v>
+        <v>Challenge 16</v>
       </c>
       <c r="B70" t="str">
-        <v>Route 38</v>
+        <v>Burned Tower</v>
       </c>
       <c r="C70" t="str">
         <v/>
       </c>
       <c r="D70" t="str">
-        <v>Exeggcute</v>
+        <v>Magmar</v>
       </c>
       <c r="E70" t="str">
-        <v>31-36</v>
+        <v>32-37</v>
       </c>
       <c r="F70" t="str">
-        <v>20%</v>
+        <v>10%</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -2023,13 +2023,13 @@
         <v/>
       </c>
       <c r="D71" t="str">
-        <v>Tauros</v>
+        <v>Raticate</v>
       </c>
       <c r="E71" t="str">
-        <v>32-37</v>
+        <v>31-36</v>
       </c>
       <c r="F71" t="str">
-        <v>10%</v>
+        <v>30%</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -2037,19 +2037,19 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Challenge 19</v>
+        <v>Challenge 18</v>
       </c>
       <c r="B72" t="str">
-        <v>Route 39</v>
+        <v>Route 38</v>
       </c>
       <c r="C72" t="str">
         <v/>
       </c>
       <c r="D72" t="str">
-        <v>Meowth</v>
+        <v>Pidgeotto</v>
       </c>
       <c r="E72" t="str">
-        <v>33-38</v>
+        <v>31-36</v>
       </c>
       <c r="F72" t="str">
         <v>25%</v>
@@ -2060,22 +2060,22 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Challenge 19</v>
+        <v>Challenge 18</v>
       </c>
       <c r="B73" t="str">
-        <v>Route 39</v>
+        <v>Route 38</v>
       </c>
       <c r="C73" t="str">
         <v/>
       </c>
       <c r="D73" t="str">
-        <v>Magnemite</v>
+        <v>Snubbull</v>
       </c>
       <c r="E73" t="str">
-        <v>34-39</v>
+        <v>30-35</v>
       </c>
       <c r="F73" t="str">
-        <v>25%</v>
+        <v>15%</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -2083,22 +2083,22 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Challenge 19</v>
+        <v>Challenge 18</v>
       </c>
       <c r="B74" t="str">
-        <v>Route 39</v>
+        <v>Route 38</v>
       </c>
       <c r="C74" t="str">
         <v/>
       </c>
       <c r="D74" t="str">
-        <v>Miltank</v>
+        <v>Exeggcute</v>
       </c>
       <c r="E74" t="str">
-        <v>34-39</v>
+        <v>31-36</v>
       </c>
       <c r="F74" t="str">
-        <v>15%</v>
+        <v>20%</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -2106,22 +2106,22 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Challenge 19</v>
+        <v>Challenge 18</v>
       </c>
       <c r="B75" t="str">
-        <v>Route 39</v>
+        <v>Route 38</v>
       </c>
       <c r="C75" t="str">
         <v/>
       </c>
       <c r="D75" t="str">
-        <v>Farfetch'd</v>
+        <v>Tauros</v>
       </c>
       <c r="E75" t="str">
-        <v>33-38</v>
+        <v>32-37</v>
       </c>
       <c r="F75" t="str">
-        <v>15%</v>
+        <v>10%</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -2138,13 +2138,13 @@
         <v/>
       </c>
       <c r="D76" t="str">
-        <v>Butterfree</v>
+        <v>Meowth</v>
       </c>
       <c r="E76" t="str">
-        <v>35-40</v>
+        <v>33-38</v>
       </c>
       <c r="F76" t="str">
-        <v>10%</v>
+        <v>25%</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="D77" t="str">
-        <v>Beedrill</v>
+        <v>Magnemite</v>
       </c>
       <c r="E77" t="str">
-        <v>35-40</v>
+        <v>34-39</v>
       </c>
       <c r="F77" t="str">
-        <v>10%</v>
+        <v>25%</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -2175,22 +2175,22 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Challenge 20</v>
+        <v>Challenge 19</v>
       </c>
       <c r="B78" t="str">
-        <v>Small Fishing Spot</v>
+        <v>Route 39</v>
       </c>
       <c r="C78" t="str">
         <v/>
       </c>
       <c r="D78" t="str">
-        <v>Psyduck</v>
+        <v>Miltank</v>
       </c>
       <c r="E78" t="str">
-        <v>36-41</v>
+        <v>34-39</v>
       </c>
       <c r="F78" t="str">
-        <v>20%</v>
+        <v>15%</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -2198,19 +2198,19 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Challenge 20</v>
+        <v>Challenge 19</v>
       </c>
       <c r="B79" t="str">
-        <v>Small Fishing Spot</v>
+        <v>Route 39</v>
       </c>
       <c r="C79" t="str">
         <v/>
       </c>
       <c r="D79" t="str">
-        <v>Marill</v>
+        <v>Farfetch'd</v>
       </c>
       <c r="E79" t="str">
-        <v>36-41</v>
+        <v>33-38</v>
       </c>
       <c r="F79" t="str">
         <v>15%</v>
@@ -2221,22 +2221,22 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Challenge 20</v>
+        <v>Challenge 19</v>
       </c>
       <c r="B80" t="str">
-        <v>Small Fishing Spot</v>
+        <v>Route 39</v>
       </c>
       <c r="C80" t="str">
         <v/>
       </c>
       <c r="D80" t="str">
-        <v>Chinchou</v>
+        <v>Butterfree</v>
       </c>
       <c r="E80" t="str">
-        <v>36-41</v>
+        <v>35-40</v>
       </c>
       <c r="F80" t="str">
-        <v>15%</v>
+        <v>10%</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -2244,22 +2244,22 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Challenge 20</v>
+        <v>Challenge 19</v>
       </c>
       <c r="B81" t="str">
-        <v>Small Fishing Spot</v>
+        <v>Route 39</v>
       </c>
       <c r="C81" t="str">
         <v/>
       </c>
       <c r="D81" t="str">
-        <v>Remoraid</v>
+        <v>Beedrill</v>
       </c>
       <c r="E81" t="str">
-        <v>36-41</v>
+        <v>35-40</v>
       </c>
       <c r="F81" t="str">
-        <v>15%</v>
+        <v>10%</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -2276,13 +2276,13 @@
         <v/>
       </c>
       <c r="D82" t="str">
-        <v>Corsola</v>
+        <v>Psyduck</v>
       </c>
       <c r="E82" t="str">
         <v>36-41</v>
       </c>
       <c r="F82" t="str">
-        <v>15%</v>
+        <v>20%</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -2299,13 +2299,13 @@
         <v/>
       </c>
       <c r="D83" t="str">
-        <v>Qwilfish</v>
+        <v>Marill</v>
       </c>
       <c r="E83" t="str">
-        <v>37-42</v>
+        <v>36-41</v>
       </c>
       <c r="F83" t="str">
-        <v>10%</v>
+        <v>15%</v>
       </c>
       <c r="G83">
         <v>1</v>
@@ -2322,13 +2322,13 @@
         <v/>
       </c>
       <c r="D84" t="str">
-        <v>Dratini</v>
+        <v>Chinchou</v>
       </c>
       <c r="E84" t="str">
-        <v>37-42</v>
+        <v>36-41</v>
       </c>
       <c r="F84" t="str">
-        <v>10%</v>
+        <v>15%</v>
       </c>
       <c r="G84">
         <v>1</v>
@@ -2336,22 +2336,22 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Challenge 22</v>
+        <v>Challenge 20</v>
       </c>
       <c r="B85" t="str">
-        <v>Route 47</v>
+        <v>Small Fishing Spot</v>
       </c>
       <c r="C85" t="str">
         <v/>
       </c>
       <c r="D85" t="str">
-        <v>Mankey</v>
+        <v>Remoraid</v>
       </c>
       <c r="E85" t="str">
-        <v>38-43</v>
+        <v>36-41</v>
       </c>
       <c r="F85" t="str">
-        <v>25%</v>
+        <v>15%</v>
       </c>
       <c r="G85">
         <v>1</v>
@@ -2359,22 +2359,22 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Challenge 22</v>
+        <v>Challenge 20</v>
       </c>
       <c r="B86" t="str">
-        <v>Route 47</v>
+        <v>Small Fishing Spot</v>
       </c>
       <c r="C86" t="str">
         <v/>
       </c>
       <c r="D86" t="str">
-        <v>Fearow</v>
+        <v>Corsola</v>
       </c>
       <c r="E86" t="str">
-        <v>38-43</v>
+        <v>36-41</v>
       </c>
       <c r="F86" t="str">
-        <v>25%</v>
+        <v>15%</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -2382,22 +2382,22 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Challenge 22</v>
+        <v>Challenge 20</v>
       </c>
       <c r="B87" t="str">
-        <v>Route 47</v>
+        <v>Small Fishing Spot</v>
       </c>
       <c r="C87" t="str">
         <v/>
       </c>
       <c r="D87" t="str">
-        <v>Mareep</v>
+        <v>Qwilfish</v>
       </c>
       <c r="E87" t="str">
-        <v>38-43</v>
+        <v>37-42</v>
       </c>
       <c r="F87" t="str">
-        <v>15%</v>
+        <v>10%</v>
       </c>
       <c r="G87">
         <v>1</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Challenge 22</v>
+        <v>Challenge 20</v>
       </c>
       <c r="B88" t="str">
-        <v>Route 47</v>
+        <v>Small Fishing Spot</v>
       </c>
       <c r="C88" t="str">
         <v/>
       </c>
       <c r="D88" t="str">
-        <v>Flaaffy</v>
+        <v>Dratini</v>
       </c>
       <c r="E88" t="str">
-        <v>38-43</v>
+        <v>37-42</v>
       </c>
       <c r="F88" t="str">
-        <v>15%</v>
+        <v>10%</v>
       </c>
       <c r="G88">
         <v>1</v>
@@ -2437,13 +2437,13 @@
         <v/>
       </c>
       <c r="D89" t="str">
-        <v>Arbok</v>
+        <v>Mankey</v>
       </c>
       <c r="E89" t="str">
         <v>38-43</v>
       </c>
       <c r="F89" t="str">
-        <v>10%</v>
+        <v>25%</v>
       </c>
       <c r="G89">
         <v>1</v>
@@ -2460,13 +2460,13 @@
         <v/>
       </c>
       <c r="D90" t="str">
-        <v>Golbat</v>
+        <v>Fearow</v>
       </c>
       <c r="E90" t="str">
         <v>38-43</v>
       </c>
       <c r="F90" t="str">
-        <v>10%</v>
+        <v>25%</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -2474,22 +2474,22 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Challenge 25</v>
+        <v>Challenge 22</v>
       </c>
       <c r="B91" t="str">
-        <v>Mount Mortar</v>
+        <v>Route 47</v>
       </c>
       <c r="C91" t="str">
         <v/>
       </c>
       <c r="D91" t="str">
-        <v>Geodude</v>
+        <v>Mareep</v>
       </c>
       <c r="E91" t="str">
-        <v>40-45</v>
+        <v>38-43</v>
       </c>
       <c r="F91" t="str">
-        <v>20%</v>
+        <v>15%</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Challenge 25</v>
+        <v>Challenge 22</v>
       </c>
       <c r="B92" t="str">
-        <v>Mount Mortar</v>
+        <v>Route 47</v>
       </c>
       <c r="C92" t="str">
         <v/>
       </c>
       <c r="D92" t="str">
-        <v>Machop</v>
+        <v>Flaaffy</v>
       </c>
       <c r="E92" t="str">
-        <v>40-45</v>
+        <v>38-43</v>
       </c>
       <c r="F92" t="str">
-        <v>20%</v>
+        <v>15%</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -2520,22 +2520,22 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Challenge 25</v>
+        <v>Challenge 22</v>
       </c>
       <c r="B93" t="str">
-        <v>Mount Mortar</v>
+        <v>Route 47</v>
       </c>
       <c r="C93" t="str">
         <v/>
       </c>
       <c r="D93" t="str">
-        <v>Graveler</v>
+        <v>Arbok</v>
       </c>
       <c r="E93" t="str">
-        <v>42-47</v>
+        <v>38-43</v>
       </c>
       <c r="F93" t="str">
-        <v>15%</v>
+        <v>10%</v>
       </c>
       <c r="G93">
         <v>1</v>
@@ -2543,22 +2543,22 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Challenge 25</v>
+        <v>Challenge 22</v>
       </c>
       <c r="B94" t="str">
-        <v>Mount Mortar</v>
+        <v>Route 47</v>
       </c>
       <c r="C94" t="str">
         <v/>
       </c>
       <c r="D94" t="str">
-        <v>Machoke</v>
+        <v>Golbat</v>
       </c>
       <c r="E94" t="str">
-        <v>42-47</v>
+        <v>38-43</v>
       </c>
       <c r="F94" t="str">
-        <v>15%</v>
+        <v>10%</v>
       </c>
       <c r="G94">
         <v>1</v>
@@ -2575,13 +2575,13 @@
         <v/>
       </c>
       <c r="D95" t="str">
-        <v>Onix</v>
+        <v>Geodude</v>
       </c>
       <c r="E95" t="str">
-        <v>42-47</v>
+        <v>40-45</v>
       </c>
       <c r="F95" t="str">
-        <v>10%</v>
+        <v>20%</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -2598,13 +2598,13 @@
         <v/>
       </c>
       <c r="D96" t="str">
-        <v>Tyrogue</v>
+        <v>Machop</v>
       </c>
       <c r="E96" t="str">
-        <v>42-47</v>
+        <v>40-45</v>
       </c>
       <c r="F96" t="str">
-        <v>10%</v>
+        <v>20%</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -2621,13 +2621,13 @@
         <v/>
       </c>
       <c r="D97" t="str">
-        <v>Misdreavus</v>
+        <v>Graveler</v>
       </c>
       <c r="E97" t="str">
-        <v>43-48</v>
+        <v>42-47</v>
       </c>
       <c r="F97" t="str">
-        <v>10%</v>
+        <v>15%</v>
       </c>
       <c r="G97">
         <v>1</v>
@@ -2635,22 +2635,22 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Challenge 27</v>
+        <v>Challenge 25</v>
       </c>
       <c r="B98" t="str">
-        <v>Standard Fishing Spot</v>
+        <v>Mount Mortar</v>
       </c>
       <c r="C98" t="str">
         <v/>
       </c>
       <c r="D98" t="str">
-        <v>Seaking</v>
+        <v>Machoke</v>
       </c>
       <c r="E98" t="str">
-        <v>48-54</v>
+        <v>42-47</v>
       </c>
       <c r="F98" t="str">
-        <v>35%</v>
+        <v>15%</v>
       </c>
       <c r="G98">
         <v>1</v>
@@ -2658,22 +2658,22 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Challenge 27</v>
+        <v>Challenge 25</v>
       </c>
       <c r="B99" t="str">
-        <v>Standard Fishing Spot</v>
+        <v>Mount Mortar</v>
       </c>
       <c r="C99" t="str">
         <v/>
       </c>
       <c r="D99" t="str">
-        <v>Kingler</v>
+        <v>Onix</v>
       </c>
       <c r="E99" t="str">
-        <v>48-54</v>
+        <v>42-47</v>
       </c>
       <c r="F99" t="str">
-        <v>30%</v>
+        <v>10%</v>
       </c>
       <c r="G99">
         <v>1</v>
@@ -2681,22 +2681,22 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Challenge 27</v>
+        <v>Challenge 25</v>
       </c>
       <c r="B100" t="str">
-        <v>Standard Fishing Spot</v>
+        <v>Mount Mortar</v>
       </c>
       <c r="C100" t="str">
         <v/>
       </c>
       <c r="D100" t="str">
-        <v>Poliwhirl</v>
+        <v>Tyrogue</v>
       </c>
       <c r="E100" t="str">
-        <v>49-55</v>
+        <v>42-47</v>
       </c>
       <c r="F100" t="str">
-        <v>25%</v>
+        <v>10%</v>
       </c>
       <c r="G100">
         <v>1</v>
@@ -2704,19 +2704,19 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Challenge 27</v>
+        <v>Challenge 25</v>
       </c>
       <c r="B101" t="str">
-        <v>Standard Fishing Spot</v>
+        <v>Mount Mortar</v>
       </c>
       <c r="C101" t="str">
         <v/>
       </c>
       <c r="D101" t="str">
-        <v>Lanturn</v>
+        <v>Misdreavus</v>
       </c>
       <c r="E101" t="str">
-        <v>50-56</v>
+        <v>43-48</v>
       </c>
       <c r="F101" t="str">
         <v>10%</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Challenge 28</v>
+        <v>Challenge 27</v>
       </c>
       <c r="B102" t="str">
-        <v>Ice Path</v>
+        <v>Standard Fishing Spot</v>
       </c>
       <c r="C102" t="str">
         <v/>
       </c>
       <c r="D102" t="str">
-        <v>Swinub</v>
+        <v>Seaking</v>
       </c>
       <c r="E102" t="str">
-        <v>52-57</v>
+        <v>48-54</v>
       </c>
       <c r="F102" t="str">
-        <v>25%</v>
+        <v>35%</v>
       </c>
       <c r="G102">
         <v>1</v>
@@ -2750,22 +2750,22 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Challenge 28</v>
+        <v>Challenge 27</v>
       </c>
       <c r="B103" t="str">
-        <v>Ice Path</v>
+        <v>Standard Fishing Spot</v>
       </c>
       <c r="C103" t="str">
         <v/>
       </c>
       <c r="D103" t="str">
-        <v>Zubat</v>
+        <v>Kingler</v>
       </c>
       <c r="E103" t="str">
-        <v>50-55</v>
+        <v>48-54</v>
       </c>
       <c r="F103" t="str">
-        <v>25%</v>
+        <v>30%</v>
       </c>
       <c r="G103">
         <v>1</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Challenge 28</v>
+        <v>Challenge 27</v>
       </c>
       <c r="B104" t="str">
-        <v>Ice Path</v>
+        <v>Standard Fishing Spot</v>
       </c>
       <c r="C104" t="str">
         <v/>
       </c>
       <c r="D104" t="str">
-        <v>Delibird</v>
+        <v>Poliwhirl</v>
       </c>
       <c r="E104" t="str">
-        <v>52-57</v>
+        <v>49-55</v>
       </c>
       <c r="F104" t="str">
-        <v>15%</v>
+        <v>25%</v>
       </c>
       <c r="G104">
         <v>1</v>
@@ -2796,22 +2796,22 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Challenge 28</v>
+        <v>Challenge 27</v>
       </c>
       <c r="B105" t="str">
-        <v>Ice Path</v>
+        <v>Standard Fishing Spot</v>
       </c>
       <c r="C105" t="str">
         <v/>
       </c>
       <c r="D105" t="str">
-        <v>Golbat</v>
+        <v>Lanturn</v>
       </c>
       <c r="E105" t="str">
-        <v>54-59</v>
+        <v>50-56</v>
       </c>
       <c r="F105" t="str">
-        <v>15%</v>
+        <v>10%</v>
       </c>
       <c r="G105">
         <v>1</v>
@@ -2828,13 +2828,13 @@
         <v/>
       </c>
       <c r="D106" t="str">
-        <v>Sneasel</v>
+        <v>Swinub</v>
       </c>
       <c r="E106" t="str">
-        <v>53-58</v>
+        <v>52-57</v>
       </c>
       <c r="F106" t="str">
-        <v>10%</v>
+        <v>25%</v>
       </c>
       <c r="G106">
         <v>1</v>
@@ -2851,13 +2851,13 @@
         <v/>
       </c>
       <c r="D107" t="str">
-        <v>Jynx</v>
+        <v>Zubat</v>
       </c>
       <c r="E107" t="str">
-        <v>54-60</v>
+        <v>50-55</v>
       </c>
       <c r="F107" t="str">
-        <v>10%</v>
+        <v>25%</v>
       </c>
       <c r="G107">
         <v>1</v>
@@ -2865,22 +2865,22 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Challenge 29</v>
+        <v>Challenge 28</v>
       </c>
       <c r="B108" t="str">
-        <v>Route 45</v>
+        <v>Ice Path</v>
       </c>
       <c r="C108" t="str">
         <v/>
       </c>
       <c r="D108" t="str">
-        <v>Graveler</v>
+        <v>Delibird</v>
       </c>
       <c r="E108" t="str">
-        <v>58-64</v>
+        <v>52-57</v>
       </c>
       <c r="F108" t="str">
-        <v>25%</v>
+        <v>15%</v>
       </c>
       <c r="G108">
         <v>1</v>
@@ -2888,22 +2888,22 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Challenge 29</v>
+        <v>Challenge 28</v>
       </c>
       <c r="B109" t="str">
-        <v>Route 45</v>
+        <v>Ice Path</v>
       </c>
       <c r="C109" t="str">
         <v/>
       </c>
       <c r="D109" t="str">
-        <v>Gligar</v>
+        <v>Golbat</v>
       </c>
       <c r="E109" t="str">
-        <v>58-64</v>
+        <v>54-59</v>
       </c>
       <c r="F109" t="str">
-        <v>25%</v>
+        <v>15%</v>
       </c>
       <c r="G109">
         <v>1</v>
@@ -2911,22 +2911,22 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Challenge 29</v>
+        <v>Challenge 28</v>
       </c>
       <c r="B110" t="str">
-        <v>Route 45</v>
+        <v>Ice Path</v>
       </c>
       <c r="C110" t="str">
         <v/>
       </c>
       <c r="D110" t="str">
-        <v>Phanpy</v>
+        <v>Sneasel</v>
       </c>
       <c r="E110" t="str">
-        <v>57-63</v>
+        <v>53-58</v>
       </c>
       <c r="F110" t="str">
-        <v>20%</v>
+        <v>10%</v>
       </c>
       <c r="G110">
         <v>1</v>
@@ -2934,22 +2934,22 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Challenge 29</v>
+        <v>Challenge 28</v>
       </c>
       <c r="B111" t="str">
-        <v>Route 45</v>
+        <v>Ice Path</v>
       </c>
       <c r="C111" t="str">
         <v/>
       </c>
       <c r="D111" t="str">
-        <v>Pineco</v>
+        <v>Jynx</v>
       </c>
       <c r="E111" t="str">
-        <v>58-64</v>
+        <v>54-60</v>
       </c>
       <c r="F111" t="str">
-        <v>30%</v>
+        <v>10%</v>
       </c>
       <c r="G111">
         <v>1</v>
@@ -2957,22 +2957,22 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Challenge 31</v>
+        <v>Challenge 29</v>
       </c>
       <c r="B112" t="str">
-        <v>Big Fishing Spot</v>
+        <v>Route 45</v>
       </c>
       <c r="C112" t="str">
         <v/>
       </c>
       <c r="D112" t="str">
-        <v>Golduck</v>
+        <v>Graveler</v>
       </c>
       <c r="E112" t="str">
-        <v>62-68</v>
+        <v>58-64</v>
       </c>
       <c r="F112" t="str">
-        <v>30%</v>
+        <v>19%</v>
       </c>
       <c r="G112">
         <v>1</v>
@@ -2980,22 +2980,22 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Challenge 31</v>
+        <v>Challenge 29</v>
       </c>
       <c r="B113" t="str">
-        <v>Big Fishing Spot</v>
+        <v>Route 45</v>
       </c>
       <c r="C113" t="str">
         <v/>
       </c>
       <c r="D113" t="str">
-        <v>Tentacruel</v>
+        <v>Gligar</v>
       </c>
       <c r="E113" t="str">
-        <v>63-69</v>
+        <v>58-64</v>
       </c>
       <c r="F113" t="str">
-        <v>25%</v>
+        <v>19%</v>
       </c>
       <c r="G113">
         <v>1</v>
@@ -3003,22 +3003,22 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Challenge 31</v>
+        <v>Challenge 29</v>
       </c>
       <c r="B114" t="str">
-        <v>Big Fishing Spot</v>
+        <v>Route 45</v>
       </c>
       <c r="C114" t="str">
         <v/>
       </c>
       <c r="D114" t="str">
-        <v>Quagsire</v>
+        <v>Phanpy</v>
       </c>
       <c r="E114" t="str">
-        <v>62-68</v>
+        <v>57-63</v>
       </c>
       <c r="F114" t="str">
-        <v>20%</v>
+        <v>15%</v>
       </c>
       <c r="G114">
         <v>1</v>
@@ -3026,22 +3026,22 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Challenge 31</v>
+        <v>Challenge 29</v>
       </c>
       <c r="B115" t="str">
-        <v>Big Fishing Spot</v>
+        <v>Route 45</v>
       </c>
       <c r="C115" t="str">
         <v/>
       </c>
       <c r="D115" t="str">
-        <v>Gyarados</v>
+        <v>Pineco</v>
       </c>
       <c r="E115" t="str">
-        <v>64-70</v>
+        <v>58-64</v>
       </c>
       <c r="F115" t="str">
-        <v>10%</v>
+        <v>23%</v>
       </c>
       <c r="G115">
         <v>1</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Challenge 31</v>
+        <v>Challenge 29</v>
       </c>
       <c r="B116" t="str">
-        <v>Big Fishing Spot</v>
+        <v>Route 45</v>
       </c>
       <c r="C116" t="str">
         <v/>
       </c>
       <c r="D116" t="str">
-        <v>Mantine</v>
+        <v>Weepinbell</v>
       </c>
       <c r="E116" t="str">
-        <v>64-70</v>
+        <v>57-64</v>
       </c>
       <c r="F116" t="str">
-        <v>10%</v>
+        <v>7%</v>
       </c>
       <c r="G116">
         <v>1</v>
@@ -3072,22 +3072,22 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Challenge 31</v>
+        <v>Challenge 29</v>
       </c>
       <c r="B117" t="str">
-        <v>Big Fishing Spot</v>
+        <v>Route 45</v>
       </c>
       <c r="C117" t="str">
         <v/>
       </c>
       <c r="D117" t="str">
-        <v>Dragonair</v>
+        <v>Girafarig</v>
       </c>
       <c r="E117" t="str">
-        <v>65-71</v>
+        <v>57-64</v>
       </c>
       <c r="F117" t="str">
-        <v>5%</v>
+        <v>8%</v>
       </c>
       <c r="G117">
         <v>1</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Challenge 32</v>
+        <v>Challenge 29</v>
       </c>
       <c r="B118" t="str">
-        <v>Dark Cave</v>
+        <v>Route 45</v>
       </c>
       <c r="C118" t="str">
         <v/>
       </c>
       <c r="D118" t="str">
-        <v>Graveler</v>
+        <v>Tangela</v>
       </c>
       <c r="E118" t="str">
-        <v>64-70</v>
+        <v>57-64</v>
       </c>
       <c r="F118" t="str">
-        <v>25%</v>
+        <v>9%</v>
       </c>
       <c r="G118">
         <v>1</v>
@@ -3118,22 +3118,22 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Challenge 32</v>
+        <v>Challenge 31</v>
       </c>
       <c r="B119" t="str">
-        <v>Dark Cave</v>
+        <v>Big Fishing Spot</v>
       </c>
       <c r="C119" t="str">
         <v/>
       </c>
       <c r="D119" t="str">
-        <v>Teddiursa</v>
+        <v>Golduck</v>
       </c>
       <c r="E119" t="str">
-        <v>63-69</v>
+        <v>62-68</v>
       </c>
       <c r="F119" t="str">
-        <v>15%</v>
+        <v>30%</v>
       </c>
       <c r="G119">
         <v>1</v>
@@ -3141,22 +3141,22 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Challenge 32</v>
+        <v>Challenge 31</v>
       </c>
       <c r="B120" t="str">
-        <v>Dark Cave</v>
+        <v>Big Fishing Spot</v>
       </c>
       <c r="C120" t="str">
         <v/>
       </c>
       <c r="D120" t="str">
-        <v>Shuckle</v>
+        <v>Tentacruel</v>
       </c>
       <c r="E120" t="str">
-        <v>64-70</v>
+        <v>63-69</v>
       </c>
       <c r="F120" t="str">
-        <v>15%</v>
+        <v>25%</v>
       </c>
       <c r="G120">
         <v>1</v>
@@ -3164,22 +3164,22 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Challenge 32</v>
+        <v>Challenge 31</v>
       </c>
       <c r="B121" t="str">
-        <v>Dark Cave</v>
+        <v>Big Fishing Spot</v>
       </c>
       <c r="C121" t="str">
         <v/>
       </c>
       <c r="D121" t="str">
-        <v>Ursaring</v>
+        <v>Quagsire</v>
       </c>
       <c r="E121" t="str">
-        <v>68-74</v>
+        <v>62-68</v>
       </c>
       <c r="F121" t="str">
-        <v>10%</v>
+        <v>20%</v>
       </c>
       <c r="G121">
         <v>1</v>
@@ -3187,19 +3187,19 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Challenge 32</v>
+        <v>Challenge 31</v>
       </c>
       <c r="B122" t="str">
-        <v>Dark Cave</v>
+        <v>Big Fishing Spot</v>
       </c>
       <c r="C122" t="str">
         <v/>
       </c>
       <c r="D122" t="str">
-        <v>Wobbuffet</v>
+        <v>Gyarados</v>
       </c>
       <c r="E122" t="str">
-        <v>65-71</v>
+        <v>64-70</v>
       </c>
       <c r="F122" t="str">
         <v>10%</v>
@@ -3210,22 +3210,22 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Challenge 32</v>
+        <v>Challenge 31</v>
       </c>
       <c r="B123" t="str">
-        <v>Dark Cave</v>
+        <v>Big Fishing Spot</v>
       </c>
       <c r="C123" t="str">
         <v/>
       </c>
       <c r="D123" t="str">
-        <v>Dunsparce</v>
+        <v>Mantine</v>
       </c>
       <c r="E123" t="str">
         <v>64-70</v>
       </c>
       <c r="F123" t="str">
-        <v>25%</v>
+        <v>10%</v>
       </c>
       <c r="G123">
         <v>1</v>
@@ -3233,22 +3233,22 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Challenge 33</v>
+        <v>Challenge 31</v>
       </c>
       <c r="B124" t="str">
-        <v>Route 46</v>
+        <v>Big Fishing Spot</v>
       </c>
       <c r="C124" t="str">
         <v/>
       </c>
       <c r="D124" t="str">
-        <v>Donphan</v>
+        <v>Dragonair</v>
       </c>
       <c r="E124" t="str">
-        <v>68-74</v>
+        <v>65-71</v>
       </c>
       <c r="F124" t="str">
-        <v>40%</v>
+        <v>5%</v>
       </c>
       <c r="G124">
         <v>1</v>
@@ -3256,22 +3256,22 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Challenge 33</v>
+        <v>Challenge 32</v>
       </c>
       <c r="B125" t="str">
-        <v>Route 46</v>
+        <v>Dark Cave</v>
       </c>
       <c r="C125" t="str">
         <v/>
       </c>
       <c r="D125" t="str">
-        <v>Teddiursa</v>
+        <v>Graveler</v>
       </c>
       <c r="E125" t="str">
-        <v>66-72</v>
+        <v>64-70</v>
       </c>
       <c r="F125" t="str">
-        <v>35%</v>
+        <v>25%</v>
       </c>
       <c r="G125">
         <v>1</v>
@@ -3279,22 +3279,22 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Challenge 33</v>
+        <v>Challenge 32</v>
       </c>
       <c r="B126" t="str">
-        <v>Route 46</v>
+        <v>Dark Cave</v>
       </c>
       <c r="C126" t="str">
         <v/>
       </c>
       <c r="D126" t="str">
-        <v>Skarmory</v>
+        <v>Teddiursa</v>
       </c>
       <c r="E126" t="str">
-        <v>70-76</v>
+        <v>63-69</v>
       </c>
       <c r="F126" t="str">
-        <v>25%</v>
+        <v>15%</v>
       </c>
       <c r="G126">
         <v>1</v>
@@ -3302,22 +3302,22 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Challenge 11</v>
+        <v>Challenge 32</v>
       </c>
       <c r="B127" t="str">
-        <v>Goldenrod Game Corner</v>
+        <v>Dark Cave</v>
       </c>
       <c r="C127" t="str">
         <v/>
       </c>
       <c r="D127" t="str">
-        <v>Abra</v>
+        <v>Shuckle</v>
       </c>
       <c r="E127" t="str">
-        <v>18-22</v>
+        <v>64-70</v>
       </c>
       <c r="F127" t="str">
-        <v>25%</v>
+        <v>15%</v>
       </c>
       <c r="G127">
         <v>1</v>
@@ -3325,22 +3325,22 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Challenge 11</v>
+        <v>Challenge 32</v>
       </c>
       <c r="B128" t="str">
-        <v>Goldenrod Game Corner</v>
+        <v>Dark Cave</v>
       </c>
       <c r="C128" t="str">
         <v/>
       </c>
       <c r="D128" t="str">
-        <v>Sandshrew</v>
+        <v>Ursaring</v>
       </c>
       <c r="E128" t="str">
-        <v>18-22</v>
+        <v>68-74</v>
       </c>
       <c r="F128" t="str">
-        <v>25%</v>
+        <v>10%</v>
       </c>
       <c r="G128">
         <v>1</v>
@@ -3348,22 +3348,22 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Challenge 11</v>
+        <v>Challenge 32</v>
       </c>
       <c r="B129" t="str">
-        <v>Goldenrod Game Corner</v>
+        <v>Dark Cave</v>
       </c>
       <c r="C129" t="str">
         <v/>
       </c>
       <c r="D129" t="str">
-        <v>Machop</v>
+        <v>Wobbuffet</v>
       </c>
       <c r="E129" t="str">
-        <v>18-22</v>
+        <v>65-71</v>
       </c>
       <c r="F129" t="str">
-        <v>20%</v>
+        <v>10%</v>
       </c>
       <c r="G129">
         <v>1</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Challenge 11</v>
+        <v>Challenge 32</v>
       </c>
       <c r="B130" t="str">
-        <v>Goldenrod Game Corner</v>
+        <v>Dark Cave</v>
       </c>
       <c r="C130" t="str">
         <v/>
       </c>
       <c r="D130" t="str">
-        <v>Cubone</v>
+        <v>Dunsparce</v>
       </c>
       <c r="E130" t="str">
-        <v>18-22</v>
+        <v>64-70</v>
       </c>
       <c r="F130" t="str">
-        <v>15%</v>
+        <v>25%</v>
       </c>
       <c r="G130">
         <v>1</v>
@@ -3394,22 +3394,22 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Challenge 11</v>
+        <v>Challenge 33</v>
       </c>
       <c r="B131" t="str">
-        <v>Goldenrod Game Corner</v>
+        <v>Route 46</v>
       </c>
       <c r="C131" t="str">
         <v/>
       </c>
       <c r="D131" t="str">
-        <v>Eevee</v>
+        <v>Donphan</v>
       </c>
       <c r="E131" t="str">
-        <v>20-24</v>
+        <v>68-74</v>
       </c>
       <c r="F131" t="str">
-        <v>15%</v>
+        <v>40%</v>
       </c>
       <c r="G131">
         <v>1</v>
@@ -3417,19 +3417,19 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Johto Extra Challenge 1</v>
+        <v>Challenge 33</v>
       </c>
       <c r="B132" t="str">
-        <v>Team Rocket HQ</v>
+        <v>Route 46</v>
       </c>
       <c r="C132" t="str">
         <v/>
       </c>
       <c r="D132" t="str">
-        <v>Voltorb</v>
+        <v>Teddiursa</v>
       </c>
       <c r="E132" t="str">
-        <v>33-38</v>
+        <v>66-72</v>
       </c>
       <c r="F132" t="str">
         <v>35%</v>
@@ -3440,19 +3440,19 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Johto Extra Challenge 1</v>
+        <v>Challenge 33</v>
       </c>
       <c r="B133" t="str">
-        <v>Team Rocket HQ</v>
+        <v>Route 46</v>
       </c>
       <c r="C133" t="str">
         <v/>
       </c>
       <c r="D133" t="str">
-        <v>Geodude</v>
+        <v>Skarmory</v>
       </c>
       <c r="E133" t="str">
-        <v>32-37</v>
+        <v>70-76</v>
       </c>
       <c r="F133" t="str">
         <v>25%</v>
@@ -3463,19 +3463,19 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Johto Extra Challenge 1</v>
+        <v>Challenge 11</v>
       </c>
       <c r="B134" t="str">
-        <v>Team Rocket HQ</v>
+        <v>Goldenrod Game Corner</v>
       </c>
       <c r="C134" t="str">
         <v/>
       </c>
       <c r="D134" t="str">
-        <v>Koffing</v>
+        <v>Abra</v>
       </c>
       <c r="E134" t="str">
-        <v>33-38</v>
+        <v>18-22</v>
       </c>
       <c r="F134" t="str">
         <v>25%</v>
@@ -3486,22 +3486,22 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Johto Extra Challenge 1</v>
+        <v>Challenge 11</v>
       </c>
       <c r="B135" t="str">
-        <v>Team Rocket HQ</v>
+        <v>Goldenrod Game Corner</v>
       </c>
       <c r="C135" t="str">
         <v/>
       </c>
       <c r="D135" t="str">
-        <v>Electrode</v>
+        <v>Sandshrew</v>
       </c>
       <c r="E135" t="str">
-        <v>36-40</v>
+        <v>18-22</v>
       </c>
       <c r="F135" t="str">
-        <v>15%</v>
+        <v>25%</v>
       </c>
       <c r="G135">
         <v>1</v>
@@ -3509,22 +3509,22 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Johto Extra Challenge 2</v>
+        <v>Challenge 11</v>
       </c>
       <c r="B136" t="str">
-        <v>Lake of Rage</v>
+        <v>Goldenrod Game Corner</v>
       </c>
       <c r="C136" t="str">
         <v/>
       </c>
       <c r="D136" t="str">
-        <v>Magikarp</v>
+        <v>Machop</v>
       </c>
       <c r="E136" t="str">
-        <v>48-55</v>
+        <v>18-22</v>
       </c>
       <c r="F136" t="str">
-        <v>95%</v>
+        <v>20%</v>
       </c>
       <c r="G136">
         <v>1</v>
@@ -3532,22 +3532,22 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Johto Extra Challenge 2</v>
+        <v>Challenge 11</v>
       </c>
       <c r="B137" t="str">
-        <v>Lake of Rage</v>
+        <v>Goldenrod Game Corner</v>
       </c>
       <c r="C137" t="str">
         <v/>
       </c>
       <c r="D137" t="str">
-        <v>Gyarados</v>
+        <v>Cubone</v>
       </c>
       <c r="E137" t="str">
-        <v>55-60</v>
+        <v>18-22</v>
       </c>
       <c r="F137" t="str">
-        <v>5%</v>
+        <v>15%</v>
       </c>
       <c r="G137">
         <v>1</v>
@@ -3555,22 +3555,22 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Johto Extra Challenge 3</v>
+        <v>Challenge 11</v>
       </c>
       <c r="B138" t="str">
-        <v>Mount Silver</v>
+        <v>Goldenrod Game Corner</v>
       </c>
       <c r="C138" t="str">
         <v/>
       </c>
       <c r="D138" t="str">
-        <v>Donphan</v>
+        <v>Eevee</v>
       </c>
       <c r="E138" t="str">
-        <v>74-80</v>
+        <v>20-24</v>
       </c>
       <c r="F138" t="str">
-        <v>25%</v>
+        <v>15%</v>
       </c>
       <c r="G138">
         <v>1</v>
@@ -3578,22 +3578,22 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Johto Extra Challenge 3</v>
+        <v>Johto Extra Challenge 1</v>
       </c>
       <c r="B139" t="str">
-        <v>Mount Silver</v>
+        <v>Team Rocket HQ</v>
       </c>
       <c r="C139" t="str">
         <v/>
       </c>
       <c r="D139" t="str">
-        <v>Quagsire</v>
+        <v>Voltorb</v>
       </c>
       <c r="E139" t="str">
-        <v>74-80</v>
+        <v>33-38</v>
       </c>
       <c r="F139" t="str">
-        <v>20%</v>
+        <v>35%</v>
       </c>
       <c r="G139">
         <v>1</v>
@@ -3601,22 +3601,22 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Johto Extra Challenge 3</v>
+        <v>Johto Extra Challenge 1</v>
       </c>
       <c r="B140" t="str">
-        <v>Mount Silver</v>
+        <v>Team Rocket HQ</v>
       </c>
       <c r="C140" t="str">
         <v/>
       </c>
       <c r="D140" t="str">
-        <v>Doduo</v>
+        <v>Geodude</v>
       </c>
       <c r="E140" t="str">
-        <v>73-79</v>
+        <v>32-37</v>
       </c>
       <c r="F140" t="str">
-        <v>20%</v>
+        <v>25%</v>
       </c>
       <c r="G140">
         <v>1</v>
@@ -3624,22 +3624,22 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Johto Extra Challenge 3</v>
+        <v>Johto Extra Challenge 1</v>
       </c>
       <c r="B141" t="str">
-        <v>Mount Silver</v>
+        <v>Team Rocket HQ</v>
       </c>
       <c r="C141" t="str">
         <v/>
       </c>
       <c r="D141" t="str">
-        <v>Ponyta</v>
+        <v>Koffing</v>
       </c>
       <c r="E141" t="str">
-        <v>74-80</v>
+        <v>33-38</v>
       </c>
       <c r="F141" t="str">
-        <v>15%</v>
+        <v>25%</v>
       </c>
       <c r="G141">
         <v>1</v>
@@ -3647,22 +3647,22 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Johto Extra Challenge 3</v>
+        <v>Johto Extra Challenge 1</v>
       </c>
       <c r="B142" t="str">
-        <v>Mount Silver</v>
+        <v>Team Rocket HQ</v>
       </c>
       <c r="C142" t="str">
         <v/>
       </c>
       <c r="D142" t="str">
-        <v>Parasect</v>
+        <v>Electrode</v>
       </c>
       <c r="E142" t="str">
-        <v>75-81</v>
+        <v>36-40</v>
       </c>
       <c r="F142" t="str">
-        <v>10%</v>
+        <v>15%</v>
       </c>
       <c r="G142">
         <v>1</v>
@@ -3670,22 +3670,22 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Johto Extra Challenge 3</v>
+        <v>Johto Extra Challenge 2</v>
       </c>
       <c r="B143" t="str">
-        <v>Mount Silver</v>
+        <v>Lake of Rage</v>
       </c>
       <c r="C143" t="str">
         <v/>
       </c>
       <c r="D143" t="str">
-        <v>Larvitar</v>
+        <v>Magikarp</v>
       </c>
       <c r="E143" t="str">
-        <v>75-82</v>
+        <v>48-55</v>
       </c>
       <c r="F143" t="str">
-        <v>10%</v>
+        <v>95%</v>
       </c>
       <c r="G143">
         <v>1</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Johto Extra Challenge 4</v>
+        <v>Johto Extra Challenge 2</v>
       </c>
       <c r="B144" t="str">
-        <v>Ilex Forest 2</v>
+        <v>Lake of Rage</v>
       </c>
       <c r="C144" t="str">
         <v/>
       </c>
       <c r="D144" t="str">
-        <v>Parasect</v>
+        <v>Gyarados</v>
       </c>
       <c r="E144" t="str">
-        <v>77-82</v>
+        <v>55-60</v>
       </c>
       <c r="F144" t="str">
-        <v>30%</v>
+        <v>5%</v>
       </c>
       <c r="G144">
         <v>1</v>
@@ -3716,22 +3716,22 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Johto Extra Challenge 4</v>
+        <v>Johto Extra Challenge 3</v>
       </c>
       <c r="B145" t="str">
-        <v>Ilex Forest 2</v>
+        <v>Mount Silver</v>
       </c>
       <c r="C145" t="str">
         <v/>
       </c>
       <c r="D145" t="str">
-        <v>Butterfree</v>
+        <v>Donphan</v>
       </c>
       <c r="E145" t="str">
-        <v>77-82</v>
+        <v>74-80</v>
       </c>
       <c r="F145" t="str">
-        <v>20%</v>
+        <v>25%</v>
       </c>
       <c r="G145">
         <v>1</v>
@@ -3739,19 +3739,19 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Johto Extra Challenge 4</v>
+        <v>Johto Extra Challenge 3</v>
       </c>
       <c r="B146" t="str">
-        <v>Ilex Forest 2</v>
+        <v>Mount Silver</v>
       </c>
       <c r="C146" t="str">
         <v/>
       </c>
       <c r="D146" t="str">
-        <v>Beedrill</v>
+        <v>Quagsire</v>
       </c>
       <c r="E146" t="str">
-        <v>77-82</v>
+        <v>74-80</v>
       </c>
       <c r="F146" t="str">
         <v>20%</v>
@@ -3762,22 +3762,22 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Johto Extra Challenge 4</v>
+        <v>Johto Extra Challenge 3</v>
       </c>
       <c r="B147" t="str">
-        <v>Ilex Forest 2</v>
+        <v>Mount Silver</v>
       </c>
       <c r="C147" t="str">
         <v/>
       </c>
       <c r="D147" t="str">
-        <v>Noctowl</v>
+        <v>Doduo</v>
       </c>
       <c r="E147" t="str">
-        <v>79-83</v>
+        <v>73-79</v>
       </c>
       <c r="F147" t="str">
-        <v>15%</v>
+        <v>20%</v>
       </c>
       <c r="G147">
         <v>1</v>
@@ -3785,22 +3785,22 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Johto Extra Challenge 4</v>
+        <v>Johto Extra Challenge 3</v>
       </c>
       <c r="B148" t="str">
-        <v>Ilex Forest 2</v>
+        <v>Mount Silver</v>
       </c>
       <c r="C148" t="str">
         <v/>
       </c>
       <c r="D148" t="str">
-        <v>Exeggutor</v>
+        <v>Ponyta</v>
       </c>
       <c r="E148" t="str">
-        <v>79-83</v>
+        <v>74-80</v>
       </c>
       <c r="F148" t="str">
-        <v>10%</v>
+        <v>15%</v>
       </c>
       <c r="G148">
         <v>1</v>
@@ -3808,22 +3808,22 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Johto Extra Challenge 4</v>
+        <v>Johto Extra Challenge 3</v>
       </c>
       <c r="B149" t="str">
-        <v>Ilex Forest 2</v>
+        <v>Mount Silver</v>
       </c>
       <c r="C149" t="str">
         <v/>
       </c>
       <c r="D149" t="str">
-        <v>Celebi</v>
+        <v>Parasect</v>
       </c>
       <c r="E149" t="str">
-        <v>85-85</v>
+        <v>75-81</v>
       </c>
       <c r="F149" t="str">
-        <v>5%</v>
+        <v>10%</v>
       </c>
       <c r="G149">
         <v>1</v>
@@ -3831,91 +3831,91 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Challenge 12</v>
+        <v>Johto Extra Challenge 3</v>
       </c>
       <c r="B150" t="str">
-        <v>Extra Challenge (Roaming)</v>
+        <v>Mount Silver</v>
       </c>
       <c r="C150" t="str">
         <v/>
       </c>
       <c r="D150" t="str">
-        <v>Raikou</v>
+        <v>Larvitar</v>
       </c>
       <c r="E150" t="str">
-        <v>50-50</v>
+        <v>75-82</v>
       </c>
       <c r="F150" t="str">
-        <v>33.33%</v>
+        <v>10%</v>
       </c>
       <c r="G150">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Challenge 12</v>
+        <v>Johto Extra Challenge 4</v>
       </c>
       <c r="B151" t="str">
-        <v>Extra Challenge (Roaming)</v>
+        <v>Ilex Forest 2</v>
       </c>
       <c r="C151" t="str">
         <v/>
       </c>
       <c r="D151" t="str">
-        <v>Entei</v>
+        <v>Parasect</v>
       </c>
       <c r="E151" t="str">
-        <v>50-50</v>
+        <v>77-82</v>
       </c>
       <c r="F151" t="str">
-        <v>33.33%</v>
+        <v>30%</v>
       </c>
       <c r="G151">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Challenge 12</v>
+        <v>Johto Extra Challenge 4</v>
       </c>
       <c r="B152" t="str">
-        <v>Extra Challenge (Roaming)</v>
+        <v>Ilex Forest 2</v>
       </c>
       <c r="C152" t="str">
         <v/>
       </c>
       <c r="D152" t="str">
-        <v>Suicune</v>
+        <v>Butterfree</v>
       </c>
       <c r="E152" t="str">
-        <v>50-50</v>
+        <v>77-82</v>
       </c>
       <c r="F152" t="str">
-        <v>33.33%</v>
+        <v>20%</v>
       </c>
       <c r="G152">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Challenge 35</v>
+        <v>Johto Extra Challenge 4</v>
       </c>
       <c r="B153" t="str">
-        <v>Viridian Forest</v>
+        <v>Ilex Forest 2</v>
       </c>
       <c r="C153" t="str">
         <v/>
       </c>
       <c r="D153" t="str">
-        <v>Oddish</v>
+        <v>Beedrill</v>
       </c>
       <c r="E153" t="str">
-        <v>72-76</v>
+        <v>77-82</v>
       </c>
       <c r="F153" t="str">
-        <v>25%</v>
+        <v>20%</v>
       </c>
       <c r="G153">
         <v>1</v>
@@ -3923,22 +3923,22 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Challenge 35</v>
+        <v>Johto Extra Challenge 4</v>
       </c>
       <c r="B154" t="str">
-        <v>Viridian Forest</v>
+        <v>Ilex Forest 2</v>
       </c>
       <c r="C154" t="str">
         <v/>
       </c>
       <c r="D154" t="str">
-        <v>Gloom</v>
+        <v>Noctowl</v>
       </c>
       <c r="E154" t="str">
-        <v>72-76</v>
+        <v>79-83</v>
       </c>
       <c r="F154" t="str">
-        <v>25%</v>
+        <v>15%</v>
       </c>
       <c r="G154">
         <v>1</v>
@@ -3946,22 +3946,22 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Challenge 35</v>
+        <v>Johto Extra Challenge 4</v>
       </c>
       <c r="B155" t="str">
-        <v>Viridian Forest</v>
+        <v>Ilex Forest 2</v>
       </c>
       <c r="C155" t="str">
         <v/>
       </c>
       <c r="D155" t="str">
-        <v>Butterfree</v>
+        <v>Exeggutor</v>
       </c>
       <c r="E155" t="str">
-        <v>74-78</v>
+        <v>79-83</v>
       </c>
       <c r="F155" t="str">
-        <v>15%</v>
+        <v>10%</v>
       </c>
       <c r="G155">
         <v>1</v>
@@ -3969,22 +3969,22 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Challenge 35</v>
+        <v>Johto Extra Challenge 4</v>
       </c>
       <c r="B156" t="str">
-        <v>Viridian Forest</v>
+        <v>Ilex Forest 2</v>
       </c>
       <c r="C156" t="str">
         <v/>
       </c>
       <c r="D156" t="str">
-        <v>Beedrill</v>
+        <v>Celebi</v>
       </c>
       <c r="E156" t="str">
-        <v>74-78</v>
+        <v>85-85</v>
       </c>
       <c r="F156" t="str">
-        <v>15%</v>
+        <v>5%</v>
       </c>
       <c r="G156">
         <v>1</v>
@@ -3992,91 +3992,91 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Challenge 35</v>
+        <v>Challenge 12</v>
       </c>
       <c r="B157" t="str">
-        <v>Viridian Forest</v>
+        <v>Extra Challenge (Roaming)</v>
       </c>
       <c r="C157" t="str">
         <v/>
       </c>
       <c r="D157" t="str">
-        <v>Vileplume</v>
+        <v>Raikou</v>
       </c>
       <c r="E157" t="str">
-        <v>75-78</v>
+        <v>50-50</v>
       </c>
       <c r="F157" t="str">
-        <v>10%</v>
+        <v>33.33%</v>
       </c>
       <c r="G157">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Challenge 35</v>
+        <v>Challenge 12</v>
       </c>
       <c r="B158" t="str">
-        <v>Viridian Forest</v>
+        <v>Extra Challenge (Roaming)</v>
       </c>
       <c r="C158" t="str">
         <v/>
       </c>
       <c r="D158" t="str">
-        <v>Bellossom</v>
+        <v>Entei</v>
       </c>
       <c r="E158" t="str">
-        <v>75-78</v>
+        <v>50-50</v>
       </c>
       <c r="F158" t="str">
-        <v>10%</v>
+        <v>33.33%</v>
       </c>
       <c r="G158">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Challenge 37</v>
+        <v>Challenge 12</v>
       </c>
       <c r="B159" t="str">
-        <v>Mount Moon</v>
+        <v>Extra Challenge (Roaming)</v>
       </c>
       <c r="C159" t="str">
         <v/>
       </c>
       <c r="D159" t="str">
-        <v>Geodude</v>
+        <v>Suicune</v>
       </c>
       <c r="E159" t="str">
-        <v>76-80</v>
+        <v>50-50</v>
       </c>
       <c r="F159" t="str">
-        <v>25%</v>
+        <v>33.33%</v>
       </c>
       <c r="G159">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Challenge 37</v>
+        <v>Challenge 35</v>
       </c>
       <c r="B160" t="str">
-        <v>Mount Moon</v>
+        <v>Viridian Forest</v>
       </c>
       <c r="C160" t="str">
         <v/>
       </c>
       <c r="D160" t="str">
-        <v>Golbat</v>
+        <v>Oddish</v>
       </c>
       <c r="E160" t="str">
-        <v>76-81</v>
+        <v>72-76</v>
       </c>
       <c r="F160" t="str">
-        <v>25%</v>
+        <v>23%</v>
       </c>
       <c r="G160">
         <v>1</v>
@@ -4084,22 +4084,22 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Challenge 37</v>
+        <v>Challenge 35</v>
       </c>
       <c r="B161" t="str">
-        <v>Mount Moon</v>
+        <v>Viridian Forest</v>
       </c>
       <c r="C161" t="str">
         <v/>
       </c>
       <c r="D161" t="str">
-        <v>Graveler</v>
+        <v>Gloom</v>
       </c>
       <c r="E161" t="str">
-        <v>78-82</v>
+        <v>72-76</v>
       </c>
       <c r="F161" t="str">
-        <v>20%</v>
+        <v>24%</v>
       </c>
       <c r="G161">
         <v>1</v>
@@ -4107,22 +4107,22 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Challenge 37</v>
+        <v>Challenge 35</v>
       </c>
       <c r="B162" t="str">
-        <v>Mount Moon</v>
+        <v>Viridian Forest</v>
       </c>
       <c r="C162" t="str">
         <v/>
       </c>
       <c r="D162" t="str">
-        <v>Onix</v>
+        <v>Butterfree</v>
       </c>
       <c r="E162" t="str">
-        <v>77-81</v>
+        <v>74-78</v>
       </c>
       <c r="F162" t="str">
-        <v>15%</v>
+        <v>14%</v>
       </c>
       <c r="G162">
         <v>1</v>
@@ -4130,22 +4130,22 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Challenge 37</v>
+        <v>Challenge 35</v>
       </c>
       <c r="B163" t="str">
-        <v>Mount Moon</v>
+        <v>Viridian Forest</v>
       </c>
       <c r="C163" t="str">
         <v/>
       </c>
       <c r="D163" t="str">
-        <v>Crobat</v>
+        <v>Beedrill</v>
       </c>
       <c r="E163" t="str">
-        <v>78-82</v>
+        <v>74-78</v>
       </c>
       <c r="F163" t="str">
-        <v>15%</v>
+        <v>14%</v>
       </c>
       <c r="G163">
         <v>1</v>
@@ -4153,22 +4153,22 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Challenge 38</v>
+        <v>Challenge 35</v>
       </c>
       <c r="B164" t="str">
-        <v>Rock Tunnel</v>
+        <v>Viridian Forest</v>
       </c>
       <c r="C164" t="str">
         <v/>
       </c>
       <c r="D164" t="str">
-        <v>Golbat</v>
+        <v>Vileplume</v>
       </c>
       <c r="E164" t="str">
-        <v>79-83</v>
+        <v>75-78</v>
       </c>
       <c r="F164" t="str">
-        <v>30%</v>
+        <v>10%</v>
       </c>
       <c r="G164">
         <v>1</v>
@@ -4176,22 +4176,22 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Challenge 38</v>
+        <v>Challenge 35</v>
       </c>
       <c r="B165" t="str">
-        <v>Rock Tunnel</v>
+        <v>Viridian Forest</v>
       </c>
       <c r="C165" t="str">
         <v/>
       </c>
       <c r="D165" t="str">
-        <v>Golem</v>
+        <v>Bellossom</v>
       </c>
       <c r="E165" t="str">
-        <v>81-85</v>
+        <v>75-78</v>
       </c>
       <c r="F165" t="str">
-        <v>25%</v>
+        <v>10%</v>
       </c>
       <c r="G165">
         <v>1</v>
@@ -4199,22 +4199,22 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Challenge 38</v>
+        <v>Challenge 35</v>
       </c>
       <c r="B166" t="str">
-        <v>Rock Tunnel</v>
+        <v>Viridian Forest</v>
       </c>
       <c r="C166" t="str">
         <v/>
       </c>
       <c r="D166" t="str">
-        <v>Steelix</v>
+        <v>Pikachu</v>
       </c>
       <c r="E166" t="str">
-        <v>81-85</v>
+        <v>72-78</v>
       </c>
       <c r="F166" t="str">
-        <v>25%</v>
+        <v>5%</v>
       </c>
       <c r="G166">
         <v>1</v>
@@ -4222,22 +4222,22 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Challenge 38</v>
+        <v>Challenge 37</v>
       </c>
       <c r="B167" t="str">
-        <v>Rock Tunnel</v>
+        <v>Mount Moon</v>
       </c>
       <c r="C167" t="str">
         <v/>
       </c>
       <c r="D167" t="str">
-        <v>Crobat</v>
+        <v>Geodude</v>
       </c>
       <c r="E167" t="str">
-        <v>81-85</v>
+        <v>76-80</v>
       </c>
       <c r="F167" t="str">
-        <v>20%</v>
+        <v>22%</v>
       </c>
       <c r="G167">
         <v>1</v>
@@ -4245,22 +4245,22 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Challenge 40</v>
+        <v>Challenge 37</v>
       </c>
       <c r="B168" t="str">
-        <v>Route 8</v>
+        <v>Mount Moon</v>
       </c>
       <c r="C168" t="str">
         <v/>
       </c>
       <c r="D168" t="str">
-        <v>Slowpoke</v>
+        <v>Golbat</v>
       </c>
       <c r="E168" t="str">
-        <v>82-86</v>
+        <v>76-81</v>
       </c>
       <c r="F168" t="str">
-        <v>40%</v>
+        <v>23%</v>
       </c>
       <c r="G168">
         <v>1</v>
@@ -4268,22 +4268,22 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Challenge 40</v>
+        <v>Challenge 37</v>
       </c>
       <c r="B169" t="str">
-        <v>Route 8</v>
+        <v>Mount Moon</v>
       </c>
       <c r="C169" t="str">
         <v/>
       </c>
       <c r="D169" t="str">
-        <v>Kadabra</v>
+        <v>Graveler</v>
       </c>
       <c r="E169" t="str">
-        <v>83-87</v>
+        <v>78-82</v>
       </c>
       <c r="F169" t="str">
-        <v>30%</v>
+        <v>18%</v>
       </c>
       <c r="G169">
         <v>1</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Challenge 40</v>
+        <v>Challenge 37</v>
       </c>
       <c r="B170" t="str">
-        <v>Route 8</v>
+        <v>Mount Moon</v>
       </c>
       <c r="C170" t="str">
         <v/>
       </c>
       <c r="D170" t="str">
-        <v>Mr. Mime</v>
+        <v>Onix</v>
       </c>
       <c r="E170" t="str">
-        <v>83-87</v>
+        <v>77-81</v>
       </c>
       <c r="F170" t="str">
-        <v>30%</v>
+        <v>14%</v>
       </c>
       <c r="G170">
         <v>1</v>
@@ -4314,22 +4314,22 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Challenge 43</v>
+        <v>Challenge 37</v>
       </c>
       <c r="B171" t="str">
-        <v>Route 12</v>
+        <v>Mount Moon</v>
       </c>
       <c r="C171" t="str">
         <v/>
       </c>
       <c r="D171" t="str">
-        <v>Grimer</v>
+        <v>Crobat</v>
       </c>
       <c r="E171" t="str">
-        <v>84-88</v>
+        <v>78-82</v>
       </c>
       <c r="F171" t="str">
-        <v>25%</v>
+        <v>14%</v>
       </c>
       <c r="G171">
         <v>1</v>
@@ -4337,22 +4337,22 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Challenge 43</v>
+        <v>Challenge 37</v>
       </c>
       <c r="B172" t="str">
-        <v>Route 12</v>
+        <v>Mount Moon</v>
       </c>
       <c r="C172" t="str">
         <v/>
       </c>
       <c r="D172" t="str">
-        <v>Horsea</v>
+        <v>Clefairy</v>
       </c>
       <c r="E172" t="str">
-        <v>84-88</v>
+        <v>76-82</v>
       </c>
       <c r="F172" t="str">
-        <v>25%</v>
+        <v>9%</v>
       </c>
       <c r="G172">
         <v>1</v>
@@ -4360,22 +4360,22 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Challenge 43</v>
+        <v>Challenge 38</v>
       </c>
       <c r="B173" t="str">
-        <v>Route 12</v>
+        <v>Rock Tunnel</v>
       </c>
       <c r="C173" t="str">
         <v/>
       </c>
       <c r="D173" t="str">
-        <v>Hypno</v>
+        <v>Golbat</v>
       </c>
       <c r="E173" t="str">
-        <v>85-89</v>
+        <v>79-83</v>
       </c>
       <c r="F173" t="str">
-        <v>20%</v>
+        <v>30%</v>
       </c>
       <c r="G173">
         <v>1</v>
@@ -4383,22 +4383,22 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Challenge 43</v>
+        <v>Challenge 38</v>
       </c>
       <c r="B174" t="str">
-        <v>Route 12</v>
+        <v>Rock Tunnel</v>
       </c>
       <c r="C174" t="str">
         <v/>
       </c>
       <c r="D174" t="str">
-        <v>Seadra</v>
+        <v>Golem</v>
       </c>
       <c r="E174" t="str">
-        <v>86-89</v>
+        <v>81-85</v>
       </c>
       <c r="F174" t="str">
-        <v>15%</v>
+        <v>25%</v>
       </c>
       <c r="G174">
         <v>1</v>
@@ -4406,22 +4406,22 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Challenge 43</v>
+        <v>Challenge 38</v>
       </c>
       <c r="B175" t="str">
-        <v>Route 12</v>
+        <v>Rock Tunnel</v>
       </c>
       <c r="C175" t="str">
         <v/>
       </c>
       <c r="D175" t="str">
-        <v>Slowking</v>
+        <v>Steelix</v>
       </c>
       <c r="E175" t="str">
-        <v>86-89</v>
+        <v>81-85</v>
       </c>
       <c r="F175" t="str">
-        <v>10%</v>
+        <v>25%</v>
       </c>
       <c r="G175">
         <v>1</v>
@@ -4429,22 +4429,22 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Challenge 43</v>
+        <v>Challenge 38</v>
       </c>
       <c r="B176" t="str">
-        <v>Route 12</v>
+        <v>Rock Tunnel</v>
       </c>
       <c r="C176" t="str">
         <v/>
       </c>
       <c r="D176" t="str">
-        <v>Snorlax</v>
+        <v>Crobat</v>
       </c>
       <c r="E176" t="str">
-        <v>88-89</v>
+        <v>81-85</v>
       </c>
       <c r="F176" t="str">
-        <v>5%</v>
+        <v>20%</v>
       </c>
       <c r="G176">
         <v>1</v>
@@ -4452,22 +4452,22 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Challenge 44</v>
+        <v>Challenge 40</v>
       </c>
       <c r="B177" t="str">
-        <v>Kanto Safari Zone</v>
+        <v>Route 8</v>
       </c>
       <c r="C177" t="str">
         <v/>
       </c>
       <c r="D177" t="str">
-        <v>Nidoking</v>
+        <v>Slowpoke</v>
       </c>
       <c r="E177" t="str">
-        <v>86-90</v>
+        <v>82-86</v>
       </c>
       <c r="F177" t="str">
-        <v>10%</v>
+        <v>40%</v>
       </c>
       <c r="G177">
         <v>1</v>
@@ -4475,22 +4475,22 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Challenge 44</v>
+        <v>Challenge 40</v>
       </c>
       <c r="B178" t="str">
-        <v>Kanto Safari Zone</v>
+        <v>Route 8</v>
       </c>
       <c r="C178" t="str">
         <v/>
       </c>
       <c r="D178" t="str">
-        <v>Nidoqueen</v>
+        <v>Kadabra</v>
       </c>
       <c r="E178" t="str">
-        <v>86-90</v>
+        <v>83-87</v>
       </c>
       <c r="F178" t="str">
-        <v>10%</v>
+        <v>30%</v>
       </c>
       <c r="G178">
         <v>1</v>
@@ -4498,22 +4498,22 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Challenge 44</v>
+        <v>Challenge 40</v>
       </c>
       <c r="B179" t="str">
-        <v>Kanto Safari Zone</v>
+        <v>Route 8</v>
       </c>
       <c r="C179" t="str">
         <v/>
       </c>
       <c r="D179" t="str">
-        <v>Rhydon</v>
+        <v>Mr. Mime</v>
       </c>
       <c r="E179" t="str">
-        <v>87-90</v>
+        <v>83-87</v>
       </c>
       <c r="F179" t="str">
-        <v>15%</v>
+        <v>30%</v>
       </c>
       <c r="G179">
         <v>1</v>
@@ -4521,65 +4521,65 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Challenge 44</v>
+        <v>Challenge 40</v>
       </c>
       <c r="B180" t="str">
-        <v>Kanto Safari Zone</v>
+        <v>Diglett Cave</v>
       </c>
       <c r="C180" t="str">
         <v/>
       </c>
       <c r="D180" t="str">
-        <v>Tauros</v>
+        <v>Diglett</v>
       </c>
       <c r="E180" t="str">
-        <v>87-91</v>
+        <v>82-86</v>
       </c>
       <c r="F180" t="str">
-        <v>20%</v>
+        <v>90%</v>
       </c>
       <c r="G180">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Challenge 44</v>
+        <v>Challenge 40</v>
       </c>
       <c r="B181" t="str">
-        <v>Kanto Safari Zone</v>
+        <v>Diglett Cave</v>
       </c>
       <c r="C181" t="str">
         <v/>
       </c>
       <c r="D181" t="str">
-        <v>Scizor</v>
+        <v>Dugtrio</v>
       </c>
       <c r="E181" t="str">
-        <v>87-90</v>
+        <v>85-89</v>
       </c>
       <c r="F181" t="str">
-        <v>20%</v>
+        <v>10%</v>
       </c>
       <c r="G181">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Challenge 44</v>
+        <v>Challenge 43</v>
       </c>
       <c r="B182" t="str">
-        <v>Kanto Safari Zone</v>
+        <v>Route 12</v>
       </c>
       <c r="C182" t="str">
         <v/>
       </c>
       <c r="D182" t="str">
-        <v>Chansey</v>
+        <v>Grimer</v>
       </c>
       <c r="E182" t="str">
-        <v>88-91</v>
+        <v>84-88</v>
       </c>
       <c r="F182" t="str">
         <v>25%</v>
@@ -4590,19 +4590,19 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Challenge 23</v>
+        <v>Challenge 43</v>
       </c>
       <c r="B183" t="str">
-        <v>Safari Zone</v>
+        <v>Route 12</v>
       </c>
       <c r="C183" t="str">
         <v/>
       </c>
       <c r="D183" t="str">
-        <v>Nidorino</v>
+        <v>Horsea</v>
       </c>
       <c r="E183" t="str">
-        <v>39-44</v>
+        <v>84-88</v>
       </c>
       <c r="F183" t="str">
         <v>25%</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Challenge 23</v>
+        <v>Challenge 43</v>
       </c>
       <c r="B184" t="str">
-        <v>Safari Zone</v>
+        <v>Route 12</v>
       </c>
       <c r="C184" t="str">
         <v/>
       </c>
       <c r="D184" t="str">
-        <v>Nidorina</v>
+        <v>Hypno</v>
       </c>
       <c r="E184" t="str">
-        <v>39-44</v>
+        <v>85-89</v>
       </c>
       <c r="F184" t="str">
-        <v>25%</v>
+        <v>20%</v>
       </c>
       <c r="G184">
         <v>1</v>
@@ -4636,19 +4636,19 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Challenge 23</v>
+        <v>Challenge 43</v>
       </c>
       <c r="B185" t="str">
-        <v>Safari Zone</v>
+        <v>Route 12</v>
       </c>
       <c r="C185" t="str">
         <v/>
       </c>
       <c r="D185" t="str">
-        <v>Rhyhorn</v>
+        <v>Seadra</v>
       </c>
       <c r="E185" t="str">
-        <v>40-45</v>
+        <v>86-89</v>
       </c>
       <c r="F185" t="str">
         <v>15%</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Challenge 23</v>
+        <v>Challenge 43</v>
       </c>
       <c r="B186" t="str">
-        <v>Safari Zone</v>
+        <v>Route 12</v>
       </c>
       <c r="C186" t="str">
         <v/>
       </c>
       <c r="D186" t="str">
-        <v>Kangaskhan</v>
+        <v>Slowking</v>
       </c>
       <c r="E186" t="str">
-        <v>40-45</v>
+        <v>86-89</v>
       </c>
       <c r="F186" t="str">
-        <v>15%</v>
+        <v>10%</v>
       </c>
       <c r="G186">
         <v>1</v>
@@ -4682,22 +4682,22 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Challenge 23</v>
+        <v>Challenge 43</v>
       </c>
       <c r="B187" t="str">
-        <v>Safari Zone</v>
+        <v>Route 12</v>
       </c>
       <c r="C187" t="str">
         <v/>
       </c>
       <c r="D187" t="str">
-        <v>Murkrow</v>
+        <v>Snorlax</v>
       </c>
       <c r="E187" t="str">
-        <v>39-44</v>
+        <v>88-89</v>
       </c>
       <c r="F187" t="str">
-        <v>10%</v>
+        <v>5%</v>
       </c>
       <c r="G187">
         <v>1</v>
@@ -4705,19 +4705,19 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Challenge 23</v>
+        <v>Challenge 44</v>
       </c>
       <c r="B188" t="str">
-        <v>Safari Zone</v>
+        <v>Kanto Safari Zone</v>
       </c>
       <c r="C188" t="str">
         <v/>
       </c>
       <c r="D188" t="str">
-        <v>Chansey</v>
+        <v>Nidoking</v>
       </c>
       <c r="E188" t="str">
-        <v>39-44</v>
+        <v>86-90</v>
       </c>
       <c r="F188" t="str">
         <v>10%</v>
@@ -4728,22 +4728,22 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Challenge 45</v>
+        <v>Challenge 44</v>
       </c>
       <c r="B189" t="str">
-        <v>Cycling Road</v>
+        <v>Kanto Safari Zone</v>
       </c>
       <c r="C189" t="str">
         <v/>
       </c>
       <c r="D189" t="str">
-        <v>Doduo</v>
+        <v>Nidoqueen</v>
       </c>
       <c r="E189" t="str">
-        <v>88-92</v>
+        <v>86-90</v>
       </c>
       <c r="F189" t="str">
-        <v>25%</v>
+        <v>10%</v>
       </c>
       <c r="G189">
         <v>1</v>
@@ -4751,22 +4751,22 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Challenge 45</v>
+        <v>Challenge 44</v>
       </c>
       <c r="B190" t="str">
-        <v>Cycling Road</v>
+        <v>Kanto Safari Zone</v>
       </c>
       <c r="C190" t="str">
         <v/>
       </c>
       <c r="D190" t="str">
-        <v>Fearow</v>
+        <v>Rhydon</v>
       </c>
       <c r="E190" t="str">
-        <v>88-92</v>
+        <v>87-90</v>
       </c>
       <c r="F190" t="str">
-        <v>25%</v>
+        <v>15%</v>
       </c>
       <c r="G190">
         <v>1</v>
@@ -4774,19 +4774,19 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Challenge 45</v>
+        <v>Challenge 44</v>
       </c>
       <c r="B191" t="str">
-        <v>Cycling Road</v>
+        <v>Kanto Safari Zone</v>
       </c>
       <c r="C191" t="str">
         <v/>
       </c>
       <c r="D191" t="str">
-        <v>Dodrio</v>
+        <v>Tauros</v>
       </c>
       <c r="E191" t="str">
-        <v>90-93</v>
+        <v>87-91</v>
       </c>
       <c r="F191" t="str">
         <v>20%</v>
@@ -4797,19 +4797,19 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Challenge 45</v>
+        <v>Challenge 44</v>
       </c>
       <c r="B192" t="str">
-        <v>Cycling Road</v>
+        <v>Kanto Safari Zone</v>
       </c>
       <c r="C192" t="str">
         <v/>
       </c>
       <c r="D192" t="str">
-        <v>Pidgeot</v>
+        <v>Scizor</v>
       </c>
       <c r="E192" t="str">
-        <v>90-93</v>
+        <v>87-90</v>
       </c>
       <c r="F192" t="str">
         <v>20%</v>
@@ -4820,22 +4820,22 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Challenge 45</v>
+        <v>Challenge 44</v>
       </c>
       <c r="B193" t="str">
-        <v>Cycling Road</v>
+        <v>Kanto Safari Zone</v>
       </c>
       <c r="C193" t="str">
         <v/>
       </c>
       <c r="D193" t="str">
-        <v>Snorlax</v>
+        <v>Chansey</v>
       </c>
       <c r="E193" t="str">
-        <v>92-93</v>
+        <v>88-91</v>
       </c>
       <c r="F193" t="str">
-        <v>10%</v>
+        <v>25%</v>
       </c>
       <c r="G193">
         <v>1</v>
@@ -4843,19 +4843,19 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Challenge 45</v>
+        <v>Challenge 23</v>
       </c>
       <c r="B194" t="str">
-        <v>Sea Routes</v>
+        <v>Safari Zone</v>
       </c>
       <c r="C194" t="str">
         <v/>
       </c>
       <c r="D194" t="str">
-        <v>Seel</v>
+        <v>Nidorino</v>
       </c>
       <c r="E194" t="str">
-        <v>90-94</v>
+        <v>39-44</v>
       </c>
       <c r="F194" t="str">
         <v>25%</v>
@@ -4866,19 +4866,19 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Challenge 45</v>
+        <v>Challenge 23</v>
       </c>
       <c r="B195" t="str">
-        <v>Sea Routes</v>
+        <v>Safari Zone</v>
       </c>
       <c r="C195" t="str">
         <v/>
       </c>
       <c r="D195" t="str">
-        <v>Seaking</v>
+        <v>Nidorina</v>
       </c>
       <c r="E195" t="str">
-        <v>90-94</v>
+        <v>39-44</v>
       </c>
       <c r="F195" t="str">
         <v>25%</v>
@@ -4889,19 +4889,19 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Challenge 45</v>
+        <v>Challenge 23</v>
       </c>
       <c r="B196" t="str">
-        <v>Sea Routes</v>
+        <v>Safari Zone</v>
       </c>
       <c r="C196" t="str">
         <v/>
       </c>
       <c r="D196" t="str">
-        <v>Dewgong</v>
+        <v>Rhyhorn</v>
       </c>
       <c r="E196" t="str">
-        <v>91-94</v>
+        <v>40-45</v>
       </c>
       <c r="F196" t="str">
         <v>15%</v>
@@ -4912,19 +4912,19 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Challenge 45</v>
+        <v>Challenge 23</v>
       </c>
       <c r="B197" t="str">
-        <v>Sea Routes</v>
+        <v>Safari Zone</v>
       </c>
       <c r="C197" t="str">
         <v/>
       </c>
       <c r="D197" t="str">
-        <v>Tentacruel</v>
+        <v>Kangaskhan</v>
       </c>
       <c r="E197" t="str">
-        <v>91-94</v>
+        <v>40-45</v>
       </c>
       <c r="F197" t="str">
         <v>15%</v>
@@ -4935,19 +4935,19 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Challenge 45</v>
+        <v>Challenge 23</v>
       </c>
       <c r="B198" t="str">
-        <v>Sea Routes</v>
+        <v>Safari Zone</v>
       </c>
       <c r="C198" t="str">
         <v/>
       </c>
       <c r="D198" t="str">
-        <v>Starmie</v>
+        <v>Murkrow</v>
       </c>
       <c r="E198" t="str">
-        <v>92-94</v>
+        <v>39-44</v>
       </c>
       <c r="F198" t="str">
         <v>10%</v>
@@ -4958,19 +4958,19 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Challenge 45</v>
+        <v>Challenge 23</v>
       </c>
       <c r="B199" t="str">
-        <v>Sea Routes</v>
+        <v>Safari Zone</v>
       </c>
       <c r="C199" t="str">
         <v/>
       </c>
       <c r="D199" t="str">
-        <v>Kingdra</v>
+        <v>Chansey</v>
       </c>
       <c r="E199" t="str">
-        <v>92-94</v>
+        <v>39-44</v>
       </c>
       <c r="F199" t="str">
         <v>10%</v>
@@ -4981,22 +4981,22 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Challenge 36</v>
+        <v>Challenge 45</v>
       </c>
       <c r="B200" t="str">
-        <v>Fossil Revival Lab</v>
+        <v>Cycling Road</v>
       </c>
       <c r="C200" t="str">
         <v/>
       </c>
       <c r="D200" t="str">
-        <v>Omanyte</v>
+        <v>Doduo</v>
       </c>
       <c r="E200" t="str">
-        <v>91-93</v>
+        <v>88-92</v>
       </c>
       <c r="F200" t="str">
-        <v>30%</v>
+        <v>25%</v>
       </c>
       <c r="G200">
         <v>1</v>
@@ -5004,22 +5004,22 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Challenge 36</v>
+        <v>Challenge 45</v>
       </c>
       <c r="B201" t="str">
-        <v>Fossil Revival Lab</v>
+        <v>Cycling Road</v>
       </c>
       <c r="C201" t="str">
         <v/>
       </c>
       <c r="D201" t="str">
-        <v>Kabuto</v>
+        <v>Fearow</v>
       </c>
       <c r="E201" t="str">
-        <v>91-93</v>
+        <v>88-92</v>
       </c>
       <c r="F201" t="str">
-        <v>30%</v>
+        <v>25%</v>
       </c>
       <c r="G201">
         <v>1</v>
@@ -5027,22 +5027,22 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Challenge 36</v>
+        <v>Challenge 45</v>
       </c>
       <c r="B202" t="str">
-        <v>Fossil Revival Lab</v>
+        <v>Cycling Road</v>
       </c>
       <c r="C202" t="str">
         <v/>
       </c>
       <c r="D202" t="str">
-        <v>Aerodactyl</v>
+        <v>Dodrio</v>
       </c>
       <c r="E202" t="str">
-        <v>94-95</v>
+        <v>90-93</v>
       </c>
       <c r="F202" t="str">
-        <v>10%</v>
+        <v>20%</v>
       </c>
       <c r="G202">
         <v>1</v>
@@ -5050,22 +5050,22 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Challenge 36</v>
+        <v>Challenge 45</v>
       </c>
       <c r="B203" t="str">
-        <v>Fossil Revival Lab</v>
+        <v>Cycling Road</v>
       </c>
       <c r="C203" t="str">
         <v/>
       </c>
       <c r="D203" t="str">
-        <v>Omastar</v>
+        <v>Pidgeot</v>
       </c>
       <c r="E203" t="str">
-        <v>92-94</v>
+        <v>90-93</v>
       </c>
       <c r="F203" t="str">
-        <v>15%</v>
+        <v>20%</v>
       </c>
       <c r="G203">
         <v>1</v>
@@ -5073,22 +5073,22 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Challenge 36</v>
+        <v>Challenge 45</v>
       </c>
       <c r="B204" t="str">
-        <v>Fossil Revival Lab</v>
+        <v>Cycling Road</v>
       </c>
       <c r="C204" t="str">
         <v/>
       </c>
       <c r="D204" t="str">
-        <v>Kabutops</v>
+        <v>Snorlax</v>
       </c>
       <c r="E204" t="str">
-        <v>92-94</v>
+        <v>92-93</v>
       </c>
       <c r="F204" t="str">
-        <v>15%</v>
+        <v>10%</v>
       </c>
       <c r="G204">
         <v>1</v>
@@ -5096,22 +5096,22 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B205" t="str">
-        <v>Pokémon Mansion</v>
+        <v>Sea Routes</v>
       </c>
       <c r="C205" t="str">
         <v/>
       </c>
       <c r="D205" t="str">
-        <v>Koffing</v>
+        <v>Seel</v>
       </c>
       <c r="E205" t="str">
-        <v>91-95</v>
+        <v>90-94</v>
       </c>
       <c r="F205" t="str">
-        <v>20%</v>
+        <v>25%</v>
       </c>
       <c r="G205">
         <v>1</v>
@@ -5119,22 +5119,22 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B206" t="str">
-        <v>Pokémon Mansion</v>
+        <v>Sea Routes</v>
       </c>
       <c r="C206" t="str">
         <v/>
       </c>
       <c r="D206" t="str">
-        <v>Slugma</v>
+        <v>Seaking</v>
       </c>
       <c r="E206" t="str">
-        <v>91-95</v>
+        <v>90-94</v>
       </c>
       <c r="F206" t="str">
-        <v>20%</v>
+        <v>25%</v>
       </c>
       <c r="G206">
         <v>1</v>
@@ -5142,22 +5142,22 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B207" t="str">
-        <v>Pokémon Mansion</v>
+        <v>Sea Routes</v>
       </c>
       <c r="C207" t="str">
         <v/>
       </c>
       <c r="D207" t="str">
-        <v>Houndour</v>
+        <v>Dewgong</v>
       </c>
       <c r="E207" t="str">
-        <v>91-95</v>
+        <v>91-94</v>
       </c>
       <c r="F207" t="str">
-        <v>20%</v>
+        <v>15%</v>
       </c>
       <c r="G207">
         <v>1</v>
@@ -5165,19 +5165,19 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B208" t="str">
-        <v>Pokémon Mansion</v>
+        <v>Sea Routes</v>
       </c>
       <c r="C208" t="str">
         <v/>
       </c>
       <c r="D208" t="str">
-        <v>Magmar</v>
+        <v>Tentacruel</v>
       </c>
       <c r="E208" t="str">
-        <v>92-95</v>
+        <v>91-94</v>
       </c>
       <c r="F208" t="str">
         <v>15%</v>
@@ -5188,22 +5188,22 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B209" t="str">
-        <v>Pokémon Mansion</v>
+        <v>Sea Routes</v>
       </c>
       <c r="C209" t="str">
         <v/>
       </c>
       <c r="D209" t="str">
-        <v>Weezing</v>
+        <v>Starmie</v>
       </c>
       <c r="E209" t="str">
-        <v>93-95</v>
+        <v>92-94</v>
       </c>
       <c r="F209" t="str">
-        <v>15%</v>
+        <v>10%</v>
       </c>
       <c r="G209">
         <v>1</v>
@@ -5211,22 +5211,22 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B210" t="str">
-        <v>Pokémon Mansion</v>
+        <v>Sea Routes</v>
       </c>
       <c r="C210" t="str">
         <v/>
       </c>
       <c r="D210" t="str">
-        <v>Magcargo</v>
+        <v>Kingdra</v>
       </c>
       <c r="E210" t="str">
-        <v>93-95</v>
+        <v>92-94</v>
       </c>
       <c r="F210" t="str">
-        <v>5%</v>
+        <v>10%</v>
       </c>
       <c r="G210">
         <v>1</v>
@@ -5234,22 +5234,22 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="B211" t="str">
-        <v>Pokémon Mansion</v>
+        <v>Fossil Revival Lab</v>
       </c>
       <c r="C211" t="str">
         <v/>
       </c>
       <c r="D211" t="str">
-        <v>Houndoom</v>
+        <v>Omanyte</v>
       </c>
       <c r="E211" t="str">
-        <v>93-95</v>
+        <v>91-93</v>
       </c>
       <c r="F211" t="str">
-        <v>5%</v>
+        <v>30%</v>
       </c>
       <c r="G211">
         <v>1</v>
@@ -5257,275 +5257,275 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Challenge 41</v>
+        <v>Challenge 36</v>
       </c>
       <c r="B212" t="str">
-        <v>Casino Starter Trupe</v>
+        <v>Fossil Revival Lab</v>
       </c>
       <c r="C212" t="str">
         <v/>
       </c>
       <c r="D212" t="str">
-        <v>Bulbasaur</v>
+        <v>Kabuto</v>
       </c>
       <c r="E212" t="str">
-        <v>80-85</v>
+        <v>91-93</v>
       </c>
       <c r="F212" t="str">
-        <v>16.67%</v>
+        <v>30%</v>
       </c>
       <c r="G212">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Challenge 41</v>
+        <v>Challenge 36</v>
       </c>
       <c r="B213" t="str">
-        <v>Casino Starter Trupe</v>
+        <v>Fossil Revival Lab</v>
       </c>
       <c r="C213" t="str">
         <v/>
       </c>
       <c r="D213" t="str">
-        <v>Charmander</v>
+        <v>Aerodactyl</v>
       </c>
       <c r="E213" t="str">
-        <v>80-85</v>
+        <v>94-95</v>
       </c>
       <c r="F213" t="str">
-        <v>16.67%</v>
+        <v>10%</v>
       </c>
       <c r="G213">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Challenge 41</v>
+        <v>Challenge 36</v>
       </c>
       <c r="B214" t="str">
-        <v>Casino Starter Trupe</v>
+        <v>Fossil Revival Lab</v>
       </c>
       <c r="C214" t="str">
         <v/>
       </c>
       <c r="D214" t="str">
-        <v>Squirtle</v>
+        <v>Omastar</v>
       </c>
       <c r="E214" t="str">
-        <v>80-85</v>
+        <v>92-94</v>
       </c>
       <c r="F214" t="str">
-        <v>16.67%</v>
+        <v>15%</v>
       </c>
       <c r="G214">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Challenge 41</v>
+        <v>Challenge 36</v>
       </c>
       <c r="B215" t="str">
-        <v>Casino Starter Trupe</v>
+        <v>Fossil Revival Lab</v>
       </c>
       <c r="C215" t="str">
         <v/>
       </c>
       <c r="D215" t="str">
-        <v>Chikorita</v>
+        <v>Kabutops</v>
       </c>
       <c r="E215" t="str">
-        <v>80-85</v>
+        <v>92-94</v>
       </c>
       <c r="F215" t="str">
-        <v>16.67%</v>
+        <v>15%</v>
       </c>
       <c r="G215">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Challenge 41</v>
+        <v/>
       </c>
       <c r="B216" t="str">
-        <v>Casino Starter Trupe</v>
+        <v>Pokémon Mansion</v>
       </c>
       <c r="C216" t="str">
         <v/>
       </c>
       <c r="D216" t="str">
-        <v>Cyndaquil</v>
+        <v>Koffing</v>
       </c>
       <c r="E216" t="str">
-        <v>80-85</v>
+        <v>91-95</v>
       </c>
       <c r="F216" t="str">
-        <v>16.67%</v>
+        <v>20%</v>
       </c>
       <c r="G216">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Challenge 41</v>
+        <v/>
       </c>
       <c r="B217" t="str">
-        <v>Casino Starter Trupe</v>
+        <v>Pokémon Mansion</v>
       </c>
       <c r="C217" t="str">
         <v/>
       </c>
       <c r="D217" t="str">
-        <v>Totodile</v>
+        <v>Slugma</v>
       </c>
       <c r="E217" t="str">
-        <v>80-85</v>
+        <v>91-95</v>
       </c>
       <c r="F217" t="str">
-        <v>16.67%</v>
+        <v>20%</v>
       </c>
       <c r="G217">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Kanto Extra Challenge 1</v>
+        <v/>
       </c>
       <c r="B218" t="str">
-        <v>Casino Babies</v>
+        <v>Pokémon Mansion</v>
       </c>
       <c r="C218" t="str">
         <v/>
       </c>
       <c r="D218" t="str">
-        <v>Pichu</v>
+        <v>Houndour</v>
       </c>
       <c r="E218" t="str">
-        <v>84-89</v>
+        <v>91-95</v>
       </c>
       <c r="F218" t="str">
-        <v>15%</v>
+        <v>20%</v>
       </c>
       <c r="G218">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Kanto Extra Challenge 1</v>
+        <v/>
       </c>
       <c r="B219" t="str">
-        <v>Casino Babies</v>
+        <v>Pokémon Mansion</v>
       </c>
       <c r="C219" t="str">
         <v/>
       </c>
       <c r="D219" t="str">
-        <v>Cleffa</v>
+        <v>Magmar</v>
       </c>
       <c r="E219" t="str">
-        <v>84-89</v>
+        <v>92-95</v>
       </c>
       <c r="F219" t="str">
         <v>15%</v>
       </c>
       <c r="G219">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Kanto Extra Challenge 1</v>
+        <v/>
       </c>
       <c r="B220" t="str">
-        <v>Casino Babies</v>
+        <v>Pokémon Mansion</v>
       </c>
       <c r="C220" t="str">
         <v/>
       </c>
       <c r="D220" t="str">
-        <v>Igglybuff</v>
+        <v>Weezing</v>
       </c>
       <c r="E220" t="str">
-        <v>84-89</v>
+        <v>93-95</v>
       </c>
       <c r="F220" t="str">
         <v>15%</v>
       </c>
       <c r="G220">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Kanto Extra Challenge 1</v>
+        <v/>
       </c>
       <c r="B221" t="str">
-        <v>Casino Babies</v>
+        <v>Pokémon Mansion</v>
       </c>
       <c r="C221" t="str">
         <v/>
       </c>
       <c r="D221" t="str">
-        <v>Togepi</v>
+        <v>Magcargo</v>
       </c>
       <c r="E221" t="str">
-        <v>84-89</v>
+        <v>93-95</v>
       </c>
       <c r="F221" t="str">
-        <v>15%</v>
+        <v>5%</v>
       </c>
       <c r="G221">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Kanto Extra Challenge 1</v>
+        <v/>
       </c>
       <c r="B222" t="str">
-        <v>Casino Babies</v>
+        <v>Pokémon Mansion</v>
       </c>
       <c r="C222" t="str">
         <v/>
       </c>
       <c r="D222" t="str">
-        <v>Elekid</v>
+        <v>Houndoom</v>
       </c>
       <c r="E222" t="str">
-        <v>84-89</v>
+        <v>93-95</v>
       </c>
       <c r="F222" t="str">
-        <v>10%</v>
+        <v>5%</v>
       </c>
       <c r="G222">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Kanto Extra Challenge 1</v>
+        <v>Challenge 41</v>
       </c>
       <c r="B223" t="str">
-        <v>Casino Babies</v>
+        <v>Casino Starter Trupe</v>
       </c>
       <c r="C223" t="str">
         <v/>
       </c>
       <c r="D223" t="str">
-        <v>Magby</v>
+        <v>Bulbasaur</v>
       </c>
       <c r="E223" t="str">
-        <v>84-89</v>
+        <v>80-85</v>
       </c>
       <c r="F223" t="str">
-        <v>10%</v>
+        <v>16.67%</v>
       </c>
       <c r="G223">
         <v>0</v>
@@ -5533,22 +5533,22 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Kanto Extra Challenge 1</v>
+        <v>Challenge 41</v>
       </c>
       <c r="B224" t="str">
-        <v>Casino Babies</v>
+        <v>Casino Starter Trupe</v>
       </c>
       <c r="C224" t="str">
         <v/>
       </c>
       <c r="D224" t="str">
-        <v>Smoochum</v>
+        <v>Charmander</v>
       </c>
       <c r="E224" t="str">
-        <v>84-89</v>
+        <v>80-85</v>
       </c>
       <c r="F224" t="str">
-        <v>10%</v>
+        <v>16.67%</v>
       </c>
       <c r="G224">
         <v>0</v>
@@ -5556,22 +5556,22 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Kanto Extra Challenge 1</v>
+        <v>Challenge 41</v>
       </c>
       <c r="B225" t="str">
-        <v>Casino Babies</v>
+        <v>Casino Starter Trupe</v>
       </c>
       <c r="C225" t="str">
         <v/>
       </c>
       <c r="D225" t="str">
-        <v>Blissey</v>
+        <v>Squirtle</v>
       </c>
       <c r="E225" t="str">
-        <v>84-89</v>
+        <v>80-85</v>
       </c>
       <c r="F225" t="str">
-        <v>10%</v>
+        <v>16.67%</v>
       </c>
       <c r="G225">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Kanto Extra Challenge 2</v>
+        <v>Challenge 41</v>
       </c>
       <c r="B226" t="str">
-        <v>Casino Special Spot</v>
+        <v>Casino Starter Trupe</v>
       </c>
       <c r="C226" t="str">
         <v/>
       </c>
       <c r="D226" t="str">
-        <v>Lickitung</v>
+        <v>Chikorita</v>
       </c>
       <c r="E226" t="str">
-        <v>84-89</v>
+        <v>80-85</v>
       </c>
       <c r="F226" t="str">
-        <v>30%</v>
+        <v>16.67%</v>
       </c>
       <c r="G226">
         <v>0</v>
@@ -5602,22 +5602,22 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Kanto Extra Challenge 2</v>
+        <v>Challenge 41</v>
       </c>
       <c r="B227" t="str">
-        <v>Casino Special Spot</v>
+        <v>Casino Starter Trupe</v>
       </c>
       <c r="C227" t="str">
         <v/>
       </c>
       <c r="D227" t="str">
-        <v>Porygon</v>
+        <v>Cyndaquil</v>
       </c>
       <c r="E227" t="str">
-        <v>84-89</v>
+        <v>80-85</v>
       </c>
       <c r="F227" t="str">
-        <v>30%</v>
+        <v>16.67%</v>
       </c>
       <c r="G227">
         <v>0</v>
@@ -5625,22 +5625,22 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Kanto Extra Challenge 2</v>
+        <v>Challenge 41</v>
       </c>
       <c r="B228" t="str">
-        <v>Casino Special Spot</v>
+        <v>Casino Starter Trupe</v>
       </c>
       <c r="C228" t="str">
         <v/>
       </c>
       <c r="D228" t="str">
-        <v>Lapras</v>
+        <v>Totodile</v>
       </c>
       <c r="E228" t="str">
-        <v>84-89</v>
+        <v>80-85</v>
       </c>
       <c r="F228" t="str">
-        <v>30%</v>
+        <v>16.67%</v>
       </c>
       <c r="G228">
         <v>0</v>
@@ -5648,22 +5648,22 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Kanto Extra Challenge 2</v>
+        <v>Kanto Extra Challenge 1</v>
       </c>
       <c r="B229" t="str">
-        <v>Casino Special Spot</v>
+        <v>Casino Babies</v>
       </c>
       <c r="C229" t="str">
         <v/>
       </c>
       <c r="D229" t="str">
-        <v>Porygon2</v>
+        <v>Pichu</v>
       </c>
       <c r="E229" t="str">
-        <v>85-90</v>
+        <v>84-89</v>
       </c>
       <c r="F229" t="str">
-        <v>10%</v>
+        <v>15%</v>
       </c>
       <c r="G229">
         <v>0</v>
@@ -5671,22 +5671,22 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Kanto Extra Challenge 3</v>
+        <v>Kanto Extra Challenge 1</v>
       </c>
       <c r="B230" t="str">
-        <v>Casino Eeveelution</v>
+        <v>Casino Babies</v>
       </c>
       <c r="C230" t="str">
         <v/>
       </c>
       <c r="D230" t="str">
-        <v>Eevee</v>
+        <v>Cleffa</v>
       </c>
       <c r="E230" t="str">
-        <v>85-90</v>
+        <v>84-89</v>
       </c>
       <c r="F230" t="str">
-        <v>20%</v>
+        <v>15%</v>
       </c>
       <c r="G230">
         <v>0</v>
@@ -5694,22 +5694,22 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Kanto Extra Challenge 3</v>
+        <v>Kanto Extra Challenge 1</v>
       </c>
       <c r="B231" t="str">
-        <v>Casino Eeveelution</v>
+        <v>Casino Babies</v>
       </c>
       <c r="C231" t="str">
         <v/>
       </c>
       <c r="D231" t="str">
-        <v>Vaporeon</v>
+        <v>Igglybuff</v>
       </c>
       <c r="E231" t="str">
-        <v>86-91</v>
+        <v>84-89</v>
       </c>
       <c r="F231" t="str">
-        <v>10%</v>
+        <v>15%</v>
       </c>
       <c r="G231">
         <v>0</v>
@@ -5717,22 +5717,22 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Kanto Extra Challenge 3</v>
+        <v>Kanto Extra Challenge 1</v>
       </c>
       <c r="B232" t="str">
-        <v>Casino Eeveelution</v>
+        <v>Casino Babies</v>
       </c>
       <c r="C232" t="str">
         <v/>
       </c>
       <c r="D232" t="str">
-        <v>Jolteon</v>
+        <v>Togepi</v>
       </c>
       <c r="E232" t="str">
-        <v>86-91</v>
+        <v>84-89</v>
       </c>
       <c r="F232" t="str">
-        <v>10%</v>
+        <v>15%</v>
       </c>
       <c r="G232">
         <v>0</v>
@@ -5740,19 +5740,19 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Kanto Extra Challenge 3</v>
+        <v>Kanto Extra Challenge 1</v>
       </c>
       <c r="B233" t="str">
-        <v>Casino Eeveelution</v>
+        <v>Casino Babies</v>
       </c>
       <c r="C233" t="str">
         <v/>
       </c>
       <c r="D233" t="str">
-        <v>Flareon</v>
+        <v>Elekid</v>
       </c>
       <c r="E233" t="str">
-        <v>86-91</v>
+        <v>84-89</v>
       </c>
       <c r="F233" t="str">
         <v>10%</v>
@@ -5763,19 +5763,19 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Kanto Extra Challenge 3</v>
+        <v>Kanto Extra Challenge 1</v>
       </c>
       <c r="B234" t="str">
-        <v>Casino Eeveelution</v>
+        <v>Casino Babies</v>
       </c>
       <c r="C234" t="str">
         <v/>
       </c>
       <c r="D234" t="str">
-        <v>Espeon</v>
+        <v>Magby</v>
       </c>
       <c r="E234" t="str">
-        <v>86-91</v>
+        <v>84-89</v>
       </c>
       <c r="F234" t="str">
         <v>10%</v>
@@ -5786,19 +5786,19 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Kanto Extra Challenge 3</v>
+        <v>Kanto Extra Challenge 1</v>
       </c>
       <c r="B235" t="str">
-        <v>Casino Eeveelution</v>
+        <v>Casino Babies</v>
       </c>
       <c r="C235" t="str">
         <v/>
       </c>
       <c r="D235" t="str">
-        <v>Umbreon</v>
+        <v>Smoochum</v>
       </c>
       <c r="E235" t="str">
-        <v>86-91</v>
+        <v>84-89</v>
       </c>
       <c r="F235" t="str">
         <v>10%</v>
@@ -5809,19 +5809,19 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Kanto Extra Challenge 3</v>
+        <v>Kanto Extra Challenge 1</v>
       </c>
       <c r="B236" t="str">
-        <v>Casino Eeveelution</v>
+        <v>Casino Babies</v>
       </c>
       <c r="C236" t="str">
         <v/>
       </c>
       <c r="D236" t="str">
-        <v>Leafeon</v>
+        <v>Blissey</v>
       </c>
       <c r="E236" t="str">
-        <v>86-91</v>
+        <v>84-89</v>
       </c>
       <c r="F236" t="str">
         <v>10%</v>
@@ -5832,22 +5832,22 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Kanto Extra Challenge 3</v>
+        <v>Kanto Extra Challenge 2</v>
       </c>
       <c r="B237" t="str">
-        <v>Casino Eeveelution</v>
+        <v>Casino Special Spot</v>
       </c>
       <c r="C237" t="str">
         <v/>
       </c>
       <c r="D237" t="str">
-        <v>Glaceon</v>
+        <v>Lickitung</v>
       </c>
       <c r="E237" t="str">
-        <v>86-91</v>
+        <v>84-89</v>
       </c>
       <c r="F237" t="str">
-        <v>10%</v>
+        <v>30%</v>
       </c>
       <c r="G237">
         <v>0</v>
@@ -5855,22 +5855,22 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Kanto Extra Challenge 3</v>
+        <v>Kanto Extra Challenge 2</v>
       </c>
       <c r="B238" t="str">
-        <v>Casino Eeveelution</v>
+        <v>Casino Special Spot</v>
       </c>
       <c r="C238" t="str">
         <v/>
       </c>
       <c r="D238" t="str">
-        <v>Sylveon</v>
+        <v>Porygon</v>
       </c>
       <c r="E238" t="str">
-        <v>86-91</v>
+        <v>84-89</v>
       </c>
       <c r="F238" t="str">
-        <v>10%</v>
+        <v>30%</v>
       </c>
       <c r="G238">
         <v>0</v>
@@ -5878,48 +5878,48 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Kanto Extra Challenge 3</v>
+        <v>Kanto Extra Challenge 2</v>
       </c>
       <c r="B239" t="str">
-        <v>Dojo</v>
+        <v>Casino Special Spot</v>
       </c>
       <c r="C239" t="str">
         <v/>
       </c>
       <c r="D239" t="str">
-        <v>Tyrogue</v>
+        <v>Lapras</v>
       </c>
       <c r="E239" t="str">
-        <v>88-92</v>
+        <v>84-89</v>
       </c>
       <c r="F239" t="str">
-        <v>40%</v>
+        <v>30%</v>
       </c>
       <c r="G239">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Kanto Extra Challenge 3</v>
+        <v>Kanto Extra Challenge 2</v>
       </c>
       <c r="B240" t="str">
-        <v>Dojo</v>
+        <v>Casino Special Spot</v>
       </c>
       <c r="C240" t="str">
         <v/>
       </c>
       <c r="D240" t="str">
-        <v>Hitmonlee</v>
+        <v>Porygon2</v>
       </c>
       <c r="E240" t="str">
-        <v>89-93</v>
+        <v>85-90</v>
       </c>
       <c r="F240" t="str">
-        <v>20%</v>
+        <v>10%</v>
       </c>
       <c r="G240">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -5927,22 +5927,22 @@
         <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B241" t="str">
-        <v>Dojo</v>
+        <v>Casino Eeveelution</v>
       </c>
       <c r="C241" t="str">
         <v/>
       </c>
       <c r="D241" t="str">
-        <v>Hitmonchan</v>
+        <v>Eevee</v>
       </c>
       <c r="E241" t="str">
-        <v>89-93</v>
+        <v>85-90</v>
       </c>
       <c r="F241" t="str">
         <v>20%</v>
       </c>
       <c r="G241">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -5950,42 +5950,42 @@
         <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B242" t="str">
-        <v>Dojo</v>
+        <v>Casino Eeveelution</v>
       </c>
       <c r="C242" t="str">
         <v/>
       </c>
       <c r="D242" t="str">
-        <v>Hitmontop</v>
+        <v>Vaporeon</v>
       </c>
       <c r="E242" t="str">
-        <v>89-93</v>
+        <v>86-91</v>
       </c>
       <c r="F242" t="str">
-        <v>20%</v>
+        <v>10%</v>
       </c>
       <c r="G242">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Kanto Extra Challenge 4</v>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B243" t="str">
-        <v>Casino Late Trupe</v>
+        <v>Casino Eeveelution</v>
       </c>
       <c r="C243" t="str">
         <v/>
       </c>
       <c r="D243" t="str">
-        <v>Venusaur</v>
+        <v>Jolteon</v>
       </c>
       <c r="E243" t="str">
-        <v>90-98</v>
+        <v>86-91</v>
       </c>
       <c r="F243" t="str">
-        <v>17%</v>
+        <v>10%</v>
       </c>
       <c r="G243">
         <v>0</v>
@@ -5993,22 +5993,22 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Kanto Extra Challenge 4</v>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B244" t="str">
-        <v>Casino Late Trupe</v>
+        <v>Casino Eeveelution</v>
       </c>
       <c r="C244" t="str">
         <v/>
       </c>
       <c r="D244" t="str">
-        <v>Charizard</v>
+        <v>Flareon</v>
       </c>
       <c r="E244" t="str">
-        <v>90-98</v>
+        <v>86-91</v>
       </c>
       <c r="F244" t="str">
-        <v>17%</v>
+        <v>10%</v>
       </c>
       <c r="G244">
         <v>0</v>
@@ -6016,22 +6016,22 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Kanto Extra Challenge 4</v>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B245" t="str">
-        <v>Casino Late Trupe</v>
+        <v>Casino Eeveelution</v>
       </c>
       <c r="C245" t="str">
         <v/>
       </c>
       <c r="D245" t="str">
-        <v>Blastoise</v>
+        <v>Espeon</v>
       </c>
       <c r="E245" t="str">
-        <v>90-98</v>
+        <v>86-91</v>
       </c>
       <c r="F245" t="str">
-        <v>17%</v>
+        <v>10%</v>
       </c>
       <c r="G245">
         <v>0</v>
@@ -6039,22 +6039,22 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Kanto Extra Challenge 4</v>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B246" t="str">
-        <v>Casino Late Trupe</v>
+        <v>Casino Eeveelution</v>
       </c>
       <c r="C246" t="str">
         <v/>
       </c>
       <c r="D246" t="str">
-        <v>Meganium</v>
+        <v>Umbreon</v>
       </c>
       <c r="E246" t="str">
-        <v>90-98</v>
+        <v>86-91</v>
       </c>
       <c r="F246" t="str">
-        <v>17%</v>
+        <v>10%</v>
       </c>
       <c r="G246">
         <v>0</v>
@@ -6062,22 +6062,22 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Kanto Extra Challenge 4</v>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B247" t="str">
-        <v>Casino Late Trupe</v>
+        <v>Casino Eeveelution</v>
       </c>
       <c r="C247" t="str">
         <v/>
       </c>
       <c r="D247" t="str">
-        <v>Typhlosion</v>
+        <v>Leafeon</v>
       </c>
       <c r="E247" t="str">
-        <v>90-98</v>
+        <v>86-91</v>
       </c>
       <c r="F247" t="str">
-        <v>17%</v>
+        <v>10%</v>
       </c>
       <c r="G247">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Kanto Extra Challenge 4</v>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B248" t="str">
-        <v>Casino Late Trupe</v>
+        <v>Casino Eeveelution</v>
       </c>
       <c r="C248" t="str">
         <v/>
       </c>
       <c r="D248" t="str">
-        <v>Feraligatr</v>
+        <v>Glaceon</v>
       </c>
       <c r="E248" t="str">
-        <v>90-98</v>
+        <v>86-91</v>
       </c>
       <c r="F248" t="str">
-        <v>17%</v>
+        <v>10%</v>
       </c>
       <c r="G248">
         <v>0</v>
@@ -6108,45 +6108,45 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Kanto Extra Challenge 5</v>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B249" t="str">
-        <v>Legendaries Nest</v>
+        <v>Casino Eeveelution</v>
       </c>
       <c r="C249" t="str">
         <v/>
       </c>
       <c r="D249" t="str">
-        <v>Articuno</v>
+        <v>Sylveon</v>
       </c>
       <c r="E249" t="str">
-        <v>100-100</v>
+        <v>86-91</v>
       </c>
       <c r="F249" t="str">
-        <v>20%</v>
+        <v>10%</v>
       </c>
       <c r="G249">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Kanto Extra Challenge 5</v>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B250" t="str">
-        <v>Legendaries Nest</v>
+        <v>Dojo</v>
       </c>
       <c r="C250" t="str">
         <v/>
       </c>
       <c r="D250" t="str">
-        <v>Zapdos</v>
+        <v>Tyrogue</v>
       </c>
       <c r="E250" t="str">
-        <v>100-100</v>
+        <v>88-92</v>
       </c>
       <c r="F250" t="str">
-        <v>20%</v>
+        <v>40%</v>
       </c>
       <c r="G250">
         <v>1</v>
@@ -6154,19 +6154,19 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Kanto Extra Challenge 5</v>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B251" t="str">
-        <v>Legendaries Nest</v>
+        <v>Dojo</v>
       </c>
       <c r="C251" t="str">
         <v/>
       </c>
       <c r="D251" t="str">
-        <v>Moltres</v>
+        <v>Hitmonlee</v>
       </c>
       <c r="E251" t="str">
-        <v>100-100</v>
+        <v>89-93</v>
       </c>
       <c r="F251" t="str">
         <v>20%</v>
@@ -6177,19 +6177,19 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Kanto Extra Challenge 5</v>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B252" t="str">
-        <v>Legendaries Nest</v>
+        <v>Dojo</v>
       </c>
       <c r="C252" t="str">
         <v/>
       </c>
       <c r="D252" t="str">
-        <v>Ho-oh</v>
+        <v>Hitmonchan</v>
       </c>
       <c r="E252" t="str">
-        <v>110-110</v>
+        <v>89-93</v>
       </c>
       <c r="F252" t="str">
         <v>20%</v>
@@ -6200,19 +6200,19 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Kanto Extra Challenge 5</v>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B253" t="str">
-        <v>Legendaries Nest</v>
+        <v>Dojo</v>
       </c>
       <c r="C253" t="str">
         <v/>
       </c>
       <c r="D253" t="str">
-        <v>Lugia</v>
+        <v>Hitmontop</v>
       </c>
       <c r="E253" t="str">
-        <v>110-110</v>
+        <v>89-93</v>
       </c>
       <c r="F253" t="str">
         <v>20%</v>
@@ -6223,160 +6223,160 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Keys to Temporal Sanctuary Challenge</v>
+        <v>Kanto Extra Challenge 4</v>
       </c>
       <c r="B254" t="str">
-        <v>Temporal Sanctuary Spot</v>
+        <v>Casino Late Trupe</v>
       </c>
       <c r="C254" t="str">
         <v/>
       </c>
       <c r="D254" t="str">
-        <v>Raikou</v>
+        <v>Venusaur</v>
       </c>
       <c r="E254" t="str">
-        <v>110-110</v>
+        <v>90-98</v>
       </c>
       <c r="F254" t="str">
-        <v>20%</v>
+        <v>17%</v>
       </c>
       <c r="G254">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Keys to Temporal Sanctuary Challenge</v>
+        <v>Kanto Extra Challenge 4</v>
       </c>
       <c r="B255" t="str">
-        <v>Temporal Sanctuary Spot</v>
+        <v>Casino Late Trupe</v>
       </c>
       <c r="C255" t="str">
         <v/>
       </c>
       <c r="D255" t="str">
-        <v>Entei</v>
+        <v>Charizard</v>
       </c>
       <c r="E255" t="str">
-        <v>110-110</v>
+        <v>90-98</v>
       </c>
       <c r="F255" t="str">
-        <v>20%</v>
+        <v>17%</v>
       </c>
       <c r="G255">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Keys to Temporal Sanctuary Challenge</v>
+        <v>Kanto Extra Challenge 4</v>
       </c>
       <c r="B256" t="str">
-        <v>Temporal Sanctuary Spot</v>
+        <v>Casino Late Trupe</v>
       </c>
       <c r="C256" t="str">
         <v/>
       </c>
       <c r="D256" t="str">
-        <v>Suicune</v>
+        <v>Blastoise</v>
       </c>
       <c r="E256" t="str">
-        <v>110-110</v>
+        <v>90-98</v>
       </c>
       <c r="F256" t="str">
-        <v>20%</v>
+        <v>17%</v>
       </c>
       <c r="G256">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Keys to Temporal Sanctuary Challenge</v>
+        <v>Kanto Extra Challenge 4</v>
       </c>
       <c r="B257" t="str">
-        <v>Temporal Sanctuary Spot</v>
+        <v>Casino Late Trupe</v>
       </c>
       <c r="C257" t="str">
         <v/>
       </c>
       <c r="D257" t="str">
-        <v>Mew</v>
+        <v>Meganium</v>
       </c>
       <c r="E257" t="str">
-        <v>120-120</v>
+        <v>90-98</v>
       </c>
       <c r="F257" t="str">
-        <v>13.33%</v>
+        <v>17%</v>
       </c>
       <c r="G257">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Keys to Temporal Sanctuary Challenge</v>
+        <v>Kanto Extra Challenge 4</v>
       </c>
       <c r="B258" t="str">
-        <v>Temporal Sanctuary Spot</v>
+        <v>Casino Late Trupe</v>
       </c>
       <c r="C258" t="str">
         <v/>
       </c>
       <c r="D258" t="str">
-        <v>Mewtwo</v>
+        <v>Typhlosion</v>
       </c>
       <c r="E258" t="str">
-        <v>120-120</v>
+        <v>90-98</v>
       </c>
       <c r="F258" t="str">
-        <v>13.33%</v>
+        <v>17%</v>
       </c>
       <c r="G258">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Keys to Temporal Sanctuary Challenge</v>
+        <v>Kanto Extra Challenge 4</v>
       </c>
       <c r="B259" t="str">
-        <v>Temporal Sanctuary Spot</v>
+        <v>Casino Late Trupe</v>
       </c>
       <c r="C259" t="str">
         <v/>
       </c>
       <c r="D259" t="str">
-        <v>Celebi</v>
+        <v>Feraligatr</v>
       </c>
       <c r="E259" t="str">
-        <v>120-120</v>
+        <v>90-98</v>
       </c>
       <c r="F259" t="str">
-        <v>13.33%</v>
+        <v>17%</v>
       </c>
       <c r="G259">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Challenge 47</v>
+        <v>Kanto Extra Challenge 5</v>
       </c>
       <c r="B260" t="str">
-        <v>Trade With Friends Hub</v>
+        <v>Legendaries Nest</v>
       </c>
       <c r="C260" t="str">
         <v/>
       </c>
       <c r="D260" t="str">
-        <v>Alakazam</v>
+        <v>Articuno</v>
       </c>
       <c r="E260" t="str">
-        <v>91-95</v>
+        <v>100-100</v>
       </c>
       <c r="F260" t="str">
-        <v>25%</v>
+        <v>20%</v>
       </c>
       <c r="G260">
         <v>1</v>
@@ -6384,22 +6384,22 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Challenge 47</v>
+        <v>Kanto Extra Challenge 5</v>
       </c>
       <c r="B261" t="str">
-        <v>Trade With Friends Hub</v>
+        <v>Legendaries Nest</v>
       </c>
       <c r="C261" t="str">
         <v/>
       </c>
       <c r="D261" t="str">
-        <v>Machamp</v>
+        <v>Zapdos</v>
       </c>
       <c r="E261" t="str">
-        <v>91-95</v>
+        <v>100-100</v>
       </c>
       <c r="F261" t="str">
-        <v>25%</v>
+        <v>20%</v>
       </c>
       <c r="G261">
         <v>1</v>
@@ -6407,22 +6407,22 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Challenge 47</v>
+        <v>Kanto Extra Challenge 5</v>
       </c>
       <c r="B262" t="str">
-        <v>Trade With Friends Hub</v>
+        <v>Legendaries Nest</v>
       </c>
       <c r="C262" t="str">
         <v/>
       </c>
       <c r="D262" t="str">
-        <v>Golem</v>
+        <v>Moltres</v>
       </c>
       <c r="E262" t="str">
-        <v>91-95</v>
+        <v>100-100</v>
       </c>
       <c r="F262" t="str">
-        <v>25%</v>
+        <v>20%</v>
       </c>
       <c r="G262">
         <v>1</v>
@@ -6430,30 +6430,283 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
+        <v>Kanto Extra Challenge 5</v>
+      </c>
+      <c r="B263" t="str">
+        <v>Legendaries Nest</v>
+      </c>
+      <c r="C263" t="str">
+        <v/>
+      </c>
+      <c r="D263" t="str">
+        <v>Ho-oh</v>
+      </c>
+      <c r="E263" t="str">
+        <v>110-110</v>
+      </c>
+      <c r="F263" t="str">
+        <v>20%</v>
+      </c>
+      <c r="G263">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>Kanto Extra Challenge 5</v>
+      </c>
+      <c r="B264" t="str">
+        <v>Legendaries Nest</v>
+      </c>
+      <c r="C264" t="str">
+        <v/>
+      </c>
+      <c r="D264" t="str">
+        <v>Lugia</v>
+      </c>
+      <c r="E264" t="str">
+        <v>110-110</v>
+      </c>
+      <c r="F264" t="str">
+        <v>20%</v>
+      </c>
+      <c r="G264">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>Keys to Temporal Sanctuary Challenge</v>
+      </c>
+      <c r="B265" t="str">
+        <v>Temporal Sanctuary Spot</v>
+      </c>
+      <c r="C265" t="str">
+        <v/>
+      </c>
+      <c r="D265" t="str">
+        <v>Raikou</v>
+      </c>
+      <c r="E265" t="str">
+        <v>110-110</v>
+      </c>
+      <c r="F265" t="str">
+        <v>20%</v>
+      </c>
+      <c r="G265">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>Keys to Temporal Sanctuary Challenge</v>
+      </c>
+      <c r="B266" t="str">
+        <v>Temporal Sanctuary Spot</v>
+      </c>
+      <c r="C266" t="str">
+        <v/>
+      </c>
+      <c r="D266" t="str">
+        <v>Entei</v>
+      </c>
+      <c r="E266" t="str">
+        <v>110-110</v>
+      </c>
+      <c r="F266" t="str">
+        <v>20%</v>
+      </c>
+      <c r="G266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>Keys to Temporal Sanctuary Challenge</v>
+      </c>
+      <c r="B267" t="str">
+        <v>Temporal Sanctuary Spot</v>
+      </c>
+      <c r="C267" t="str">
+        <v/>
+      </c>
+      <c r="D267" t="str">
+        <v>Suicune</v>
+      </c>
+      <c r="E267" t="str">
+        <v>110-110</v>
+      </c>
+      <c r="F267" t="str">
+        <v>20%</v>
+      </c>
+      <c r="G267">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>Keys to Temporal Sanctuary Challenge</v>
+      </c>
+      <c r="B268" t="str">
+        <v>Temporal Sanctuary Spot</v>
+      </c>
+      <c r="C268" t="str">
+        <v/>
+      </c>
+      <c r="D268" t="str">
+        <v>Mew</v>
+      </c>
+      <c r="E268" t="str">
+        <v>120-120</v>
+      </c>
+      <c r="F268" t="str">
+        <v>13.33%</v>
+      </c>
+      <c r="G268">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>Keys to Temporal Sanctuary Challenge</v>
+      </c>
+      <c r="B269" t="str">
+        <v>Temporal Sanctuary Spot</v>
+      </c>
+      <c r="C269" t="str">
+        <v/>
+      </c>
+      <c r="D269" t="str">
+        <v>Mewtwo</v>
+      </c>
+      <c r="E269" t="str">
+        <v>120-120</v>
+      </c>
+      <c r="F269" t="str">
+        <v>13.33%</v>
+      </c>
+      <c r="G269">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>Keys to Temporal Sanctuary Challenge</v>
+      </c>
+      <c r="B270" t="str">
+        <v>Temporal Sanctuary Spot</v>
+      </c>
+      <c r="C270" t="str">
+        <v/>
+      </c>
+      <c r="D270" t="str">
+        <v>Celebi</v>
+      </c>
+      <c r="E270" t="str">
+        <v>120-120</v>
+      </c>
+      <c r="F270" t="str">
+        <v>13.33%</v>
+      </c>
+      <c r="G270">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
         <v>Challenge 47</v>
       </c>
-      <c r="B263" t="str">
+      <c r="B271" t="str">
         <v>Trade With Friends Hub</v>
       </c>
-      <c r="C263" t="str">
-        <v/>
-      </c>
-      <c r="D263" t="str">
+      <c r="C271" t="str">
+        <v/>
+      </c>
+      <c r="D271" t="str">
+        <v>Alakazam</v>
+      </c>
+      <c r="E271" t="str">
+        <v>91-95</v>
+      </c>
+      <c r="F271" t="str">
+        <v>25%</v>
+      </c>
+      <c r="G271">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>Challenge 47</v>
+      </c>
+      <c r="B272" t="str">
+        <v>Trade With Friends Hub</v>
+      </c>
+      <c r="C272" t="str">
+        <v/>
+      </c>
+      <c r="D272" t="str">
+        <v>Machamp</v>
+      </c>
+      <c r="E272" t="str">
+        <v>91-95</v>
+      </c>
+      <c r="F272" t="str">
+        <v>25%</v>
+      </c>
+      <c r="G272">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>Challenge 47</v>
+      </c>
+      <c r="B273" t="str">
+        <v>Trade With Friends Hub</v>
+      </c>
+      <c r="C273" t="str">
+        <v/>
+      </c>
+      <c r="D273" t="str">
+        <v>Golem</v>
+      </c>
+      <c r="E273" t="str">
+        <v>91-95</v>
+      </c>
+      <c r="F273" t="str">
+        <v>25%</v>
+      </c>
+      <c r="G273">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>Challenge 47</v>
+      </c>
+      <c r="B274" t="str">
+        <v>Trade With Friends Hub</v>
+      </c>
+      <c r="C274" t="str">
+        <v/>
+      </c>
+      <c r="D274" t="str">
         <v>Gengar</v>
       </c>
-      <c r="E263" t="str">
+      <c r="E274" t="str">
         <v>91-95</v>
       </c>
-      <c r="F263" t="str">
+      <c r="F274" t="str">
         <v>25%</v>
       </c>
-      <c r="G263">
+      <c r="G274">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G263"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G274"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -6910,7 +7163,7 @@
         <v>Earn Badge</v>
       </c>
       <c r="C41" t="str">
-        <v>Route 8</v>
+        <v>Route 8, Diglett Cave</v>
       </c>
     </row>
     <row r="42">
@@ -7175,7 +7428,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7219,7 +7472,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Pikachu</v>
+        <v>Raichu</v>
       </c>
       <c r="B6" t="str">
         <v>Evolve</v>
@@ -7227,15 +7480,15 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Raichu</v>
+        <v>Clefable</v>
       </c>
       <c r="B7" t="str">
-        <v>2xEvolution</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Clefairy</v>
+        <v>Wigglytuff</v>
       </c>
       <c r="B8" t="str">
         <v>Evolve</v>
@@ -7243,15 +7496,15 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Clefable</v>
+        <v>Togetic</v>
       </c>
       <c r="B9" t="str">
-        <v>2xEvolution</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Wigglytuff</v>
+        <v>Sandslash</v>
       </c>
       <c r="B10" t="str">
         <v>Evolve</v>
@@ -7259,7 +7512,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Togetic</v>
+        <v>Ampharos</v>
       </c>
       <c r="B11" t="str">
         <v>Evolve</v>
@@ -7267,7 +7520,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Sandslash</v>
+        <v>Haunter</v>
       </c>
       <c r="B12" t="str">
         <v>Evolve</v>
@@ -7275,7 +7528,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Ampharos</v>
+        <v>Victreebel</v>
       </c>
       <c r="B13" t="str">
         <v>Evolve</v>
@@ -7283,7 +7536,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Haunter</v>
+        <v>Jumpluff</v>
       </c>
       <c r="B14" t="str">
         <v>Evolve</v>
@@ -7291,7 +7544,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Weepinbell</v>
+        <v>Poliwrath</v>
       </c>
       <c r="B15" t="str">
         <v>Evolve</v>
@@ -7299,15 +7552,15 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Victreebel</v>
+        <v>Politoed</v>
       </c>
       <c r="B16" t="str">
-        <v>2xEvolution</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Skiploom</v>
+        <v>Slowbro</v>
       </c>
       <c r="B17" t="str">
         <v>Evolve</v>
@@ -7315,15 +7568,15 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Jumpluff</v>
+        <v>Forretress</v>
       </c>
       <c r="B18" t="str">
-        <v>2xEvolution</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Poliwrath</v>
+        <v>Sunflora</v>
       </c>
       <c r="B19" t="str">
         <v>Evolve</v>
@@ -7331,7 +7584,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Politoed</v>
+        <v>Venomoth</v>
       </c>
       <c r="B20" t="str">
         <v>Evolve</v>
@@ -7339,7 +7592,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Slowbro</v>
+        <v>Muk</v>
       </c>
       <c r="B21" t="str">
         <v>Evolve</v>
@@ -7347,7 +7600,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Forretress</v>
+        <v>Magneton</v>
       </c>
       <c r="B22" t="str">
         <v>Evolve</v>
@@ -7355,7 +7608,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Sunflora</v>
+        <v>Granbull</v>
       </c>
       <c r="B23" t="str">
         <v>Evolve</v>
@@ -7363,31 +7616,31 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Venonat</v>
+        <v>Ninetales</v>
       </c>
       <c r="B24" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Venomoth</v>
+        <v>Arcanine</v>
       </c>
       <c r="B25" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Heracross</v>
+        <v>Azumarill</v>
       </c>
       <c r="B26" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Muk</v>
+        <v>Primeape</v>
       </c>
       <c r="B27" t="str">
         <v>Evolve</v>
@@ -7395,7 +7648,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Magneton</v>
+        <v>Persian</v>
       </c>
       <c r="B28" t="str">
         <v>Evolve</v>
@@ -7403,15 +7656,15 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Aipom</v>
+        <v>Electabuzz</v>
       </c>
       <c r="B29" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Granbull</v>
+        <v>Xatu</v>
       </c>
       <c r="B30" t="str">
         <v>Evolve</v>
@@ -7419,7 +7672,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Ninetales</v>
+        <v>Cloyster</v>
       </c>
       <c r="B31" t="str">
         <v>Evolve</v>
@@ -7427,7 +7680,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Arcanine</v>
+        <v>Octillery</v>
       </c>
       <c r="B32" t="str">
         <v>Evolve</v>
@@ -7435,7 +7688,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Azumarill</v>
+        <v>Piloswine</v>
       </c>
       <c r="B33" t="str">
         <v>Evolve</v>
@@ -7443,23 +7696,23 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Diglett</v>
+        <v>Rapidash</v>
       </c>
       <c r="B34" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Dugtrio</v>
+        <v>Marowak</v>
       </c>
       <c r="B35" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Primeape</v>
+        <v>Ivysaur</v>
       </c>
       <c r="B36" t="str">
         <v>Evolve</v>
@@ -7467,7 +7720,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Persian</v>
+        <v>Charmeleon</v>
       </c>
       <c r="B37" t="str">
         <v>Evolve</v>
@@ -7475,15 +7728,15 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Girafarig</v>
+        <v>Wartortle</v>
       </c>
       <c r="B38" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Electabuzz</v>
+        <v>Dragonite</v>
       </c>
       <c r="B39" t="str">
         <v>Evolve</v>
@@ -7491,7 +7744,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Xatu</v>
+        <v>Pupitar</v>
       </c>
       <c r="B40" t="str">
         <v>Evolve</v>
@@ -7499,110 +7752,22 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Cloyster</v>
+        <v>Tyranitar</v>
       </c>
       <c r="B41" t="str">
-        <v>Evolve</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>Octillery</v>
-      </c>
-      <c r="B42" t="str">
-        <v>Evolve</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>Tangela</v>
-      </c>
-      <c r="B43" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>Piloswine</v>
-      </c>
-      <c r="B44" t="str">
-        <v>Evolve</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>Rapidash</v>
-      </c>
-      <c r="B45" t="str">
-        <v>Evolve</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>Marowak</v>
-      </c>
-      <c r="B46" t="str">
-        <v>Evolve</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>Ivysaur</v>
-      </c>
-      <c r="B47" t="str">
-        <v>Evolve</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>Charmeleon</v>
-      </c>
-      <c r="B48" t="str">
-        <v>Evolve</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>Wartortle</v>
-      </c>
-      <c r="B49" t="str">
-        <v>Evolve</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>Dragonite</v>
-      </c>
-      <c r="B50" t="str">
-        <v>Evolve</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>Pupitar</v>
-      </c>
-      <c r="B51" t="str">
-        <v>Evolve</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>Tyranitar</v>
-      </c>
-      <c r="B52" t="str">
         <v>2xEvolution</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B41"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C54"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8013,21 +8178,21 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Challenge 43</v>
+        <v>Challenge 40</v>
       </c>
       <c r="B38" t="str">
-        <v>Route 12</v>
+        <v>Diglett Cave</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Challenge 44</v>
+        <v>Challenge 43</v>
       </c>
       <c r="B39" t="str">
-        <v>Kanto Safari Zone</v>
+        <v>Route 12</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -8035,10 +8200,10 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Challenge 23</v>
+        <v>Challenge 44</v>
       </c>
       <c r="B40" t="str">
-        <v>Safari Zone</v>
+        <v>Kanto Safari Zone</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -8046,10 +8211,10 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Challenge 45</v>
+        <v>Challenge 23</v>
       </c>
       <c r="B41" t="str">
-        <v>Cycling Road</v>
+        <v>Safari Zone</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -8060,7 +8225,7 @@
         <v>Challenge 45</v>
       </c>
       <c r="B42" t="str">
-        <v>Sea Routes</v>
+        <v>Cycling Road</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -8068,10 +8233,10 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Challenge 36</v>
+        <v>Challenge 45</v>
       </c>
       <c r="B43" t="str">
-        <v>Fossil Revival Lab</v>
+        <v>Sea Routes</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -8079,10 +8244,10 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="B44" t="str">
-        <v>Pokémon Mansion</v>
+        <v>Fossil Revival Lab</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -8090,21 +8255,21 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Challenge 41</v>
+        <v/>
       </c>
       <c r="B45" t="str">
-        <v>Casino Starter Trupe</v>
+        <v>Pokémon Mansion</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Kanto Extra Challenge 1</v>
+        <v>Challenge 41</v>
       </c>
       <c r="B46" t="str">
-        <v>Casino Babies</v>
+        <v>Casino Starter Trupe</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -8112,10 +8277,10 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Kanto Extra Challenge 2</v>
+        <v>Kanto Extra Challenge 1</v>
       </c>
       <c r="B47" t="str">
-        <v>Casino Special Spot</v>
+        <v>Casino Babies</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -8123,10 +8288,10 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Kanto Extra Challenge 3</v>
+        <v>Kanto Extra Challenge 2</v>
       </c>
       <c r="B48" t="str">
-        <v>Casino Eeveelution</v>
+        <v>Casino Special Spot</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -8137,40 +8302,40 @@
         <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B49" t="str">
-        <v>Dojo</v>
+        <v>Casino Eeveelution</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Kanto Extra Challenge 4</v>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B50" t="str">
-        <v>Casino Late Trupe</v>
+        <v>Dojo</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Kanto Extra Challenge 5</v>
+        <v>Kanto Extra Challenge 4</v>
       </c>
       <c r="B51" t="str">
-        <v>Legendaries Nest</v>
+        <v>Casino Late Trupe</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Keys to Temporal Sanctuary Challenge</v>
+        <v>Kanto Extra Challenge 5</v>
       </c>
       <c r="B52" t="str">
-        <v>Temporal Sanctuary Spot</v>
+        <v>Legendaries Nest</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -8178,18 +8343,29 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
+        <v>Keys to Temporal Sanctuary Challenge</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Temporal Sanctuary Spot</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
         <v>Challenge 47</v>
       </c>
-      <c r="B53" t="str">
+      <c r="B54" t="str">
         <v>Trade With Friends Hub</v>
       </c>
-      <c r="C53">
+      <c r="C54">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C53"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C54"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/2_Johto_Data.xlsx
+++ b/2_Johto_Data.xlsx
@@ -4539,7 +4539,7 @@
         <v>90%</v>
       </c>
       <c r="G180">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
@@ -4562,7 +4562,7 @@
         <v>10%</v>
       </c>
       <c r="G181">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -8184,7 +8184,7 @@
         <v>Diglett Cave</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">

--- a/2_Johto_Data.xlsx
+++ b/2_Johto_Data.xlsx
@@ -493,11 +493,14 @@
       <c r="C3" t="str">
         <v/>
       </c>
+      <c r="D3" t="str">
+        <v>Pidgey</v>
+      </c>
       <c r="E3" t="str">
-        <v>undefined-undefined</v>
+        <v>2-5</v>
       </c>
       <c r="F3" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -531,11 +534,14 @@
       <c r="C4" t="str">
         <v/>
       </c>
+      <c r="D4" t="str">
+        <v>Sentret</v>
+      </c>
       <c r="E4" t="str">
-        <v>undefined-undefined</v>
+        <v>2-5</v>
       </c>
       <c r="F4" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -569,11 +575,14 @@
       <c r="C5" t="str">
         <v/>
       </c>
+      <c r="D5" t="str">
+        <v>Rattata</v>
+      </c>
       <c r="E5" t="str">
-        <v>undefined-undefined</v>
+        <v>2-4</v>
       </c>
       <c r="F5" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -607,11 +616,14 @@
       <c r="C6" t="str">
         <v/>
       </c>
+      <c r="D6" t="str">
+        <v>Hoothoot</v>
+      </c>
       <c r="E6" t="str">
-        <v>undefined-undefined</v>
+        <v>3-5</v>
       </c>
       <c r="F6" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -645,11 +657,14 @@
       <c r="C7" t="str">
         <v/>
       </c>
+      <c r="D7" t="str">
+        <v>Hoppip</v>
+      </c>
       <c r="E7" t="str">
-        <v>undefined-undefined</v>
+        <v>3-5</v>
       </c>
       <c r="F7" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -683,11 +698,14 @@
       <c r="C8" t="str">
         <v/>
       </c>
+      <c r="D8" t="str">
+        <v>Caterpie</v>
+      </c>
       <c r="E8" t="str">
-        <v>undefined-undefined</v>
+        <v>3-6</v>
       </c>
       <c r="F8" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -721,11 +739,14 @@
       <c r="C9" t="str">
         <v/>
       </c>
+      <c r="D9" t="str">
+        <v>Weedle</v>
+      </c>
       <c r="E9" t="str">
-        <v>undefined-undefined</v>
+        <v>3-6</v>
       </c>
       <c r="F9" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -759,11 +780,14 @@
       <c r="C10" t="str">
         <v/>
       </c>
+      <c r="D10" t="str">
+        <v>Ledyba</v>
+      </c>
       <c r="E10" t="str">
-        <v>undefined-undefined</v>
+        <v>4-7</v>
       </c>
       <c r="F10" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -797,11 +821,14 @@
       <c r="C11" t="str">
         <v/>
       </c>
+      <c r="D11" t="str">
+        <v>Spinarak</v>
+      </c>
       <c r="E11" t="str">
-        <v>undefined-undefined</v>
+        <v>4-7</v>
       </c>
       <c r="F11" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -835,11 +862,14 @@
       <c r="C12" t="str">
         <v/>
       </c>
+      <c r="D12" t="str">
+        <v>Paras</v>
+      </c>
       <c r="E12" t="str">
-        <v>undefined-undefined</v>
+        <v>3-6</v>
       </c>
       <c r="F12" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -873,11 +903,14 @@
       <c r="C13" t="str">
         <v/>
       </c>
+      <c r="D13" t="str">
+        <v>Bellsprout</v>
+      </c>
       <c r="E13" t="str">
-        <v>undefined-undefined</v>
+        <v>5-8</v>
       </c>
       <c r="F13" t="str">
-        <v>0.5%</v>
+        <v>50%</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -911,11 +944,14 @@
       <c r="C14" t="str">
         <v/>
       </c>
+      <c r="D14" t="str">
+        <v>Metapod</v>
+      </c>
       <c r="E14" t="str">
-        <v>undefined-undefined</v>
+        <v>5-8</v>
       </c>
       <c r="F14" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -949,11 +985,14 @@
       <c r="C15" t="str">
         <v/>
       </c>
+      <c r="D15" t="str">
+        <v>Kakuna</v>
+      </c>
       <c r="E15" t="str">
-        <v>undefined-undefined</v>
+        <v>5-8</v>
       </c>
       <c r="F15" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -987,11 +1026,14 @@
       <c r="C16" t="str">
         <v/>
       </c>
+      <c r="D16" t="str">
+        <v>Wooper</v>
+      </c>
       <c r="E16" t="str">
-        <v>undefined-undefined</v>
+        <v>7-11</v>
       </c>
       <c r="F16" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1025,11 +1067,14 @@
       <c r="C17" t="str">
         <v/>
       </c>
+      <c r="D17" t="str">
+        <v>Zubat</v>
+      </c>
       <c r="E17" t="str">
-        <v>undefined-undefined</v>
+        <v>7-11</v>
       </c>
       <c r="F17" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1063,11 +1108,14 @@
       <c r="C18" t="str">
         <v/>
       </c>
+      <c r="D18" t="str">
+        <v>Ekans</v>
+      </c>
       <c r="E18" t="str">
-        <v>undefined-undefined</v>
+        <v>7-11</v>
       </c>
       <c r="F18" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1101,11 +1149,14 @@
       <c r="C19" t="str">
         <v/>
       </c>
+      <c r="D19" t="str">
+        <v>Hoppip</v>
+      </c>
       <c r="E19" t="str">
-        <v>undefined-undefined</v>
+        <v>8-11</v>
       </c>
       <c r="F19" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1139,11 +1190,14 @@
       <c r="C20" t="str">
         <v/>
       </c>
+      <c r="D20" t="str">
+        <v>Magikarp</v>
+      </c>
       <c r="E20" t="str">
-        <v>undefined-undefined</v>
+        <v>8-12</v>
       </c>
       <c r="F20" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1177,11 +1231,14 @@
       <c r="C21" t="str">
         <v/>
       </c>
+      <c r="D21" t="str">
+        <v>Goldeen</v>
+      </c>
       <c r="E21" t="str">
-        <v>undefined-undefined</v>
+        <v>8-12</v>
       </c>
       <c r="F21" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1215,11 +1272,14 @@
       <c r="C22" t="str">
         <v/>
       </c>
+      <c r="D22" t="str">
+        <v>Poliwag</v>
+      </c>
       <c r="E22" t="str">
-        <v>undefined-undefined</v>
+        <v>8-12</v>
       </c>
       <c r="F22" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1253,11 +1313,14 @@
       <c r="C23" t="str">
         <v/>
       </c>
+      <c r="D23" t="str">
+        <v>Krabby</v>
+      </c>
       <c r="E23" t="str">
-        <v>undefined-undefined</v>
+        <v>8-12</v>
       </c>
       <c r="F23" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1291,11 +1354,14 @@
       <c r="C24" t="str">
         <v/>
       </c>
+      <c r="D24" t="str">
+        <v>Tentacool</v>
+      </c>
       <c r="E24" t="str">
-        <v>undefined-undefined</v>
+        <v>8-12</v>
       </c>
       <c r="F24" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1329,11 +1395,14 @@
       <c r="C25" t="str">
         <v/>
       </c>
+      <c r="D25" t="str">
+        <v>Staryu</v>
+      </c>
       <c r="E25" t="str">
-        <v>undefined-undefined</v>
+        <v>8-12</v>
       </c>
       <c r="F25" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1367,11 +1436,14 @@
       <c r="C26" t="str">
         <v/>
       </c>
+      <c r="D26" t="str">
+        <v>Shellder</v>
+      </c>
       <c r="E26" t="str">
-        <v>undefined-undefined</v>
+        <v>8-12</v>
       </c>
       <c r="F26" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1405,11 +1477,14 @@
       <c r="C27" t="str">
         <v/>
       </c>
+      <c r="D27" t="str">
+        <v>Unown</v>
+      </c>
       <c r="E27" t="str">
-        <v>undefined-undefined</v>
+        <v>6-10</v>
       </c>
       <c r="F27" t="str">
-        <v>0.7%</v>
+        <v>70%</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1443,11 +1518,14 @@
       <c r="C28" t="str">
         <v/>
       </c>
+      <c r="D28" t="str">
+        <v>Natu</v>
+      </c>
       <c r="E28" t="str">
-        <v>undefined-undefined</v>
+        <v>7-11</v>
       </c>
       <c r="F28" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1481,11 +1559,14 @@
       <c r="C29" t="str">
         <v/>
       </c>
+      <c r="D29" t="str">
+        <v>Smeargle</v>
+      </c>
       <c r="E29" t="str">
-        <v>undefined-undefined</v>
+        <v>7-11</v>
       </c>
       <c r="F29" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1519,11 +1600,14 @@
       <c r="C30" t="str">
         <v/>
       </c>
+      <c r="D30" t="str">
+        <v>Geodude</v>
+      </c>
       <c r="E30" t="str">
-        <v>undefined-undefined</v>
+        <v>9-13</v>
       </c>
       <c r="F30" t="str">
-        <v>0.17%</v>
+        <v>17%</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1557,11 +1641,14 @@
       <c r="C31" t="str">
         <v/>
       </c>
+      <c r="D31" t="str">
+        <v>Spearow</v>
+      </c>
       <c r="E31" t="str">
-        <v>undefined-undefined</v>
+        <v>9-13</v>
       </c>
       <c r="F31" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1595,11 +1682,14 @@
       <c r="C32" t="str">
         <v/>
       </c>
+      <c r="D32" t="str">
+        <v>Mareep</v>
+      </c>
       <c r="E32" t="str">
-        <v>undefined-undefined</v>
+        <v>9-13</v>
       </c>
       <c r="F32" t="str">
-        <v>0.16%</v>
+        <v>16%</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1633,11 +1723,14 @@
       <c r="C33" t="str">
         <v/>
       </c>
+      <c r="D33" t="str">
+        <v>Hoothoot</v>
+      </c>
       <c r="E33" t="str">
-        <v>undefined-undefined</v>
+        <v>9-13</v>
       </c>
       <c r="F33" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1671,11 +1764,14 @@
       <c r="C34" t="str">
         <v/>
       </c>
+      <c r="D34" t="str">
+        <v>Skiploom</v>
+      </c>
       <c r="E34" t="str">
-        <v>undefined-undefined</v>
+        <v>9-13</v>
       </c>
       <c r="F34" t="str">
-        <v>0.08%</v>
+        <v>8%</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1709,11 +1805,14 @@
       <c r="C35" t="str">
         <v/>
       </c>
+      <c r="D35" t="str">
+        <v>Aipom</v>
+      </c>
       <c r="E35" t="str">
-        <v>undefined-undefined</v>
+        <v>9-13</v>
       </c>
       <c r="F35" t="str">
-        <v>0.09%</v>
+        <v>9%</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1747,11 +1846,14 @@
       <c r="C36" t="str">
         <v/>
       </c>
+      <c r="D36" t="str">
+        <v>Paras</v>
+      </c>
       <c r="E36" t="str">
-        <v>undefined-undefined</v>
+        <v>13-17</v>
       </c>
       <c r="F36" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1785,11 +1887,14 @@
       <c r="C37" t="str">
         <v/>
       </c>
+      <c r="D37" t="str">
+        <v>Caterpie</v>
+      </c>
       <c r="E37" t="str">
-        <v>undefined-undefined</v>
+        <v>12-16</v>
       </c>
       <c r="F37" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1823,11 +1928,14 @@
       <c r="C38" t="str">
         <v/>
       </c>
+      <c r="D38" t="str">
+        <v>Weedle</v>
+      </c>
       <c r="E38" t="str">
-        <v>undefined-undefined</v>
+        <v>12-16</v>
       </c>
       <c r="F38" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1861,11 +1969,14 @@
       <c r="C39" t="str">
         <v/>
       </c>
+      <c r="D39" t="str">
+        <v>Metapod</v>
+      </c>
       <c r="E39" t="str">
-        <v>undefined-undefined</v>
+        <v>13-17</v>
       </c>
       <c r="F39" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1899,11 +2010,14 @@
       <c r="C40" t="str">
         <v/>
       </c>
+      <c r="D40" t="str">
+        <v>Kakuna</v>
+      </c>
       <c r="E40" t="str">
-        <v>undefined-undefined</v>
+        <v>13-17</v>
       </c>
       <c r="F40" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1937,11 +2051,14 @@
       <c r="C41" t="str">
         <v/>
       </c>
+      <c r="D41" t="str">
+        <v>Drowzee</v>
+      </c>
       <c r="E41" t="str">
-        <v>undefined-undefined</v>
+        <v>15-19</v>
       </c>
       <c r="F41" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1975,11 +2092,14 @@
       <c r="C42" t="str">
         <v/>
       </c>
+      <c r="D42" t="str">
+        <v>Snubbull</v>
+      </c>
       <c r="E42" t="str">
-        <v>undefined-undefined</v>
+        <v>15-19</v>
       </c>
       <c r="F42" t="str">
-        <v>0.35%</v>
+        <v>35%</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2013,11 +2133,14 @@
       <c r="C43" t="str">
         <v/>
       </c>
+      <c r="D43" t="str">
+        <v>Jigglypuff</v>
+      </c>
       <c r="E43" t="str">
-        <v>undefined-undefined</v>
+        <v>14-18</v>
       </c>
       <c r="F43" t="str">
-        <v>0.35%</v>
+        <v>35%</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2051,11 +2174,14 @@
       <c r="C44" t="str">
         <v/>
       </c>
+      <c r="D44" t="str">
+        <v>Ditto</v>
+      </c>
       <c r="E44" t="str">
-        <v>undefined-undefined</v>
+        <v>15-20</v>
       </c>
       <c r="F44" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2089,11 +2215,14 @@
       <c r="C45" t="str">
         <v/>
       </c>
+      <c r="D45" t="str">
+        <v>Yanma</v>
+      </c>
       <c r="E45" t="str">
-        <v>undefined-undefined</v>
+        <v>20-25</v>
       </c>
       <c r="F45" t="str">
-        <v>0.35%</v>
+        <v>35%</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2127,11 +2256,14 @@
       <c r="C46" t="str">
         <v/>
       </c>
+      <c r="D46" t="str">
+        <v>Growlithe</v>
+      </c>
       <c r="E46" t="str">
-        <v>undefined-undefined</v>
+        <v>20-25</v>
       </c>
       <c r="F46" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2165,11 +2297,14 @@
       <c r="C47" t="str">
         <v/>
       </c>
+      <c r="D47" t="str">
+        <v>Nidoran♀</v>
+      </c>
       <c r="E47" t="str">
-        <v>undefined-undefined</v>
+        <v>19-24</v>
       </c>
       <c r="F47" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2203,11 +2338,14 @@
       <c r="C48" t="str">
         <v/>
       </c>
+      <c r="D48" t="str">
+        <v>Nidoran♂</v>
+      </c>
       <c r="E48" t="str">
-        <v>undefined-undefined</v>
+        <v>19-24</v>
       </c>
       <c r="F48" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2241,11 +2379,14 @@
       <c r="C49" t="str">
         <v/>
       </c>
+      <c r="D49" t="str">
+        <v>Sunkern</v>
+      </c>
       <c r="E49" t="str">
-        <v>undefined-undefined</v>
+        <v>22-27</v>
       </c>
       <c r="F49" t="str">
-        <v>0.27%</v>
+        <v>27%</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2279,11 +2420,14 @@
       <c r="C50" t="str">
         <v/>
       </c>
+      <c r="D50" t="str">
+        <v>Caterpie</v>
+      </c>
       <c r="E50" t="str">
-        <v>undefined-undefined</v>
+        <v>20-25</v>
       </c>
       <c r="F50" t="str">
-        <v>0.18%</v>
+        <v>18%</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2317,11 +2461,14 @@
       <c r="C51" t="str">
         <v/>
       </c>
+      <c r="D51" t="str">
+        <v>Weedle</v>
+      </c>
       <c r="E51" t="str">
-        <v>undefined-undefined</v>
+        <v>20-25</v>
       </c>
       <c r="F51" t="str">
-        <v>0.18%</v>
+        <v>18%</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2355,11 +2502,14 @@
       <c r="C52" t="str">
         <v/>
       </c>
+      <c r="D52" t="str">
+        <v>Scyther</v>
+      </c>
       <c r="E52" t="str">
-        <v>undefined-undefined</v>
+        <v>24-28</v>
       </c>
       <c r="F52" t="str">
-        <v>0.14%</v>
+        <v>14%</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2368,7 +2518,7 @@
         <v>Yes</v>
       </c>
       <c r="I52" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J52" t="str">
         <v>NONONO</v>
@@ -2393,11 +2543,14 @@
       <c r="C53" t="str">
         <v/>
       </c>
+      <c r="D53" t="str">
+        <v>Pinsir</v>
+      </c>
       <c r="E53" t="str">
-        <v>undefined-undefined</v>
+        <v>24-28</v>
       </c>
       <c r="F53" t="str">
-        <v>0.14%</v>
+        <v>14%</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2406,7 +2559,7 @@
         <v>Yes</v>
       </c>
       <c r="I53" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J53" t="str">
         <v>NONONO</v>
@@ -2431,11 +2584,14 @@
       <c r="C54" t="str">
         <v/>
       </c>
+      <c r="D54" t="str">
+        <v>Venonat</v>
+      </c>
       <c r="E54" t="str">
-        <v>undefined-undefined</v>
+        <v>20-28</v>
       </c>
       <c r="F54" t="str">
-        <v>0.09%</v>
+        <v>9%</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2469,11 +2625,14 @@
       <c r="C55" t="str">
         <v/>
       </c>
+      <c r="D55" t="str">
+        <v>Stantler</v>
+      </c>
       <c r="E55" t="str">
-        <v>undefined-undefined</v>
+        <v>24-29</v>
       </c>
       <c r="F55" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2507,11 +2666,14 @@
       <c r="C56" t="str">
         <v/>
       </c>
+      <c r="D56" t="str">
+        <v>Vulpix</v>
+      </c>
       <c r="E56" t="str">
-        <v>undefined-undefined</v>
+        <v>24-29</v>
       </c>
       <c r="F56" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2545,11 +2707,14 @@
       <c r="C57" t="str">
         <v/>
       </c>
+      <c r="D57" t="str">
+        <v>Growlithe</v>
+      </c>
       <c r="E57" t="str">
-        <v>undefined-undefined</v>
+        <v>24-29</v>
       </c>
       <c r="F57" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2583,11 +2748,14 @@
       <c r="C58" t="str">
         <v/>
       </c>
+      <c r="D58" t="str">
+        <v>Gastly</v>
+      </c>
       <c r="E58" t="str">
-        <v>undefined-undefined</v>
+        <v>23-28</v>
       </c>
       <c r="F58" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2621,11 +2789,14 @@
       <c r="C59" t="str">
         <v/>
       </c>
+      <c r="D59" t="str">
+        <v>Sudowoodo</v>
+      </c>
       <c r="E59" t="str">
-        <v>undefined-undefined</v>
+        <v>26-30</v>
       </c>
       <c r="F59" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2659,11 +2830,14 @@
       <c r="C60" t="str">
         <v/>
       </c>
+      <c r="D60" t="str">
+        <v>Pidgeotto</v>
+      </c>
       <c r="E60" t="str">
-        <v>undefined-undefined</v>
+        <v>26-31</v>
       </c>
       <c r="F60" t="str">
-        <v>0.28%</v>
+        <v>28%</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2697,11 +2871,14 @@
       <c r="C61" t="str">
         <v/>
       </c>
+      <c r="D61" t="str">
+        <v>Noctowl</v>
+      </c>
       <c r="E61" t="str">
-        <v>undefined-undefined</v>
+        <v>26-31</v>
       </c>
       <c r="F61" t="str">
-        <v>0.29%</v>
+        <v>29%</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2735,11 +2912,14 @@
       <c r="C62" t="str">
         <v/>
       </c>
+      <c r="D62" t="str">
+        <v>Ledian</v>
+      </c>
       <c r="E62" t="str">
-        <v>undefined-undefined</v>
+        <v>27-32</v>
       </c>
       <c r="F62" t="str">
-        <v>0.19%</v>
+        <v>19%</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2773,11 +2953,14 @@
       <c r="C63" t="str">
         <v/>
       </c>
+      <c r="D63" t="str">
+        <v>Ariados</v>
+      </c>
       <c r="E63" t="str">
-        <v>undefined-undefined</v>
+        <v>27-32</v>
       </c>
       <c r="F63" t="str">
-        <v>0.19%</v>
+        <v>19%</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2811,11 +2994,14 @@
       <c r="C64" t="str">
         <v/>
       </c>
+      <c r="D64" t="str">
+        <v>Heracross</v>
+      </c>
       <c r="E64" t="str">
-        <v>undefined-undefined</v>
+        <v>26-32</v>
       </c>
       <c r="F64" t="str">
-        <v>0.05%</v>
+        <v>5%</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2824,7 +3010,7 @@
         <v>Yes</v>
       </c>
       <c r="I64" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J64" t="str">
         <v>NONONO</v>
@@ -2849,11 +3035,14 @@
       <c r="C65" t="str">
         <v/>
       </c>
+      <c r="D65" t="str">
+        <v>Koffing</v>
+      </c>
       <c r="E65" t="str">
-        <v>undefined-undefined</v>
+        <v>28-33</v>
       </c>
       <c r="F65" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2887,11 +3076,14 @@
       <c r="C66" t="str">
         <v/>
       </c>
+      <c r="D66" t="str">
+        <v>Zubat</v>
+      </c>
       <c r="E66" t="str">
-        <v>undefined-undefined</v>
+        <v>27-32</v>
       </c>
       <c r="F66" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2925,11 +3117,14 @@
       <c r="C67" t="str">
         <v/>
       </c>
+      <c r="D67" t="str">
+        <v>Krabby</v>
+      </c>
       <c r="E67" t="str">
-        <v>undefined-undefined</v>
+        <v>27-32</v>
       </c>
       <c r="F67" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2963,11 +3158,14 @@
       <c r="C68" t="str">
         <v/>
       </c>
+      <c r="D68" t="str">
+        <v>Shuckle</v>
+      </c>
       <c r="E68" t="str">
-        <v>undefined-undefined</v>
+        <v>28-33</v>
       </c>
       <c r="F68" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2976,7 +3174,7 @@
         <v>Yes</v>
       </c>
       <c r="I68" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J68" t="str">
         <v>NONONO</v>
@@ -3001,11 +3199,14 @@
       <c r="C69" t="str">
         <v/>
       </c>
+      <c r="D69" t="str">
+        <v>Weezing</v>
+      </c>
       <c r="E69" t="str">
-        <v>undefined-undefined</v>
+        <v>32-36</v>
       </c>
       <c r="F69" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3039,11 +3240,14 @@
       <c r="C70" t="str">
         <v/>
       </c>
+      <c r="D70" t="str">
+        <v>Magmar</v>
+      </c>
       <c r="E70" t="str">
-        <v>undefined-undefined</v>
+        <v>32-37</v>
       </c>
       <c r="F70" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3077,11 +3281,14 @@
       <c r="C71" t="str">
         <v/>
       </c>
+      <c r="D71" t="str">
+        <v>Raticate</v>
+      </c>
       <c r="E71" t="str">
-        <v>undefined-undefined</v>
+        <v>31-36</v>
       </c>
       <c r="F71" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3115,11 +3322,14 @@
       <c r="C72" t="str">
         <v/>
       </c>
+      <c r="D72" t="str">
+        <v>Pidgeotto</v>
+      </c>
       <c r="E72" t="str">
-        <v>undefined-undefined</v>
+        <v>31-36</v>
       </c>
       <c r="F72" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3153,11 +3363,14 @@
       <c r="C73" t="str">
         <v/>
       </c>
+      <c r="D73" t="str">
+        <v>Snubbull</v>
+      </c>
       <c r="E73" t="str">
-        <v>undefined-undefined</v>
+        <v>30-35</v>
       </c>
       <c r="F73" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3191,11 +3404,14 @@
       <c r="C74" t="str">
         <v/>
       </c>
+      <c r="D74" t="str">
+        <v>Exeggcute</v>
+      </c>
       <c r="E74" t="str">
-        <v>undefined-undefined</v>
+        <v>31-36</v>
       </c>
       <c r="F74" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3229,11 +3445,14 @@
       <c r="C75" t="str">
         <v/>
       </c>
+      <c r="D75" t="str">
+        <v>Tauros</v>
+      </c>
       <c r="E75" t="str">
-        <v>undefined-undefined</v>
+        <v>32-37</v>
       </c>
       <c r="F75" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3267,11 +3486,14 @@
       <c r="C76" t="str">
         <v/>
       </c>
+      <c r="D76" t="str">
+        <v>Meowth</v>
+      </c>
       <c r="E76" t="str">
-        <v>undefined-undefined</v>
+        <v>33-38</v>
       </c>
       <c r="F76" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3305,11 +3527,14 @@
       <c r="C77" t="str">
         <v/>
       </c>
+      <c r="D77" t="str">
+        <v>Magnemite</v>
+      </c>
       <c r="E77" t="str">
-        <v>undefined-undefined</v>
+        <v>34-39</v>
       </c>
       <c r="F77" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3343,11 +3568,14 @@
       <c r="C78" t="str">
         <v/>
       </c>
+      <c r="D78" t="str">
+        <v>Miltank</v>
+      </c>
       <c r="E78" t="str">
-        <v>undefined-undefined</v>
+        <v>34-39</v>
       </c>
       <c r="F78" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3381,11 +3609,14 @@
       <c r="C79" t="str">
         <v/>
       </c>
+      <c r="D79" t="str">
+        <v>Farfetch'd</v>
+      </c>
       <c r="E79" t="str">
-        <v>undefined-undefined</v>
+        <v>33-38</v>
       </c>
       <c r="F79" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3419,11 +3650,14 @@
       <c r="C80" t="str">
         <v/>
       </c>
+      <c r="D80" t="str">
+        <v>Butterfree</v>
+      </c>
       <c r="E80" t="str">
-        <v>undefined-undefined</v>
+        <v>35-40</v>
       </c>
       <c r="F80" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3457,11 +3691,14 @@
       <c r="C81" t="str">
         <v/>
       </c>
+      <c r="D81" t="str">
+        <v>Beedrill</v>
+      </c>
       <c r="E81" t="str">
-        <v>undefined-undefined</v>
+        <v>35-40</v>
       </c>
       <c r="F81" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3495,11 +3732,14 @@
       <c r="C82" t="str">
         <v/>
       </c>
+      <c r="D82" t="str">
+        <v>Psyduck</v>
+      </c>
       <c r="E82" t="str">
-        <v>undefined-undefined</v>
+        <v>36-41</v>
       </c>
       <c r="F82" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3533,11 +3773,14 @@
       <c r="C83" t="str">
         <v/>
       </c>
+      <c r="D83" t="str">
+        <v>Marill</v>
+      </c>
       <c r="E83" t="str">
-        <v>undefined-undefined</v>
+        <v>36-41</v>
       </c>
       <c r="F83" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3571,11 +3814,14 @@
       <c r="C84" t="str">
         <v/>
       </c>
+      <c r="D84" t="str">
+        <v>Chinchou</v>
+      </c>
       <c r="E84" t="str">
-        <v>undefined-undefined</v>
+        <v>36-41</v>
       </c>
       <c r="F84" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3609,11 +3855,14 @@
       <c r="C85" t="str">
         <v/>
       </c>
+      <c r="D85" t="str">
+        <v>Remoraid</v>
+      </c>
       <c r="E85" t="str">
-        <v>undefined-undefined</v>
+        <v>36-41</v>
       </c>
       <c r="F85" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3647,11 +3896,14 @@
       <c r="C86" t="str">
         <v/>
       </c>
+      <c r="D86" t="str">
+        <v>Corsola</v>
+      </c>
       <c r="E86" t="str">
-        <v>undefined-undefined</v>
+        <v>36-41</v>
       </c>
       <c r="F86" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3685,11 +3937,14 @@
       <c r="C87" t="str">
         <v/>
       </c>
+      <c r="D87" t="str">
+        <v>Qwilfish</v>
+      </c>
       <c r="E87" t="str">
-        <v>undefined-undefined</v>
+        <v>37-42</v>
       </c>
       <c r="F87" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3723,11 +3978,14 @@
       <c r="C88" t="str">
         <v/>
       </c>
+      <c r="D88" t="str">
+        <v>Dratini</v>
+      </c>
       <c r="E88" t="str">
-        <v>undefined-undefined</v>
+        <v>37-42</v>
       </c>
       <c r="F88" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3761,11 +4019,14 @@
       <c r="C89" t="str">
         <v/>
       </c>
+      <c r="D89" t="str">
+        <v>Mankey</v>
+      </c>
       <c r="E89" t="str">
-        <v>undefined-undefined</v>
+        <v>38-43</v>
       </c>
       <c r="F89" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3799,11 +4060,14 @@
       <c r="C90" t="str">
         <v/>
       </c>
+      <c r="D90" t="str">
+        <v>Fearow</v>
+      </c>
       <c r="E90" t="str">
-        <v>undefined-undefined</v>
+        <v>38-43</v>
       </c>
       <c r="F90" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3837,11 +4101,14 @@
       <c r="C91" t="str">
         <v/>
       </c>
+      <c r="D91" t="str">
+        <v>Mareep</v>
+      </c>
       <c r="E91" t="str">
-        <v>undefined-undefined</v>
+        <v>38-43</v>
       </c>
       <c r="F91" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3875,11 +4142,14 @@
       <c r="C92" t="str">
         <v/>
       </c>
+      <c r="D92" t="str">
+        <v>Flaaffy</v>
+      </c>
       <c r="E92" t="str">
-        <v>undefined-undefined</v>
+        <v>38-43</v>
       </c>
       <c r="F92" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3913,11 +4183,14 @@
       <c r="C93" t="str">
         <v/>
       </c>
+      <c r="D93" t="str">
+        <v>Arbok</v>
+      </c>
       <c r="E93" t="str">
-        <v>undefined-undefined</v>
+        <v>38-43</v>
       </c>
       <c r="F93" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3951,11 +4224,14 @@
       <c r="C94" t="str">
         <v/>
       </c>
+      <c r="D94" t="str">
+        <v>Golbat</v>
+      </c>
       <c r="E94" t="str">
-        <v>undefined-undefined</v>
+        <v>38-43</v>
       </c>
       <c r="F94" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3989,11 +4265,14 @@
       <c r="C95" t="str">
         <v/>
       </c>
+      <c r="D95" t="str">
+        <v>Geodude</v>
+      </c>
       <c r="E95" t="str">
-        <v>undefined-undefined</v>
+        <v>40-45</v>
       </c>
       <c r="F95" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4027,11 +4306,14 @@
       <c r="C96" t="str">
         <v/>
       </c>
+      <c r="D96" t="str">
+        <v>Machop</v>
+      </c>
       <c r="E96" t="str">
-        <v>undefined-undefined</v>
+        <v>40-45</v>
       </c>
       <c r="F96" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4065,11 +4347,14 @@
       <c r="C97" t="str">
         <v/>
       </c>
+      <c r="D97" t="str">
+        <v>Graveler</v>
+      </c>
       <c r="E97" t="str">
-        <v>undefined-undefined</v>
+        <v>42-47</v>
       </c>
       <c r="F97" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4103,11 +4388,14 @@
       <c r="C98" t="str">
         <v/>
       </c>
+      <c r="D98" t="str">
+        <v>Machoke</v>
+      </c>
       <c r="E98" t="str">
-        <v>undefined-undefined</v>
+        <v>42-47</v>
       </c>
       <c r="F98" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4141,11 +4429,14 @@
       <c r="C99" t="str">
         <v/>
       </c>
+      <c r="D99" t="str">
+        <v>Onix</v>
+      </c>
       <c r="E99" t="str">
-        <v>undefined-undefined</v>
+        <v>42-47</v>
       </c>
       <c r="F99" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4179,11 +4470,14 @@
       <c r="C100" t="str">
         <v/>
       </c>
+      <c r="D100" t="str">
+        <v>Tyrogue</v>
+      </c>
       <c r="E100" t="str">
-        <v>undefined-undefined</v>
+        <v>42-47</v>
       </c>
       <c r="F100" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4217,11 +4511,14 @@
       <c r="C101" t="str">
         <v/>
       </c>
+      <c r="D101" t="str">
+        <v>Misdreavus</v>
+      </c>
       <c r="E101" t="str">
-        <v>undefined-undefined</v>
+        <v>43-48</v>
       </c>
       <c r="F101" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -4255,11 +4552,14 @@
       <c r="C102" t="str">
         <v/>
       </c>
+      <c r="D102" t="str">
+        <v>Seaking</v>
+      </c>
       <c r="E102" t="str">
-        <v>undefined-undefined</v>
+        <v>48-54</v>
       </c>
       <c r="F102" t="str">
-        <v>0.35%</v>
+        <v>35%</v>
       </c>
       <c r="G102" t="str">
         <v/>
@@ -4293,11 +4593,14 @@
       <c r="C103" t="str">
         <v/>
       </c>
+      <c r="D103" t="str">
+        <v>Kingler</v>
+      </c>
       <c r="E103" t="str">
-        <v>undefined-undefined</v>
+        <v>48-54</v>
       </c>
       <c r="F103" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G103" t="str">
         <v/>
@@ -4331,11 +4634,14 @@
       <c r="C104" t="str">
         <v/>
       </c>
+      <c r="D104" t="str">
+        <v>Poliwhirl</v>
+      </c>
       <c r="E104" t="str">
-        <v>undefined-undefined</v>
+        <v>49-55</v>
       </c>
       <c r="F104" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G104" t="str">
         <v/>
@@ -4369,11 +4675,14 @@
       <c r="C105" t="str">
         <v/>
       </c>
+      <c r="D105" t="str">
+        <v>Lanturn</v>
+      </c>
       <c r="E105" t="str">
-        <v>undefined-undefined</v>
+        <v>50-56</v>
       </c>
       <c r="F105" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G105" t="str">
         <v/>
@@ -4407,11 +4716,14 @@
       <c r="C106" t="str">
         <v/>
       </c>
+      <c r="D106" t="str">
+        <v>Swinub</v>
+      </c>
       <c r="E106" t="str">
-        <v>undefined-undefined</v>
+        <v>52-57</v>
       </c>
       <c r="F106" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G106" t="str">
         <v/>
@@ -4445,11 +4757,14 @@
       <c r="C107" t="str">
         <v/>
       </c>
+      <c r="D107" t="str">
+        <v>Zubat</v>
+      </c>
       <c r="E107" t="str">
-        <v>undefined-undefined</v>
+        <v>50-55</v>
       </c>
       <c r="F107" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G107" t="str">
         <v/>
@@ -4483,11 +4798,14 @@
       <c r="C108" t="str">
         <v/>
       </c>
+      <c r="D108" t="str">
+        <v>Delibird</v>
+      </c>
       <c r="E108" t="str">
-        <v>undefined-undefined</v>
+        <v>52-57</v>
       </c>
       <c r="F108" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G108" t="str">
         <v/>
@@ -4521,11 +4839,14 @@
       <c r="C109" t="str">
         <v/>
       </c>
+      <c r="D109" t="str">
+        <v>Golbat</v>
+      </c>
       <c r="E109" t="str">
-        <v>undefined-undefined</v>
+        <v>54-59</v>
       </c>
       <c r="F109" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G109" t="str">
         <v/>
@@ -4559,11 +4880,14 @@
       <c r="C110" t="str">
         <v/>
       </c>
+      <c r="D110" t="str">
+        <v>Sneasel</v>
+      </c>
       <c r="E110" t="str">
-        <v>undefined-undefined</v>
+        <v>53-58</v>
       </c>
       <c r="F110" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G110" t="str">
         <v/>
@@ -4597,11 +4921,14 @@
       <c r="C111" t="str">
         <v/>
       </c>
+      <c r="D111" t="str">
+        <v>Jynx</v>
+      </c>
       <c r="E111" t="str">
-        <v>undefined-undefined</v>
+        <v>54-60</v>
       </c>
       <c r="F111" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G111" t="str">
         <v/>
@@ -4635,11 +4962,14 @@
       <c r="C112" t="str">
         <v/>
       </c>
+      <c r="D112" t="str">
+        <v>Graveler</v>
+      </c>
       <c r="E112" t="str">
-        <v>undefined-undefined</v>
+        <v>58-64</v>
       </c>
       <c r="F112" t="str">
-        <v>0.19%</v>
+        <v>19%</v>
       </c>
       <c r="G112" t="str">
         <v/>
@@ -4673,11 +5003,14 @@
       <c r="C113" t="str">
         <v/>
       </c>
+      <c r="D113" t="str">
+        <v>Gligar</v>
+      </c>
       <c r="E113" t="str">
-        <v>undefined-undefined</v>
+        <v>58-64</v>
       </c>
       <c r="F113" t="str">
-        <v>0.19%</v>
+        <v>19%</v>
       </c>
       <c r="G113" t="str">
         <v/>
@@ -4711,11 +5044,14 @@
       <c r="C114" t="str">
         <v/>
       </c>
+      <c r="D114" t="str">
+        <v>Phanpy</v>
+      </c>
       <c r="E114" t="str">
-        <v>undefined-undefined</v>
+        <v>57-63</v>
       </c>
       <c r="F114" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G114" t="str">
         <v/>
@@ -4749,11 +5085,14 @@
       <c r="C115" t="str">
         <v/>
       </c>
+      <c r="D115" t="str">
+        <v>Pineco</v>
+      </c>
       <c r="E115" t="str">
-        <v>undefined-undefined</v>
+        <v>58-64</v>
       </c>
       <c r="F115" t="str">
-        <v>0.23%</v>
+        <v>23%</v>
       </c>
       <c r="G115" t="str">
         <v/>
@@ -4787,11 +5126,14 @@
       <c r="C116" t="str">
         <v/>
       </c>
+      <c r="D116" t="str">
+        <v>Weepinbell</v>
+      </c>
       <c r="E116" t="str">
-        <v>undefined-undefined</v>
+        <v>57-64</v>
       </c>
       <c r="F116" t="str">
-        <v>0.07%</v>
+        <v>7%</v>
       </c>
       <c r="G116" t="str">
         <v/>
@@ -4825,11 +5167,14 @@
       <c r="C117" t="str">
         <v/>
       </c>
+      <c r="D117" t="str">
+        <v>Girafarig</v>
+      </c>
       <c r="E117" t="str">
-        <v>undefined-undefined</v>
+        <v>57-64</v>
       </c>
       <c r="F117" t="str">
-        <v>0.08%</v>
+        <v>8%</v>
       </c>
       <c r="G117" t="str">
         <v/>
@@ -4863,11 +5208,14 @@
       <c r="C118" t="str">
         <v/>
       </c>
+      <c r="D118" t="str">
+        <v>Tangela</v>
+      </c>
       <c r="E118" t="str">
-        <v>undefined-undefined</v>
+        <v>57-64</v>
       </c>
       <c r="F118" t="str">
-        <v>0.09%</v>
+        <v>9%</v>
       </c>
       <c r="G118" t="str">
         <v/>
@@ -4901,11 +5249,14 @@
       <c r="C119" t="str">
         <v/>
       </c>
+      <c r="D119" t="str">
+        <v>Golduck</v>
+      </c>
       <c r="E119" t="str">
-        <v>undefined-undefined</v>
+        <v>62-68</v>
       </c>
       <c r="F119" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G119" t="str">
         <v/>
@@ -4914,7 +5265,7 @@
         <v>Yes</v>
       </c>
       <c r="I119" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J119" t="str">
         <v>NONONO</v>
@@ -4939,11 +5290,14 @@
       <c r="C120" t="str">
         <v/>
       </c>
+      <c r="D120" t="str">
+        <v>Tentacruel</v>
+      </c>
       <c r="E120" t="str">
-        <v>undefined-undefined</v>
+        <v>63-69</v>
       </c>
       <c r="F120" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G120" t="str">
         <v/>
@@ -4952,7 +5306,7 @@
         <v>Yes</v>
       </c>
       <c r="I120" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J120" t="str">
         <v>NONONO</v>
@@ -4977,11 +5331,14 @@
       <c r="C121" t="str">
         <v/>
       </c>
+      <c r="D121" t="str">
+        <v>Quagsire</v>
+      </c>
       <c r="E121" t="str">
-        <v>undefined-undefined</v>
+        <v>62-68</v>
       </c>
       <c r="F121" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G121" t="str">
         <v/>
@@ -5015,11 +5372,14 @@
       <c r="C122" t="str">
         <v/>
       </c>
+      <c r="D122" t="str">
+        <v>Gyarados</v>
+      </c>
       <c r="E122" t="str">
-        <v>undefined-undefined</v>
+        <v>64-70</v>
       </c>
       <c r="F122" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G122" t="str">
         <v/>
@@ -5028,7 +5388,7 @@
         <v>Yes</v>
       </c>
       <c r="I122" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J122" t="str">
         <v>NONONO</v>
@@ -5053,11 +5413,14 @@
       <c r="C123" t="str">
         <v/>
       </c>
+      <c r="D123" t="str">
+        <v>Mantine</v>
+      </c>
       <c r="E123" t="str">
-        <v>undefined-undefined</v>
+        <v>64-70</v>
       </c>
       <c r="F123" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G123" t="str">
         <v/>
@@ -5091,11 +5454,14 @@
       <c r="C124" t="str">
         <v/>
       </c>
+      <c r="D124" t="str">
+        <v>Dragonair</v>
+      </c>
       <c r="E124" t="str">
-        <v>undefined-undefined</v>
+        <v>65-71</v>
       </c>
       <c r="F124" t="str">
-        <v>0.05%</v>
+        <v>5%</v>
       </c>
       <c r="G124" t="str">
         <v/>
@@ -5129,11 +5495,14 @@
       <c r="C125" t="str">
         <v/>
       </c>
+      <c r="D125" t="str">
+        <v>Graveler</v>
+      </c>
       <c r="E125" t="str">
-        <v>undefined-undefined</v>
+        <v>64-70</v>
       </c>
       <c r="F125" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G125" t="str">
         <v/>
@@ -5167,11 +5536,14 @@
       <c r="C126" t="str">
         <v/>
       </c>
+      <c r="D126" t="str">
+        <v>Teddiursa</v>
+      </c>
       <c r="E126" t="str">
-        <v>undefined-undefined</v>
+        <v>63-69</v>
       </c>
       <c r="F126" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G126" t="str">
         <v/>
@@ -5205,11 +5577,14 @@
       <c r="C127" t="str">
         <v/>
       </c>
+      <c r="D127" t="str">
+        <v>Shuckle</v>
+      </c>
       <c r="E127" t="str">
-        <v>undefined-undefined</v>
+        <v>64-70</v>
       </c>
       <c r="F127" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G127" t="str">
         <v/>
@@ -5218,7 +5593,7 @@
         <v>Yes</v>
       </c>
       <c r="I127" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J127" t="str">
         <v>NONONO</v>
@@ -5243,11 +5618,14 @@
       <c r="C128" t="str">
         <v/>
       </c>
+      <c r="D128" t="str">
+        <v>Ursaring</v>
+      </c>
       <c r="E128" t="str">
-        <v>undefined-undefined</v>
+        <v>68-74</v>
       </c>
       <c r="F128" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G128" t="str">
         <v/>
@@ -5256,7 +5634,7 @@
         <v>Yes</v>
       </c>
       <c r="I128" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J128" t="str">
         <v>NONONO</v>
@@ -5281,11 +5659,14 @@
       <c r="C129" t="str">
         <v/>
       </c>
+      <c r="D129" t="str">
+        <v>Wobbuffet</v>
+      </c>
       <c r="E129" t="str">
-        <v>undefined-undefined</v>
+        <v>65-71</v>
       </c>
       <c r="F129" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G129" t="str">
         <v/>
@@ -5319,11 +5700,14 @@
       <c r="C130" t="str">
         <v/>
       </c>
+      <c r="D130" t="str">
+        <v>Dunsparce</v>
+      </c>
       <c r="E130" t="str">
-        <v>undefined-undefined</v>
+        <v>64-70</v>
       </c>
       <c r="F130" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G130" t="str">
         <v/>
@@ -5357,11 +5741,14 @@
       <c r="C131" t="str">
         <v/>
       </c>
+      <c r="D131" t="str">
+        <v>Donphan</v>
+      </c>
       <c r="E131" t="str">
-        <v>undefined-undefined</v>
+        <v>68-74</v>
       </c>
       <c r="F131" t="str">
-        <v>0.4%</v>
+        <v>40%</v>
       </c>
       <c r="G131" t="str">
         <v/>
@@ -5370,7 +5757,7 @@
         <v>Yes</v>
       </c>
       <c r="I131" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J131" t="str">
         <v>NONONO</v>
@@ -5395,11 +5782,14 @@
       <c r="C132" t="str">
         <v/>
       </c>
+      <c r="D132" t="str">
+        <v>Teddiursa</v>
+      </c>
       <c r="E132" t="str">
-        <v>undefined-undefined</v>
+        <v>66-72</v>
       </c>
       <c r="F132" t="str">
-        <v>0.35%</v>
+        <v>35%</v>
       </c>
       <c r="G132" t="str">
         <v/>
@@ -5433,11 +5823,14 @@
       <c r="C133" t="str">
         <v/>
       </c>
+      <c r="D133" t="str">
+        <v>Skarmory</v>
+      </c>
       <c r="E133" t="str">
-        <v>undefined-undefined</v>
+        <v>70-76</v>
       </c>
       <c r="F133" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G133" t="str">
         <v/>
@@ -5471,11 +5864,14 @@
       <c r="C134" t="str">
         <v/>
       </c>
+      <c r="D134" t="str">
+        <v>Abra</v>
+      </c>
       <c r="E134" t="str">
-        <v>undefined-undefined</v>
+        <v>18-22</v>
       </c>
       <c r="F134" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G134" t="str">
         <v/>
@@ -5509,11 +5905,14 @@
       <c r="C135" t="str">
         <v/>
       </c>
+      <c r="D135" t="str">
+        <v>Sandshrew</v>
+      </c>
       <c r="E135" t="str">
-        <v>undefined-undefined</v>
+        <v>18-22</v>
       </c>
       <c r="F135" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G135" t="str">
         <v/>
@@ -5547,11 +5946,14 @@
       <c r="C136" t="str">
         <v/>
       </c>
+      <c r="D136" t="str">
+        <v>Machop</v>
+      </c>
       <c r="E136" t="str">
-        <v>undefined-undefined</v>
+        <v>18-22</v>
       </c>
       <c r="F136" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G136" t="str">
         <v/>
@@ -5585,11 +5987,14 @@
       <c r="C137" t="str">
         <v/>
       </c>
+      <c r="D137" t="str">
+        <v>Cubone</v>
+      </c>
       <c r="E137" t="str">
-        <v>undefined-undefined</v>
+        <v>18-22</v>
       </c>
       <c r="F137" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G137" t="str">
         <v/>
@@ -5623,11 +6028,14 @@
       <c r="C138" t="str">
         <v/>
       </c>
+      <c r="D138" t="str">
+        <v>Eevee</v>
+      </c>
       <c r="E138" t="str">
-        <v>undefined-undefined</v>
+        <v>20-24</v>
       </c>
       <c r="F138" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G138" t="str">
         <v/>
@@ -5661,11 +6069,14 @@
       <c r="C139" t="str">
         <v/>
       </c>
+      <c r="D139" t="str">
+        <v>Voltorb</v>
+      </c>
       <c r="E139" t="str">
-        <v>undefined-undefined</v>
+        <v>33-38</v>
       </c>
       <c r="F139" t="str">
-        <v>0.35%</v>
+        <v>35%</v>
       </c>
       <c r="G139" t="str">
         <v/>
@@ -5699,11 +6110,14 @@
       <c r="C140" t="str">
         <v/>
       </c>
+      <c r="D140" t="str">
+        <v>Geodude</v>
+      </c>
       <c r="E140" t="str">
-        <v>undefined-undefined</v>
+        <v>32-37</v>
       </c>
       <c r="F140" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G140" t="str">
         <v/>
@@ -5737,11 +6151,14 @@
       <c r="C141" t="str">
         <v/>
       </c>
+      <c r="D141" t="str">
+        <v>Koffing</v>
+      </c>
       <c r="E141" t="str">
-        <v>undefined-undefined</v>
+        <v>33-38</v>
       </c>
       <c r="F141" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G141" t="str">
         <v/>
@@ -5775,11 +6192,14 @@
       <c r="C142" t="str">
         <v/>
       </c>
+      <c r="D142" t="str">
+        <v>Electrode</v>
+      </c>
       <c r="E142" t="str">
-        <v>undefined-undefined</v>
+        <v>36-40</v>
       </c>
       <c r="F142" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G142" t="str">
         <v/>
@@ -5813,11 +6233,14 @@
       <c r="C143" t="str">
         <v/>
       </c>
+      <c r="D143" t="str">
+        <v>Magikarp</v>
+      </c>
       <c r="E143" t="str">
-        <v>undefined-undefined</v>
+        <v>48-55</v>
       </c>
       <c r="F143" t="str">
-        <v>0.95%</v>
+        <v>95%</v>
       </c>
       <c r="G143" t="str">
         <v/>
@@ -5851,11 +6274,14 @@
       <c r="C144" t="str">
         <v/>
       </c>
+      <c r="D144" t="str">
+        <v>Gyarados</v>
+      </c>
       <c r="E144" t="str">
-        <v>undefined-undefined</v>
+        <v>55-60</v>
       </c>
       <c r="F144" t="str">
-        <v>0.05%</v>
+        <v>5%</v>
       </c>
       <c r="G144" t="str">
         <v/>
@@ -5889,11 +6315,14 @@
       <c r="C145" t="str">
         <v/>
       </c>
+      <c r="D145" t="str">
+        <v>Donphan</v>
+      </c>
       <c r="E145" t="str">
-        <v>undefined-undefined</v>
+        <v>74-80</v>
       </c>
       <c r="F145" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G145" t="str">
         <v/>
@@ -5927,11 +6356,14 @@
       <c r="C146" t="str">
         <v/>
       </c>
+      <c r="D146" t="str">
+        <v>Quagsire</v>
+      </c>
       <c r="E146" t="str">
-        <v>undefined-undefined</v>
+        <v>74-80</v>
       </c>
       <c r="F146" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G146" t="str">
         <v/>
@@ -5965,11 +6397,14 @@
       <c r="C147" t="str">
         <v/>
       </c>
+      <c r="D147" t="str">
+        <v>Doduo</v>
+      </c>
       <c r="E147" t="str">
-        <v>undefined-undefined</v>
+        <v>73-79</v>
       </c>
       <c r="F147" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G147" t="str">
         <v/>
@@ -6003,11 +6438,14 @@
       <c r="C148" t="str">
         <v/>
       </c>
+      <c r="D148" t="str">
+        <v>Ponyta</v>
+      </c>
       <c r="E148" t="str">
-        <v>undefined-undefined</v>
+        <v>74-80</v>
       </c>
       <c r="F148" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G148" t="str">
         <v/>
@@ -6041,11 +6479,14 @@
       <c r="C149" t="str">
         <v/>
       </c>
+      <c r="D149" t="str">
+        <v>Parasect</v>
+      </c>
       <c r="E149" t="str">
-        <v>undefined-undefined</v>
+        <v>75-81</v>
       </c>
       <c r="F149" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G149" t="str">
         <v/>
@@ -6079,11 +6520,14 @@
       <c r="C150" t="str">
         <v/>
       </c>
+      <c r="D150" t="str">
+        <v>Larvitar</v>
+      </c>
       <c r="E150" t="str">
-        <v>undefined-undefined</v>
+        <v>75-82</v>
       </c>
       <c r="F150" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G150" t="str">
         <v/>
@@ -6117,11 +6561,14 @@
       <c r="C151" t="str">
         <v/>
       </c>
+      <c r="D151" t="str">
+        <v>Parasect</v>
+      </c>
       <c r="E151" t="str">
-        <v>undefined-undefined</v>
+        <v>77-82</v>
       </c>
       <c r="F151" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G151" t="str">
         <v/>
@@ -6155,11 +6602,14 @@
       <c r="C152" t="str">
         <v/>
       </c>
+      <c r="D152" t="str">
+        <v>Butterfree</v>
+      </c>
       <c r="E152" t="str">
-        <v>undefined-undefined</v>
+        <v>77-82</v>
       </c>
       <c r="F152" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G152" t="str">
         <v/>
@@ -6193,11 +6643,14 @@
       <c r="C153" t="str">
         <v/>
       </c>
+      <c r="D153" t="str">
+        <v>Beedrill</v>
+      </c>
       <c r="E153" t="str">
-        <v>undefined-undefined</v>
+        <v>77-82</v>
       </c>
       <c r="F153" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G153" t="str">
         <v/>
@@ -6231,11 +6684,14 @@
       <c r="C154" t="str">
         <v/>
       </c>
+      <c r="D154" t="str">
+        <v>Noctowl</v>
+      </c>
       <c r="E154" t="str">
-        <v>undefined-undefined</v>
+        <v>79-83</v>
       </c>
       <c r="F154" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G154" t="str">
         <v/>
@@ -6269,11 +6725,14 @@
       <c r="C155" t="str">
         <v/>
       </c>
+      <c r="D155" t="str">
+        <v>Exeggutor</v>
+      </c>
       <c r="E155" t="str">
-        <v>undefined-undefined</v>
+        <v>79-83</v>
       </c>
       <c r="F155" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G155" t="str">
         <v/>
@@ -6307,11 +6766,14 @@
       <c r="C156" t="str">
         <v/>
       </c>
+      <c r="D156" t="str">
+        <v>Celebi</v>
+      </c>
       <c r="E156" t="str">
-        <v>undefined-undefined</v>
+        <v>85-85</v>
       </c>
       <c r="F156" t="str">
-        <v>0.05%</v>
+        <v>5%</v>
       </c>
       <c r="G156" t="str">
         <v/>
@@ -6345,11 +6807,14 @@
       <c r="C157" t="str">
         <v/>
       </c>
+      <c r="D157" t="str">
+        <v>Raikou</v>
+      </c>
       <c r="E157" t="str">
-        <v>undefined-undefined</v>
+        <v>50-50</v>
       </c>
       <c r="F157" t="str">
-        <v>0.3333333333333333%</v>
+        <v>33%</v>
       </c>
       <c r="G157" t="str">
         <v/>
@@ -6383,11 +6848,14 @@
       <c r="C158" t="str">
         <v/>
       </c>
+      <c r="D158" t="str">
+        <v>Entei</v>
+      </c>
       <c r="E158" t="str">
-        <v>undefined-undefined</v>
+        <v>50-50</v>
       </c>
       <c r="F158" t="str">
-        <v>0.3333333333333333%</v>
+        <v>33%</v>
       </c>
       <c r="G158" t="str">
         <v/>
@@ -6421,11 +6889,14 @@
       <c r="C159" t="str">
         <v/>
       </c>
+      <c r="D159" t="str">
+        <v>Suicune</v>
+      </c>
       <c r="E159" t="str">
-        <v>undefined-undefined</v>
+        <v>50-50</v>
       </c>
       <c r="F159" t="str">
-        <v>0.3333333333333333%</v>
+        <v>33%</v>
       </c>
       <c r="G159" t="str">
         <v/>
@@ -6459,11 +6930,14 @@
       <c r="C160" t="str">
         <v/>
       </c>
+      <c r="D160" t="str">
+        <v>Oddish</v>
+      </c>
       <c r="E160" t="str">
-        <v>undefined-undefined</v>
+        <v>72-76</v>
       </c>
       <c r="F160" t="str">
-        <v>0.23%</v>
+        <v>23%</v>
       </c>
       <c r="G160" t="str">
         <v/>
@@ -6497,11 +6971,14 @@
       <c r="C161" t="str">
         <v/>
       </c>
+      <c r="D161" t="str">
+        <v>Gloom</v>
+      </c>
       <c r="E161" t="str">
-        <v>undefined-undefined</v>
+        <v>72-76</v>
       </c>
       <c r="F161" t="str">
-        <v>0.24%</v>
+        <v>24%</v>
       </c>
       <c r="G161" t="str">
         <v/>
@@ -6535,11 +7012,14 @@
       <c r="C162" t="str">
         <v/>
       </c>
+      <c r="D162" t="str">
+        <v>Butterfree</v>
+      </c>
       <c r="E162" t="str">
-        <v>undefined-undefined</v>
+        <v>74-78</v>
       </c>
       <c r="F162" t="str">
-        <v>0.14%</v>
+        <v>14%</v>
       </c>
       <c r="G162" t="str">
         <v/>
@@ -6573,11 +7053,14 @@
       <c r="C163" t="str">
         <v/>
       </c>
+      <c r="D163" t="str">
+        <v>Beedrill</v>
+      </c>
       <c r="E163" t="str">
-        <v>undefined-undefined</v>
+        <v>74-78</v>
       </c>
       <c r="F163" t="str">
-        <v>0.14%</v>
+        <v>14%</v>
       </c>
       <c r="G163" t="str">
         <v/>
@@ -6611,11 +7094,14 @@
       <c r="C164" t="str">
         <v/>
       </c>
+      <c r="D164" t="str">
+        <v>Vileplume</v>
+      </c>
       <c r="E164" t="str">
-        <v>undefined-undefined</v>
+        <v>75-78</v>
       </c>
       <c r="F164" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G164" t="str">
         <v/>
@@ -6649,11 +7135,14 @@
       <c r="C165" t="str">
         <v/>
       </c>
+      <c r="D165" t="str">
+        <v>Bellossom</v>
+      </c>
       <c r="E165" t="str">
-        <v>undefined-undefined</v>
+        <v>75-78</v>
       </c>
       <c r="F165" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G165" t="str">
         <v/>
@@ -6687,11 +7176,14 @@
       <c r="C166" t="str">
         <v/>
       </c>
+      <c r="D166" t="str">
+        <v>Pikachu</v>
+      </c>
       <c r="E166" t="str">
-        <v>undefined-undefined</v>
+        <v>72-78</v>
       </c>
       <c r="F166" t="str">
-        <v>0.05%</v>
+        <v>5%</v>
       </c>
       <c r="G166" t="str">
         <v/>
@@ -6725,11 +7217,14 @@
       <c r="C167" t="str">
         <v/>
       </c>
+      <c r="D167" t="str">
+        <v>Geodude</v>
+      </c>
       <c r="E167" t="str">
-        <v>undefined-undefined</v>
+        <v>76-80</v>
       </c>
       <c r="F167" t="str">
-        <v>0.22%</v>
+        <v>22%</v>
       </c>
       <c r="G167" t="str">
         <v/>
@@ -6763,11 +7258,14 @@
       <c r="C168" t="str">
         <v/>
       </c>
+      <c r="D168" t="str">
+        <v>Golbat</v>
+      </c>
       <c r="E168" t="str">
-        <v>undefined-undefined</v>
+        <v>76-81</v>
       </c>
       <c r="F168" t="str">
-        <v>0.23%</v>
+        <v>23%</v>
       </c>
       <c r="G168" t="str">
         <v/>
@@ -6801,11 +7299,14 @@
       <c r="C169" t="str">
         <v/>
       </c>
+      <c r="D169" t="str">
+        <v>Graveler</v>
+      </c>
       <c r="E169" t="str">
-        <v>undefined-undefined</v>
+        <v>78-82</v>
       </c>
       <c r="F169" t="str">
-        <v>0.18%</v>
+        <v>18%</v>
       </c>
       <c r="G169" t="str">
         <v/>
@@ -6839,11 +7340,14 @@
       <c r="C170" t="str">
         <v/>
       </c>
+      <c r="D170" t="str">
+        <v>Onix</v>
+      </c>
       <c r="E170" t="str">
-        <v>undefined-undefined</v>
+        <v>77-81</v>
       </c>
       <c r="F170" t="str">
-        <v>0.14%</v>
+        <v>14%</v>
       </c>
       <c r="G170" t="str">
         <v/>
@@ -6877,11 +7381,14 @@
       <c r="C171" t="str">
         <v/>
       </c>
+      <c r="D171" t="str">
+        <v>Crobat</v>
+      </c>
       <c r="E171" t="str">
-        <v>undefined-undefined</v>
+        <v>78-82</v>
       </c>
       <c r="F171" t="str">
-        <v>0.14%</v>
+        <v>14%</v>
       </c>
       <c r="G171" t="str">
         <v/>
@@ -6915,11 +7422,14 @@
       <c r="C172" t="str">
         <v/>
       </c>
+      <c r="D172" t="str">
+        <v>Clefairy</v>
+      </c>
       <c r="E172" t="str">
-        <v>undefined-undefined</v>
+        <v>76-82</v>
       </c>
       <c r="F172" t="str">
-        <v>0.09%</v>
+        <v>9%</v>
       </c>
       <c r="G172" t="str">
         <v/>
@@ -6953,11 +7463,14 @@
       <c r="C173" t="str">
         <v/>
       </c>
+      <c r="D173" t="str">
+        <v>Golbat</v>
+      </c>
       <c r="E173" t="str">
-        <v>undefined-undefined</v>
+        <v>79-83</v>
       </c>
       <c r="F173" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G173" t="str">
         <v/>
@@ -6991,11 +7504,14 @@
       <c r="C174" t="str">
         <v/>
       </c>
+      <c r="D174" t="str">
+        <v>Golem</v>
+      </c>
       <c r="E174" t="str">
-        <v>undefined-undefined</v>
+        <v>81-85</v>
       </c>
       <c r="F174" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G174" t="str">
         <v/>
@@ -7029,11 +7545,14 @@
       <c r="C175" t="str">
         <v/>
       </c>
+      <c r="D175" t="str">
+        <v>Steelix</v>
+      </c>
       <c r="E175" t="str">
-        <v>undefined-undefined</v>
+        <v>81-85</v>
       </c>
       <c r="F175" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G175" t="str">
         <v/>
@@ -7067,11 +7586,14 @@
       <c r="C176" t="str">
         <v/>
       </c>
+      <c r="D176" t="str">
+        <v>Crobat</v>
+      </c>
       <c r="E176" t="str">
-        <v>undefined-undefined</v>
+        <v>81-85</v>
       </c>
       <c r="F176" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G176" t="str">
         <v/>
@@ -7105,11 +7627,14 @@
       <c r="C177" t="str">
         <v/>
       </c>
+      <c r="D177" t="str">
+        <v>Slowpoke</v>
+      </c>
       <c r="E177" t="str">
-        <v>undefined-undefined</v>
+        <v>82-86</v>
       </c>
       <c r="F177" t="str">
-        <v>0.4%</v>
+        <v>40%</v>
       </c>
       <c r="G177" t="str">
         <v/>
@@ -7143,11 +7668,14 @@
       <c r="C178" t="str">
         <v/>
       </c>
+      <c r="D178" t="str">
+        <v>Kadabra</v>
+      </c>
       <c r="E178" t="str">
-        <v>undefined-undefined</v>
+        <v>83-87</v>
       </c>
       <c r="F178" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G178" t="str">
         <v/>
@@ -7181,11 +7709,14 @@
       <c r="C179" t="str">
         <v/>
       </c>
+      <c r="D179" t="str">
+        <v>Mr. Mime</v>
+      </c>
       <c r="E179" t="str">
-        <v>undefined-undefined</v>
+        <v>83-87</v>
       </c>
       <c r="F179" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G179" t="str">
         <v/>
@@ -7219,11 +7750,14 @@
       <c r="C180" t="str">
         <v/>
       </c>
+      <c r="D180" t="str">
+        <v>Diglett</v>
+      </c>
       <c r="E180" t="str">
-        <v>undefined-undefined</v>
+        <v>82-86</v>
       </c>
       <c r="F180" t="str">
-        <v>0.9%</v>
+        <v>90%</v>
       </c>
       <c r="G180" t="str">
         <v/>
@@ -7257,11 +7791,14 @@
       <c r="C181" t="str">
         <v/>
       </c>
+      <c r="D181" t="str">
+        <v>Dugtrio</v>
+      </c>
       <c r="E181" t="str">
-        <v>undefined-undefined</v>
+        <v>85-89</v>
       </c>
       <c r="F181" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G181" t="str">
         <v/>
@@ -7295,11 +7832,14 @@
       <c r="C182" t="str">
         <v/>
       </c>
+      <c r="D182" t="str">
+        <v>Grimer</v>
+      </c>
       <c r="E182" t="str">
-        <v>undefined-undefined</v>
+        <v>84-88</v>
       </c>
       <c r="F182" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G182" t="str">
         <v/>
@@ -7333,11 +7873,14 @@
       <c r="C183" t="str">
         <v/>
       </c>
+      <c r="D183" t="str">
+        <v>Horsea</v>
+      </c>
       <c r="E183" t="str">
-        <v>undefined-undefined</v>
+        <v>84-88</v>
       </c>
       <c r="F183" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G183" t="str">
         <v/>
@@ -7371,11 +7914,14 @@
       <c r="C184" t="str">
         <v/>
       </c>
+      <c r="D184" t="str">
+        <v>Hypno</v>
+      </c>
       <c r="E184" t="str">
-        <v>undefined-undefined</v>
+        <v>85-89</v>
       </c>
       <c r="F184" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G184" t="str">
         <v/>
@@ -7409,11 +7955,14 @@
       <c r="C185" t="str">
         <v/>
       </c>
+      <c r="D185" t="str">
+        <v>Seadra</v>
+      </c>
       <c r="E185" t="str">
-        <v>undefined-undefined</v>
+        <v>86-89</v>
       </c>
       <c r="F185" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G185" t="str">
         <v/>
@@ -7447,11 +7996,14 @@
       <c r="C186" t="str">
         <v/>
       </c>
+      <c r="D186" t="str">
+        <v>Slowking</v>
+      </c>
       <c r="E186" t="str">
-        <v>undefined-undefined</v>
+        <v>86-89</v>
       </c>
       <c r="F186" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G186" t="str">
         <v/>
@@ -7485,11 +8037,14 @@
       <c r="C187" t="str">
         <v/>
       </c>
+      <c r="D187" t="str">
+        <v>Snorlax</v>
+      </c>
       <c r="E187" t="str">
-        <v>undefined-undefined</v>
+        <v>88-89</v>
       </c>
       <c r="F187" t="str">
-        <v>0.05%</v>
+        <v>5%</v>
       </c>
       <c r="G187" t="str">
         <v/>
@@ -7523,11 +8078,14 @@
       <c r="C188" t="str">
         <v/>
       </c>
+      <c r="D188" t="str">
+        <v>Nidoking</v>
+      </c>
       <c r="E188" t="str">
-        <v>undefined-undefined</v>
+        <v>86-90</v>
       </c>
       <c r="F188" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G188" t="str">
         <v/>
@@ -7561,11 +8119,14 @@
       <c r="C189" t="str">
         <v/>
       </c>
+      <c r="D189" t="str">
+        <v>Nidoqueen</v>
+      </c>
       <c r="E189" t="str">
-        <v>undefined-undefined</v>
+        <v>86-90</v>
       </c>
       <c r="F189" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G189" t="str">
         <v/>
@@ -7599,11 +8160,14 @@
       <c r="C190" t="str">
         <v/>
       </c>
+      <c r="D190" t="str">
+        <v>Rhydon</v>
+      </c>
       <c r="E190" t="str">
-        <v>undefined-undefined</v>
+        <v>87-90</v>
       </c>
       <c r="F190" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G190" t="str">
         <v/>
@@ -7637,11 +8201,14 @@
       <c r="C191" t="str">
         <v/>
       </c>
+      <c r="D191" t="str">
+        <v>Tauros</v>
+      </c>
       <c r="E191" t="str">
-        <v>undefined-undefined</v>
+        <v>87-91</v>
       </c>
       <c r="F191" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G191" t="str">
         <v/>
@@ -7675,11 +8242,14 @@
       <c r="C192" t="str">
         <v/>
       </c>
+      <c r="D192" t="str">
+        <v>Scizor</v>
+      </c>
       <c r="E192" t="str">
-        <v>undefined-undefined</v>
+        <v>87-90</v>
       </c>
       <c r="F192" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G192" t="str">
         <v/>
@@ -7713,11 +8283,14 @@
       <c r="C193" t="str">
         <v/>
       </c>
+      <c r="D193" t="str">
+        <v>Chansey</v>
+      </c>
       <c r="E193" t="str">
-        <v>undefined-undefined</v>
+        <v>88-91</v>
       </c>
       <c r="F193" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G193" t="str">
         <v/>
@@ -7751,11 +8324,14 @@
       <c r="C194" t="str">
         <v/>
       </c>
+      <c r="D194" t="str">
+        <v>Nidorino</v>
+      </c>
       <c r="E194" t="str">
-        <v>undefined-undefined</v>
+        <v>39-44</v>
       </c>
       <c r="F194" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G194" t="str">
         <v/>
@@ -7789,11 +8365,14 @@
       <c r="C195" t="str">
         <v/>
       </c>
+      <c r="D195" t="str">
+        <v>Nidorina</v>
+      </c>
       <c r="E195" t="str">
-        <v>undefined-undefined</v>
+        <v>39-44</v>
       </c>
       <c r="F195" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G195" t="str">
         <v/>
@@ -7827,11 +8406,14 @@
       <c r="C196" t="str">
         <v/>
       </c>
+      <c r="D196" t="str">
+        <v>Rhyhorn</v>
+      </c>
       <c r="E196" t="str">
-        <v>undefined-undefined</v>
+        <v>40-45</v>
       </c>
       <c r="F196" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G196" t="str">
         <v/>
@@ -7840,7 +8422,7 @@
         <v>Yes</v>
       </c>
       <c r="I196" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J196" t="str">
         <v>NONONO</v>
@@ -7865,11 +8447,14 @@
       <c r="C197" t="str">
         <v/>
       </c>
+      <c r="D197" t="str">
+        <v>Kangaskhan</v>
+      </c>
       <c r="E197" t="str">
-        <v>undefined-undefined</v>
+        <v>40-45</v>
       </c>
       <c r="F197" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G197" t="str">
         <v/>
@@ -7903,11 +8488,14 @@
       <c r="C198" t="str">
         <v/>
       </c>
+      <c r="D198" t="str">
+        <v>Murkrow</v>
+      </c>
       <c r="E198" t="str">
-        <v>undefined-undefined</v>
+        <v>39-44</v>
       </c>
       <c r="F198" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G198" t="str">
         <v/>
@@ -7941,11 +8529,14 @@
       <c r="C199" t="str">
         <v/>
       </c>
+      <c r="D199" t="str">
+        <v>Chansey</v>
+      </c>
       <c r="E199" t="str">
-        <v>undefined-undefined</v>
+        <v>39-44</v>
       </c>
       <c r="F199" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G199" t="str">
         <v/>
@@ -7979,11 +8570,14 @@
       <c r="C200" t="str">
         <v/>
       </c>
+      <c r="D200" t="str">
+        <v>Doduo</v>
+      </c>
       <c r="E200" t="str">
-        <v>undefined-undefined</v>
+        <v>88-92</v>
       </c>
       <c r="F200" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G200" t="str">
         <v/>
@@ -7992,7 +8586,7 @@
         <v>Yes</v>
       </c>
       <c r="I200" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J200" t="str">
         <v>NONONO</v>
@@ -8017,11 +8611,14 @@
       <c r="C201" t="str">
         <v/>
       </c>
+      <c r="D201" t="str">
+        <v>Fearow</v>
+      </c>
       <c r="E201" t="str">
-        <v>undefined-undefined</v>
+        <v>88-92</v>
       </c>
       <c r="F201" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G201" t="str">
         <v/>
@@ -8055,11 +8652,14 @@
       <c r="C202" t="str">
         <v/>
       </c>
+      <c r="D202" t="str">
+        <v>Dodrio</v>
+      </c>
       <c r="E202" t="str">
-        <v>undefined-undefined</v>
+        <v>90-93</v>
       </c>
       <c r="F202" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G202" t="str">
         <v/>
@@ -8093,11 +8693,14 @@
       <c r="C203" t="str">
         <v/>
       </c>
+      <c r="D203" t="str">
+        <v>Pidgeot</v>
+      </c>
       <c r="E203" t="str">
-        <v>undefined-undefined</v>
+        <v>90-93</v>
       </c>
       <c r="F203" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G203" t="str">
         <v/>
@@ -8131,11 +8734,14 @@
       <c r="C204" t="str">
         <v/>
       </c>
+      <c r="D204" t="str">
+        <v>Snorlax</v>
+      </c>
       <c r="E204" t="str">
-        <v>undefined-undefined</v>
+        <v>92-93</v>
       </c>
       <c r="F204" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G204" t="str">
         <v/>
@@ -8169,11 +8775,14 @@
       <c r="C205" t="str">
         <v/>
       </c>
+      <c r="D205" t="str">
+        <v>Seel</v>
+      </c>
       <c r="E205" t="str">
-        <v>undefined-undefined</v>
+        <v>90-94</v>
       </c>
       <c r="F205" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G205" t="str">
         <v/>
@@ -8182,7 +8791,7 @@
         <v>Yes</v>
       </c>
       <c r="I205" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J205" t="str">
         <v>NONONO</v>
@@ -8207,11 +8816,14 @@
       <c r="C206" t="str">
         <v/>
       </c>
+      <c r="D206" t="str">
+        <v>Seaking</v>
+      </c>
       <c r="E206" t="str">
-        <v>undefined-undefined</v>
+        <v>90-94</v>
       </c>
       <c r="F206" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G206" t="str">
         <v/>
@@ -8245,11 +8857,14 @@
       <c r="C207" t="str">
         <v/>
       </c>
+      <c r="D207" t="str">
+        <v>Dewgong</v>
+      </c>
       <c r="E207" t="str">
-        <v>undefined-undefined</v>
+        <v>91-94</v>
       </c>
       <c r="F207" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G207" t="str">
         <v/>
@@ -8283,11 +8898,14 @@
       <c r="C208" t="str">
         <v/>
       </c>
+      <c r="D208" t="str">
+        <v>Tentacruel</v>
+      </c>
       <c r="E208" t="str">
-        <v>undefined-undefined</v>
+        <v>91-94</v>
       </c>
       <c r="F208" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G208" t="str">
         <v/>
@@ -8321,11 +8939,14 @@
       <c r="C209" t="str">
         <v/>
       </c>
+      <c r="D209" t="str">
+        <v>Starmie</v>
+      </c>
       <c r="E209" t="str">
-        <v>undefined-undefined</v>
+        <v>92-94</v>
       </c>
       <c r="F209" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G209" t="str">
         <v/>
@@ -8359,11 +8980,14 @@
       <c r="C210" t="str">
         <v/>
       </c>
+      <c r="D210" t="str">
+        <v>Kingdra</v>
+      </c>
       <c r="E210" t="str">
-        <v>undefined-undefined</v>
+        <v>92-94</v>
       </c>
       <c r="F210" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G210" t="str">
         <v/>
@@ -8397,11 +9021,14 @@
       <c r="C211" t="str">
         <v/>
       </c>
+      <c r="D211" t="str">
+        <v>Omanyte</v>
+      </c>
       <c r="E211" t="str">
-        <v>undefined-undefined</v>
+        <v>91-93</v>
       </c>
       <c r="F211" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G211" t="str">
         <v/>
@@ -8435,11 +9062,14 @@
       <c r="C212" t="str">
         <v/>
       </c>
+      <c r="D212" t="str">
+        <v>Kabuto</v>
+      </c>
       <c r="E212" t="str">
-        <v>undefined-undefined</v>
+        <v>91-93</v>
       </c>
       <c r="F212" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G212" t="str">
         <v/>
@@ -8473,11 +9103,14 @@
       <c r="C213" t="str">
         <v/>
       </c>
+      <c r="D213" t="str">
+        <v>Aerodactyl</v>
+      </c>
       <c r="E213" t="str">
-        <v>undefined-undefined</v>
+        <v>94-95</v>
       </c>
       <c r="F213" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G213" t="str">
         <v/>
@@ -8511,11 +9144,14 @@
       <c r="C214" t="str">
         <v/>
       </c>
+      <c r="D214" t="str">
+        <v>Omastar</v>
+      </c>
       <c r="E214" t="str">
-        <v>undefined-undefined</v>
+        <v>92-94</v>
       </c>
       <c r="F214" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G214" t="str">
         <v/>
@@ -8549,11 +9185,14 @@
       <c r="C215" t="str">
         <v/>
       </c>
+      <c r="D215" t="str">
+        <v>Kabutops</v>
+      </c>
       <c r="E215" t="str">
-        <v>undefined-undefined</v>
+        <v>92-94</v>
       </c>
       <c r="F215" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G215" t="str">
         <v/>
@@ -8587,11 +9226,14 @@
       <c r="C216" t="str">
         <v/>
       </c>
+      <c r="D216" t="str">
+        <v>Koffing</v>
+      </c>
       <c r="E216" t="str">
-        <v>undefined-undefined</v>
+        <v>91-95</v>
       </c>
       <c r="F216" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G216" t="str">
         <v/>
@@ -8600,7 +9242,7 @@
         <v>Yes</v>
       </c>
       <c r="I216" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J216" t="str">
         <v>NONONO</v>
@@ -8625,11 +9267,14 @@
       <c r="C217" t="str">
         <v/>
       </c>
+      <c r="D217" t="str">
+        <v>Slugma</v>
+      </c>
       <c r="E217" t="str">
-        <v>undefined-undefined</v>
+        <v>91-95</v>
       </c>
       <c r="F217" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G217" t="str">
         <v/>
@@ -8638,7 +9283,7 @@
         <v>Yes</v>
       </c>
       <c r="I217" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J217" t="str">
         <v>NONONO</v>
@@ -8663,11 +9308,14 @@
       <c r="C218" t="str">
         <v/>
       </c>
+      <c r="D218" t="str">
+        <v>Houndour</v>
+      </c>
       <c r="E218" t="str">
-        <v>undefined-undefined</v>
+        <v>91-95</v>
       </c>
       <c r="F218" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G218" t="str">
         <v/>
@@ -8676,7 +9324,7 @@
         <v>Yes</v>
       </c>
       <c r="I218" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J218" t="str">
         <v>NONONO</v>
@@ -8701,11 +9349,14 @@
       <c r="C219" t="str">
         <v/>
       </c>
+      <c r="D219" t="str">
+        <v>Magmar</v>
+      </c>
       <c r="E219" t="str">
-        <v>undefined-undefined</v>
+        <v>92-95</v>
       </c>
       <c r="F219" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G219" t="str">
         <v/>
@@ -8739,11 +9390,14 @@
       <c r="C220" t="str">
         <v/>
       </c>
+      <c r="D220" t="str">
+        <v>Weezing</v>
+      </c>
       <c r="E220" t="str">
-        <v>undefined-undefined</v>
+        <v>93-95</v>
       </c>
       <c r="F220" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G220" t="str">
         <v/>
@@ -8777,11 +9431,14 @@
       <c r="C221" t="str">
         <v/>
       </c>
+      <c r="D221" t="str">
+        <v>Magcargo</v>
+      </c>
       <c r="E221" t="str">
-        <v>undefined-undefined</v>
+        <v>93-95</v>
       </c>
       <c r="F221" t="str">
-        <v>0.05%</v>
+        <v>5%</v>
       </c>
       <c r="G221" t="str">
         <v/>
@@ -8815,11 +9472,14 @@
       <c r="C222" t="str">
         <v/>
       </c>
+      <c r="D222" t="str">
+        <v>Houndoom</v>
+      </c>
       <c r="E222" t="str">
-        <v>undefined-undefined</v>
+        <v>93-95</v>
       </c>
       <c r="F222" t="str">
-        <v>0.05%</v>
+        <v>5%</v>
       </c>
       <c r="G222" t="str">
         <v/>
@@ -8853,11 +9513,14 @@
       <c r="C223" t="str">
         <v/>
       </c>
+      <c r="D223" t="str">
+        <v>Bulbasaur</v>
+      </c>
       <c r="E223" t="str">
-        <v>undefined-undefined</v>
+        <v>80-85</v>
       </c>
       <c r="F223" t="str">
-        <v>0.16670000000000001%</v>
+        <v>17%</v>
       </c>
       <c r="G223" t="str">
         <v/>
@@ -8866,7 +9529,7 @@
         <v>Yes</v>
       </c>
       <c r="I223" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J223" t="str">
         <v>NONONO</v>
@@ -8891,11 +9554,14 @@
       <c r="C224" t="str">
         <v/>
       </c>
+      <c r="D224" t="str">
+        <v>Charmander</v>
+      </c>
       <c r="E224" t="str">
-        <v>undefined-undefined</v>
+        <v>80-85</v>
       </c>
       <c r="F224" t="str">
-        <v>0.16670000000000001%</v>
+        <v>17%</v>
       </c>
       <c r="G224" t="str">
         <v/>
@@ -8904,7 +9570,7 @@
         <v>Yes</v>
       </c>
       <c r="I224" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J224" t="str">
         <v>NONONO</v>
@@ -8929,11 +9595,14 @@
       <c r="C225" t="str">
         <v/>
       </c>
+      <c r="D225" t="str">
+        <v>Squirtle</v>
+      </c>
       <c r="E225" t="str">
-        <v>undefined-undefined</v>
+        <v>80-85</v>
       </c>
       <c r="F225" t="str">
-        <v>0.16670000000000001%</v>
+        <v>17%</v>
       </c>
       <c r="G225" t="str">
         <v/>
@@ -8942,7 +9611,7 @@
         <v>Yes</v>
       </c>
       <c r="I225" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J225" t="str">
         <v>NONONO</v>
@@ -8967,11 +9636,14 @@
       <c r="C226" t="str">
         <v/>
       </c>
+      <c r="D226" t="str">
+        <v>Chikorita</v>
+      </c>
       <c r="E226" t="str">
-        <v>undefined-undefined</v>
+        <v>80-85</v>
       </c>
       <c r="F226" t="str">
-        <v>0.16670000000000001%</v>
+        <v>17%</v>
       </c>
       <c r="G226" t="str">
         <v/>
@@ -8980,7 +9652,7 @@
         <v>Yes</v>
       </c>
       <c r="I226" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J226" t="str">
         <v>NONONO</v>
@@ -9005,11 +9677,14 @@
       <c r="C227" t="str">
         <v/>
       </c>
+      <c r="D227" t="str">
+        <v>Cyndaquil</v>
+      </c>
       <c r="E227" t="str">
-        <v>undefined-undefined</v>
+        <v>80-85</v>
       </c>
       <c r="F227" t="str">
-        <v>0.16670000000000001%</v>
+        <v>17%</v>
       </c>
       <c r="G227" t="str">
         <v/>
@@ -9018,7 +9693,7 @@
         <v>Yes</v>
       </c>
       <c r="I227" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J227" t="str">
         <v>NONONO</v>
@@ -9043,11 +9718,14 @@
       <c r="C228" t="str">
         <v/>
       </c>
+      <c r="D228" t="str">
+        <v>Totodile</v>
+      </c>
       <c r="E228" t="str">
-        <v>undefined-undefined</v>
+        <v>80-85</v>
       </c>
       <c r="F228" t="str">
-        <v>0.16670000000000001%</v>
+        <v>17%</v>
       </c>
       <c r="G228" t="str">
         <v/>
@@ -9056,7 +9734,7 @@
         <v>Yes</v>
       </c>
       <c r="I228" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J228" t="str">
         <v>NONONO</v>
@@ -9081,11 +9759,14 @@
       <c r="C229" t="str">
         <v/>
       </c>
+      <c r="D229" t="str">
+        <v>Pichu</v>
+      </c>
       <c r="E229" t="str">
-        <v>undefined-undefined</v>
+        <v>84-89</v>
       </c>
       <c r="F229" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G229" t="str">
         <v/>
@@ -9094,7 +9775,7 @@
         <v>Yes</v>
       </c>
       <c r="I229" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J229" t="str">
         <v>NONONO</v>
@@ -9119,11 +9800,14 @@
       <c r="C230" t="str">
         <v/>
       </c>
+      <c r="D230" t="str">
+        <v>Cleffa</v>
+      </c>
       <c r="E230" t="str">
-        <v>undefined-undefined</v>
+        <v>84-89</v>
       </c>
       <c r="F230" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G230" t="str">
         <v/>
@@ -9132,7 +9816,7 @@
         <v>Yes</v>
       </c>
       <c r="I230" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J230" t="str">
         <v>NONONO</v>
@@ -9157,11 +9841,14 @@
       <c r="C231" t="str">
         <v/>
       </c>
+      <c r="D231" t="str">
+        <v>Igglybuff</v>
+      </c>
       <c r="E231" t="str">
-        <v>undefined-undefined</v>
+        <v>84-89</v>
       </c>
       <c r="F231" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G231" t="str">
         <v/>
@@ -9170,7 +9857,7 @@
         <v>Yes</v>
       </c>
       <c r="I231" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J231" t="str">
         <v>NONONO</v>
@@ -9195,11 +9882,14 @@
       <c r="C232" t="str">
         <v/>
       </c>
+      <c r="D232" t="str">
+        <v>Togepi</v>
+      </c>
       <c r="E232" t="str">
-        <v>undefined-undefined</v>
+        <v>84-89</v>
       </c>
       <c r="F232" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G232" t="str">
         <v/>
@@ -9208,7 +9898,7 @@
         <v>Yes</v>
       </c>
       <c r="I232" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J232" t="str">
         <v>NONONO</v>
@@ -9233,11 +9923,14 @@
       <c r="C233" t="str">
         <v/>
       </c>
+      <c r="D233" t="str">
+        <v>Elekid</v>
+      </c>
       <c r="E233" t="str">
-        <v>undefined-undefined</v>
+        <v>84-89</v>
       </c>
       <c r="F233" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G233" t="str">
         <v/>
@@ -9271,11 +9964,14 @@
       <c r="C234" t="str">
         <v/>
       </c>
+      <c r="D234" t="str">
+        <v>Magby</v>
+      </c>
       <c r="E234" t="str">
-        <v>undefined-undefined</v>
+        <v>84-89</v>
       </c>
       <c r="F234" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G234" t="str">
         <v/>
@@ -9309,11 +10005,14 @@
       <c r="C235" t="str">
         <v/>
       </c>
+      <c r="D235" t="str">
+        <v>Smoochum</v>
+      </c>
       <c r="E235" t="str">
-        <v>undefined-undefined</v>
+        <v>84-89</v>
       </c>
       <c r="F235" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G235" t="str">
         <v/>
@@ -9322,7 +10021,7 @@
         <v>Yes</v>
       </c>
       <c r="I235" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J235" t="str">
         <v>NONONO</v>
@@ -9347,11 +10046,14 @@
       <c r="C236" t="str">
         <v/>
       </c>
+      <c r="D236" t="str">
+        <v>Blissey</v>
+      </c>
       <c r="E236" t="str">
-        <v>undefined-undefined</v>
+        <v>84-89</v>
       </c>
       <c r="F236" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G236" t="str">
         <v/>
@@ -9385,11 +10087,14 @@
       <c r="C237" t="str">
         <v/>
       </c>
+      <c r="D237" t="str">
+        <v>Lickitung</v>
+      </c>
       <c r="E237" t="str">
-        <v>undefined-undefined</v>
+        <v>84-89</v>
       </c>
       <c r="F237" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G237" t="str">
         <v/>
@@ -9423,11 +10128,14 @@
       <c r="C238" t="str">
         <v/>
       </c>
+      <c r="D238" t="str">
+        <v>Porygon</v>
+      </c>
       <c r="E238" t="str">
-        <v>undefined-undefined</v>
+        <v>84-89</v>
       </c>
       <c r="F238" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G238" t="str">
         <v/>
@@ -9461,11 +10169,14 @@
       <c r="C239" t="str">
         <v/>
       </c>
+      <c r="D239" t="str">
+        <v>Lapras</v>
+      </c>
       <c r="E239" t="str">
-        <v>undefined-undefined</v>
+        <v>84-89</v>
       </c>
       <c r="F239" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G239" t="str">
         <v/>
@@ -9499,11 +10210,14 @@
       <c r="C240" t="str">
         <v/>
       </c>
+      <c r="D240" t="str">
+        <v>Porygon2</v>
+      </c>
       <c r="E240" t="str">
-        <v>undefined-undefined</v>
+        <v>85-90</v>
       </c>
       <c r="F240" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G240" t="str">
         <v/>
@@ -9537,11 +10251,14 @@
       <c r="C241" t="str">
         <v/>
       </c>
+      <c r="D241" t="str">
+        <v>Eevee</v>
+      </c>
       <c r="E241" t="str">
-        <v>undefined-undefined</v>
+        <v>85-90</v>
       </c>
       <c r="F241" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G241" t="str">
         <v/>
@@ -9550,7 +10267,7 @@
         <v>Yes</v>
       </c>
       <c r="I241" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J241" t="str">
         <v>NONONO</v>
@@ -9575,11 +10292,14 @@
       <c r="C242" t="str">
         <v/>
       </c>
+      <c r="D242" t="str">
+        <v>Vaporeon</v>
+      </c>
       <c r="E242" t="str">
-        <v>undefined-undefined</v>
+        <v>86-91</v>
       </c>
       <c r="F242" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G242" t="str">
         <v/>
@@ -9613,11 +10333,14 @@
       <c r="C243" t="str">
         <v/>
       </c>
+      <c r="D243" t="str">
+        <v>Jolteon</v>
+      </c>
       <c r="E243" t="str">
-        <v>undefined-undefined</v>
+        <v>86-91</v>
       </c>
       <c r="F243" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G243" t="str">
         <v/>
@@ -9651,11 +10374,14 @@
       <c r="C244" t="str">
         <v/>
       </c>
+      <c r="D244" t="str">
+        <v>Flareon</v>
+      </c>
       <c r="E244" t="str">
-        <v>undefined-undefined</v>
+        <v>86-91</v>
       </c>
       <c r="F244" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G244" t="str">
         <v/>
@@ -9689,11 +10415,14 @@
       <c r="C245" t="str">
         <v/>
       </c>
+      <c r="D245" t="str">
+        <v>Espeon</v>
+      </c>
       <c r="E245" t="str">
-        <v>undefined-undefined</v>
+        <v>86-91</v>
       </c>
       <c r="F245" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G245" t="str">
         <v/>
@@ -9727,11 +10456,14 @@
       <c r="C246" t="str">
         <v/>
       </c>
+      <c r="D246" t="str">
+        <v>Umbreon</v>
+      </c>
       <c r="E246" t="str">
-        <v>undefined-undefined</v>
+        <v>86-91</v>
       </c>
       <c r="F246" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G246" t="str">
         <v/>
@@ -9765,11 +10497,14 @@
       <c r="C247" t="str">
         <v/>
       </c>
+      <c r="D247" t="str">
+        <v>Leafeon</v>
+      </c>
       <c r="E247" t="str">
-        <v>undefined-undefined</v>
+        <v>86-91</v>
       </c>
       <c r="F247" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G247" t="str">
         <v/>
@@ -9803,11 +10538,14 @@
       <c r="C248" t="str">
         <v/>
       </c>
+      <c r="D248" t="str">
+        <v>Glaceon</v>
+      </c>
       <c r="E248" t="str">
-        <v>undefined-undefined</v>
+        <v>86-91</v>
       </c>
       <c r="F248" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G248" t="str">
         <v/>
@@ -9841,11 +10579,14 @@
       <c r="C249" t="str">
         <v/>
       </c>
+      <c r="D249" t="str">
+        <v>Sylveon</v>
+      </c>
       <c r="E249" t="str">
-        <v>undefined-undefined</v>
+        <v>86-91</v>
       </c>
       <c r="F249" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G249" t="str">
         <v/>
@@ -9879,11 +10620,14 @@
       <c r="C250" t="str">
         <v/>
       </c>
+      <c r="D250" t="str">
+        <v>Tyrogue</v>
+      </c>
       <c r="E250" t="str">
-        <v>undefined-undefined</v>
+        <v>88-92</v>
       </c>
       <c r="F250" t="str">
-        <v>0.4%</v>
+        <v>40%</v>
       </c>
       <c r="G250" t="str">
         <v/>
@@ -9892,7 +10636,7 @@
         <v>Yes</v>
       </c>
       <c r="I250" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J250" t="str">
         <v>NONONO</v>
@@ -9917,11 +10661,14 @@
       <c r="C251" t="str">
         <v/>
       </c>
+      <c r="D251" t="str">
+        <v>Hitmonlee</v>
+      </c>
       <c r="E251" t="str">
-        <v>undefined-undefined</v>
+        <v>89-93</v>
       </c>
       <c r="F251" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G251" t="str">
         <v/>
@@ -9955,11 +10702,14 @@
       <c r="C252" t="str">
         <v/>
       </c>
+      <c r="D252" t="str">
+        <v>Hitmonchan</v>
+      </c>
       <c r="E252" t="str">
-        <v>undefined-undefined</v>
+        <v>89-93</v>
       </c>
       <c r="F252" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G252" t="str">
         <v/>
@@ -9993,11 +10743,14 @@
       <c r="C253" t="str">
         <v/>
       </c>
+      <c r="D253" t="str">
+        <v>Hitmontop</v>
+      </c>
       <c r="E253" t="str">
-        <v>undefined-undefined</v>
+        <v>89-93</v>
       </c>
       <c r="F253" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G253" t="str">
         <v/>
@@ -10031,11 +10784,14 @@
       <c r="C254" t="str">
         <v/>
       </c>
+      <c r="D254" t="str">
+        <v>Venusaur</v>
+      </c>
       <c r="E254" t="str">
-        <v>undefined-undefined</v>
+        <v>90-98</v>
       </c>
       <c r="F254" t="str">
-        <v>0.17%</v>
+        <v>17%</v>
       </c>
       <c r="G254" t="str">
         <v/>
@@ -10069,11 +10825,14 @@
       <c r="C255" t="str">
         <v/>
       </c>
+      <c r="D255" t="str">
+        <v>Charizard</v>
+      </c>
       <c r="E255" t="str">
-        <v>undefined-undefined</v>
+        <v>90-98</v>
       </c>
       <c r="F255" t="str">
-        <v>0.17%</v>
+        <v>17%</v>
       </c>
       <c r="G255" t="str">
         <v/>
@@ -10107,11 +10866,14 @@
       <c r="C256" t="str">
         <v/>
       </c>
+      <c r="D256" t="str">
+        <v>Blastoise</v>
+      </c>
       <c r="E256" t="str">
-        <v>undefined-undefined</v>
+        <v>90-98</v>
       </c>
       <c r="F256" t="str">
-        <v>0.17%</v>
+        <v>17%</v>
       </c>
       <c r="G256" t="str">
         <v/>
@@ -10145,11 +10907,14 @@
       <c r="C257" t="str">
         <v/>
       </c>
+      <c r="D257" t="str">
+        <v>Meganium</v>
+      </c>
       <c r="E257" t="str">
-        <v>undefined-undefined</v>
+        <v>90-98</v>
       </c>
       <c r="F257" t="str">
-        <v>0.17%</v>
+        <v>17%</v>
       </c>
       <c r="G257" t="str">
         <v/>
@@ -10183,11 +10948,14 @@
       <c r="C258" t="str">
         <v/>
       </c>
+      <c r="D258" t="str">
+        <v>Typhlosion</v>
+      </c>
       <c r="E258" t="str">
-        <v>undefined-undefined</v>
+        <v>90-98</v>
       </c>
       <c r="F258" t="str">
-        <v>0.17%</v>
+        <v>17%</v>
       </c>
       <c r="G258" t="str">
         <v/>
@@ -10221,11 +10989,14 @@
       <c r="C259" t="str">
         <v/>
       </c>
+      <c r="D259" t="str">
+        <v>Feraligatr</v>
+      </c>
       <c r="E259" t="str">
-        <v>undefined-undefined</v>
+        <v>90-98</v>
       </c>
       <c r="F259" t="str">
-        <v>0.17%</v>
+        <v>17%</v>
       </c>
       <c r="G259" t="str">
         <v/>
@@ -10259,11 +11030,14 @@
       <c r="C260" t="str">
         <v/>
       </c>
+      <c r="D260" t="str">
+        <v>Articuno</v>
+      </c>
       <c r="E260" t="str">
-        <v>undefined-undefined</v>
+        <v>100-100</v>
       </c>
       <c r="F260" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G260" t="str">
         <v/>
@@ -10297,11 +11071,14 @@
       <c r="C261" t="str">
         <v/>
       </c>
+      <c r="D261" t="str">
+        <v>Zapdos</v>
+      </c>
       <c r="E261" t="str">
-        <v>undefined-undefined</v>
+        <v>100-100</v>
       </c>
       <c r="F261" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G261" t="str">
         <v/>
@@ -10335,11 +11112,14 @@
       <c r="C262" t="str">
         <v/>
       </c>
+      <c r="D262" t="str">
+        <v>Moltres</v>
+      </c>
       <c r="E262" t="str">
-        <v>undefined-undefined</v>
+        <v>100-100</v>
       </c>
       <c r="F262" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G262" t="str">
         <v/>
@@ -10373,11 +11153,14 @@
       <c r="C263" t="str">
         <v/>
       </c>
+      <c r="D263" t="str">
+        <v>Ho-oh</v>
+      </c>
       <c r="E263" t="str">
-        <v>undefined-undefined</v>
+        <v>110-110</v>
       </c>
       <c r="F263" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G263" t="str">
         <v/>
@@ -10411,11 +11194,14 @@
       <c r="C264" t="str">
         <v/>
       </c>
+      <c r="D264" t="str">
+        <v>Lugia</v>
+      </c>
       <c r="E264" t="str">
-        <v>undefined-undefined</v>
+        <v>110-110</v>
       </c>
       <c r="F264" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G264" t="str">
         <v/>
@@ -10449,11 +11235,14 @@
       <c r="C265" t="str">
         <v/>
       </c>
+      <c r="D265" t="str">
+        <v>Raikou</v>
+      </c>
       <c r="E265" t="str">
-        <v>undefined-undefined</v>
+        <v>110-110</v>
       </c>
       <c r="F265" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G265" t="str">
         <v/>
@@ -10487,11 +11276,14 @@
       <c r="C266" t="str">
         <v/>
       </c>
+      <c r="D266" t="str">
+        <v>Entei</v>
+      </c>
       <c r="E266" t="str">
-        <v>undefined-undefined</v>
+        <v>110-110</v>
       </c>
       <c r="F266" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G266" t="str">
         <v/>
@@ -10525,11 +11317,14 @@
       <c r="C267" t="str">
         <v/>
       </c>
+      <c r="D267" t="str">
+        <v>Suicune</v>
+      </c>
       <c r="E267" t="str">
-        <v>undefined-undefined</v>
+        <v>110-110</v>
       </c>
       <c r="F267" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G267" t="str">
         <v/>
@@ -10563,11 +11358,14 @@
       <c r="C268" t="str">
         <v/>
       </c>
+      <c r="D268" t="str">
+        <v>Mew</v>
+      </c>
       <c r="E268" t="str">
-        <v>undefined-undefined</v>
+        <v>120-120</v>
       </c>
       <c r="F268" t="str">
-        <v>0.13333333333333333%</v>
+        <v>13%</v>
       </c>
       <c r="G268" t="str">
         <v/>
@@ -10601,11 +11399,14 @@
       <c r="C269" t="str">
         <v/>
       </c>
+      <c r="D269" t="str">
+        <v>Mewtwo</v>
+      </c>
       <c r="E269" t="str">
-        <v>undefined-undefined</v>
+        <v>120-120</v>
       </c>
       <c r="F269" t="str">
-        <v>0.13333333333333333%</v>
+        <v>13%</v>
       </c>
       <c r="G269" t="str">
         <v/>
@@ -10639,11 +11440,14 @@
       <c r="C270" t="str">
         <v/>
       </c>
+      <c r="D270" t="str">
+        <v>Celebi</v>
+      </c>
       <c r="E270" t="str">
-        <v>undefined-undefined</v>
+        <v>120-120</v>
       </c>
       <c r="F270" t="str">
-        <v>0.13333333333333333%</v>
+        <v>13%</v>
       </c>
       <c r="G270" t="str">
         <v/>
@@ -10677,11 +11481,14 @@
       <c r="C271" t="str">
         <v/>
       </c>
+      <c r="D271" t="str">
+        <v>Alakazam</v>
+      </c>
       <c r="E271" t="str">
-        <v>undefined-undefined</v>
+        <v>91-95</v>
       </c>
       <c r="F271" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G271" t="str">
         <v/>
@@ -10715,11 +11522,14 @@
       <c r="C272" t="str">
         <v/>
       </c>
+      <c r="D272" t="str">
+        <v>Machamp</v>
+      </c>
       <c r="E272" t="str">
-        <v>undefined-undefined</v>
+        <v>91-95</v>
       </c>
       <c r="F272" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G272" t="str">
         <v/>
@@ -10753,11 +11563,14 @@
       <c r="C273" t="str">
         <v/>
       </c>
+      <c r="D273" t="str">
+        <v>Golem</v>
+      </c>
       <c r="E273" t="str">
-        <v>undefined-undefined</v>
+        <v>91-95</v>
       </c>
       <c r="F273" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G273" t="str">
         <v/>
@@ -10791,11 +11604,14 @@
       <c r="C274" t="str">
         <v/>
       </c>
+      <c r="D274" t="str">
+        <v>Gengar</v>
+      </c>
       <c r="E274" t="str">
-        <v>undefined-undefined</v>
+        <v>91-95</v>
       </c>
       <c r="F274" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G274" t="str">
         <v/>
@@ -11757,7 +12573,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B252"/>
+  <dimension ref="A1:B41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11769,2015 +12585,327 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Chikorita</v>
+        <v>Bayleef</v>
       </c>
       <c r="B2" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Bayleef</v>
+        <v>Quilava</v>
       </c>
       <c r="B3" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Meganium</v>
+        <v>Croconaw</v>
       </c>
       <c r="B4" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Cyndaquil</v>
+        <v>Furret</v>
       </c>
       <c r="B5" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Quilava</v>
+        <v>Raichu</v>
       </c>
       <c r="B6" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Typhlosion</v>
+        <v>Clefable</v>
       </c>
       <c r="B7" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Totodile</v>
+        <v>Wigglytuff</v>
       </c>
       <c r="B8" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Croconaw</v>
+        <v>Togetic</v>
       </c>
       <c r="B9" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Feraligatr</v>
+        <v>Sandslash</v>
       </c>
       <c r="B10" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Pidgey</v>
+        <v>Ampharos</v>
       </c>
       <c r="B11" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Pidgeotto</v>
+        <v>Haunter</v>
       </c>
       <c r="B12" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Pidgeot</v>
+        <v>Victreebel</v>
       </c>
       <c r="B13" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Spearow</v>
+        <v>Jumpluff</v>
       </c>
       <c r="B14" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Fearow</v>
+        <v>Poliwrath</v>
       </c>
       <c r="B15" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Hoothoot</v>
+        <v>Politoed</v>
       </c>
       <c r="B16" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Noctowl</v>
+        <v>Slowbro</v>
       </c>
       <c r="B17" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Rattata</v>
+        <v>Forretress</v>
       </c>
       <c r="B18" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Raticate</v>
+        <v>Sunflora</v>
       </c>
       <c r="B19" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Sentret</v>
+        <v>Venomoth</v>
       </c>
       <c r="B20" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Furret</v>
+        <v>Muk</v>
       </c>
       <c r="B21" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Pichu</v>
+        <v>Magneton</v>
       </c>
       <c r="B22" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Pikachu</v>
+        <v>Granbull</v>
       </c>
       <c r="B23" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Raichu</v>
+        <v>Ninetales</v>
       </c>
       <c r="B24" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Caterpie</v>
+        <v>Arcanine</v>
       </c>
       <c r="B25" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Metapod</v>
+        <v>Azumarill</v>
       </c>
       <c r="B26" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Butterfree</v>
+        <v>Primeape</v>
       </c>
       <c r="B27" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Weedle</v>
+        <v>Persian</v>
       </c>
       <c r="B28" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Kakuna</v>
+        <v>Electabuzz</v>
       </c>
       <c r="B29" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Beedrill</v>
+        <v>Xatu</v>
       </c>
       <c r="B30" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Ledyba</v>
+        <v>Cloyster</v>
       </c>
       <c r="B31" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Ledian</v>
+        <v>Octillery</v>
       </c>
       <c r="B32" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Spinarak</v>
+        <v>Piloswine</v>
       </c>
       <c r="B33" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Ariados</v>
+        <v>Rapidash</v>
       </c>
       <c r="B34" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Geodude</v>
+        <v>Marowak</v>
       </c>
       <c r="B35" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Graveler</v>
+        <v>Ivysaur</v>
       </c>
       <c r="B36" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Golem</v>
+        <v>Charmeleon</v>
       </c>
       <c r="B37" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Zubat</v>
+        <v>Wartortle</v>
       </c>
       <c r="B38" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Golbat</v>
+        <v>Dragonite</v>
       </c>
       <c r="B39" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Crobat</v>
+        <v>Pupitar</v>
       </c>
       <c r="B40" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Cleffa</v>
+        <v>Tyranitar</v>
       </c>
       <c r="B41" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>Clefairy</v>
-      </c>
-      <c r="B42" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>Clefable</v>
-      </c>
-      <c r="B43" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>Igglybuff</v>
-      </c>
-      <c r="B44" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>Jigglypuff</v>
-      </c>
-      <c r="B45" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>Wigglytuff</v>
-      </c>
-      <c r="B46" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>Togepi</v>
-      </c>
-      <c r="B47" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>Togetic</v>
-      </c>
-      <c r="B48" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>Sandshrew</v>
-      </c>
-      <c r="B49" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>Sandslash</v>
-      </c>
-      <c r="B50" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>Ekans</v>
-      </c>
-      <c r="B51" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>Arbok</v>
-      </c>
-      <c r="B52" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>Dunsparce</v>
-      </c>
-      <c r="B53" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v>Mareep</v>
-      </c>
-      <c r="B54" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v>Flaaffy</v>
-      </c>
-      <c r="B55" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v>Ampharos</v>
-      </c>
-      <c r="B56" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v>Wooper</v>
-      </c>
-      <c r="B57" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v>Quagsire</v>
-      </c>
-      <c r="B58" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v>Gastly</v>
-      </c>
-      <c r="B59" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>Haunter</v>
-      </c>
-      <c r="B60" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>Gengar</v>
-      </c>
-      <c r="B61" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>Unown</v>
-      </c>
-      <c r="B62" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>Onix</v>
-      </c>
-      <c r="B63" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v>Steelix</v>
-      </c>
-      <c r="B64" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v>Bellsprout</v>
-      </c>
-      <c r="B65" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v>Weepinbell</v>
-      </c>
-      <c r="B66" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="str">
-        <v>Victreebel</v>
-      </c>
-      <c r="B67" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v>Hoppip</v>
-      </c>
-      <c r="B68" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>Skiploom</v>
-      </c>
-      <c r="B69" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v>Jumpluff</v>
-      </c>
-      <c r="B70" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v>Paras</v>
-      </c>
-      <c r="B71" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v>Parasect</v>
-      </c>
-      <c r="B72" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v>Poliwag</v>
-      </c>
-      <c r="B73" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>Poliwhirl</v>
-      </c>
-      <c r="B74" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v>Poliwrath</v>
-      </c>
-      <c r="B75" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v>Politoed</v>
-      </c>
-      <c r="B76" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v>Magikarp</v>
-      </c>
-      <c r="B77" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v>Gyarados</v>
-      </c>
-      <c r="B78" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v>Goldeen</v>
-      </c>
-      <c r="B79" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <v>Seaking</v>
-      </c>
-      <c r="B80" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="str">
-        <v>Slowpoke</v>
-      </c>
-      <c r="B81" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="str">
-        <v>Slowbro</v>
-      </c>
-      <c r="B82" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="str">
-        <v>Slowking</v>
-      </c>
-      <c r="B83" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v>Oddish</v>
-      </c>
-      <c r="B84" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v>Gloom</v>
-      </c>
-      <c r="B85" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>Vileplume</v>
-      </c>
-      <c r="B86" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>Bellossom</v>
-      </c>
-      <c r="B87" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="str">
-        <v>Drowzee</v>
-      </c>
-      <c r="B88" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="str">
-        <v>Hypno</v>
-      </c>
-      <c r="B89" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
-        <v>Abra</v>
-      </c>
-      <c r="B90" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <v>Kadabra</v>
-      </c>
-      <c r="B91" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v>Alakazam</v>
-      </c>
-      <c r="B92" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v>Ditto</v>
-      </c>
-      <c r="B93" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v>Pineco</v>
-      </c>
-      <c r="B94" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v>Forretress</v>
-      </c>
-      <c r="B95" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v>Nidoran♀</v>
-      </c>
-      <c r="B96" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v>Nidorina</v>
-      </c>
-      <c r="B97" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v>Nidoqueen</v>
-      </c>
-      <c r="B98" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v>Nidoran♂</v>
-      </c>
-      <c r="B99" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
-        <v>Nidorino</v>
-      </c>
-      <c r="B100" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>Nidoking</v>
-      </c>
-      <c r="B101" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Yanma</v>
-      </c>
-      <c r="B102" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>Sunkern</v>
-      </c>
-      <c r="B103" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>Sunflora</v>
-      </c>
-      <c r="B104" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>Exeggcute</v>
-      </c>
-      <c r="B105" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>Exeggutor</v>
-      </c>
-      <c r="B106" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Sudowoodo</v>
-      </c>
-      <c r="B107" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="str">
-        <v>Wobbuffet</v>
-      </c>
-      <c r="B108" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="str">
-        <v>Venonat</v>
-      </c>
-      <c r="B109" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="str">
-        <v>Venomoth</v>
-      </c>
-      <c r="B110" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="str">
-        <v>Scyther</v>
-      </c>
-      <c r="B111" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="str">
-        <v>Scizor</v>
-      </c>
-      <c r="B112" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="str">
-        <v>Pinsir</v>
-      </c>
-      <c r="B113" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="str">
-        <v>Heracross</v>
-      </c>
-      <c r="B114" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="str">
-        <v>Koffing</v>
-      </c>
-      <c r="B115" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="str">
-        <v>Weezing</v>
-      </c>
-      <c r="B116" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="str">
-        <v>Grimer</v>
-      </c>
-      <c r="B117" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="str">
-        <v>Muk</v>
-      </c>
-      <c r="B118" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="str">
-        <v>Magnemite</v>
-      </c>
-      <c r="B119" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="str">
-        <v>Magneton</v>
-      </c>
-      <c r="B120" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="str">
-        <v>Voltorb</v>
-      </c>
-      <c r="B121" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="str">
-        <v>Electrode</v>
-      </c>
-      <c r="B122" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="str">
-        <v>Aipom</v>
-      </c>
-      <c r="B123" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="str">
-        <v>Snubbull</v>
-      </c>
-      <c r="B124" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="str">
-        <v>Granbull</v>
-      </c>
-      <c r="B125" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="str">
-        <v>Vulpix</v>
-      </c>
-      <c r="B126" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="str">
-        <v>Ninetales</v>
-      </c>
-      <c r="B127" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="str">
-        <v>Growlithe</v>
-      </c>
-      <c r="B128" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>Arcanine</v>
-      </c>
-      <c r="B129" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
-        <v>Stantler</v>
-      </c>
-      <c r="B130" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="str">
-        <v>Marill</v>
-      </c>
-      <c r="B131" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="str">
-        <v>Azumarill</v>
-      </c>
-      <c r="B132" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="str">
-        <v>Diglett</v>
-      </c>
-      <c r="B133" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="str">
-        <v>Dugtrio</v>
-      </c>
-      <c r="B134" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="str">
-        <v>Mankey</v>
-      </c>
-      <c r="B135" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="str">
-        <v>Primeape</v>
-      </c>
-      <c r="B136" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="str">
-        <v>Meowth</v>
-      </c>
-      <c r="B137" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="str">
-        <v>Persian</v>
-      </c>
-      <c r="B138" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="str">
-        <v>Psyduck</v>
-      </c>
-      <c r="B139" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="str">
-        <v>Golduck</v>
-      </c>
-      <c r="B140" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="str">
-        <v>Machop</v>
-      </c>
-      <c r="B141" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="str">
-        <v>Machoke</v>
-      </c>
-      <c r="B142" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="str">
-        <v>Machamp</v>
-      </c>
-      <c r="B143" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="str">
-        <v>Tyrogue</v>
-      </c>
-      <c r="B144" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="str">
-        <v>Hitmonlee</v>
-      </c>
-      <c r="B145" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="str">
-        <v>Hitmonchan</v>
-      </c>
-      <c r="B146" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="str">
-        <v>Hitmontop</v>
-      </c>
-      <c r="B147" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="str">
-        <v>Girafarig</v>
-      </c>
-      <c r="B148" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="str">
-        <v>Tauros</v>
-      </c>
-      <c r="B149" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="str">
-        <v>Miltank</v>
-      </c>
-      <c r="B150" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="str">
-        <v>Magby</v>
-      </c>
-      <c r="B151" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="str">
-        <v>Magmar</v>
-      </c>
-      <c r="B152" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="str">
-        <v>Smoochum</v>
-      </c>
-      <c r="B153" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="str">
-        <v>Jynx</v>
-      </c>
-      <c r="B154" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="str">
-        <v>Elekid</v>
-      </c>
-      <c r="B155" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="str">
-        <v>Electabuzz</v>
-      </c>
-      <c r="B156" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="str">
-        <v>Mr. Mime</v>
-      </c>
-      <c r="B157" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="str">
-        <v>Smeargle</v>
-      </c>
-      <c r="B158" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="str">
-        <v>Farfetch'd</v>
-      </c>
-      <c r="B159" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="str">
-        <v>Natu</v>
-      </c>
-      <c r="B160" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="str">
-        <v>Xatu</v>
-      </c>
-      <c r="B161" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="str">
-        <v>Qwilfish</v>
-      </c>
-      <c r="B162" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="str">
-        <v>Tentacool</v>
-      </c>
-      <c r="B163" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="str">
-        <v>Tentacruel</v>
-      </c>
-      <c r="B164" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="str">
-        <v>Krabby</v>
-      </c>
-      <c r="B165" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="str">
-        <v>Kingler</v>
-      </c>
-      <c r="B166" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="str">
-        <v>Shuckle</v>
-      </c>
-      <c r="B167" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="str">
-        <v>Staryu</v>
-      </c>
-      <c r="B168" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="str">
-        <v>Starmie</v>
-      </c>
-      <c r="B169" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="str">
-        <v>Shellder</v>
-      </c>
-      <c r="B170" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="str">
-        <v>Cloyster</v>
-      </c>
-      <c r="B171" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="str">
-        <v>Corsola</v>
-      </c>
-      <c r="B172" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="str">
-        <v>Remoraid</v>
-      </c>
-      <c r="B173" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="str">
-        <v>Octillery</v>
-      </c>
-      <c r="B174" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="str">
-        <v>Chinchou</v>
-      </c>
-      <c r="B175" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="str">
-        <v>Lanturn</v>
-      </c>
-      <c r="B176" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="str">
-        <v>Seel</v>
-      </c>
-      <c r="B177" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="str">
-        <v>Dewgong</v>
-      </c>
-      <c r="B178" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="str">
-        <v>Lickitung</v>
-      </c>
-      <c r="B179" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="str">
-        <v>Tangela</v>
-      </c>
-      <c r="B180" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="str">
-        <v>Eevee</v>
-      </c>
-      <c r="B181" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="str">
-        <v>Vaporeon</v>
-      </c>
-      <c r="B182" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="str">
-        <v>Jolteon</v>
-      </c>
-      <c r="B183" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="str">
-        <v>Flareon</v>
-      </c>
-      <c r="B184" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="str">
-        <v>Espeon</v>
-      </c>
-      <c r="B185" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="str">
-        <v>Umbreon</v>
-      </c>
-      <c r="B186" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="str">
-        <v>Horsea</v>
-      </c>
-      <c r="B187" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="str">
-        <v>Seadra</v>
-      </c>
-      <c r="B188" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="str">
-        <v>Kingdra</v>
-      </c>
-      <c r="B189" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="str">
-        <v>Gligar</v>
-      </c>
-      <c r="B190" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="str">
-        <v>Delibird</v>
-      </c>
-      <c r="B191" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="str">
-        <v>Swinub</v>
-      </c>
-      <c r="B192" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="str">
-        <v>Piloswine</v>
-      </c>
-      <c r="B193" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="str">
-        <v>Teddiursa</v>
-      </c>
-      <c r="B194" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="str">
-        <v>Ursaring</v>
-      </c>
-      <c r="B195" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="str">
-        <v>Phanpy</v>
-      </c>
-      <c r="B196" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>Donphan</v>
-      </c>
-      <c r="B197" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>Mantine</v>
-      </c>
-      <c r="B198" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>Skarmory</v>
-      </c>
-      <c r="B199" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>Doduo</v>
-      </c>
-      <c r="B200" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v>Dodrio</v>
-      </c>
-      <c r="B201" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>Ponyta</v>
-      </c>
-      <c r="B202" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>Rapidash</v>
-      </c>
-      <c r="B203" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>Cubone</v>
-      </c>
-      <c r="B204" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>Marowak</v>
-      </c>
-      <c r="B205" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>Kangaskhan</v>
-      </c>
-      <c r="B206" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>Rhyhorn</v>
-      </c>
-      <c r="B207" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>Rhydon</v>
-      </c>
-      <c r="B208" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="str">
-        <v>Murkrow</v>
-      </c>
-      <c r="B209" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="str">
-        <v>Houndour</v>
-      </c>
-      <c r="B210" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="str">
-        <v>Houndoom</v>
-      </c>
-      <c r="B211" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="str">
-        <v>Slugma</v>
-      </c>
-      <c r="B212" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="str">
-        <v>Magcargo</v>
-      </c>
-      <c r="B213" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="str">
-        <v>Sneasel</v>
-      </c>
-      <c r="B214" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="str">
-        <v>Misdreavus</v>
-      </c>
-      <c r="B215" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="str">
-        <v>Porygon</v>
-      </c>
-      <c r="B216" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="str">
-        <v>Porygon2</v>
-      </c>
-      <c r="B217" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="str">
-        <v>Chansey</v>
-      </c>
-      <c r="B218" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="str">
-        <v>Blissey</v>
-      </c>
-      <c r="B219" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="str">
-        <v>Lapras</v>
-      </c>
-      <c r="B220" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="str">
-        <v>Omanyte</v>
-      </c>
-      <c r="B221" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="str">
-        <v>Omastar</v>
-      </c>
-      <c r="B222" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="str">
-        <v>Kabuto</v>
-      </c>
-      <c r="B223" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="str">
-        <v>Kabutops</v>
-      </c>
-      <c r="B224" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="str">
-        <v>Aerodactyl</v>
-      </c>
-      <c r="B225" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="str">
-        <v>Snorlax</v>
-      </c>
-      <c r="B226" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="str">
-        <v>Bulbasaur</v>
-      </c>
-      <c r="B227" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="str">
-        <v>Ivysaur</v>
-      </c>
-      <c r="B228" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="str">
-        <v>Venusaur</v>
-      </c>
-      <c r="B229" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="str">
-        <v>Charmander</v>
-      </c>
-      <c r="B230" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="str">
-        <v>Charmeleon</v>
-      </c>
-      <c r="B231" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="str">
-        <v>Charizard</v>
-      </c>
-      <c r="B232" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="str">
-        <v>Squirtle</v>
-      </c>
-      <c r="B233" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="str">
-        <v>Wartortle</v>
-      </c>
-      <c r="B234" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="str">
-        <v>Blastoise</v>
-      </c>
-      <c r="B235" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="str">
-        <v>Articuno</v>
-      </c>
-      <c r="B236" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="str">
-        <v>Zapdos</v>
-      </c>
-      <c r="B237" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="str">
-        <v>Moltres</v>
-      </c>
-      <c r="B238" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="str">
-        <v>Raikou</v>
-      </c>
-      <c r="B239" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="str">
-        <v>Entei</v>
-      </c>
-      <c r="B240" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="str">
-        <v>Suicune</v>
-      </c>
-      <c r="B241" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="str">
-        <v>Dratini</v>
-      </c>
-      <c r="B242" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="str">
-        <v>Dragonair</v>
-      </c>
-      <c r="B243" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="str">
-        <v>Dragonite</v>
-      </c>
-      <c r="B244" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="str">
-        <v>Larvitar</v>
-      </c>
-      <c r="B245" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="str">
-        <v>Pupitar</v>
-      </c>
-      <c r="B246" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="str">
-        <v>Tyranitar</v>
-      </c>
-      <c r="B247" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="str">
-        <v>Lugia</v>
-      </c>
-      <c r="B248" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="str">
-        <v>Ho-oh</v>
-      </c>
-      <c r="B249" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="str">
-        <v>Mewtwo</v>
-      </c>
-      <c r="B250" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="str">
-        <v>Mew</v>
-      </c>
-      <c r="B251" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="str">
-        <v>Celebi</v>
-      </c>
-      <c r="B252" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B252"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B41"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/2_Johto_Data.xlsx
+++ b/2_Johto_Data.xlsx
@@ -662,8 +662,8 @@
       <c r="H6" s="1">
         <v>0.1</v>
       </c>
-      <c r="I6" t="str">
-        <v/>
+      <c r="I6" s="1">
+        <v>0.2</v>
       </c>
       <c r="J6" t="str">
         <v>Yes</v>
@@ -709,8 +709,8 @@
       <c r="H7" s="1">
         <v>0.1</v>
       </c>
-      <c r="I7" t="str">
-        <v/>
+      <c r="I7" s="1">
+        <v>0.2</v>
       </c>
       <c r="J7" t="str">
         <v>Yes</v>
@@ -991,8 +991,8 @@
       <c r="H13" s="1">
         <v>0.5</v>
       </c>
-      <c r="I13" t="str">
-        <v/>
+      <c r="I13" s="1">
+        <v>0.3333333333333333</v>
       </c>
       <c r="J13" t="str">
         <v>Yes</v>
@@ -1315,13 +1315,13 @@
         <v>8-12</v>
       </c>
       <c r="G20" t="str">
-        <v>4-6</v>
+        <v>3-5</v>
       </c>
       <c r="H20" s="1">
         <v>0.25</v>
       </c>
-      <c r="I20" t="str">
-        <v/>
+      <c r="I20" s="1">
+        <v>0.14285714285714285</v>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -1362,7 +1362,7 @@
         <v>8-12</v>
       </c>
       <c r="G21" t="str">
-        <v>4-6</v>
+        <v>3-5</v>
       </c>
       <c r="H21" s="1">
         <v>0.15</v>
@@ -1409,7 +1409,7 @@
         <v>8-12</v>
       </c>
       <c r="G22" t="str">
-        <v>4-6</v>
+        <v>3-5</v>
       </c>
       <c r="H22" s="1">
         <v>0.15</v>
@@ -1456,7 +1456,7 @@
         <v>8-12</v>
       </c>
       <c r="G23" t="str">
-        <v>4-6</v>
+        <v>3-5</v>
       </c>
       <c r="H23" s="1">
         <v>0.15</v>
@@ -1503,7 +1503,7 @@
         <v>8-12</v>
       </c>
       <c r="G24" t="str">
-        <v>4-6</v>
+        <v>3-5</v>
       </c>
       <c r="H24" s="1">
         <v>0.1</v>
@@ -1550,7 +1550,7 @@
         <v>8-12</v>
       </c>
       <c r="G25" t="str">
-        <v>4-6</v>
+        <v>3-5</v>
       </c>
       <c r="H25" s="1">
         <v>0.1</v>
@@ -1597,7 +1597,7 @@
         <v>8-12</v>
       </c>
       <c r="G26" t="str">
-        <v>4-6</v>
+        <v>3-5</v>
       </c>
       <c r="H26" s="1">
         <v>0.1</v>
@@ -1649,8 +1649,8 @@
       <c r="H27" s="1">
         <v>0.7</v>
       </c>
-      <c r="I27" t="str">
-        <v/>
+      <c r="I27" s="1">
+        <v>0.3333333333333333</v>
       </c>
       <c r="J27" t="str">
         <v>Legacy</v>
@@ -1696,8 +1696,8 @@
       <c r="H28" s="1">
         <v>0.2</v>
       </c>
-      <c r="I28" t="str">
-        <v/>
+      <c r="I28" s="1">
+        <v>0.3333333333333333</v>
       </c>
       <c r="J28" t="str">
         <v>Legacy</v>
@@ -1743,8 +1743,8 @@
       <c r="H29" s="1">
         <v>0.1</v>
       </c>
-      <c r="I29" t="str">
-        <v/>
+      <c r="I29" s="1">
+        <v>0.3333333333333333</v>
       </c>
       <c r="J29" t="str">
         <v>Legacy</v>
@@ -1785,7 +1785,7 @@
         <v>9-13</v>
       </c>
       <c r="G30" t="str">
-        <v>7-9</v>
+        <v>6-8</v>
       </c>
       <c r="H30" s="1">
         <v>0.17</v>
@@ -1832,7 +1832,7 @@
         <v>9-13</v>
       </c>
       <c r="G31" t="str">
-        <v>7-9</v>
+        <v>6-8</v>
       </c>
       <c r="H31" s="1">
         <v>0.25</v>
@@ -1879,7 +1879,7 @@
         <v>9-13</v>
       </c>
       <c r="G32" t="str">
-        <v>7-9</v>
+        <v>6-8</v>
       </c>
       <c r="H32" s="1">
         <v>0.16</v>
@@ -1926,7 +1926,7 @@
         <v>9-13</v>
       </c>
       <c r="G33" t="str">
-        <v>7-9</v>
+        <v>6-8</v>
       </c>
       <c r="H33" s="1">
         <v>0.25</v>
@@ -1973,7 +1973,7 @@
         <v>9-13</v>
       </c>
       <c r="G34" t="str">
-        <v>7-9</v>
+        <v>6-8</v>
       </c>
       <c r="H34" s="1">
         <v>0.08</v>
@@ -2020,7 +2020,7 @@
         <v>9-13</v>
       </c>
       <c r="G35" t="str">
-        <v>7-9</v>
+        <v>6-8</v>
       </c>
       <c r="H35" s="1">
         <v>0.09</v>
@@ -2067,13 +2067,13 @@
         <v>13-17</v>
       </c>
       <c r="G36" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H36" s="1">
         <v>0.3</v>
       </c>
-      <c r="I36" t="str">
-        <v/>
+      <c r="I36" s="1">
+        <v>0.2</v>
       </c>
       <c r="J36" t="str">
         <v>Legacy</v>
@@ -2114,7 +2114,7 @@
         <v>12-16</v>
       </c>
       <c r="G37" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H37" s="1">
         <v>0.2</v>
@@ -2161,7 +2161,7 @@
         <v>12-16</v>
       </c>
       <c r="G38" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H38" s="1">
         <v>0.2</v>
@@ -2208,7 +2208,7 @@
         <v>13-17</v>
       </c>
       <c r="G39" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H39" s="1">
         <v>0.15</v>
@@ -2255,7 +2255,7 @@
         <v>13-17</v>
       </c>
       <c r="G40" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H40" s="1">
         <v>0.15</v>
@@ -2354,8 +2354,8 @@
       <c r="H42" s="1">
         <v>0.35</v>
       </c>
-      <c r="I42" t="str">
-        <v/>
+      <c r="I42" s="1">
+        <v>0.25</v>
       </c>
       <c r="J42" t="str">
         <v>Yes</v>
@@ -2401,8 +2401,8 @@
       <c r="H43" s="1">
         <v>0.35</v>
       </c>
-      <c r="I43" t="str">
-        <v/>
+      <c r="I43" s="1">
+        <v>0.25</v>
       </c>
       <c r="J43" t="str">
         <v>Yes</v>
@@ -2448,8 +2448,8 @@
       <c r="H44" s="1">
         <v>0.1</v>
       </c>
-      <c r="I44" t="str">
-        <v/>
+      <c r="I44" s="1">
+        <v>0.25</v>
       </c>
       <c r="J44" t="str">
         <v>Legacy</v>
@@ -2490,13 +2490,13 @@
         <v>20-25</v>
       </c>
       <c r="G45" t="str">
-        <v>12-15</v>
+        <v>11-13</v>
       </c>
       <c r="H45" s="1">
         <v>0.35</v>
       </c>
-      <c r="I45" t="str">
-        <v/>
+      <c r="I45" s="1">
+        <v>0.25</v>
       </c>
       <c r="J45" t="str">
         <v>Legacy</v>
@@ -2537,7 +2537,7 @@
         <v>20-25</v>
       </c>
       <c r="G46" t="str">
-        <v>12-15</v>
+        <v>11-13</v>
       </c>
       <c r="H46" s="1">
         <v>0.25</v>
@@ -2584,7 +2584,7 @@
         <v>19-24</v>
       </c>
       <c r="G47" t="str">
-        <v>12-15</v>
+        <v>11-13</v>
       </c>
       <c r="H47" s="1">
         <v>0.2</v>
@@ -2631,7 +2631,7 @@
         <v>19-24</v>
       </c>
       <c r="G48" t="str">
-        <v>12-15</v>
+        <v>11-13</v>
       </c>
       <c r="H48" s="1">
         <v>0.2</v>
@@ -2960,13 +2960,13 @@
         <v>24-29</v>
       </c>
       <c r="G55" t="str">
-        <v>15-18</v>
+        <v>14-17</v>
       </c>
       <c r="H55" s="1">
         <v>0.3</v>
       </c>
-      <c r="I55" t="str">
-        <v/>
+      <c r="I55" s="1">
+        <v>0.2</v>
       </c>
       <c r="J55" t="str">
         <v>Legacy</v>
@@ -3007,7 +3007,7 @@
         <v>24-29</v>
       </c>
       <c r="G56" t="str">
-        <v>15-18</v>
+        <v>14-17</v>
       </c>
       <c r="H56" s="1">
         <v>0.25</v>
@@ -3054,7 +3054,7 @@
         <v>24-29</v>
       </c>
       <c r="G57" t="str">
-        <v>15-18</v>
+        <v>14-17</v>
       </c>
       <c r="H57" s="1">
         <v>0.25</v>
@@ -3101,13 +3101,13 @@
         <v>23-28</v>
       </c>
       <c r="G58" t="str">
-        <v>15-18</v>
+        <v>14-17</v>
       </c>
       <c r="H58" s="1">
         <v>0.1</v>
       </c>
-      <c r="I58" t="str">
-        <v/>
+      <c r="I58" s="1">
+        <v>0.2</v>
       </c>
       <c r="J58" t="str">
         <v>Yes</v>
@@ -3148,13 +3148,13 @@
         <v>26-30</v>
       </c>
       <c r="G59" t="str">
-        <v>15-18</v>
+        <v>14-17</v>
       </c>
       <c r="H59" s="1">
         <v>0.1</v>
       </c>
-      <c r="I59" t="str">
-        <v/>
+      <c r="I59" s="1">
+        <v>0.2</v>
       </c>
       <c r="J59" t="str">
         <v>Legacy</v>
@@ -3388,8 +3388,8 @@
       <c r="H64" s="1">
         <v>0.05</v>
       </c>
-      <c r="I64" t="str">
-        <v/>
+      <c r="I64" s="1">
+        <v>0.2</v>
       </c>
       <c r="J64" t="str">
         <v>Yes</v>
@@ -3712,13 +3712,13 @@
         <v>31-36</v>
       </c>
       <c r="G71" t="str">
-        <v>20-23</v>
+        <v>19-22</v>
       </c>
       <c r="H71" s="1">
         <v>0.3</v>
       </c>
-      <c r="I71" t="str">
-        <v/>
+      <c r="I71" s="1">
+        <v>0.2</v>
       </c>
       <c r="J71" t="str">
         <v>Yes</v>
@@ -3759,7 +3759,7 @@
         <v>31-36</v>
       </c>
       <c r="G72" t="str">
-        <v>20-23</v>
+        <v>19-22</v>
       </c>
       <c r="H72" s="1">
         <v>0.25</v>
@@ -3806,7 +3806,7 @@
         <v>30-35</v>
       </c>
       <c r="G73" t="str">
-        <v>20-23</v>
+        <v>19-22</v>
       </c>
       <c r="H73" s="1">
         <v>0.15</v>
@@ -3853,7 +3853,7 @@
         <v>31-36</v>
       </c>
       <c r="G74" t="str">
-        <v>20-23</v>
+        <v>19-22</v>
       </c>
       <c r="H74" s="1">
         <v>0.2</v>
@@ -3900,13 +3900,13 @@
         <v>32-37</v>
       </c>
       <c r="G75" t="str">
-        <v>20-23</v>
+        <v>19-22</v>
       </c>
       <c r="H75" s="1">
         <v>0.1</v>
       </c>
-      <c r="I75" t="str">
-        <v/>
+      <c r="I75" s="1">
+        <v>0.2</v>
       </c>
       <c r="J75" t="str">
         <v>Legacy</v>
@@ -4229,7 +4229,7 @@
         <v>36-41</v>
       </c>
       <c r="G82" t="str">
-        <v>23-26</v>
+        <v>22-25</v>
       </c>
       <c r="H82" s="1">
         <v>0.2</v>
@@ -4276,7 +4276,7 @@
         <v>36-41</v>
       </c>
       <c r="G83" t="str">
-        <v>23-26</v>
+        <v>22-25</v>
       </c>
       <c r="H83" s="1">
         <v>0.15</v>
@@ -4323,7 +4323,7 @@
         <v>36-41</v>
       </c>
       <c r="G84" t="str">
-        <v>23-26</v>
+        <v>22-25</v>
       </c>
       <c r="H84" s="1">
         <v>0.15</v>
@@ -4370,7 +4370,7 @@
         <v>36-41</v>
       </c>
       <c r="G85" t="str">
-        <v>23-26</v>
+        <v>22-25</v>
       </c>
       <c r="H85" s="1">
         <v>0.15</v>
@@ -4417,7 +4417,7 @@
         <v>36-41</v>
       </c>
       <c r="G86" t="str">
-        <v>23-26</v>
+        <v>22-25</v>
       </c>
       <c r="H86" s="1">
         <v>0.15</v>
@@ -4464,7 +4464,7 @@
         <v>37-42</v>
       </c>
       <c r="G87" t="str">
-        <v>23-26</v>
+        <v>22-25</v>
       </c>
       <c r="H87" s="1">
         <v>0.1</v>
@@ -4511,7 +4511,7 @@
         <v>37-42</v>
       </c>
       <c r="G88" t="str">
-        <v>23-26</v>
+        <v>22-25</v>
       </c>
       <c r="H88" s="1">
         <v>0.1</v>
@@ -4840,7 +4840,7 @@
         <v>40-45</v>
       </c>
       <c r="G95" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H95" s="1">
         <v>0.2</v>
@@ -4887,7 +4887,7 @@
         <v>40-45</v>
       </c>
       <c r="G96" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H96" s="1">
         <v>0.2</v>
@@ -4934,7 +4934,7 @@
         <v>42-47</v>
       </c>
       <c r="G97" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H97" s="1">
         <v>0.15</v>
@@ -4981,7 +4981,7 @@
         <v>42-47</v>
       </c>
       <c r="G98" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H98" s="1">
         <v>0.15</v>
@@ -5028,7 +5028,7 @@
         <v>42-47</v>
       </c>
       <c r="G99" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H99" s="1">
         <v>0.1</v>
@@ -5075,7 +5075,7 @@
         <v>42-47</v>
       </c>
       <c r="G100" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H100" s="1">
         <v>0.1</v>
@@ -5122,7 +5122,7 @@
         <v>43-48</v>
       </c>
       <c r="G101" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H101" s="1">
         <v>0.1</v>
@@ -5174,8 +5174,8 @@
       <c r="H102" s="1">
         <v>0.35</v>
       </c>
-      <c r="I102" t="str">
-        <v/>
+      <c r="I102" s="1">
+        <v>0.25</v>
       </c>
       <c r="J102" t="str">
         <v/>
@@ -5315,8 +5315,8 @@
       <c r="H105" s="1">
         <v>0.1</v>
       </c>
-      <c r="I105" t="str">
-        <v/>
+      <c r="I105" s="1">
+        <v>0.25</v>
       </c>
       <c r="J105" t="str">
         <v/>
@@ -5639,7 +5639,7 @@
         <v>58-64</v>
       </c>
       <c r="G112" t="str">
-        <v>31-35</v>
+        <v>30-33</v>
       </c>
       <c r="H112" s="1">
         <v>0.19</v>
@@ -5686,7 +5686,7 @@
         <v>58-64</v>
       </c>
       <c r="G113" t="str">
-        <v>31-35</v>
+        <v>30-33</v>
       </c>
       <c r="H113" s="1">
         <v>0.19</v>
@@ -5733,7 +5733,7 @@
         <v>57-63</v>
       </c>
       <c r="G114" t="str">
-        <v>31-35</v>
+        <v>30-33</v>
       </c>
       <c r="H114" s="1">
         <v>0.15</v>
@@ -5780,7 +5780,7 @@
         <v>58-64</v>
       </c>
       <c r="G115" t="str">
-        <v>31-35</v>
+        <v>30-33</v>
       </c>
       <c r="H115" s="1">
         <v>0.23</v>
@@ -5827,7 +5827,7 @@
         <v>57-64</v>
       </c>
       <c r="G116" t="str">
-        <v>31-35</v>
+        <v>30-33</v>
       </c>
       <c r="H116" s="1">
         <v>0.07</v>
@@ -5874,7 +5874,7 @@
         <v>57-64</v>
       </c>
       <c r="G117" t="str">
-        <v>31-35</v>
+        <v>30-33</v>
       </c>
       <c r="H117" s="1">
         <v>0.08</v>
@@ -5921,7 +5921,7 @@
         <v>57-64</v>
       </c>
       <c r="G118" t="str">
-        <v>31-35</v>
+        <v>30-33</v>
       </c>
       <c r="H118" s="1">
         <v>0.09</v>
@@ -5968,13 +5968,13 @@
         <v>62-68</v>
       </c>
       <c r="G119" t="str">
-        <v>32-36</v>
+        <v>32-35</v>
       </c>
       <c r="H119" s="1">
         <v>0.3</v>
       </c>
-      <c r="I119" t="str">
-        <v/>
+      <c r="I119" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J119" t="str">
         <v/>
@@ -6015,7 +6015,7 @@
         <v>63-69</v>
       </c>
       <c r="G120" t="str">
-        <v>32-36</v>
+        <v>32-35</v>
       </c>
       <c r="H120" s="1">
         <v>0.25</v>
@@ -6062,7 +6062,7 @@
         <v>62-68</v>
       </c>
       <c r="G121" t="str">
-        <v>32-36</v>
+        <v>32-35</v>
       </c>
       <c r="H121" s="1">
         <v>0.2</v>
@@ -6109,7 +6109,7 @@
         <v>64-70</v>
       </c>
       <c r="G122" t="str">
-        <v>32-36</v>
+        <v>32-35</v>
       </c>
       <c r="H122" s="1">
         <v>0.1</v>
@@ -6156,7 +6156,7 @@
         <v>64-70</v>
       </c>
       <c r="G123" t="str">
-        <v>32-36</v>
+        <v>32-35</v>
       </c>
       <c r="H123" s="1">
         <v>0.1</v>
@@ -6203,13 +6203,13 @@
         <v>65-71</v>
       </c>
       <c r="G124" t="str">
-        <v>32-36</v>
+        <v>32-35</v>
       </c>
       <c r="H124" s="1">
         <v>0.05</v>
       </c>
-      <c r="I124" t="str">
-        <v/>
+      <c r="I124" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J124" t="str">
         <v/>
@@ -6250,7 +6250,7 @@
         <v>64-70</v>
       </c>
       <c r="G125" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H125" s="1">
         <v>0.25</v>
@@ -6297,7 +6297,7 @@
         <v>63-69</v>
       </c>
       <c r="G126" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H126" s="1">
         <v>0.15</v>
@@ -6344,7 +6344,7 @@
         <v>64-70</v>
       </c>
       <c r="G127" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H127" s="1">
         <v>0.15</v>
@@ -6391,7 +6391,7 @@
         <v>68-74</v>
       </c>
       <c r="G128" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H128" s="1">
         <v>0.1</v>
@@ -6438,7 +6438,7 @@
         <v>65-71</v>
       </c>
       <c r="G129" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H129" s="1">
         <v>0.1</v>
@@ -6485,7 +6485,7 @@
         <v>64-70</v>
       </c>
       <c r="G130" t="str">
-        <v>34-38</v>
+        <v>33-36</v>
       </c>
       <c r="H130" s="1">
         <v>0.25</v>
@@ -6532,7 +6532,7 @@
         <v>68-74</v>
       </c>
       <c r="G131" t="str">
-        <v>35-39</v>
+        <v>35-38</v>
       </c>
       <c r="H131" s="1">
         <v>0.4</v>
@@ -6579,7 +6579,7 @@
         <v>66-72</v>
       </c>
       <c r="G132" t="str">
-        <v>35-39</v>
+        <v>35-38</v>
       </c>
       <c r="H132" s="1">
         <v>0.35</v>
@@ -6626,7 +6626,7 @@
         <v>70-76</v>
       </c>
       <c r="G133" t="str">
-        <v>35-39</v>
+        <v>35-38</v>
       </c>
       <c r="H133" s="1">
         <v>0.25</v>
@@ -6673,7 +6673,7 @@
         <v>18-22</v>
       </c>
       <c r="G134" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H134" s="1">
         <v>0.25</v>
@@ -6720,7 +6720,7 @@
         <v>18-22</v>
       </c>
       <c r="G135" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H135" s="1">
         <v>0.25</v>
@@ -6767,7 +6767,7 @@
         <v>18-22</v>
       </c>
       <c r="G136" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H136" s="1">
         <v>0.2</v>
@@ -6814,7 +6814,7 @@
         <v>18-22</v>
       </c>
       <c r="G137" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H137" s="1">
         <v>0.15</v>
@@ -6861,7 +6861,7 @@
         <v>20-24</v>
       </c>
       <c r="G138" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H138" s="1">
         <v>0.15</v>
@@ -6908,13 +6908,13 @@
         <v>33-38</v>
       </c>
       <c r="G139" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H139" s="1">
         <v>0.35</v>
       </c>
-      <c r="I139" t="str">
-        <v/>
+      <c r="I139" s="1">
+        <v>0.25</v>
       </c>
       <c r="J139" t="str">
         <v>Legacy</v>
@@ -6955,7 +6955,7 @@
         <v>32-37</v>
       </c>
       <c r="G140" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H140" s="1">
         <v>0.25</v>
@@ -7002,7 +7002,7 @@
         <v>33-38</v>
       </c>
       <c r="G141" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H141" s="1">
         <v>0.25</v>
@@ -7049,13 +7049,13 @@
         <v>36-40</v>
       </c>
       <c r="G142" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H142" s="1">
         <v>0.15</v>
       </c>
-      <c r="I142" t="str">
-        <v/>
+      <c r="I142" s="1">
+        <v>0.25</v>
       </c>
       <c r="J142" t="str">
         <v>Legacy</v>
@@ -7096,13 +7096,13 @@
         <v>48-55</v>
       </c>
       <c r="G143" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H143" s="1">
         <v>0.95</v>
       </c>
-      <c r="I143" t="str">
-        <v/>
+      <c r="I143" s="1">
+        <v>0.5</v>
       </c>
       <c r="J143" t="str">
         <v>Legacy</v>
@@ -7143,13 +7143,13 @@
         <v>55-60</v>
       </c>
       <c r="G144" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H144" s="1">
         <v>0.05</v>
       </c>
-      <c r="I144" t="str">
-        <v/>
+      <c r="I144" s="1">
+        <v>0.5</v>
       </c>
       <c r="J144" t="str">
         <v>Legacy</v>
@@ -7190,7 +7190,7 @@
         <v>74-80</v>
       </c>
       <c r="G145" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H145" s="1">
         <v>0.25</v>
@@ -7237,7 +7237,7 @@
         <v>74-80</v>
       </c>
       <c r="G146" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H146" s="1">
         <v>0.2</v>
@@ -7284,7 +7284,7 @@
         <v>73-79</v>
       </c>
       <c r="G147" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H147" s="1">
         <v>0.2</v>
@@ -7331,7 +7331,7 @@
         <v>74-80</v>
       </c>
       <c r="G148" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H148" s="1">
         <v>0.15</v>
@@ -7378,7 +7378,7 @@
         <v>75-81</v>
       </c>
       <c r="G149" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H149" s="1">
         <v>0.1</v>
@@ -7425,7 +7425,7 @@
         <v>75-82</v>
       </c>
       <c r="G150" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H150" s="1">
         <v>0.1</v>
@@ -7472,13 +7472,13 @@
         <v>77-82</v>
       </c>
       <c r="G151" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H151" s="1">
         <v>0.3</v>
       </c>
-      <c r="I151" t="str">
-        <v/>
+      <c r="I151" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J151" t="str">
         <v>Yes</v>
@@ -7519,7 +7519,7 @@
         <v>77-82</v>
       </c>
       <c r="G152" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H152" s="1">
         <v>0.2</v>
@@ -7566,7 +7566,7 @@
         <v>77-82</v>
       </c>
       <c r="G153" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H153" s="1">
         <v>0.2</v>
@@ -7613,7 +7613,7 @@
         <v>79-83</v>
       </c>
       <c r="G154" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H154" s="1">
         <v>0.15</v>
@@ -7660,7 +7660,7 @@
         <v>79-83</v>
       </c>
       <c r="G155" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H155" s="1">
         <v>0.1</v>
@@ -7707,13 +7707,13 @@
         <v>85-85</v>
       </c>
       <c r="G156" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H156" s="1">
         <v>0.05</v>
       </c>
-      <c r="I156" t="str">
-        <v/>
+      <c r="I156" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J156" t="str">
         <v>Yes</v>
@@ -7754,7 +7754,7 @@
         <v>50-50</v>
       </c>
       <c r="G157" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H157" s="1">
         <v>0.3333333333333333</v>
@@ -7801,7 +7801,7 @@
         <v>50-50</v>
       </c>
       <c r="G158" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H158" s="1">
         <v>0.3333333333333333</v>
@@ -7848,7 +7848,7 @@
         <v>50-50</v>
       </c>
       <c r="G159" t="str">
-        <v>35-39</v>
+        <v>96-104</v>
       </c>
       <c r="H159" s="1">
         <v>0.3333333333333333</v>
@@ -7895,7 +7895,7 @@
         <v>72-76</v>
       </c>
       <c r="G160" t="str">
-        <v>37-41</v>
+        <v>37-40</v>
       </c>
       <c r="H160" s="1">
         <v>0.23</v>
@@ -7942,13 +7942,13 @@
         <v>72-76</v>
       </c>
       <c r="G161" t="str">
-        <v>37-41</v>
+        <v>37-40</v>
       </c>
       <c r="H161" s="1">
         <v>0.24</v>
       </c>
-      <c r="I161" t="str">
-        <v/>
+      <c r="I161" s="1">
+        <v>0.14285714285714285</v>
       </c>
       <c r="J161" t="str">
         <v>Yes</v>
@@ -7989,7 +7989,7 @@
         <v>74-78</v>
       </c>
       <c r="G162" t="str">
-        <v>37-41</v>
+        <v>37-40</v>
       </c>
       <c r="H162" s="1">
         <v>0.14</v>
@@ -8036,7 +8036,7 @@
         <v>74-78</v>
       </c>
       <c r="G163" t="str">
-        <v>37-41</v>
+        <v>37-40</v>
       </c>
       <c r="H163" s="1">
         <v>0.14</v>
@@ -8083,7 +8083,7 @@
         <v>75-78</v>
       </c>
       <c r="G164" t="str">
-        <v>37-41</v>
+        <v>37-40</v>
       </c>
       <c r="H164" s="1">
         <v>0.1</v>
@@ -8130,7 +8130,7 @@
         <v>75-78</v>
       </c>
       <c r="G165" t="str">
-        <v>37-41</v>
+        <v>37-40</v>
       </c>
       <c r="H165" s="1">
         <v>0.1</v>
@@ -8177,7 +8177,7 @@
         <v>72-78</v>
       </c>
       <c r="G166" t="str">
-        <v>37-41</v>
+        <v>37-40</v>
       </c>
       <c r="H166" s="1">
         <v>0.05</v>
@@ -8224,7 +8224,7 @@
         <v>76-80</v>
       </c>
       <c r="G167" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H167" s="1">
         <v>0.22</v>
@@ -8271,7 +8271,7 @@
         <v>76-81</v>
       </c>
       <c r="G168" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H168" s="1">
         <v>0.23</v>
@@ -8318,7 +8318,7 @@
         <v>78-82</v>
       </c>
       <c r="G169" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H169" s="1">
         <v>0.18</v>
@@ -8365,7 +8365,7 @@
         <v>77-81</v>
       </c>
       <c r="G170" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H170" s="1">
         <v>0.14</v>
@@ -8412,7 +8412,7 @@
         <v>78-82</v>
       </c>
       <c r="G171" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H171" s="1">
         <v>0.14</v>
@@ -8459,7 +8459,7 @@
         <v>76-82</v>
       </c>
       <c r="G172" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H172" s="1">
         <v>0.09</v>
@@ -8506,7 +8506,7 @@
         <v>79-83</v>
       </c>
       <c r="G173" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H173" s="1">
         <v>0.3</v>
@@ -8553,7 +8553,7 @@
         <v>81-85</v>
       </c>
       <c r="G174" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H174" s="1">
         <v>0.25</v>
@@ -8600,7 +8600,7 @@
         <v>81-85</v>
       </c>
       <c r="G175" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H175" s="1">
         <v>0.25</v>
@@ -8647,7 +8647,7 @@
         <v>81-85</v>
       </c>
       <c r="G176" t="str">
-        <v>38-42</v>
+        <v>38-41</v>
       </c>
       <c r="H176" s="1">
         <v>0.2</v>
@@ -8694,7 +8694,7 @@
         <v>82-86</v>
       </c>
       <c r="G177" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H177" s="1">
         <v>0.4</v>
@@ -8741,7 +8741,7 @@
         <v>83-87</v>
       </c>
       <c r="G178" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H178" s="1">
         <v>0.3</v>
@@ -8788,7 +8788,7 @@
         <v>83-87</v>
       </c>
       <c r="G179" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H179" s="1">
         <v>0.3</v>
@@ -8835,13 +8835,13 @@
         <v>82-86</v>
       </c>
       <c r="G180" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H180" s="1">
         <v>0.9</v>
       </c>
-      <c r="I180" t="str">
-        <v/>
+      <c r="I180" s="1">
+        <v>0.5</v>
       </c>
       <c r="J180" t="str">
         <v>Yes</v>
@@ -8882,13 +8882,13 @@
         <v>85-89</v>
       </c>
       <c r="G181" t="str">
-        <v>40-45</v>
+        <v>40-44</v>
       </c>
       <c r="H181" s="1">
         <v>0.1</v>
       </c>
-      <c r="I181" t="str">
-        <v/>
+      <c r="I181" s="1">
+        <v>0.5</v>
       </c>
       <c r="J181" t="str">
         <v>Yes</v>
@@ -8929,7 +8929,7 @@
         <v>84-88</v>
       </c>
       <c r="G182" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H182" s="1">
         <v>0.25</v>
@@ -8976,7 +8976,7 @@
         <v>84-88</v>
       </c>
       <c r="G183" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H183" s="1">
         <v>0.25</v>
@@ -9023,7 +9023,7 @@
         <v>85-89</v>
       </c>
       <c r="G184" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H184" s="1">
         <v>0.2</v>
@@ -9070,7 +9070,7 @@
         <v>86-89</v>
       </c>
       <c r="G185" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H185" s="1">
         <v>0.15</v>
@@ -9117,7 +9117,7 @@
         <v>86-89</v>
       </c>
       <c r="G186" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H186" s="1">
         <v>0.1</v>
@@ -9164,13 +9164,13 @@
         <v>88-89</v>
       </c>
       <c r="G187" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H187" s="1">
         <v>0.05</v>
       </c>
-      <c r="I187" t="str">
-        <v/>
+      <c r="I187" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J187" t="str">
         <v>Legacy</v>
@@ -9211,7 +9211,7 @@
         <v>86-90</v>
       </c>
       <c r="G188" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H188" s="1">
         <v>0.1</v>
@@ -9258,7 +9258,7 @@
         <v>86-90</v>
       </c>
       <c r="G189" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H189" s="1">
         <v>0.1</v>
@@ -9305,7 +9305,7 @@
         <v>87-90</v>
       </c>
       <c r="G190" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H190" s="1">
         <v>0.15</v>
@@ -9352,7 +9352,7 @@
         <v>87-91</v>
       </c>
       <c r="G191" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H191" s="1">
         <v>0.2</v>
@@ -9399,7 +9399,7 @@
         <v>87-90</v>
       </c>
       <c r="G192" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H192" s="1">
         <v>0.2</v>
@@ -9446,7 +9446,7 @@
         <v>88-91</v>
       </c>
       <c r="G193" t="str">
-        <v>41-46</v>
+        <v>41-45</v>
       </c>
       <c r="H193" s="1">
         <v>0.25</v>
@@ -9493,7 +9493,7 @@
         <v>39-44</v>
       </c>
       <c r="G194" t="str">
-        <v>43-48</v>
+        <v>43-47</v>
       </c>
       <c r="H194" s="1">
         <v>0.25</v>
@@ -9540,7 +9540,7 @@
         <v>39-44</v>
       </c>
       <c r="G195" t="str">
-        <v>43-48</v>
+        <v>43-47</v>
       </c>
       <c r="H195" s="1">
         <v>0.25</v>
@@ -9587,7 +9587,7 @@
         <v>40-45</v>
       </c>
       <c r="G196" t="str">
-        <v>43-48</v>
+        <v>43-47</v>
       </c>
       <c r="H196" s="1">
         <v>0.15</v>
@@ -9634,7 +9634,7 @@
         <v>40-45</v>
       </c>
       <c r="G197" t="str">
-        <v>43-48</v>
+        <v>43-47</v>
       </c>
       <c r="H197" s="1">
         <v>0.15</v>
@@ -9681,7 +9681,7 @@
         <v>39-44</v>
       </c>
       <c r="G198" t="str">
-        <v>43-48</v>
+        <v>43-47</v>
       </c>
       <c r="H198" s="1">
         <v>0.1</v>
@@ -9728,7 +9728,7 @@
         <v>39-44</v>
       </c>
       <c r="G199" t="str">
-        <v>43-48</v>
+        <v>43-47</v>
       </c>
       <c r="H199" s="1">
         <v>0.1</v>
@@ -9775,7 +9775,7 @@
         <v>88-92</v>
       </c>
       <c r="G200" t="str">
-        <v>43-48</v>
+        <v>43-47</v>
       </c>
       <c r="H200" s="1">
         <v>0.25</v>
@@ -9822,7 +9822,7 @@
         <v>88-92</v>
       </c>
       <c r="G201" t="str">
-        <v>43-48</v>
+        <v>43-47</v>
       </c>
       <c r="H201" s="1">
         <v>0.25</v>
@@ -9869,7 +9869,7 @@
         <v>90-93</v>
       </c>
       <c r="G202" t="str">
-        <v>43-48</v>
+        <v>43-47</v>
       </c>
       <c r="H202" s="1">
         <v>0.2</v>
@@ -9916,7 +9916,7 @@
         <v>90-93</v>
       </c>
       <c r="G203" t="str">
-        <v>43-48</v>
+        <v>43-47</v>
       </c>
       <c r="H203" s="1">
         <v>0.2</v>
@@ -9963,13 +9963,13 @@
         <v>92-93</v>
       </c>
       <c r="G204" t="str">
-        <v>43-48</v>
+        <v>43-47</v>
       </c>
       <c r="H204" s="1">
         <v>0.1</v>
       </c>
-      <c r="I204" t="str">
-        <v/>
+      <c r="I204" s="1">
+        <v>0.2</v>
       </c>
       <c r="J204" t="str">
         <v>Yes</v>
@@ -10010,7 +10010,7 @@
         <v>90-94</v>
       </c>
       <c r="G205" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H205" s="1">
         <v>0.25</v>
@@ -10057,7 +10057,7 @@
         <v>90-94</v>
       </c>
       <c r="G206" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H206" s="1">
         <v>0.25</v>
@@ -10104,7 +10104,7 @@
         <v>91-94</v>
       </c>
       <c r="G207" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H207" s="1">
         <v>0.15</v>
@@ -10151,7 +10151,7 @@
         <v>91-94</v>
       </c>
       <c r="G208" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H208" s="1">
         <v>0.15</v>
@@ -10198,7 +10198,7 @@
         <v>92-94</v>
       </c>
       <c r="G209" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H209" s="1">
         <v>0.1</v>
@@ -10245,7 +10245,7 @@
         <v>92-94</v>
       </c>
       <c r="G210" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H210" s="1">
         <v>0.1</v>
@@ -10292,13 +10292,13 @@
         <v>91-93</v>
       </c>
       <c r="G211" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H211" s="1">
         <v>0.3</v>
       </c>
-      <c r="I211" t="str">
-        <v/>
+      <c r="I211" s="1">
+        <v>0.2</v>
       </c>
       <c r="J211" t="str">
         <v/>
@@ -10339,13 +10339,13 @@
         <v>91-93</v>
       </c>
       <c r="G212" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H212" s="1">
         <v>0.3</v>
       </c>
-      <c r="I212" t="str">
-        <v/>
+      <c r="I212" s="1">
+        <v>0.2</v>
       </c>
       <c r="J212" t="str">
         <v/>
@@ -10386,13 +10386,13 @@
         <v>94-95</v>
       </c>
       <c r="G213" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H213" s="1">
         <v>0.1</v>
       </c>
-      <c r="I213" t="str">
-        <v/>
+      <c r="I213" s="1">
+        <v>0.2</v>
       </c>
       <c r="J213" t="str">
         <v/>
@@ -10433,7 +10433,7 @@
         <v>92-94</v>
       </c>
       <c r="G214" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H214" s="1">
         <v>0.15</v>
@@ -10480,7 +10480,7 @@
         <v>92-94</v>
       </c>
       <c r="G215" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H215" s="1">
         <v>0.15</v>
@@ -10527,7 +10527,7 @@
         <v>91-95</v>
       </c>
       <c r="G216" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H216" s="1">
         <v>0.2</v>
@@ -10574,7 +10574,7 @@
         <v>91-95</v>
       </c>
       <c r="G217" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H217" s="1">
         <v>0.2</v>
@@ -10621,7 +10621,7 @@
         <v>91-95</v>
       </c>
       <c r="G218" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H218" s="1">
         <v>0.2</v>
@@ -10668,7 +10668,7 @@
         <v>92-95</v>
       </c>
       <c r="G219" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H219" s="1">
         <v>0.15</v>
@@ -10715,7 +10715,7 @@
         <v>93-95</v>
       </c>
       <c r="G220" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H220" s="1">
         <v>0.15</v>
@@ -10762,7 +10762,7 @@
         <v>93-95</v>
       </c>
       <c r="G221" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H221" s="1">
         <v>0.05</v>
@@ -10809,7 +10809,7 @@
         <v>93-95</v>
       </c>
       <c r="G222" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H222" s="1">
         <v>0.05</v>
@@ -10856,7 +10856,7 @@
         <v>80-85</v>
       </c>
       <c r="G223" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H223" s="1">
         <v>0.16670000000000001</v>
@@ -10903,7 +10903,7 @@
         <v>80-85</v>
       </c>
       <c r="G224" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H224" s="1">
         <v>0.16670000000000001</v>
@@ -10950,7 +10950,7 @@
         <v>80-85</v>
       </c>
       <c r="G225" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H225" s="1">
         <v>0.16670000000000001</v>
@@ -10997,7 +10997,7 @@
         <v>80-85</v>
       </c>
       <c r="G226" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H226" s="1">
         <v>0.16670000000000001</v>
@@ -11044,7 +11044,7 @@
         <v>80-85</v>
       </c>
       <c r="G227" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H227" s="1">
         <v>0.16670000000000001</v>
@@ -11091,7 +11091,7 @@
         <v>80-85</v>
       </c>
       <c r="G228" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H228" s="1">
         <v>0.16670000000000001</v>
@@ -11138,7 +11138,7 @@
         <v>84-89</v>
       </c>
       <c r="G229" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H229" s="1">
         <v>0.15</v>
@@ -11185,7 +11185,7 @@
         <v>84-89</v>
       </c>
       <c r="G230" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H230" s="1">
         <v>0.15</v>
@@ -11232,7 +11232,7 @@
         <v>84-89</v>
       </c>
       <c r="G231" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H231" s="1">
         <v>0.15</v>
@@ -11279,7 +11279,7 @@
         <v>84-89</v>
       </c>
       <c r="G232" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H232" s="1">
         <v>0.15</v>
@@ -11326,7 +11326,7 @@
         <v>84-89</v>
       </c>
       <c r="G233" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H233" s="1">
         <v>0.1</v>
@@ -11373,7 +11373,7 @@
         <v>84-89</v>
       </c>
       <c r="G234" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H234" s="1">
         <v>0.1</v>
@@ -11420,7 +11420,7 @@
         <v>84-89</v>
       </c>
       <c r="G235" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H235" s="1">
         <v>0.1</v>
@@ -11467,7 +11467,7 @@
         <v>84-89</v>
       </c>
       <c r="G236" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H236" s="1">
         <v>0.1</v>
@@ -11514,7 +11514,7 @@
         <v>84-89</v>
       </c>
       <c r="G237" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H237" s="1">
         <v>0.3</v>
@@ -11561,7 +11561,7 @@
         <v>84-89</v>
       </c>
       <c r="G238" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H238" s="1">
         <v>0.3</v>
@@ -11608,7 +11608,7 @@
         <v>84-89</v>
       </c>
       <c r="G239" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H239" s="1">
         <v>0.3</v>
@@ -11655,13 +11655,13 @@
         <v>85-90</v>
       </c>
       <c r="G240" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H240" s="1">
         <v>0.1</v>
       </c>
-      <c r="I240" t="str">
-        <v/>
+      <c r="I240" s="1">
+        <v>0.25</v>
       </c>
       <c r="J240" t="str">
         <v/>
@@ -11702,7 +11702,7 @@
         <v>85-90</v>
       </c>
       <c r="G241" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H241" s="1">
         <v>0.2</v>
@@ -11749,7 +11749,7 @@
         <v>86-91</v>
       </c>
       <c r="G242" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H242" s="1">
         <v>0.1</v>
@@ -11796,7 +11796,7 @@
         <v>86-91</v>
       </c>
       <c r="G243" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H243" s="1">
         <v>0.1</v>
@@ -11843,7 +11843,7 @@
         <v>86-91</v>
       </c>
       <c r="G244" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H244" s="1">
         <v>0.1</v>
@@ -11890,7 +11890,7 @@
         <v>86-91</v>
       </c>
       <c r="G245" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H245" s="1">
         <v>0.1</v>
@@ -11937,7 +11937,7 @@
         <v>86-91</v>
       </c>
       <c r="G246" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H246" s="1">
         <v>0.1</v>
@@ -11984,7 +11984,7 @@
         <v>86-91</v>
       </c>
       <c r="G247" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H247" s="1">
         <v>0.1</v>
@@ -12031,7 +12031,7 @@
         <v>86-91</v>
       </c>
       <c r="G248" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H248" s="1">
         <v>0.1</v>
@@ -12078,7 +12078,7 @@
         <v>86-91</v>
       </c>
       <c r="G249" t="str">
-        <v>45-50</v>
+        <v>44-48</v>
       </c>
       <c r="H249" s="1">
         <v>0.1</v>
@@ -12125,13 +12125,13 @@
         <v>88-92</v>
       </c>
       <c r="G250" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H250" s="1">
         <v>0.4</v>
       </c>
-      <c r="I250" t="str">
-        <v/>
+      <c r="I250" s="1">
+        <v>0.25</v>
       </c>
       <c r="J250" t="str">
         <v>Yes</v>
@@ -12172,7 +12172,7 @@
         <v>89-93</v>
       </c>
       <c r="G251" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H251" s="1">
         <v>0.2</v>
@@ -12219,7 +12219,7 @@
         <v>89-93</v>
       </c>
       <c r="G252" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H252" s="1">
         <v>0.2</v>
@@ -12266,7 +12266,7 @@
         <v>89-93</v>
       </c>
       <c r="G253" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H253" s="1">
         <v>0.2</v>
@@ -12313,7 +12313,7 @@
         <v>90-98</v>
       </c>
       <c r="G254" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H254" s="1">
         <v>0.17</v>
@@ -12360,7 +12360,7 @@
         <v>90-98</v>
       </c>
       <c r="G255" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H255" s="1">
         <v>0.17</v>
@@ -12407,7 +12407,7 @@
         <v>90-98</v>
       </c>
       <c r="G256" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H256" s="1">
         <v>0.17</v>
@@ -12454,7 +12454,7 @@
         <v>90-98</v>
       </c>
       <c r="G257" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H257" s="1">
         <v>0.17</v>
@@ -12501,7 +12501,7 @@
         <v>90-98</v>
       </c>
       <c r="G258" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H258" s="1">
         <v>0.17</v>
@@ -12548,7 +12548,7 @@
         <v>90-98</v>
       </c>
       <c r="G259" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H259" s="1">
         <v>0.17</v>
@@ -12595,7 +12595,7 @@
         <v>100-100</v>
       </c>
       <c r="G260" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H260" s="1">
         <v>0.2</v>
@@ -12642,7 +12642,7 @@
         <v>100-100</v>
       </c>
       <c r="G261" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H261" s="1">
         <v>0.2</v>
@@ -12689,7 +12689,7 @@
         <v>100-100</v>
       </c>
       <c r="G262" t="str">
-        <v>45-50</v>
+        <v>96-104</v>
       </c>
       <c r="H262" s="1">
         <v>0.2</v>
@@ -12736,7 +12736,7 @@
         <v>110-110</v>
       </c>
       <c r="G263" t="str">
-        <v>45-50</v>
+        <v>110-110</v>
       </c>
       <c r="H263" s="1">
         <v>0.2</v>
@@ -12783,7 +12783,7 @@
         <v>110-110</v>
       </c>
       <c r="G264" t="str">
-        <v>45-50</v>
+        <v>110-110</v>
       </c>
       <c r="H264" s="1">
         <v>0.2</v>
@@ -12830,7 +12830,7 @@
         <v>110-110</v>
       </c>
       <c r="G265" t="str">
-        <v>46-51</v>
+        <v>110-110</v>
       </c>
       <c r="H265" s="1">
         <v>0.2</v>
@@ -12877,7 +12877,7 @@
         <v>110-110</v>
       </c>
       <c r="G266" t="str">
-        <v>46-51</v>
+        <v>110-110</v>
       </c>
       <c r="H266" s="1">
         <v>0.2</v>
@@ -12924,7 +12924,7 @@
         <v>110-110</v>
       </c>
       <c r="G267" t="str">
-        <v>46-51</v>
+        <v>110-110</v>
       </c>
       <c r="H267" s="1">
         <v>0.2</v>
@@ -12971,7 +12971,7 @@
         <v>120-120</v>
       </c>
       <c r="G268" t="str">
-        <v>46-51</v>
+        <v>120-120</v>
       </c>
       <c r="H268" s="1">
         <v>0.13333333333333333</v>
@@ -13018,7 +13018,7 @@
         <v>120-120</v>
       </c>
       <c r="G269" t="str">
-        <v>46-51</v>
+        <v>120-120</v>
       </c>
       <c r="H269" s="1">
         <v>0.13333333333333333</v>
@@ -13065,7 +13065,7 @@
         <v>120-120</v>
       </c>
       <c r="G270" t="str">
-        <v>46-51</v>
+        <v>120-120</v>
       </c>
       <c r="H270" s="1">
         <v>0.13333333333333333</v>
@@ -13112,7 +13112,7 @@
         <v>91-95</v>
       </c>
       <c r="G271" t="str">
-        <v>46-51</v>
+        <v>46-50</v>
       </c>
       <c r="H271" s="1">
         <v>0.25</v>
@@ -13159,7 +13159,7 @@
         <v>91-95</v>
       </c>
       <c r="G272" t="str">
-        <v>46-51</v>
+        <v>46-50</v>
       </c>
       <c r="H272" s="1">
         <v>0.25</v>
@@ -13206,7 +13206,7 @@
         <v>91-95</v>
       </c>
       <c r="G273" t="str">
-        <v>46-51</v>
+        <v>46-50</v>
       </c>
       <c r="H273" s="1">
         <v>0.25</v>
@@ -13253,7 +13253,7 @@
         <v>91-95</v>
       </c>
       <c r="G274" t="str">
-        <v>46-51</v>
+        <v>46-50</v>
       </c>
       <c r="H274" s="1">
         <v>0.25</v>

--- a/2_Johto_Data.xlsx
+++ b/2_Johto_Data.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O274"/>
+  <dimension ref="A1:O293"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -521,8 +521,8 @@
       <c r="H3" s="1">
         <v>0.25</v>
       </c>
-      <c r="I3" t="str">
-        <v/>
+      <c r="I3" s="1">
+        <v>0.2</v>
       </c>
       <c r="J3" t="str">
         <v>Yes</v>
@@ -548,7 +548,7 @@
         <v/>
       </c>
       <c r="B4" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="C4" t="str">
         <v>Route 29</v>
@@ -568,8 +568,8 @@
       <c r="H4" s="1">
         <v>0.2</v>
       </c>
-      <c r="I4" t="str">
-        <v/>
+      <c r="I4" s="1">
+        <v>0.2</v>
       </c>
       <c r="J4" t="str">
         <v>Yes</v>
@@ -581,10 +581,10 @@
         <v>Yes</v>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>Route 30</v>
       </c>
       <c r="N4" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 29","count":25}}</v>
       </c>
       <c r="O4" t="str">
         <v/>
@@ -595,7 +595,7 @@
         <v/>
       </c>
       <c r="B5" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="C5" t="str">
         <v>Route 29</v>
@@ -615,8 +615,8 @@
       <c r="H5" s="1">
         <v>0.25</v>
       </c>
-      <c r="I5" t="str">
-        <v/>
+      <c r="I5" s="1">
+        <v>0.2</v>
       </c>
       <c r="J5" t="str">
         <v>Yes</v>
@@ -628,10 +628,10 @@
         <v>Yes</v>
       </c>
       <c r="M5" t="str">
-        <v/>
+        <v>Route 30</v>
       </c>
       <c r="N5" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 29","count":25}}</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -642,7 +642,7 @@
         <v/>
       </c>
       <c r="B6" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="C6" t="str">
         <v>Route 29</v>
@@ -675,10 +675,10 @@
         <v>Yes</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>Route 30</v>
       </c>
       <c r="N6" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 29","count":25}}</v>
       </c>
       <c r="O6" t="str">
         <v/>
@@ -689,7 +689,7 @@
         <v/>
       </c>
       <c r="B7" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="C7" t="str">
         <v>Route 29</v>
@@ -722,10 +722,10 @@
         <v>Yes</v>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>Route 30</v>
       </c>
       <c r="N7" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 29","count":25}}</v>
       </c>
       <c r="O7" t="str">
         <v/>
@@ -780,10 +780,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="B9" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="C9" t="str">
         <v>Route 30</v>
@@ -816,10 +816,10 @@
         <v>Yes</v>
       </c>
       <c r="M9" t="str">
-        <v/>
+        <v>Route 31</v>
       </c>
       <c r="N9" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Ledyba","count":1},{"species":"Spinarak","count":1}]}</v>
       </c>
       <c r="O9" t="str">
         <v/>
@@ -827,10 +827,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="B10" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="C10" t="str">
         <v>Route 30</v>
@@ -850,8 +850,8 @@
       <c r="H10" s="1">
         <v>0.15</v>
       </c>
-      <c r="I10" t="str">
-        <v/>
+      <c r="I10" s="1">
+        <v>0.2</v>
       </c>
       <c r="J10" t="str">
         <v>Yes</v>
@@ -863,10 +863,10 @@
         <v>Yes</v>
       </c>
       <c r="M10" t="str">
-        <v/>
+        <v>Route 31</v>
       </c>
       <c r="N10" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Ledyba","count":1},{"species":"Spinarak","count":1}]}</v>
       </c>
       <c r="O10" t="str">
         <v/>
@@ -874,10 +874,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="B11" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="C11" t="str">
         <v>Route 30</v>
@@ -897,8 +897,8 @@
       <c r="H11" s="1">
         <v>0.15</v>
       </c>
-      <c r="I11" t="str">
-        <v/>
+      <c r="I11" s="1">
+        <v>0.2</v>
       </c>
       <c r="J11" t="str">
         <v>Yes</v>
@@ -910,10 +910,10 @@
         <v>Yes</v>
       </c>
       <c r="M11" t="str">
-        <v/>
+        <v>Route 31</v>
       </c>
       <c r="N11" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Ledyba","count":1},{"species":"Spinarak","count":1}]}</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -921,10 +921,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="B12" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="C12" t="str">
         <v>Route 30</v>
@@ -957,10 +957,10 @@
         <v>Yes</v>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>Route 31</v>
       </c>
       <c r="N12" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Ledyba","count":1},{"species":"Spinarak","count":1}]}</v>
       </c>
       <c r="O12" t="str">
         <v/>
@@ -986,13 +986,13 @@
         <v>5-8</v>
       </c>
       <c r="G13" t="str">
-        <v>1-3</v>
+        <v>2-4</v>
       </c>
       <c r="H13" s="1">
         <v>0.5</v>
       </c>
       <c r="I13" s="1">
-        <v>0.3333333333333333</v>
+        <v>0.33</v>
       </c>
       <c r="J13" t="str">
         <v>Yes</v>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B14" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C14" t="str">
         <v>Route 31</v>
@@ -1033,13 +1033,13 @@
         <v>5-8</v>
       </c>
       <c r="G14" t="str">
-        <v>1-3</v>
+        <v>2-4</v>
       </c>
       <c r="H14" s="1">
         <v>0.25</v>
       </c>
-      <c r="I14" t="str">
-        <v/>
+      <c r="I14" s="1">
+        <v>0.33</v>
       </c>
       <c r="J14" t="str">
         <v>Yes</v>
@@ -1051,10 +1051,10 @@
         <v>Yes</v>
       </c>
       <c r="M14" t="str">
-        <v/>
+        <v>Violet Gym</v>
       </c>
       <c r="N14" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Bellsprout","count":10}}</v>
       </c>
       <c r="O14" t="str">
         <v/>
@@ -1062,10 +1062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B15" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C15" t="str">
         <v>Route 31</v>
@@ -1080,13 +1080,13 @@
         <v>5-8</v>
       </c>
       <c r="G15" t="str">
-        <v>1-3</v>
+        <v>2-4</v>
       </c>
       <c r="H15" s="1">
         <v>0.25</v>
       </c>
-      <c r="I15" t="str">
-        <v/>
+      <c r="I15" s="1">
+        <v>0.34</v>
       </c>
       <c r="J15" t="str">
         <v>Yes</v>
@@ -1098,10 +1098,10 @@
         <v>Yes</v>
       </c>
       <c r="M15" t="str">
-        <v/>
+        <v>Violet Gym</v>
       </c>
       <c r="N15" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Bellsprout","count":10}}</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -1127,7 +1127,7 @@
         <v>7-11</v>
       </c>
       <c r="G16" t="str">
-        <v>2-4</v>
+        <v>4-6</v>
       </c>
       <c r="H16" s="1">
         <v>0.2</v>
@@ -1156,10 +1156,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B17" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="C17" t="str">
         <v>Route 32</v>
@@ -1174,7 +1174,7 @@
         <v>7-11</v>
       </c>
       <c r="G17" t="str">
-        <v>2-4</v>
+        <v>4-6</v>
       </c>
       <c r="H17" s="1">
         <v>0.3</v>
@@ -1192,10 +1192,10 @@
         <v>Yes</v>
       </c>
       <c r="M17" t="str">
-        <v/>
+        <v>Tiny Fishing Spot</v>
       </c>
       <c r="N17" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Any","quality":"Rare","count":1}]}</v>
       </c>
       <c r="O17" t="str">
         <v/>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B18" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="C18" t="str">
         <v>Route 32</v>
@@ -1221,7 +1221,7 @@
         <v>7-11</v>
       </c>
       <c r="G18" t="str">
-        <v>2-4</v>
+        <v>4-6</v>
       </c>
       <c r="H18" s="1">
         <v>0.2</v>
@@ -1239,10 +1239,10 @@
         <v>Yes</v>
       </c>
       <c r="M18" t="str">
-        <v/>
+        <v>Tiny Fishing Spot</v>
       </c>
       <c r="N18" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Any","quality":"Rare","count":1}]}</v>
       </c>
       <c r="O18" t="str">
         <v/>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B19" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="C19" t="str">
         <v>Route 32</v>
@@ -1268,7 +1268,7 @@
         <v>8-11</v>
       </c>
       <c r="G19" t="str">
-        <v>2-4</v>
+        <v>4-6</v>
       </c>
       <c r="H19" s="1">
         <v>0.3</v>
@@ -1286,10 +1286,10 @@
         <v>Yes</v>
       </c>
       <c r="M19" t="str">
-        <v/>
+        <v>Tiny Fishing Spot</v>
       </c>
       <c r="N19" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Any","quality":"Rare","count":1}]}</v>
       </c>
       <c r="O19" t="str">
         <v/>
@@ -1315,13 +1315,13 @@
         <v>8-12</v>
       </c>
       <c r="G20" t="str">
-        <v>3-5</v>
+        <v>6-8</v>
       </c>
       <c r="H20" s="1">
         <v>0.25</v>
       </c>
       <c r="I20" s="1">
-        <v>0.14285714285714285</v>
+        <v>0.14</v>
       </c>
       <c r="J20" t="str">
         <v/>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="B21" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="C21" t="str">
         <v>Tiny Fishing Spot</v>
@@ -1362,7 +1362,7 @@
         <v>8-12</v>
       </c>
       <c r="G21" t="str">
-        <v>3-5</v>
+        <v>6-8</v>
       </c>
       <c r="H21" s="1">
         <v>0.15</v>
@@ -1380,10 +1380,10 @@
         <v>Yes</v>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>Route 33</v>
       </c>
       <c r="N21" t="str">
-        <v/>
+        <v>{"catchByType":{"type":"Water","count":5}}</v>
       </c>
       <c r="O21" t="str">
         <v/>
@@ -1391,10 +1391,10 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="B22" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="C22" t="str">
         <v>Tiny Fishing Spot</v>
@@ -1409,7 +1409,7 @@
         <v>8-12</v>
       </c>
       <c r="G22" t="str">
-        <v>3-5</v>
+        <v>6-8</v>
       </c>
       <c r="H22" s="1">
         <v>0.15</v>
@@ -1427,10 +1427,10 @@
         <v>Yes</v>
       </c>
       <c r="M22" t="str">
-        <v/>
+        <v>Route 33</v>
       </c>
       <c r="N22" t="str">
-        <v/>
+        <v>{"catchByType":{"type":"Water","count":5}}</v>
       </c>
       <c r="O22" t="str">
         <v/>
@@ -1438,10 +1438,10 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="B23" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="C23" t="str">
         <v>Tiny Fishing Spot</v>
@@ -1456,7 +1456,7 @@
         <v>8-12</v>
       </c>
       <c r="G23" t="str">
-        <v>3-5</v>
+        <v>6-8</v>
       </c>
       <c r="H23" s="1">
         <v>0.15</v>
@@ -1474,10 +1474,10 @@
         <v>Yes</v>
       </c>
       <c r="M23" t="str">
-        <v/>
+        <v>Route 33</v>
       </c>
       <c r="N23" t="str">
-        <v/>
+        <v>{"catchByType":{"type":"Water","count":5}}</v>
       </c>
       <c r="O23" t="str">
         <v/>
@@ -1485,10 +1485,10 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="B24" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="C24" t="str">
         <v>Tiny Fishing Spot</v>
@@ -1503,7 +1503,7 @@
         <v>8-12</v>
       </c>
       <c r="G24" t="str">
-        <v>3-5</v>
+        <v>6-8</v>
       </c>
       <c r="H24" s="1">
         <v>0.1</v>
@@ -1521,10 +1521,10 @@
         <v>Yes</v>
       </c>
       <c r="M24" t="str">
-        <v/>
+        <v>Route 33</v>
       </c>
       <c r="N24" t="str">
-        <v/>
+        <v>{"catchByType":{"type":"Water","count":5}}</v>
       </c>
       <c r="O24" t="str">
         <v/>
@@ -1532,10 +1532,10 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="B25" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="C25" t="str">
         <v>Tiny Fishing Spot</v>
@@ -1550,7 +1550,7 @@
         <v>8-12</v>
       </c>
       <c r="G25" t="str">
-        <v>3-5</v>
+        <v>6-8</v>
       </c>
       <c r="H25" s="1">
         <v>0.1</v>
@@ -1568,10 +1568,10 @@
         <v>Yes</v>
       </c>
       <c r="M25" t="str">
-        <v/>
+        <v>Route 33</v>
       </c>
       <c r="N25" t="str">
-        <v/>
+        <v>{"catchByType":{"type":"Water","count":5}}</v>
       </c>
       <c r="O25" t="str">
         <v/>
@@ -1579,10 +1579,10 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="B26" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="C26" t="str">
         <v>Tiny Fishing Spot</v>
@@ -1597,13 +1597,13 @@
         <v>8-12</v>
       </c>
       <c r="G26" t="str">
-        <v>3-5</v>
+        <v>6-8</v>
       </c>
       <c r="H26" s="1">
         <v>0.1</v>
       </c>
-      <c r="I26" t="str">
-        <v/>
+      <c r="I26" s="1">
+        <v>0.16</v>
       </c>
       <c r="J26" t="str">
         <v/>
@@ -1615,10 +1615,10 @@
         <v>Yes</v>
       </c>
       <c r="M26" t="str">
-        <v/>
+        <v>Route 33</v>
       </c>
       <c r="N26" t="str">
-        <v/>
+        <v>{"catchByType":{"type":"Water","count":5}}</v>
       </c>
       <c r="O26" t="str">
         <v/>
@@ -1644,13 +1644,13 @@
         <v>6-10</v>
       </c>
       <c r="G27" t="str">
-        <v>5-7</v>
+        <v>9-11</v>
       </c>
       <c r="H27" s="1">
         <v>0.7</v>
       </c>
       <c r="I27" s="1">
-        <v>0.3333333333333333</v>
+        <v>0.33</v>
       </c>
       <c r="J27" t="str">
         <v>Legacy</v>
@@ -1673,10 +1673,10 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B28" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C28" t="str">
         <v>Ruins of Alph</v>
@@ -1691,13 +1691,13 @@
         <v>7-11</v>
       </c>
       <c r="G28" t="str">
-        <v>5-7</v>
+        <v>9-11</v>
       </c>
       <c r="H28" s="1">
         <v>0.2</v>
       </c>
       <c r="I28" s="1">
-        <v>0.3333333333333333</v>
+        <v>0.33</v>
       </c>
       <c r="J28" t="str">
         <v>Legacy</v>
@@ -1709,10 +1709,10 @@
         <v>Yes</v>
       </c>
       <c r="M28" t="str">
-        <v/>
+        <v>Route 32</v>
       </c>
       <c r="N28" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Unown","count":20}}</v>
       </c>
       <c r="O28" t="str">
         <v/>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B29" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C29" t="str">
         <v>Ruins of Alph</v>
@@ -1738,13 +1738,13 @@
         <v>7-11</v>
       </c>
       <c r="G29" t="str">
-        <v>5-7</v>
+        <v>9-11</v>
       </c>
       <c r="H29" s="1">
         <v>0.1</v>
       </c>
       <c r="I29" s="1">
-        <v>0.3333333333333333</v>
+        <v>0.34</v>
       </c>
       <c r="J29" t="str">
         <v>Legacy</v>
@@ -1756,10 +1756,10 @@
         <v>Yes</v>
       </c>
       <c r="M29" t="str">
-        <v/>
+        <v>Route 32</v>
       </c>
       <c r="N29" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Unown","count":20}}</v>
       </c>
       <c r="O29" t="str">
         <v/>
@@ -1785,7 +1785,7 @@
         <v>9-13</v>
       </c>
       <c r="G30" t="str">
-        <v>6-8</v>
+        <v>11-13</v>
       </c>
       <c r="H30" s="1">
         <v>0.17</v>
@@ -1814,10 +1814,10 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B31" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="C31" t="str">
         <v>Route 33</v>
@@ -1832,13 +1832,13 @@
         <v>9-13</v>
       </c>
       <c r="G31" t="str">
-        <v>6-8</v>
+        <v>11-13</v>
       </c>
       <c r="H31" s="1">
         <v>0.25</v>
       </c>
-      <c r="I31" t="str">
-        <v/>
+      <c r="I31" s="1">
+        <v>0.17</v>
       </c>
       <c r="J31" t="str">
         <v>Yes</v>
@@ -1850,10 +1850,10 @@
         <v>Yes</v>
       </c>
       <c r="M31" t="str">
-        <v/>
+        <v>Azalea Gym</v>
       </c>
       <c r="N31" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Mareep","count":2}]}</v>
       </c>
       <c r="O31" t="str">
         <v/>
@@ -1861,10 +1861,10 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B32" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="C32" t="str">
         <v>Route 33</v>
@@ -1879,7 +1879,7 @@
         <v>9-13</v>
       </c>
       <c r="G32" t="str">
-        <v>6-8</v>
+        <v>11-13</v>
       </c>
       <c r="H32" s="1">
         <v>0.16</v>
@@ -1897,10 +1897,10 @@
         <v>Yes</v>
       </c>
       <c r="M32" t="str">
-        <v/>
+        <v>Azalea Gym</v>
       </c>
       <c r="N32" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Mareep","count":2}]}</v>
       </c>
       <c r="O32" t="str">
         <v/>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B33" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="C33" t="str">
         <v>Route 33</v>
@@ -1926,13 +1926,13 @@
         <v>9-13</v>
       </c>
       <c r="G33" t="str">
-        <v>6-8</v>
+        <v>11-13</v>
       </c>
       <c r="H33" s="1">
         <v>0.25</v>
       </c>
-      <c r="I33" t="str">
-        <v/>
+      <c r="I33" s="1">
+        <v>0.17</v>
       </c>
       <c r="J33" t="str">
         <v>Yes</v>
@@ -1944,10 +1944,10 @@
         <v>Yes</v>
       </c>
       <c r="M33" t="str">
-        <v/>
+        <v>Azalea Gym</v>
       </c>
       <c r="N33" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Mareep","count":2}]}</v>
       </c>
       <c r="O33" t="str">
         <v/>
@@ -1955,10 +1955,10 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B34" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="C34" t="str">
         <v>Route 33</v>
@@ -1973,13 +1973,13 @@
         <v>9-13</v>
       </c>
       <c r="G34" t="str">
-        <v>6-8</v>
+        <v>11-13</v>
       </c>
       <c r="H34" s="1">
         <v>0.08</v>
       </c>
-      <c r="I34" t="str">
-        <v/>
+      <c r="I34" s="1">
+        <v>0.17</v>
       </c>
       <c r="J34" t="str">
         <v>Yes</v>
@@ -1991,10 +1991,10 @@
         <v>Yes</v>
       </c>
       <c r="M34" t="str">
-        <v/>
+        <v>Azalea Gym</v>
       </c>
       <c r="N34" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Mareep","count":2}]}</v>
       </c>
       <c r="O34" t="str">
         <v/>
@@ -2002,10 +2002,10 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B35" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="C35" t="str">
         <v>Route 33</v>
@@ -2020,13 +2020,13 @@
         <v>9-13</v>
       </c>
       <c r="G35" t="str">
-        <v>6-8</v>
+        <v>11-13</v>
       </c>
       <c r="H35" s="1">
         <v>0.09</v>
       </c>
-      <c r="I35" t="str">
-        <v/>
+      <c r="I35" s="1">
+        <v>0.15</v>
       </c>
       <c r="J35" t="str">
         <v>Legacy</v>
@@ -2038,10 +2038,10 @@
         <v>Yes</v>
       </c>
       <c r="M35" t="str">
-        <v/>
+        <v>Azalea Gym</v>
       </c>
       <c r="N35" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Mareep","count":2}]}</v>
       </c>
       <c r="O35" t="str">
         <v/>
@@ -2067,7 +2067,7 @@
         <v>13-17</v>
       </c>
       <c r="G36" t="str">
-        <v>8-10</v>
+        <v>13-16</v>
       </c>
       <c r="H36" s="1">
         <v>0.3</v>
@@ -2096,10 +2096,10 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="B37" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="C37" t="str">
         <v>Ilex Forest</v>
@@ -2114,7 +2114,7 @@
         <v>12-16</v>
       </c>
       <c r="G37" t="str">
-        <v>8-10</v>
+        <v>13-16</v>
       </c>
       <c r="H37" s="1">
         <v>0.2</v>
@@ -2132,10 +2132,10 @@
         <v>Yes</v>
       </c>
       <c r="M37" t="str">
-        <v/>
+        <v>Route 34</v>
       </c>
       <c r="N37" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Paras","quality":"Rare","count":1}]}</v>
       </c>
       <c r="O37" t="str">
         <v/>
@@ -2143,10 +2143,10 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="B38" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="C38" t="str">
         <v>Ilex Forest</v>
@@ -2161,7 +2161,7 @@
         <v>12-16</v>
       </c>
       <c r="G38" t="str">
-        <v>8-10</v>
+        <v>13-16</v>
       </c>
       <c r="H38" s="1">
         <v>0.2</v>
@@ -2179,10 +2179,10 @@
         <v>Yes</v>
       </c>
       <c r="M38" t="str">
-        <v/>
+        <v>Route 34</v>
       </c>
       <c r="N38" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Paras","quality":"Rare","count":1}]}</v>
       </c>
       <c r="O38" t="str">
         <v/>
@@ -2190,10 +2190,10 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="B39" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="C39" t="str">
         <v>Ilex Forest</v>
@@ -2208,13 +2208,13 @@
         <v>13-17</v>
       </c>
       <c r="G39" t="str">
-        <v>8-10</v>
+        <v>13-16</v>
       </c>
       <c r="H39" s="1">
         <v>0.15</v>
       </c>
-      <c r="I39" t="str">
-        <v/>
+      <c r="I39" s="1">
+        <v>0.2</v>
       </c>
       <c r="J39" t="str">
         <v>Legacy</v>
@@ -2226,10 +2226,10 @@
         <v>Yes</v>
       </c>
       <c r="M39" t="str">
-        <v/>
+        <v>Route 34</v>
       </c>
       <c r="N39" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Paras","quality":"Rare","count":1}]}</v>
       </c>
       <c r="O39" t="str">
         <v/>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="B40" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="C40" t="str">
         <v>Ilex Forest</v>
@@ -2255,13 +2255,13 @@
         <v>13-17</v>
       </c>
       <c r="G40" t="str">
-        <v>8-10</v>
+        <v>13-16</v>
       </c>
       <c r="H40" s="1">
         <v>0.15</v>
       </c>
-      <c r="I40" t="str">
-        <v/>
+      <c r="I40" s="1">
+        <v>0.2</v>
       </c>
       <c r="J40" t="str">
         <v>Legacy</v>
@@ -2273,10 +2273,10 @@
         <v>Yes</v>
       </c>
       <c r="M40" t="str">
-        <v/>
+        <v>Route 34</v>
       </c>
       <c r="N40" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Paras","quality":"Rare","count":1}]}</v>
       </c>
       <c r="O40" t="str">
         <v/>
@@ -2302,7 +2302,7 @@
         <v>15-19</v>
       </c>
       <c r="G41" t="str">
-        <v>10-12</v>
+        <v>16-19</v>
       </c>
       <c r="H41" s="1">
         <v>0.2</v>
@@ -2331,10 +2331,10 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="B42" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="C42" t="str">
         <v>Route 34</v>
@@ -2349,7 +2349,7 @@
         <v>15-19</v>
       </c>
       <c r="G42" t="str">
-        <v>10-12</v>
+        <v>16-19</v>
       </c>
       <c r="H42" s="1">
         <v>0.35</v>
@@ -2367,10 +2367,10 @@
         <v>Yes</v>
       </c>
       <c r="M42" t="str">
-        <v/>
+        <v>Goldenrod Gym, Goldenrod Game Corner, Daycare</v>
       </c>
       <c r="N42" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Ditto","count":2}]}</v>
       </c>
       <c r="O42" t="str">
         <v/>
@@ -2378,10 +2378,10 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="B43" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="C43" t="str">
         <v>Route 34</v>
@@ -2396,7 +2396,7 @@
         <v>14-18</v>
       </c>
       <c r="G43" t="str">
-        <v>10-12</v>
+        <v>16-19</v>
       </c>
       <c r="H43" s="1">
         <v>0.35</v>
@@ -2414,10 +2414,10 @@
         <v>Yes</v>
       </c>
       <c r="M43" t="str">
-        <v/>
+        <v>Goldenrod Gym, Goldenrod Game Corner, Daycare</v>
       </c>
       <c r="N43" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Ditto","count":2}]}</v>
       </c>
       <c r="O43" t="str">
         <v/>
@@ -2425,10 +2425,10 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="B44" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="C44" t="str">
         <v>Route 34</v>
@@ -2443,7 +2443,7 @@
         <v>15-20</v>
       </c>
       <c r="G44" t="str">
-        <v>10-12</v>
+        <v>16-19</v>
       </c>
       <c r="H44" s="1">
         <v>0.1</v>
@@ -2461,10 +2461,10 @@
         <v>Yes</v>
       </c>
       <c r="M44" t="str">
-        <v/>
+        <v>Goldenrod Gym, Goldenrod Game Corner, Daycare</v>
       </c>
       <c r="N44" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Ditto","count":2}]}</v>
       </c>
       <c r="O44" t="str">
         <v/>
@@ -2490,7 +2490,7 @@
         <v>20-25</v>
       </c>
       <c r="G45" t="str">
-        <v>11-13</v>
+        <v>18-21</v>
       </c>
       <c r="H45" s="1">
         <v>0.35</v>
@@ -2519,10 +2519,10 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B46" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="C46" t="str">
         <v>Route 35</v>
@@ -2537,7 +2537,7 @@
         <v>20-25</v>
       </c>
       <c r="G46" t="str">
-        <v>11-13</v>
+        <v>18-21</v>
       </c>
       <c r="H46" s="1">
         <v>0.25</v>
@@ -2555,10 +2555,10 @@
         <v>Yes</v>
       </c>
       <c r="M46" t="str">
-        <v/>
+        <v>National Park</v>
       </c>
       <c r="N46" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Nidoran♀","count":1},{"species":"Nidoran♂","count":1}]}</v>
       </c>
       <c r="O46" t="str">
         <v/>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B47" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="C47" t="str">
         <v>Route 35</v>
@@ -2584,7 +2584,7 @@
         <v>19-24</v>
       </c>
       <c r="G47" t="str">
-        <v>11-13</v>
+        <v>18-21</v>
       </c>
       <c r="H47" s="1">
         <v>0.2</v>
@@ -2602,10 +2602,10 @@
         <v>Yes</v>
       </c>
       <c r="M47" t="str">
-        <v/>
+        <v>National Park</v>
       </c>
       <c r="N47" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Nidoran♀","count":1},{"species":"Nidoran♂","count":1}]}</v>
       </c>
       <c r="O47" t="str">
         <v/>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B48" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="C48" t="str">
         <v>Route 35</v>
@@ -2631,7 +2631,7 @@
         <v>19-24</v>
       </c>
       <c r="G48" t="str">
-        <v>11-13</v>
+        <v>18-21</v>
       </c>
       <c r="H48" s="1">
         <v>0.2</v>
@@ -2649,10 +2649,10 @@
         <v>Yes</v>
       </c>
       <c r="M48" t="str">
-        <v/>
+        <v>National Park</v>
       </c>
       <c r="N48" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Nidoran♀","count":1},{"species":"Nidoran♂","count":1}]}</v>
       </c>
       <c r="O48" t="str">
         <v/>
@@ -2678,13 +2678,13 @@
         <v>20-25</v>
       </c>
       <c r="G49" t="str">
-        <v>13-16</v>
+        <v>20-23</v>
       </c>
       <c r="H49" s="1">
         <v>0.23</v>
       </c>
-      <c r="I49" t="str">
-        <v/>
+      <c r="I49" s="1">
+        <v>0.17</v>
       </c>
       <c r="J49" t="str">
         <v>Legacy</v>
@@ -2707,10 +2707,10 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B50" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="C50" t="str">
         <v>National Park</v>
@@ -2725,13 +2725,13 @@
         <v>20-25</v>
       </c>
       <c r="G50" t="str">
-        <v>13-16</v>
+        <v>20-23</v>
       </c>
       <c r="H50" s="1">
         <v>0.23</v>
       </c>
-      <c r="I50" t="str">
-        <v/>
+      <c r="I50" s="1">
+        <v>0.17</v>
       </c>
       <c r="J50" t="str">
         <v>Legacy</v>
@@ -2743,10 +2743,10 @@
         <v>Yes</v>
       </c>
       <c r="M50" t="str">
-        <v/>
+        <v>Route 36</v>
       </c>
       <c r="N50" t="str">
-        <v/>
+        <v>{"defeatMultipleSpecific":[{"name":"Scyther","count":4},{"name":"Pinsir","count":4}]}</v>
       </c>
       <c r="O50" t="str">
         <v/>
@@ -2754,10 +2754,10 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B51" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="C51" t="str">
         <v>National Park</v>
@@ -2772,13 +2772,13 @@
         <v>20-25</v>
       </c>
       <c r="G51" t="str">
-        <v>13-16</v>
+        <v>20-23</v>
       </c>
       <c r="H51" s="1">
         <v>0.23</v>
       </c>
-      <c r="I51" t="str">
-        <v/>
+      <c r="I51" s="1">
+        <v>0.17</v>
       </c>
       <c r="J51" t="str">
         <v>Legacy</v>
@@ -2790,10 +2790,10 @@
         <v>Yes</v>
       </c>
       <c r="M51" t="str">
-        <v/>
+        <v>Route 36</v>
       </c>
       <c r="N51" t="str">
-        <v/>
+        <v>{"defeatMultipleSpecific":[{"name":"Scyther","count":4},{"name":"Pinsir","count":4}]}</v>
       </c>
       <c r="O51" t="str">
         <v/>
@@ -2801,10 +2801,10 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B52" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="C52" t="str">
         <v>National Park</v>
@@ -2819,13 +2819,13 @@
         <v>24-28</v>
       </c>
       <c r="G52" t="str">
-        <v>13-16</v>
+        <v>20-23</v>
       </c>
       <c r="H52" s="1">
         <v>0.09</v>
       </c>
-      <c r="I52" t="str">
-        <v/>
+      <c r="I52" s="1">
+        <v>0.17</v>
       </c>
       <c r="J52" t="str">
         <v>Legacy</v>
@@ -2837,10 +2837,10 @@
         <v>Yes</v>
       </c>
       <c r="M52" t="str">
-        <v/>
+        <v>Route 36</v>
       </c>
       <c r="N52" t="str">
-        <v/>
+        <v>{"defeatMultipleSpecific":[{"name":"Scyther","count":4},{"name":"Pinsir","count":4}]}</v>
       </c>
       <c r="O52" t="str">
         <v/>
@@ -2848,10 +2848,10 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B53" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="C53" t="str">
         <v>National Park</v>
@@ -2866,13 +2866,13 @@
         <v>24-28</v>
       </c>
       <c r="G53" t="str">
-        <v>13-16</v>
+        <v>20-23</v>
       </c>
       <c r="H53" s="1">
         <v>0.09</v>
       </c>
-      <c r="I53" t="str">
-        <v/>
+      <c r="I53" s="1">
+        <v>0.17</v>
       </c>
       <c r="J53" t="str">
         <v>Legacy</v>
@@ -2884,10 +2884,10 @@
         <v>Yes</v>
       </c>
       <c r="M53" t="str">
-        <v/>
+        <v>Route 36</v>
       </c>
       <c r="N53" t="str">
-        <v/>
+        <v>{"defeatMultipleSpecific":[{"name":"Scyther","count":4},{"name":"Pinsir","count":4}]}</v>
       </c>
       <c r="O53" t="str">
         <v/>
@@ -2895,10 +2895,10 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B54" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="C54" t="str">
         <v>National Park</v>
@@ -2913,7 +2913,7 @@
         <v>22-27</v>
       </c>
       <c r="G54" t="str">
-        <v>13-16</v>
+        <v>20-23</v>
       </c>
       <c r="H54" s="1">
         <v>0.13</v>
@@ -2931,10 +2931,10 @@
         <v>Yes</v>
       </c>
       <c r="M54" t="str">
-        <v/>
+        <v>Route 36</v>
       </c>
       <c r="N54" t="str">
-        <v/>
+        <v>{"defeatMultipleSpecific":[{"name":"Scyther","count":4},{"name":"Pinsir","count":4}]}</v>
       </c>
       <c r="O54" t="str">
         <v/>
@@ -2960,7 +2960,7 @@
         <v>24-29</v>
       </c>
       <c r="G55" t="str">
-        <v>14-17</v>
+        <v>23-26</v>
       </c>
       <c r="H55" s="1">
         <v>0.3</v>
@@ -2989,10 +2989,10 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="B56" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="C56" t="str">
         <v>Route 36</v>
@@ -3007,7 +3007,7 @@
         <v>24-29</v>
       </c>
       <c r="G56" t="str">
-        <v>14-17</v>
+        <v>23-26</v>
       </c>
       <c r="H56" s="1">
         <v>0.25</v>
@@ -3025,10 +3025,10 @@
         <v>Yes</v>
       </c>
       <c r="M56" t="str">
-        <v/>
+        <v>Route 37</v>
       </c>
       <c r="N56" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Sudowoodo","count":5}}</v>
       </c>
       <c r="O56" t="str">
         <v/>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="B57" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="C57" t="str">
         <v>Route 36</v>
@@ -3054,7 +3054,7 @@
         <v>24-29</v>
       </c>
       <c r="G57" t="str">
-        <v>14-17</v>
+        <v>23-26</v>
       </c>
       <c r="H57" s="1">
         <v>0.25</v>
@@ -3072,10 +3072,10 @@
         <v>Yes</v>
       </c>
       <c r="M57" t="str">
-        <v/>
+        <v>Route 37</v>
       </c>
       <c r="N57" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Sudowoodo","count":5}}</v>
       </c>
       <c r="O57" t="str">
         <v/>
@@ -3083,10 +3083,10 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="B58" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="C58" t="str">
         <v>Route 36</v>
@@ -3101,7 +3101,7 @@
         <v>23-28</v>
       </c>
       <c r="G58" t="str">
-        <v>14-17</v>
+        <v>23-26</v>
       </c>
       <c r="H58" s="1">
         <v>0.1</v>
@@ -3119,10 +3119,10 @@
         <v>Yes</v>
       </c>
       <c r="M58" t="str">
-        <v/>
+        <v>Route 37</v>
       </c>
       <c r="N58" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Sudowoodo","count":5}}</v>
       </c>
       <c r="O58" t="str">
         <v/>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="C59" t="str">
         <v>Route 36</v>
@@ -3148,7 +3148,7 @@
         <v>26-30</v>
       </c>
       <c r="G59" t="str">
-        <v>14-17</v>
+        <v>23-26</v>
       </c>
       <c r="H59" s="1">
         <v>0.1</v>
@@ -3166,10 +3166,10 @@
         <v>Yes</v>
       </c>
       <c r="M59" t="str">
-        <v/>
+        <v>Route 37</v>
       </c>
       <c r="N59" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Sudowoodo","count":5}}</v>
       </c>
       <c r="O59" t="str">
         <v/>
@@ -3195,13 +3195,13 @@
         <v>26-31</v>
       </c>
       <c r="G60" t="str">
-        <v>16-19</v>
+        <v>25-28</v>
       </c>
       <c r="H60" s="1">
         <v>0.28</v>
       </c>
-      <c r="I60" t="str">
-        <v/>
+      <c r="I60" s="1">
+        <v>0.2</v>
       </c>
       <c r="J60" t="str">
         <v>Yes</v>
@@ -3224,10 +3224,10 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="C61" t="str">
         <v>Route 37</v>
@@ -3242,13 +3242,13 @@
         <v>26-31</v>
       </c>
       <c r="G61" t="str">
-        <v>16-19</v>
+        <v>25-28</v>
       </c>
       <c r="H61" s="1">
         <v>0.29</v>
       </c>
-      <c r="I61" t="str">
-        <v/>
+      <c r="I61" s="1">
+        <v>0.2</v>
       </c>
       <c r="J61" t="str">
         <v>Yes</v>
@@ -3260,10 +3260,10 @@
         <v>Yes</v>
       </c>
       <c r="M61" t="str">
-        <v/>
+        <v>Burned Tower</v>
       </c>
       <c r="N61" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Ledian","count":1},{"species":"Ariados","count":1}]}</v>
       </c>
       <c r="O61" t="str">
         <v/>
@@ -3271,10 +3271,10 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="B62" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="C62" t="str">
         <v>Route 37</v>
@@ -3289,7 +3289,7 @@
         <v>27-32</v>
       </c>
       <c r="G62" t="str">
-        <v>16-19</v>
+        <v>25-28</v>
       </c>
       <c r="H62" s="1">
         <v>0.19</v>
@@ -3307,10 +3307,10 @@
         <v>Yes</v>
       </c>
       <c r="M62" t="str">
-        <v/>
+        <v>Burned Tower</v>
       </c>
       <c r="N62" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Ledian","count":1},{"species":"Ariados","count":1}]}</v>
       </c>
       <c r="O62" t="str">
         <v/>
@@ -3318,10 +3318,10 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="B63" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="C63" t="str">
         <v>Route 37</v>
@@ -3336,7 +3336,7 @@
         <v>27-32</v>
       </c>
       <c r="G63" t="str">
-        <v>16-19</v>
+        <v>25-28</v>
       </c>
       <c r="H63" s="1">
         <v>0.19</v>
@@ -3354,10 +3354,10 @@
         <v>Yes</v>
       </c>
       <c r="M63" t="str">
-        <v/>
+        <v>Burned Tower</v>
       </c>
       <c r="N63" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Ledian","count":1},{"species":"Ariados","count":1}]}</v>
       </c>
       <c r="O63" t="str">
         <v/>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="C64" t="str">
         <v>Route 37</v>
@@ -3383,7 +3383,7 @@
         <v>26-32</v>
       </c>
       <c r="G64" t="str">
-        <v>16-19</v>
+        <v>25-28</v>
       </c>
       <c r="H64" s="1">
         <v>0.05</v>
@@ -3401,10 +3401,10 @@
         <v>Yes</v>
       </c>
       <c r="M64" t="str">
-        <v/>
+        <v>Burned Tower</v>
       </c>
       <c r="N64" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Ledian","count":1},{"species":"Ariados","count":1}]}</v>
       </c>
       <c r="O64" t="str">
         <v/>
@@ -3430,13 +3430,13 @@
         <v>28-33</v>
       </c>
       <c r="G65" t="str">
-        <v>18-21</v>
+        <v>27-30</v>
       </c>
       <c r="H65" s="1">
         <v>0.25</v>
       </c>
-      <c r="I65" t="str">
-        <v/>
+      <c r="I65" s="1">
+        <v>0.17</v>
       </c>
       <c r="J65" t="str">
         <v>Legacy</v>
@@ -3459,10 +3459,10 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B66" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C66" t="str">
         <v>Burned Tower</v>
@@ -3477,13 +3477,13 @@
         <v>27-32</v>
       </c>
       <c r="G66" t="str">
-        <v>18-21</v>
+        <v>27-30</v>
       </c>
       <c r="H66" s="1">
         <v>0.25</v>
       </c>
-      <c r="I66" t="str">
-        <v/>
+      <c r="I66" s="1">
+        <v>0.17</v>
       </c>
       <c r="J66" t="str">
         <v>Legacy</v>
@@ -3495,10 +3495,10 @@
         <v>Yes</v>
       </c>
       <c r="M66" t="str">
-        <v/>
+        <v>Ecruteak Gym</v>
       </c>
       <c r="N66" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Magmar","count":3}}</v>
       </c>
       <c r="O66" t="str">
         <v/>
@@ -3506,10 +3506,10 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B67" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C67" t="str">
         <v>Burned Tower</v>
@@ -3524,7 +3524,7 @@
         <v>27-32</v>
       </c>
       <c r="G67" t="str">
-        <v>18-21</v>
+        <v>27-30</v>
       </c>
       <c r="H67" s="1">
         <v>0.15</v>
@@ -3542,10 +3542,10 @@
         <v>Yes</v>
       </c>
       <c r="M67" t="str">
-        <v/>
+        <v>Ecruteak Gym</v>
       </c>
       <c r="N67" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Magmar","count":3}}</v>
       </c>
       <c r="O67" t="str">
         <v/>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C68" t="str">
         <v>Burned Tower</v>
@@ -3571,7 +3571,7 @@
         <v>28-33</v>
       </c>
       <c r="G68" t="str">
-        <v>18-21</v>
+        <v>27-30</v>
       </c>
       <c r="H68" s="1">
         <v>0.15</v>
@@ -3589,10 +3589,10 @@
         <v>Yes</v>
       </c>
       <c r="M68" t="str">
-        <v/>
+        <v>Ecruteak Gym</v>
       </c>
       <c r="N68" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Magmar","count":3}}</v>
       </c>
       <c r="O68" t="str">
         <v/>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B69" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C69" t="str">
         <v>Burned Tower</v>
@@ -3618,13 +3618,13 @@
         <v>32-36</v>
       </c>
       <c r="G69" t="str">
-        <v>18-21</v>
+        <v>27-30</v>
       </c>
       <c r="H69" s="1">
         <v>0.1</v>
       </c>
-      <c r="I69" t="str">
-        <v/>
+      <c r="I69" s="1">
+        <v>0.17</v>
       </c>
       <c r="J69" t="str">
         <v>Legacy</v>
@@ -3636,10 +3636,10 @@
         <v>Yes</v>
       </c>
       <c r="M69" t="str">
-        <v/>
+        <v>Ecruteak Gym</v>
       </c>
       <c r="N69" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Magmar","count":3}}</v>
       </c>
       <c r="O69" t="str">
         <v/>
@@ -3647,10 +3647,10 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B70" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C70" t="str">
         <v>Burned Tower</v>
@@ -3665,7 +3665,7 @@
         <v>32-37</v>
       </c>
       <c r="G70" t="str">
-        <v>18-21</v>
+        <v>27-30</v>
       </c>
       <c r="H70" s="1">
         <v>0.1</v>
@@ -3683,10 +3683,10 @@
         <v>Yes</v>
       </c>
       <c r="M70" t="str">
-        <v/>
+        <v>Ecruteak Gym</v>
       </c>
       <c r="N70" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Magmar","count":3}}</v>
       </c>
       <c r="O70" t="str">
         <v/>
@@ -3712,7 +3712,7 @@
         <v>31-36</v>
       </c>
       <c r="G71" t="str">
-        <v>19-22</v>
+        <v>30-33</v>
       </c>
       <c r="H71" s="1">
         <v>0.3</v>
@@ -3741,10 +3741,10 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="B72" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="C72" t="str">
         <v>Route 38</v>
@@ -3759,7 +3759,7 @@
         <v>31-36</v>
       </c>
       <c r="G72" t="str">
-        <v>19-22</v>
+        <v>30-33</v>
       </c>
       <c r="H72" s="1">
         <v>0.25</v>
@@ -3777,10 +3777,10 @@
         <v>Yes</v>
       </c>
       <c r="M72" t="str">
-        <v/>
+        <v>Route 39</v>
       </c>
       <c r="N72" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tauros","count":1}]}</v>
       </c>
       <c r="O72" t="str">
         <v/>
@@ -3788,10 +3788,10 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="B73" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="C73" t="str">
         <v>Route 38</v>
@@ -3806,13 +3806,13 @@
         <v>30-35</v>
       </c>
       <c r="G73" t="str">
-        <v>19-22</v>
+        <v>30-33</v>
       </c>
       <c r="H73" s="1">
         <v>0.15</v>
       </c>
-      <c r="I73" t="str">
-        <v/>
+      <c r="I73" s="1">
+        <v>0.2</v>
       </c>
       <c r="J73" t="str">
         <v>Legacy</v>
@@ -3824,10 +3824,10 @@
         <v>Yes</v>
       </c>
       <c r="M73" t="str">
-        <v/>
+        <v>Route 39</v>
       </c>
       <c r="N73" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tauros","count":1}]}</v>
       </c>
       <c r="O73" t="str">
         <v/>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="B74" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="C74" t="str">
         <v>Route 38</v>
@@ -3853,7 +3853,7 @@
         <v>31-36</v>
       </c>
       <c r="G74" t="str">
-        <v>19-22</v>
+        <v>30-33</v>
       </c>
       <c r="H74" s="1">
         <v>0.2</v>
@@ -3871,10 +3871,10 @@
         <v>Yes</v>
       </c>
       <c r="M74" t="str">
-        <v/>
+        <v>Route 39</v>
       </c>
       <c r="N74" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tauros","count":1}]}</v>
       </c>
       <c r="O74" t="str">
         <v/>
@@ -3882,10 +3882,10 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="B75" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="C75" t="str">
         <v>Route 38</v>
@@ -3900,7 +3900,7 @@
         <v>32-37</v>
       </c>
       <c r="G75" t="str">
-        <v>19-22</v>
+        <v>30-33</v>
       </c>
       <c r="H75" s="1">
         <v>0.1</v>
@@ -3918,10 +3918,10 @@
         <v>Yes</v>
       </c>
       <c r="M75" t="str">
-        <v/>
+        <v>Route 39</v>
       </c>
       <c r="N75" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tauros","count":1}]}</v>
       </c>
       <c r="O75" t="str">
         <v/>
@@ -3947,13 +3947,13 @@
         <v>33-38</v>
       </c>
       <c r="G76" t="str">
-        <v>21-24</v>
+        <v>32-35</v>
       </c>
       <c r="H76" s="1">
         <v>0.25</v>
       </c>
-      <c r="I76" t="str">
-        <v/>
+      <c r="I76" s="1">
+        <v>0.17</v>
       </c>
       <c r="J76" t="str">
         <v>Yes</v>
@@ -3976,10 +3976,10 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="B77" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="C77" t="str">
         <v>Route 39</v>
@@ -3994,13 +3994,13 @@
         <v>34-39</v>
       </c>
       <c r="G77" t="str">
-        <v>21-24</v>
+        <v>32-35</v>
       </c>
       <c r="H77" s="1">
         <v>0.25</v>
       </c>
-      <c r="I77" t="str">
-        <v/>
+      <c r="I77" s="1">
+        <v>0.17</v>
       </c>
       <c r="J77" t="str">
         <v>Yes</v>
@@ -4012,10 +4012,10 @@
         <v>Yes</v>
       </c>
       <c r="M77" t="str">
-        <v/>
+        <v>Small Fishing Spot</v>
       </c>
       <c r="N77" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Farfetch'd","count":1}]}</v>
       </c>
       <c r="O77" t="str">
         <v/>
@@ -4023,10 +4023,10 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="B78" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="C78" t="str">
         <v>Route 39</v>
@@ -4041,7 +4041,7 @@
         <v>34-39</v>
       </c>
       <c r="G78" t="str">
-        <v>21-24</v>
+        <v>32-35</v>
       </c>
       <c r="H78" s="1">
         <v>0.15</v>
@@ -4059,10 +4059,10 @@
         <v>Yes</v>
       </c>
       <c r="M78" t="str">
-        <v/>
+        <v>Small Fishing Spot</v>
       </c>
       <c r="N78" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Farfetch'd","count":1}]}</v>
       </c>
       <c r="O78" t="str">
         <v/>
@@ -4070,10 +4070,10 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="B79" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="C79" t="str">
         <v>Route 39</v>
@@ -4088,7 +4088,7 @@
         <v>33-38</v>
       </c>
       <c r="G79" t="str">
-        <v>21-24</v>
+        <v>32-35</v>
       </c>
       <c r="H79" s="1">
         <v>0.15</v>
@@ -4106,10 +4106,10 @@
         <v>Yes</v>
       </c>
       <c r="M79" t="str">
-        <v/>
+        <v>Small Fishing Spot</v>
       </c>
       <c r="N79" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Farfetch'd","count":1}]}</v>
       </c>
       <c r="O79" t="str">
         <v/>
@@ -4117,10 +4117,10 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="B80" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="C80" t="str">
         <v>Route 39</v>
@@ -4135,13 +4135,13 @@
         <v>35-40</v>
       </c>
       <c r="G80" t="str">
-        <v>21-24</v>
+        <v>32-35</v>
       </c>
       <c r="H80" s="1">
         <v>0.1</v>
       </c>
-      <c r="I80" t="str">
-        <v/>
+      <c r="I80" s="1">
+        <v>0.17</v>
       </c>
       <c r="J80" t="str">
         <v>Yes</v>
@@ -4153,10 +4153,10 @@
         <v>Yes</v>
       </c>
       <c r="M80" t="str">
-        <v/>
+        <v>Small Fishing Spot</v>
       </c>
       <c r="N80" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Farfetch'd","count":1}]}</v>
       </c>
       <c r="O80" t="str">
         <v/>
@@ -4164,10 +4164,10 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="B81" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="C81" t="str">
         <v>Route 39</v>
@@ -4182,7 +4182,7 @@
         <v>35-40</v>
       </c>
       <c r="G81" t="str">
-        <v>21-24</v>
+        <v>32-35</v>
       </c>
       <c r="H81" s="1">
         <v>0.1</v>
@@ -4200,10 +4200,10 @@
         <v>Yes</v>
       </c>
       <c r="M81" t="str">
-        <v/>
+        <v>Small Fishing Spot</v>
       </c>
       <c r="N81" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Farfetch'd","count":1}]}</v>
       </c>
       <c r="O81" t="str">
         <v/>
@@ -4229,13 +4229,13 @@
         <v>36-41</v>
       </c>
       <c r="G82" t="str">
-        <v>22-25</v>
+        <v>34-37</v>
       </c>
       <c r="H82" s="1">
         <v>0.2</v>
       </c>
-      <c r="I82" t="str">
-        <v/>
+      <c r="I82" s="1">
+        <v>0.14</v>
       </c>
       <c r="J82" t="str">
         <v/>
@@ -4258,10 +4258,10 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B83" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="C83" t="str">
         <v>Small Fishing Spot</v>
@@ -4276,7 +4276,7 @@
         <v>36-41</v>
       </c>
       <c r="G83" t="str">
-        <v>22-25</v>
+        <v>34-37</v>
       </c>
       <c r="H83" s="1">
         <v>0.15</v>
@@ -4294,10 +4294,10 @@
         <v>Yes</v>
       </c>
       <c r="M83" t="str">
-        <v/>
+        <v>Cianwood Gym</v>
       </c>
       <c r="N83" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Dratini","count":2}]}</v>
       </c>
       <c r="O83" t="str">
         <v/>
@@ -4305,10 +4305,10 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B84" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="C84" t="str">
         <v>Small Fishing Spot</v>
@@ -4323,7 +4323,7 @@
         <v>36-41</v>
       </c>
       <c r="G84" t="str">
-        <v>22-25</v>
+        <v>34-37</v>
       </c>
       <c r="H84" s="1">
         <v>0.15</v>
@@ -4341,10 +4341,10 @@
         <v>Yes</v>
       </c>
       <c r="M84" t="str">
-        <v/>
+        <v>Cianwood Gym</v>
       </c>
       <c r="N84" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Dratini","count":2}]}</v>
       </c>
       <c r="O84" t="str">
         <v/>
@@ -4352,10 +4352,10 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B85" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="C85" t="str">
         <v>Small Fishing Spot</v>
@@ -4370,7 +4370,7 @@
         <v>36-41</v>
       </c>
       <c r="G85" t="str">
-        <v>22-25</v>
+        <v>34-37</v>
       </c>
       <c r="H85" s="1">
         <v>0.15</v>
@@ -4388,10 +4388,10 @@
         <v>Yes</v>
       </c>
       <c r="M85" t="str">
-        <v/>
+        <v>Cianwood Gym</v>
       </c>
       <c r="N85" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Dratini","count":2}]}</v>
       </c>
       <c r="O85" t="str">
         <v/>
@@ -4399,10 +4399,10 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B86" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="C86" t="str">
         <v>Small Fishing Spot</v>
@@ -4417,7 +4417,7 @@
         <v>36-41</v>
       </c>
       <c r="G86" t="str">
-        <v>22-25</v>
+        <v>34-37</v>
       </c>
       <c r="H86" s="1">
         <v>0.15</v>
@@ -4435,10 +4435,10 @@
         <v>Yes</v>
       </c>
       <c r="M86" t="str">
-        <v/>
+        <v>Cianwood Gym</v>
       </c>
       <c r="N86" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Dratini","count":2}]}</v>
       </c>
       <c r="O86" t="str">
         <v/>
@@ -4446,10 +4446,10 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B87" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="C87" t="str">
         <v>Small Fishing Spot</v>
@@ -4464,7 +4464,7 @@
         <v>37-42</v>
       </c>
       <c r="G87" t="str">
-        <v>22-25</v>
+        <v>34-37</v>
       </c>
       <c r="H87" s="1">
         <v>0.1</v>
@@ -4482,10 +4482,10 @@
         <v>Yes</v>
       </c>
       <c r="M87" t="str">
-        <v/>
+        <v>Cianwood Gym</v>
       </c>
       <c r="N87" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Dratini","count":2}]}</v>
       </c>
       <c r="O87" t="str">
         <v/>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B88" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="C88" t="str">
         <v>Small Fishing Spot</v>
@@ -4511,13 +4511,13 @@
         <v>37-42</v>
       </c>
       <c r="G88" t="str">
-        <v>22-25</v>
+        <v>34-37</v>
       </c>
       <c r="H88" s="1">
         <v>0.1</v>
       </c>
-      <c r="I88" t="str">
-        <v/>
+      <c r="I88" s="1">
+        <v>0.16</v>
       </c>
       <c r="J88" t="str">
         <v/>
@@ -4529,10 +4529,10 @@
         <v>Yes</v>
       </c>
       <c r="M88" t="str">
-        <v/>
+        <v>Cianwood Gym</v>
       </c>
       <c r="N88" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Dratini","count":2}]}</v>
       </c>
       <c r="O88" t="str">
         <v/>
@@ -4558,13 +4558,13 @@
         <v>38-43</v>
       </c>
       <c r="G89" t="str">
-        <v>24-27</v>
+        <v>37-40</v>
       </c>
       <c r="H89" s="1">
         <v>0.25</v>
       </c>
-      <c r="I89" t="str">
-        <v/>
+      <c r="I89" s="1">
+        <v>0.17</v>
       </c>
       <c r="J89" t="str">
         <v>Yes</v>
@@ -4587,10 +4587,10 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="B90" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="C90" t="str">
         <v>Route 47</v>
@@ -4605,13 +4605,13 @@
         <v>38-43</v>
       </c>
       <c r="G90" t="str">
-        <v>24-27</v>
+        <v>37-40</v>
       </c>
       <c r="H90" s="1">
         <v>0.25</v>
       </c>
-      <c r="I90" t="str">
-        <v/>
+      <c r="I90" s="1">
+        <v>0.17</v>
       </c>
       <c r="J90" t="str">
         <v>Yes</v>
@@ -4623,10 +4623,10 @@
         <v>Yes</v>
       </c>
       <c r="M90" t="str">
-        <v/>
+        <v>Safari Zone</v>
       </c>
       <c r="N90" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 47","count":50}}</v>
       </c>
       <c r="O90" t="str">
         <v/>
@@ -4634,10 +4634,10 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="B91" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="C91" t="str">
         <v>Route 47</v>
@@ -4652,7 +4652,7 @@
         <v>38-43</v>
       </c>
       <c r="G91" t="str">
-        <v>24-27</v>
+        <v>37-40</v>
       </c>
       <c r="H91" s="1">
         <v>0.15</v>
@@ -4670,10 +4670,10 @@
         <v>Yes</v>
       </c>
       <c r="M91" t="str">
-        <v/>
+        <v>Safari Zone</v>
       </c>
       <c r="N91" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 47","count":50}}</v>
       </c>
       <c r="O91" t="str">
         <v/>
@@ -4681,10 +4681,10 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="B92" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="C92" t="str">
         <v>Route 47</v>
@@ -4699,7 +4699,7 @@
         <v>38-43</v>
       </c>
       <c r="G92" t="str">
-        <v>24-27</v>
+        <v>37-40</v>
       </c>
       <c r="H92" s="1">
         <v>0.15</v>
@@ -4717,10 +4717,10 @@
         <v>Yes</v>
       </c>
       <c r="M92" t="str">
-        <v/>
+        <v>Safari Zone</v>
       </c>
       <c r="N92" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 47","count":50}}</v>
       </c>
       <c r="O92" t="str">
         <v/>
@@ -4728,10 +4728,10 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="B93" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="C93" t="str">
         <v>Route 47</v>
@@ -4746,13 +4746,13 @@
         <v>38-43</v>
       </c>
       <c r="G93" t="str">
-        <v>24-27</v>
+        <v>37-40</v>
       </c>
       <c r="H93" s="1">
         <v>0.1</v>
       </c>
-      <c r="I93" t="str">
-        <v/>
+      <c r="I93" s="1">
+        <v>0.17</v>
       </c>
       <c r="J93" t="str">
         <v>Yes</v>
@@ -4764,10 +4764,10 @@
         <v>Yes</v>
       </c>
       <c r="M93" t="str">
-        <v/>
+        <v>Safari Zone</v>
       </c>
       <c r="N93" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 47","count":50}}</v>
       </c>
       <c r="O93" t="str">
         <v/>
@@ -4775,10 +4775,10 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="B94" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="C94" t="str">
         <v>Route 47</v>
@@ -4793,7 +4793,7 @@
         <v>38-43</v>
       </c>
       <c r="G94" t="str">
-        <v>24-27</v>
+        <v>37-40</v>
       </c>
       <c r="H94" s="1">
         <v>0.1</v>
@@ -4811,10 +4811,10 @@
         <v>Yes</v>
       </c>
       <c r="M94" t="str">
-        <v/>
+        <v>Safari Zone</v>
       </c>
       <c r="N94" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 47","count":50}}</v>
       </c>
       <c r="O94" t="str">
         <v/>
@@ -4840,13 +4840,13 @@
         <v>40-45</v>
       </c>
       <c r="G95" t="str">
-        <v>25-28</v>
+        <v>39-42</v>
       </c>
       <c r="H95" s="1">
         <v>0.2</v>
       </c>
-      <c r="I95" t="str">
-        <v/>
+      <c r="I95" s="1">
+        <v>0.14</v>
       </c>
       <c r="J95" t="str">
         <v>Yes</v>
@@ -4869,10 +4869,10 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B96" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="C96" t="str">
         <v>Mount Mortar</v>
@@ -4887,13 +4887,13 @@
         <v>40-45</v>
       </c>
       <c r="G96" t="str">
-        <v>25-28</v>
+        <v>39-42</v>
       </c>
       <c r="H96" s="1">
         <v>0.2</v>
       </c>
-      <c r="I96" t="str">
-        <v/>
+      <c r="I96" s="1">
+        <v>0.14</v>
       </c>
       <c r="J96" t="str">
         <v>Yes</v>
@@ -4905,10 +4905,10 @@
         <v>Yes</v>
       </c>
       <c r="M96" t="str">
-        <v/>
+        <v>Mahogany Gym</v>
       </c>
       <c r="N96" t="str">
-        <v/>
+        <v>{"catchByType":{"type":"Ghost","count":1}}</v>
       </c>
       <c r="O96" t="str">
         <v/>
@@ -4916,10 +4916,10 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B97" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="C97" t="str">
         <v>Mount Mortar</v>
@@ -4934,7 +4934,7 @@
         <v>42-47</v>
       </c>
       <c r="G97" t="str">
-        <v>25-28</v>
+        <v>39-42</v>
       </c>
       <c r="H97" s="1">
         <v>0.15</v>
@@ -4952,10 +4952,10 @@
         <v>Yes</v>
       </c>
       <c r="M97" t="str">
-        <v/>
+        <v>Mahogany Gym</v>
       </c>
       <c r="N97" t="str">
-        <v/>
+        <v>{"catchByType":{"type":"Ghost","count":1}}</v>
       </c>
       <c r="O97" t="str">
         <v/>
@@ -4963,10 +4963,10 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B98" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="C98" t="str">
         <v>Mount Mortar</v>
@@ -4981,7 +4981,7 @@
         <v>42-47</v>
       </c>
       <c r="G98" t="str">
-        <v>25-28</v>
+        <v>39-42</v>
       </c>
       <c r="H98" s="1">
         <v>0.15</v>
@@ -4999,10 +4999,10 @@
         <v>Yes</v>
       </c>
       <c r="M98" t="str">
-        <v/>
+        <v>Mahogany Gym</v>
       </c>
       <c r="N98" t="str">
-        <v/>
+        <v>{"catchByType":{"type":"Ghost","count":1}}</v>
       </c>
       <c r="O98" t="str">
         <v/>
@@ -5010,10 +5010,10 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B99" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="C99" t="str">
         <v>Mount Mortar</v>
@@ -5028,7 +5028,7 @@
         <v>42-47</v>
       </c>
       <c r="G99" t="str">
-        <v>25-28</v>
+        <v>39-42</v>
       </c>
       <c r="H99" s="1">
         <v>0.1</v>
@@ -5046,10 +5046,10 @@
         <v>Yes</v>
       </c>
       <c r="M99" t="str">
-        <v/>
+        <v>Mahogany Gym</v>
       </c>
       <c r="N99" t="str">
-        <v/>
+        <v>{"catchByType":{"type":"Ghost","count":1}}</v>
       </c>
       <c r="O99" t="str">
         <v/>
@@ -5057,10 +5057,10 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B100" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="C100" t="str">
         <v>Mount Mortar</v>
@@ -5075,7 +5075,7 @@
         <v>42-47</v>
       </c>
       <c r="G100" t="str">
-        <v>25-28</v>
+        <v>39-42</v>
       </c>
       <c r="H100" s="1">
         <v>0.1</v>
@@ -5093,10 +5093,10 @@
         <v>Yes</v>
       </c>
       <c r="M100" t="str">
-        <v/>
+        <v>Mahogany Gym</v>
       </c>
       <c r="N100" t="str">
-        <v/>
+        <v>{"catchByType":{"type":"Ghost","count":1}}</v>
       </c>
       <c r="O100" t="str">
         <v/>
@@ -5104,10 +5104,10 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B101" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="C101" t="str">
         <v>Mount Mortar</v>
@@ -5122,13 +5122,13 @@
         <v>43-48</v>
       </c>
       <c r="G101" t="str">
-        <v>25-28</v>
+        <v>39-42</v>
       </c>
       <c r="H101" s="1">
         <v>0.1</v>
       </c>
-      <c r="I101" t="str">
-        <v/>
+      <c r="I101" s="1">
+        <v>0.16</v>
       </c>
       <c r="J101" t="str">
         <v>Yes</v>
@@ -5140,10 +5140,10 @@
         <v>Yes</v>
       </c>
       <c r="M101" t="str">
-        <v/>
+        <v>Mahogany Gym</v>
       </c>
       <c r="N101" t="str">
-        <v/>
+        <v>{"catchByType":{"type":"Ghost","count":1}}</v>
       </c>
       <c r="O101" t="str">
         <v/>
@@ -5169,7 +5169,7 @@
         <v>48-54</v>
       </c>
       <c r="G102" t="str">
-        <v>27-30</v>
+        <v>41-45</v>
       </c>
       <c r="H102" s="1">
         <v>0.35</v>
@@ -5198,10 +5198,10 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C103" t="str">
         <v>Standard Fishing Spot</v>
@@ -5216,7 +5216,7 @@
         <v>48-54</v>
       </c>
       <c r="G103" t="str">
-        <v>27-30</v>
+        <v>41-45</v>
       </c>
       <c r="H103" s="1">
         <v>0.3</v>
@@ -5234,10 +5234,10 @@
         <v>Yes</v>
       </c>
       <c r="M103" t="str">
-        <v/>
+        <v>Ice Path</v>
       </c>
       <c r="N103" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Lanturn","count":1}]}</v>
       </c>
       <c r="O103" t="str">
         <v/>
@@ -5245,10 +5245,10 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C104" t="str">
         <v>Standard Fishing Spot</v>
@@ -5263,7 +5263,7 @@
         <v>49-55</v>
       </c>
       <c r="G104" t="str">
-        <v>27-30</v>
+        <v>41-45</v>
       </c>
       <c r="H104" s="1">
         <v>0.25</v>
@@ -5281,10 +5281,10 @@
         <v>Yes</v>
       </c>
       <c r="M104" t="str">
-        <v/>
+        <v>Ice Path</v>
       </c>
       <c r="N104" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Lanturn","count":1}]}</v>
       </c>
       <c r="O104" t="str">
         <v/>
@@ -5292,10 +5292,10 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C105" t="str">
         <v>Standard Fishing Spot</v>
@@ -5310,7 +5310,7 @@
         <v>50-56</v>
       </c>
       <c r="G105" t="str">
-        <v>27-30</v>
+        <v>41-45</v>
       </c>
       <c r="H105" s="1">
         <v>0.1</v>
@@ -5328,10 +5328,10 @@
         <v>Yes</v>
       </c>
       <c r="M105" t="str">
-        <v/>
+        <v>Ice Path</v>
       </c>
       <c r="N105" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Lanturn","count":1}]}</v>
       </c>
       <c r="O105" t="str">
         <v/>
@@ -5357,13 +5357,13 @@
         <v>52-57</v>
       </c>
       <c r="G106" t="str">
-        <v>29-32</v>
+        <v>43-47</v>
       </c>
       <c r="H106" s="1">
         <v>0.25</v>
       </c>
-      <c r="I106" t="str">
-        <v/>
+      <c r="I106" s="1">
+        <v>0.17</v>
       </c>
       <c r="J106" t="str">
         <v>Legacy</v>
@@ -5386,10 +5386,10 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C107" t="str">
         <v>Ice Path</v>
@@ -5404,13 +5404,13 @@
         <v>50-55</v>
       </c>
       <c r="G107" t="str">
-        <v>29-32</v>
+        <v>43-47</v>
       </c>
       <c r="H107" s="1">
         <v>0.25</v>
       </c>
-      <c r="I107" t="str">
-        <v/>
+      <c r="I107" s="1">
+        <v>0.17</v>
       </c>
       <c r="J107" t="str">
         <v>Legacy</v>
@@ -5422,10 +5422,10 @@
         <v>Yes</v>
       </c>
       <c r="M107" t="str">
-        <v/>
+        <v>Route 45</v>
       </c>
       <c r="N107" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Jynx","count":2}}</v>
       </c>
       <c r="O107" t="str">
         <v/>
@@ -5433,10 +5433,10 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C108" t="str">
         <v>Ice Path</v>
@@ -5451,7 +5451,7 @@
         <v>52-57</v>
       </c>
       <c r="G108" t="str">
-        <v>29-32</v>
+        <v>43-47</v>
       </c>
       <c r="H108" s="1">
         <v>0.15</v>
@@ -5469,10 +5469,10 @@
         <v>Yes</v>
       </c>
       <c r="M108" t="str">
-        <v/>
+        <v>Route 45</v>
       </c>
       <c r="N108" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Jynx","count":2}}</v>
       </c>
       <c r="O108" t="str">
         <v/>
@@ -5480,10 +5480,10 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C109" t="str">
         <v>Ice Path</v>
@@ -5498,7 +5498,7 @@
         <v>54-59</v>
       </c>
       <c r="G109" t="str">
-        <v>29-32</v>
+        <v>43-47</v>
       </c>
       <c r="H109" s="1">
         <v>0.15</v>
@@ -5516,10 +5516,10 @@
         <v>Yes</v>
       </c>
       <c r="M109" t="str">
-        <v/>
+        <v>Route 45</v>
       </c>
       <c r="N109" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Jynx","count":2}}</v>
       </c>
       <c r="O109" t="str">
         <v/>
@@ -5527,10 +5527,10 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C110" t="str">
         <v>Ice Path</v>
@@ -5545,13 +5545,13 @@
         <v>53-58</v>
       </c>
       <c r="G110" t="str">
-        <v>29-32</v>
+        <v>43-47</v>
       </c>
       <c r="H110" s="1">
         <v>0.1</v>
       </c>
-      <c r="I110" t="str">
-        <v/>
+      <c r="I110" s="1">
+        <v>0.17</v>
       </c>
       <c r="J110" t="str">
         <v>Legacy</v>
@@ -5563,10 +5563,10 @@
         <v>Yes</v>
       </c>
       <c r="M110" t="str">
-        <v/>
+        <v>Route 45</v>
       </c>
       <c r="N110" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Jynx","count":2}}</v>
       </c>
       <c r="O110" t="str">
         <v/>
@@ -5574,10 +5574,10 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C111" t="str">
         <v>Ice Path</v>
@@ -5592,7 +5592,7 @@
         <v>54-60</v>
       </c>
       <c r="G111" t="str">
-        <v>29-32</v>
+        <v>43-47</v>
       </c>
       <c r="H111" s="1">
         <v>0.1</v>
@@ -5610,10 +5610,10 @@
         <v>Yes</v>
       </c>
       <c r="M111" t="str">
-        <v/>
+        <v>Route 45</v>
       </c>
       <c r="N111" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Jynx","count":2}}</v>
       </c>
       <c r="O111" t="str">
         <v/>
@@ -5639,7 +5639,7 @@
         <v>58-64</v>
       </c>
       <c r="G112" t="str">
-        <v>30-33</v>
+        <v>46-50</v>
       </c>
       <c r="H112" s="1">
         <v>0.19</v>
@@ -5668,10 +5668,10 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B113" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="C113" t="str">
         <v>Route 45</v>
@@ -5686,7 +5686,7 @@
         <v>58-64</v>
       </c>
       <c r="G113" t="str">
-        <v>30-33</v>
+        <v>46-50</v>
       </c>
       <c r="H113" s="1">
         <v>0.19</v>
@@ -5704,10 +5704,10 @@
         <v>Yes</v>
       </c>
       <c r="M113" t="str">
-        <v/>
+        <v>Blackthorn Gym</v>
       </c>
       <c r="N113" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Pineco","quality":"Weak","count":1}]}</v>
       </c>
       <c r="O113" t="str">
         <v/>
@@ -5715,10 +5715,10 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B114" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="C114" t="str">
         <v>Route 45</v>
@@ -5733,7 +5733,7 @@
         <v>57-63</v>
       </c>
       <c r="G114" t="str">
-        <v>30-33</v>
+        <v>46-50</v>
       </c>
       <c r="H114" s="1">
         <v>0.15</v>
@@ -5751,10 +5751,10 @@
         <v>Yes</v>
       </c>
       <c r="M114" t="str">
-        <v/>
+        <v>Blackthorn Gym</v>
       </c>
       <c r="N114" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Pineco","quality":"Weak","count":1}]}</v>
       </c>
       <c r="O114" t="str">
         <v/>
@@ -5762,10 +5762,10 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B115" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="C115" t="str">
         <v>Route 45</v>
@@ -5780,13 +5780,13 @@
         <v>58-64</v>
       </c>
       <c r="G115" t="str">
-        <v>30-33</v>
+        <v>46-50</v>
       </c>
       <c r="H115" s="1">
         <v>0.23</v>
       </c>
-      <c r="I115" t="str">
-        <v/>
+      <c r="I115" s="1">
+        <v>0.14</v>
       </c>
       <c r="J115" t="str">
         <v>Yes</v>
@@ -5798,10 +5798,10 @@
         <v>Yes</v>
       </c>
       <c r="M115" t="str">
-        <v/>
+        <v>Blackthorn Gym</v>
       </c>
       <c r="N115" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Pineco","quality":"Weak","count":1}]}</v>
       </c>
       <c r="O115" t="str">
         <v/>
@@ -5809,10 +5809,10 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B116" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="C116" t="str">
         <v>Route 45</v>
@@ -5827,13 +5827,13 @@
         <v>57-64</v>
       </c>
       <c r="G116" t="str">
-        <v>30-33</v>
+        <v>46-50</v>
       </c>
       <c r="H116" s="1">
         <v>0.07</v>
       </c>
-      <c r="I116" t="str">
-        <v/>
+      <c r="I116" s="1">
+        <v>0.14</v>
       </c>
       <c r="J116" t="str">
         <v>Yes</v>
@@ -5845,10 +5845,10 @@
         <v>Yes</v>
       </c>
       <c r="M116" t="str">
-        <v/>
+        <v>Blackthorn Gym</v>
       </c>
       <c r="N116" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Pineco","quality":"Weak","count":1}]}</v>
       </c>
       <c r="O116" t="str">
         <v/>
@@ -5856,10 +5856,10 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B117" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="C117" t="str">
         <v>Route 45</v>
@@ -5874,13 +5874,13 @@
         <v>57-64</v>
       </c>
       <c r="G117" t="str">
-        <v>30-33</v>
+        <v>46-50</v>
       </c>
       <c r="H117" s="1">
         <v>0.08</v>
       </c>
-      <c r="I117" t="str">
-        <v/>
+      <c r="I117" s="1">
+        <v>0.14</v>
       </c>
       <c r="J117" t="str">
         <v>Yes</v>
@@ -5892,10 +5892,10 @@
         <v>Yes</v>
       </c>
       <c r="M117" t="str">
-        <v/>
+        <v>Blackthorn Gym</v>
       </c>
       <c r="N117" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Pineco","quality":"Weak","count":1}]}</v>
       </c>
       <c r="O117" t="str">
         <v/>
@@ -5903,10 +5903,10 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B118" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="C118" t="str">
         <v>Route 45</v>
@@ -5921,13 +5921,13 @@
         <v>57-64</v>
       </c>
       <c r="G118" t="str">
-        <v>30-33</v>
+        <v>46-50</v>
       </c>
       <c r="H118" s="1">
         <v>0.09</v>
       </c>
-      <c r="I118" t="str">
-        <v/>
+      <c r="I118" s="1">
+        <v>0.16</v>
       </c>
       <c r="J118" t="str">
         <v>Yes</v>
@@ -5939,10 +5939,10 @@
         <v>Yes</v>
       </c>
       <c r="M118" t="str">
-        <v/>
+        <v>Blackthorn Gym</v>
       </c>
       <c r="N118" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Pineco","quality":"Weak","count":1}]}</v>
       </c>
       <c r="O118" t="str">
         <v/>
@@ -5968,13 +5968,13 @@
         <v>62-68</v>
       </c>
       <c r="G119" t="str">
-        <v>32-35</v>
+        <v>48-52</v>
       </c>
       <c r="H119" s="1">
         <v>0.3</v>
       </c>
       <c r="I119" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J119" t="str">
         <v/>
@@ -5997,10 +5997,10 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="B120" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="C120" t="str">
         <v>Big Fishing Spot</v>
@@ -6015,13 +6015,13 @@
         <v>63-69</v>
       </c>
       <c r="G120" t="str">
-        <v>32-35</v>
+        <v>48-52</v>
       </c>
       <c r="H120" s="1">
         <v>0.25</v>
       </c>
-      <c r="I120" t="str">
-        <v/>
+      <c r="I120" s="1">
+        <v>0.17</v>
       </c>
       <c r="J120" t="str">
         <v/>
@@ -6033,10 +6033,10 @@
         <v>Yes</v>
       </c>
       <c r="M120" t="str">
-        <v/>
+        <v>Dark Cave</v>
       </c>
       <c r="N120" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Mantine","count":1}]}</v>
       </c>
       <c r="O120" t="str">
         <v/>
@@ -6044,10 +6044,10 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="B121" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="C121" t="str">
         <v>Big Fishing Spot</v>
@@ -6062,7 +6062,7 @@
         <v>62-68</v>
       </c>
       <c r="G121" t="str">
-        <v>32-35</v>
+        <v>48-52</v>
       </c>
       <c r="H121" s="1">
         <v>0.2</v>
@@ -6080,10 +6080,10 @@
         <v>Yes</v>
       </c>
       <c r="M121" t="str">
-        <v/>
+        <v>Dark Cave</v>
       </c>
       <c r="N121" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Mantine","count":1}]}</v>
       </c>
       <c r="O121" t="str">
         <v/>
@@ -6091,10 +6091,10 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="B122" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="C122" t="str">
         <v>Big Fishing Spot</v>
@@ -6109,13 +6109,13 @@
         <v>64-70</v>
       </c>
       <c r="G122" t="str">
-        <v>32-35</v>
+        <v>48-52</v>
       </c>
       <c r="H122" s="1">
         <v>0.1</v>
       </c>
-      <c r="I122" t="str">
-        <v/>
+      <c r="I122" s="1">
+        <v>0.17</v>
       </c>
       <c r="J122" t="str">
         <v/>
@@ -6127,10 +6127,10 @@
         <v>Yes</v>
       </c>
       <c r="M122" t="str">
-        <v/>
+        <v>Dark Cave</v>
       </c>
       <c r="N122" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Mantine","count":1}]}</v>
       </c>
       <c r="O122" t="str">
         <v/>
@@ -6138,10 +6138,10 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="B123" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="C123" t="str">
         <v>Big Fishing Spot</v>
@@ -6156,13 +6156,13 @@
         <v>64-70</v>
       </c>
       <c r="G123" t="str">
-        <v>32-35</v>
+        <v>48-52</v>
       </c>
       <c r="H123" s="1">
         <v>0.1</v>
       </c>
-      <c r="I123" t="str">
-        <v/>
+      <c r="I123" s="1">
+        <v>0.17</v>
       </c>
       <c r="J123" t="str">
         <v/>
@@ -6174,10 +6174,10 @@
         <v>Yes</v>
       </c>
       <c r="M123" t="str">
-        <v/>
+        <v>Dark Cave</v>
       </c>
       <c r="N123" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Mantine","count":1}]}</v>
       </c>
       <c r="O123" t="str">
         <v/>
@@ -6185,10 +6185,10 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="B124" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="C124" t="str">
         <v>Big Fishing Spot</v>
@@ -6203,13 +6203,13 @@
         <v>65-71</v>
       </c>
       <c r="G124" t="str">
-        <v>32-35</v>
+        <v>48-52</v>
       </c>
       <c r="H124" s="1">
         <v>0.05</v>
       </c>
       <c r="I124" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J124" t="str">
         <v/>
@@ -6221,10 +6221,10 @@
         <v>Yes</v>
       </c>
       <c r="M124" t="str">
-        <v/>
+        <v>Dark Cave</v>
       </c>
       <c r="N124" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Mantine","count":1}]}</v>
       </c>
       <c r="O124" t="str">
         <v/>
@@ -6250,13 +6250,13 @@
         <v>64-70</v>
       </c>
       <c r="G125" t="str">
-        <v>33-36</v>
+        <v>50-55</v>
       </c>
       <c r="H125" s="1">
         <v>0.25</v>
       </c>
-      <c r="I125" t="str">
-        <v/>
+      <c r="I125" s="1">
+        <v>0.17</v>
       </c>
       <c r="J125" t="str">
         <v>Legacy</v>
@@ -6279,10 +6279,10 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="B126" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="C126" t="str">
         <v>Dark Cave</v>
@@ -6297,7 +6297,7 @@
         <v>63-69</v>
       </c>
       <c r="G126" t="str">
-        <v>33-36</v>
+        <v>50-55</v>
       </c>
       <c r="H126" s="1">
         <v>0.15</v>
@@ -6315,10 +6315,10 @@
         <v>Yes</v>
       </c>
       <c r="M126" t="str">
-        <v/>
+        <v>Route 46</v>
       </c>
       <c r="N126" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Dunsparce","count":20}}</v>
       </c>
       <c r="O126" t="str">
         <v/>
@@ -6326,10 +6326,10 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="B127" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="C127" t="str">
         <v>Dark Cave</v>
@@ -6344,7 +6344,7 @@
         <v>64-70</v>
       </c>
       <c r="G127" t="str">
-        <v>33-36</v>
+        <v>50-55</v>
       </c>
       <c r="H127" s="1">
         <v>0.15</v>
@@ -6362,10 +6362,10 @@
         <v>Yes</v>
       </c>
       <c r="M127" t="str">
-        <v/>
+        <v>Route 46</v>
       </c>
       <c r="N127" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Dunsparce","count":20}}</v>
       </c>
       <c r="O127" t="str">
         <v/>
@@ -6373,10 +6373,10 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="B128" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="C128" t="str">
         <v>Dark Cave</v>
@@ -6391,13 +6391,13 @@
         <v>68-74</v>
       </c>
       <c r="G128" t="str">
-        <v>33-36</v>
+        <v>50-55</v>
       </c>
       <c r="H128" s="1">
         <v>0.1</v>
       </c>
-      <c r="I128" t="str">
-        <v/>
+      <c r="I128" s="1">
+        <v>0.17</v>
       </c>
       <c r="J128" t="str">
         <v>Legacy</v>
@@ -6409,10 +6409,10 @@
         <v>Yes</v>
       </c>
       <c r="M128" t="str">
-        <v/>
+        <v>Route 46</v>
       </c>
       <c r="N128" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Dunsparce","count":20}}</v>
       </c>
       <c r="O128" t="str">
         <v/>
@@ -6420,10 +6420,10 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="B129" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="C129" t="str">
         <v>Dark Cave</v>
@@ -6438,13 +6438,13 @@
         <v>65-71</v>
       </c>
       <c r="G129" t="str">
-        <v>33-36</v>
+        <v>50-55</v>
       </c>
       <c r="H129" s="1">
         <v>0.1</v>
       </c>
-      <c r="I129" t="str">
-        <v/>
+      <c r="I129" s="1">
+        <v>0.17</v>
       </c>
       <c r="J129" t="str">
         <v>Legacy</v>
@@ -6456,10 +6456,10 @@
         <v>Yes</v>
       </c>
       <c r="M129" t="str">
-        <v/>
+        <v>Route 46</v>
       </c>
       <c r="N129" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Dunsparce","count":20}}</v>
       </c>
       <c r="O129" t="str">
         <v/>
@@ -6467,10 +6467,10 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v/>
+        <v>Challenge 32</v>
       </c>
       <c r="B130" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="C130" t="str">
         <v>Dark Cave</v>
@@ -6485,13 +6485,13 @@
         <v>64-70</v>
       </c>
       <c r="G130" t="str">
-        <v>33-36</v>
+        <v>50-55</v>
       </c>
       <c r="H130" s="1">
         <v>0.25</v>
       </c>
-      <c r="I130" t="str">
-        <v/>
+      <c r="I130" s="1">
+        <v>0.15</v>
       </c>
       <c r="J130" t="str">
         <v>Legacy</v>
@@ -6503,10 +6503,10 @@
         <v>Yes</v>
       </c>
       <c r="M130" t="str">
-        <v/>
+        <v>Route 46</v>
       </c>
       <c r="N130" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Dunsparce","count":20}}</v>
       </c>
       <c r="O130" t="str">
         <v/>
@@ -6532,13 +6532,13 @@
         <v>68-74</v>
       </c>
       <c r="G131" t="str">
-        <v>35-38</v>
+        <v>53-58</v>
       </c>
       <c r="H131" s="1">
         <v>0.4</v>
       </c>
-      <c r="I131" t="str">
-        <v/>
+      <c r="I131" s="1">
+        <v>0.33</v>
       </c>
       <c r="J131" t="str">
         <v>Yes</v>
@@ -6561,10 +6561,10 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B132" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="C132" t="str">
         <v>Route 46</v>
@@ -6579,7 +6579,7 @@
         <v>66-72</v>
       </c>
       <c r="G132" t="str">
-        <v>35-38</v>
+        <v>53-58</v>
       </c>
       <c r="H132" s="1">
         <v>0.35</v>
@@ -6597,10 +6597,10 @@
         <v>Yes</v>
       </c>
       <c r="M132" t="str">
-        <v/>
+        <v>Johto Pokemon League</v>
       </c>
       <c r="N132" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Skarmory","count":10}}</v>
       </c>
       <c r="O132" t="str">
         <v/>
@@ -6608,10 +6608,10 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B133" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="C133" t="str">
         <v>Route 46</v>
@@ -6626,13 +6626,13 @@
         <v>70-76</v>
       </c>
       <c r="G133" t="str">
-        <v>35-38</v>
+        <v>53-58</v>
       </c>
       <c r="H133" s="1">
         <v>0.25</v>
       </c>
-      <c r="I133" t="str">
-        <v/>
+      <c r="I133" s="1">
+        <v>0.34</v>
       </c>
       <c r="J133" t="str">
         <v>Yes</v>
@@ -6644,10 +6644,10 @@
         <v>Yes</v>
       </c>
       <c r="M133" t="str">
-        <v/>
+        <v>Johto Pokemon League</v>
       </c>
       <c r="N133" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Skarmory","count":10}}</v>
       </c>
       <c r="O133" t="str">
         <v/>
@@ -6702,10 +6702,10 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="B135" t="str">
-        <v/>
+        <v>Johto Extra Challenge 1</v>
       </c>
       <c r="C135" t="str">
         <v>Goldenrod Game Corner</v>
@@ -6738,10 +6738,10 @@
         <v>Yes</v>
       </c>
       <c r="M135" t="str">
-        <v/>
+        <v>Team Rocket HQ</v>
       </c>
       <c r="N135" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Eevee","count":8}}</v>
       </c>
       <c r="O135" t="str">
         <v/>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="B136" t="str">
-        <v/>
+        <v>Johto Extra Challenge 1</v>
       </c>
       <c r="C136" t="str">
         <v>Goldenrod Game Corner</v>
@@ -6785,10 +6785,10 @@
         <v>Yes</v>
       </c>
       <c r="M136" t="str">
-        <v/>
+        <v>Team Rocket HQ</v>
       </c>
       <c r="N136" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Eevee","count":8}}</v>
       </c>
       <c r="O136" t="str">
         <v/>
@@ -6796,10 +6796,10 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="B137" t="str">
-        <v/>
+        <v>Johto Extra Challenge 1</v>
       </c>
       <c r="C137" t="str">
         <v>Goldenrod Game Corner</v>
@@ -6819,8 +6819,8 @@
       <c r="H137" s="1">
         <v>0.15</v>
       </c>
-      <c r="I137" t="str">
-        <v/>
+      <c r="I137" s="1">
+        <v>0.2</v>
       </c>
       <c r="J137" t="str">
         <v>Yes</v>
@@ -6832,10 +6832,10 @@
         <v>Yes</v>
       </c>
       <c r="M137" t="str">
-        <v/>
+        <v>Team Rocket HQ</v>
       </c>
       <c r="N137" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Eevee","count":8}}</v>
       </c>
       <c r="O137" t="str">
         <v/>
@@ -6843,10 +6843,10 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="B138" t="str">
-        <v/>
+        <v>Johto Extra Challenge 1</v>
       </c>
       <c r="C138" t="str">
         <v>Goldenrod Game Corner</v>
@@ -6866,8 +6866,8 @@
       <c r="H138" s="1">
         <v>0.15</v>
       </c>
-      <c r="I138" t="str">
-        <v/>
+      <c r="I138" s="1">
+        <v>0.2</v>
       </c>
       <c r="J138" t="str">
         <v>Yes</v>
@@ -6879,10 +6879,10 @@
         <v>Yes</v>
       </c>
       <c r="M138" t="str">
-        <v/>
+        <v>Team Rocket HQ</v>
       </c>
       <c r="N138" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Eevee","count":8}}</v>
       </c>
       <c r="O138" t="str">
         <v/>
@@ -6937,10 +6937,10 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v/>
+        <v>Johto Extra Challenge 1</v>
       </c>
       <c r="B140" t="str">
-        <v/>
+        <v>Johto Extra Challenge 2</v>
       </c>
       <c r="C140" t="str">
         <v>Team Rocket HQ</v>
@@ -6973,10 +6973,10 @@
         <v>Yes</v>
       </c>
       <c r="M140" t="str">
-        <v/>
+        <v>Lake of Rage</v>
       </c>
       <c r="N140" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Voltorb","count":10}}</v>
       </c>
       <c r="O140" t="str">
         <v/>
@@ -6984,10 +6984,10 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v/>
+        <v>Johto Extra Challenge 1</v>
       </c>
       <c r="B141" t="str">
-        <v/>
+        <v>Johto Extra Challenge 2</v>
       </c>
       <c r="C141" t="str">
         <v>Team Rocket HQ</v>
@@ -7020,10 +7020,10 @@
         <v>Yes</v>
       </c>
       <c r="M141" t="str">
-        <v/>
+        <v>Lake of Rage</v>
       </c>
       <c r="N141" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Voltorb","count":10}}</v>
       </c>
       <c r="O141" t="str">
         <v/>
@@ -7031,10 +7031,10 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v/>
+        <v>Johto Extra Challenge 1</v>
       </c>
       <c r="B142" t="str">
-        <v/>
+        <v>Johto Extra Challenge 2</v>
       </c>
       <c r="C142" t="str">
         <v>Team Rocket HQ</v>
@@ -7067,10 +7067,10 @@
         <v>Yes</v>
       </c>
       <c r="M142" t="str">
-        <v/>
+        <v>Lake of Rage</v>
       </c>
       <c r="N142" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Voltorb","count":10}}</v>
       </c>
       <c r="O142" t="str">
         <v/>
@@ -7125,10 +7125,10 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v/>
+        <v>Johto Extra Challenge 2</v>
       </c>
       <c r="B144" t="str">
-        <v/>
+        <v>Johto Extra Challenge 3</v>
       </c>
       <c r="C144" t="str">
         <v>Lake of Rage</v>
@@ -7161,10 +7161,10 @@
         <v>Yes</v>
       </c>
       <c r="M144" t="str">
-        <v/>
+        <v>Mount Silver</v>
       </c>
       <c r="N144" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Gyarados","count":1}]}</v>
       </c>
       <c r="O144" t="str">
         <v/>
@@ -7195,8 +7195,8 @@
       <c r="H145" s="1">
         <v>0.25</v>
       </c>
-      <c r="I145" t="str">
-        <v/>
+      <c r="I145" s="1">
+        <v>0.17</v>
       </c>
       <c r="J145" t="str">
         <v>Yes</v>
@@ -7219,10 +7219,10 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v/>
+        <v>Johto Extra Challenge 3</v>
       </c>
       <c r="B146" t="str">
-        <v/>
+        <v>Johto Extra Challenge 4</v>
       </c>
       <c r="C146" t="str">
         <v>Mount Silver</v>
@@ -7255,10 +7255,10 @@
         <v>Yes</v>
       </c>
       <c r="M146" t="str">
-        <v/>
+        <v>Ilex Forest 2</v>
       </c>
       <c r="N146" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Larvitar","count":5}]}</v>
       </c>
       <c r="O146" t="str">
         <v/>
@@ -7266,10 +7266,10 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v/>
+        <v>Johto Extra Challenge 3</v>
       </c>
       <c r="B147" t="str">
-        <v/>
+        <v>Johto Extra Challenge 4</v>
       </c>
       <c r="C147" t="str">
         <v>Mount Silver</v>
@@ -7302,10 +7302,10 @@
         <v>Yes</v>
       </c>
       <c r="M147" t="str">
-        <v/>
+        <v>Ilex Forest 2</v>
       </c>
       <c r="N147" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Larvitar","count":5}]}</v>
       </c>
       <c r="O147" t="str">
         <v/>
@@ -7313,10 +7313,10 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v/>
+        <v>Johto Extra Challenge 3</v>
       </c>
       <c r="B148" t="str">
-        <v/>
+        <v>Johto Extra Challenge 4</v>
       </c>
       <c r="C148" t="str">
         <v>Mount Silver</v>
@@ -7349,10 +7349,10 @@
         <v>Yes</v>
       </c>
       <c r="M148" t="str">
-        <v/>
+        <v>Ilex Forest 2</v>
       </c>
       <c r="N148" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Larvitar","count":5}]}</v>
       </c>
       <c r="O148" t="str">
         <v/>
@@ -7360,10 +7360,10 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v/>
+        <v>Johto Extra Challenge 3</v>
       </c>
       <c r="B149" t="str">
-        <v/>
+        <v>Johto Extra Challenge 4</v>
       </c>
       <c r="C149" t="str">
         <v>Mount Silver</v>
@@ -7383,8 +7383,8 @@
       <c r="H149" s="1">
         <v>0.1</v>
       </c>
-      <c r="I149" t="str">
-        <v/>
+      <c r="I149" s="1">
+        <v>0.17</v>
       </c>
       <c r="J149" t="str">
         <v>Yes</v>
@@ -7396,10 +7396,10 @@
         <v>Yes</v>
       </c>
       <c r="M149" t="str">
-        <v/>
+        <v>Ilex Forest 2</v>
       </c>
       <c r="N149" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Larvitar","count":5}]}</v>
       </c>
       <c r="O149" t="str">
         <v/>
@@ -7407,10 +7407,10 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v/>
+        <v>Johto Extra Challenge 3</v>
       </c>
       <c r="B150" t="str">
-        <v/>
+        <v>Johto Extra Challenge 4</v>
       </c>
       <c r="C150" t="str">
         <v>Mount Silver</v>
@@ -7443,10 +7443,10 @@
         <v>Yes</v>
       </c>
       <c r="M150" t="str">
-        <v/>
+        <v>Ilex Forest 2</v>
       </c>
       <c r="N150" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Larvitar","count":5}]}</v>
       </c>
       <c r="O150" t="str">
         <v/>
@@ -7478,7 +7478,7 @@
         <v>0.3</v>
       </c>
       <c r="I151" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J151" t="str">
         <v>Yes</v>
@@ -7501,10 +7501,10 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v/>
+        <v>Johto Extra Challenge 4</v>
       </c>
       <c r="B152" t="str">
-        <v/>
+        <v>Johto Extra Challenge 5</v>
       </c>
       <c r="C152" t="str">
         <v>Ilex Forest 2</v>
@@ -7537,10 +7537,10 @@
         <v>Yes</v>
       </c>
       <c r="M152" t="str">
-        <v/>
+        <v>Keys to Temporal Sanctuary Challenge</v>
       </c>
       <c r="N152" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Celebi","count":1}]}</v>
       </c>
       <c r="O152" t="str">
         <v/>
@@ -7548,10 +7548,10 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v/>
+        <v>Johto Extra Challenge 4</v>
       </c>
       <c r="B153" t="str">
-        <v/>
+        <v>Johto Extra Challenge 5</v>
       </c>
       <c r="C153" t="str">
         <v>Ilex Forest 2</v>
@@ -7584,10 +7584,10 @@
         <v>Yes</v>
       </c>
       <c r="M153" t="str">
-        <v/>
+        <v>Keys to Temporal Sanctuary Challenge</v>
       </c>
       <c r="N153" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Celebi","count":1}]}</v>
       </c>
       <c r="O153" t="str">
         <v/>
@@ -7595,10 +7595,10 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v/>
+        <v>Johto Extra Challenge 4</v>
       </c>
       <c r="B154" t="str">
-        <v/>
+        <v>Johto Extra Challenge 5</v>
       </c>
       <c r="C154" t="str">
         <v>Ilex Forest 2</v>
@@ -7631,10 +7631,10 @@
         <v>Yes</v>
       </c>
       <c r="M154" t="str">
-        <v/>
+        <v>Keys to Temporal Sanctuary Challenge</v>
       </c>
       <c r="N154" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Celebi","count":1}]}</v>
       </c>
       <c r="O154" t="str">
         <v/>
@@ -7642,10 +7642,10 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v/>
+        <v>Johto Extra Challenge 4</v>
       </c>
       <c r="B155" t="str">
-        <v/>
+        <v>Johto Extra Challenge 5</v>
       </c>
       <c r="C155" t="str">
         <v>Ilex Forest 2</v>
@@ -7665,8 +7665,8 @@
       <c r="H155" s="1">
         <v>0.1</v>
       </c>
-      <c r="I155" t="str">
-        <v/>
+      <c r="I155" s="1">
+        <v>0.17</v>
       </c>
       <c r="J155" t="str">
         <v>Yes</v>
@@ -7678,10 +7678,10 @@
         <v>Yes</v>
       </c>
       <c r="M155" t="str">
-        <v/>
+        <v>Keys to Temporal Sanctuary Challenge</v>
       </c>
       <c r="N155" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Celebi","count":1}]}</v>
       </c>
       <c r="O155" t="str">
         <v/>
@@ -7689,10 +7689,10 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v/>
+        <v>Johto Extra Challenge 4</v>
       </c>
       <c r="B156" t="str">
-        <v/>
+        <v>Johto Extra Challenge 5</v>
       </c>
       <c r="C156" t="str">
         <v>Ilex Forest 2</v>
@@ -7713,7 +7713,7 @@
         <v>0.05</v>
       </c>
       <c r="I156" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J156" t="str">
         <v>Yes</v>
@@ -7725,10 +7725,10 @@
         <v>Yes</v>
       </c>
       <c r="M156" t="str">
-        <v/>
+        <v>Keys to Temporal Sanctuary Challenge</v>
       </c>
       <c r="N156" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Celebi","count":1}]}</v>
       </c>
       <c r="O156" t="str">
         <v/>
@@ -7783,10 +7783,10 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B158" t="str">
-        <v/>
+        <v>Extra Challenge (Roaming)</v>
       </c>
       <c r="C158" t="str">
         <v>Extra Challenge (Roaming)</v>
@@ -7819,10 +7819,10 @@
         <v>No</v>
       </c>
       <c r="M158" t="str">
-        <v/>
+        <v>Keys to Temporal Sanctuary Challenge</v>
       </c>
       <c r="N158" t="str">
-        <v/>
+        <v>{"defeatMultipleSpecific":[{"name":"Raikou","count":1},{"name":"Entei","count":1},{"name":"Suicune","count":1}]}</v>
       </c>
       <c r="O158" t="str">
         <v/>
@@ -7830,10 +7830,10 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B159" t="str">
-        <v/>
+        <v>Extra Challenge (Roaming)</v>
       </c>
       <c r="C159" t="str">
         <v>Extra Challenge (Roaming)</v>
@@ -7866,10 +7866,10 @@
         <v>No</v>
       </c>
       <c r="M159" t="str">
-        <v/>
+        <v>Keys to Temporal Sanctuary Challenge</v>
       </c>
       <c r="N159" t="str">
-        <v/>
+        <v>{"defeatMultipleSpecific":[{"name":"Raikou","count":1},{"name":"Entei","count":1},{"name":"Suicune","count":1}]}</v>
       </c>
       <c r="O159" t="str">
         <v/>
@@ -7895,13 +7895,13 @@
         <v>72-76</v>
       </c>
       <c r="G160" t="str">
-        <v>37-40</v>
+        <v>55-60</v>
       </c>
       <c r="H160" s="1">
         <v>0.23</v>
       </c>
-      <c r="I160" t="str">
-        <v/>
+      <c r="I160" s="1">
+        <v>0.14</v>
       </c>
       <c r="J160" t="str">
         <v>Legacy</v>
@@ -7924,10 +7924,10 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="B161" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="C161" t="str">
         <v>Viridian Forest</v>
@@ -7942,13 +7942,13 @@
         <v>72-76</v>
       </c>
       <c r="G161" t="str">
-        <v>37-40</v>
+        <v>55-60</v>
       </c>
       <c r="H161" s="1">
         <v>0.24</v>
       </c>
       <c r="I161" s="1">
-        <v>0.14285714285714285</v>
+        <v>0.14</v>
       </c>
       <c r="J161" t="str">
         <v>Yes</v>
@@ -7960,10 +7960,10 @@
         <v>Yes</v>
       </c>
       <c r="M161" t="str">
-        <v/>
+        <v>Pewter Gym, Fossil Revival Lab</v>
       </c>
       <c r="N161" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Bellossom","count":2}]}</v>
       </c>
       <c r="O161" t="str">
         <v/>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="B162" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="C162" t="str">
         <v>Viridian Forest</v>
@@ -7989,7 +7989,7 @@
         <v>74-78</v>
       </c>
       <c r="G162" t="str">
-        <v>37-40</v>
+        <v>55-60</v>
       </c>
       <c r="H162" s="1">
         <v>0.14</v>
@@ -8007,10 +8007,10 @@
         <v>Yes</v>
       </c>
       <c r="M162" t="str">
-        <v/>
+        <v>Pewter Gym, Fossil Revival Lab</v>
       </c>
       <c r="N162" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Bellossom","count":2}]}</v>
       </c>
       <c r="O162" t="str">
         <v/>
@@ -8018,10 +8018,10 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="B163" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="C163" t="str">
         <v>Viridian Forest</v>
@@ -8036,7 +8036,7 @@
         <v>74-78</v>
       </c>
       <c r="G163" t="str">
-        <v>37-40</v>
+        <v>55-60</v>
       </c>
       <c r="H163" s="1">
         <v>0.14</v>
@@ -8054,10 +8054,10 @@
         <v>Yes</v>
       </c>
       <c r="M163" t="str">
-        <v/>
+        <v>Pewter Gym, Fossil Revival Lab</v>
       </c>
       <c r="N163" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Bellossom","count":2}]}</v>
       </c>
       <c r="O163" t="str">
         <v/>
@@ -8065,10 +8065,10 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="B164" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="C164" t="str">
         <v>Viridian Forest</v>
@@ -8083,7 +8083,7 @@
         <v>75-78</v>
       </c>
       <c r="G164" t="str">
-        <v>37-40</v>
+        <v>55-60</v>
       </c>
       <c r="H164" s="1">
         <v>0.1</v>
@@ -8101,10 +8101,10 @@
         <v>Yes</v>
       </c>
       <c r="M164" t="str">
-        <v/>
+        <v>Pewter Gym, Fossil Revival Lab</v>
       </c>
       <c r="N164" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Bellossom","count":2}]}</v>
       </c>
       <c r="O164" t="str">
         <v/>
@@ -8112,10 +8112,10 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="B165" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="C165" t="str">
         <v>Viridian Forest</v>
@@ -8130,7 +8130,7 @@
         <v>75-78</v>
       </c>
       <c r="G165" t="str">
-        <v>37-40</v>
+        <v>55-60</v>
       </c>
       <c r="H165" s="1">
         <v>0.1</v>
@@ -8148,10 +8148,10 @@
         <v>Yes</v>
       </c>
       <c r="M165" t="str">
-        <v/>
+        <v>Pewter Gym, Fossil Revival Lab</v>
       </c>
       <c r="N165" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Bellossom","count":2}]}</v>
       </c>
       <c r="O165" t="str">
         <v/>
@@ -8159,10 +8159,10 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="B166" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="C166" t="str">
         <v>Viridian Forest</v>
@@ -8177,13 +8177,13 @@
         <v>72-78</v>
       </c>
       <c r="G166" t="str">
-        <v>37-40</v>
+        <v>55-60</v>
       </c>
       <c r="H166" s="1">
         <v>0.05</v>
       </c>
-      <c r="I166" t="str">
-        <v/>
+      <c r="I166" s="1">
+        <v>0.16</v>
       </c>
       <c r="J166" t="str">
         <v>Legacy</v>
@@ -8195,10 +8195,10 @@
         <v>Yes</v>
       </c>
       <c r="M166" t="str">
-        <v/>
+        <v>Pewter Gym, Fossil Revival Lab</v>
       </c>
       <c r="N166" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Bellossom","count":2}]}</v>
       </c>
       <c r="O166" t="str">
         <v/>
@@ -8224,7 +8224,7 @@
         <v>76-80</v>
       </c>
       <c r="G167" t="str">
-        <v>38-41</v>
+        <v>57-62</v>
       </c>
       <c r="H167" s="1">
         <v>0.22</v>
@@ -8253,10 +8253,10 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="B168" t="str">
-        <v/>
+        <v>Challenge 38</v>
       </c>
       <c r="C168" t="str">
         <v>Mount Moon</v>
@@ -8271,13 +8271,13 @@
         <v>76-81</v>
       </c>
       <c r="G168" t="str">
-        <v>38-41</v>
+        <v>57-62</v>
       </c>
       <c r="H168" s="1">
         <v>0.23</v>
       </c>
-      <c r="I168" t="str">
-        <v/>
+      <c r="I168" s="1">
+        <v>0.17</v>
       </c>
       <c r="J168" t="str">
         <v>Yes</v>
@@ -8289,10 +8289,10 @@
         <v>Yes</v>
       </c>
       <c r="M168" t="str">
-        <v/>
+        <v>Cerulean Gym, Rock Tunnel</v>
       </c>
       <c r="N168" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Crobat","count":1}]}</v>
       </c>
       <c r="O168" t="str">
         <v/>
@@ -8300,10 +8300,10 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="B169" t="str">
-        <v/>
+        <v>Challenge 38</v>
       </c>
       <c r="C169" t="str">
         <v>Mount Moon</v>
@@ -8318,7 +8318,7 @@
         <v>78-82</v>
       </c>
       <c r="G169" t="str">
-        <v>38-41</v>
+        <v>57-62</v>
       </c>
       <c r="H169" s="1">
         <v>0.18</v>
@@ -8336,10 +8336,10 @@
         <v>Yes</v>
       </c>
       <c r="M169" t="str">
-        <v/>
+        <v>Cerulean Gym, Rock Tunnel</v>
       </c>
       <c r="N169" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Crobat","count":1}]}</v>
       </c>
       <c r="O169" t="str">
         <v/>
@@ -8347,10 +8347,10 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="B170" t="str">
-        <v/>
+        <v>Challenge 38</v>
       </c>
       <c r="C170" t="str">
         <v>Mount Moon</v>
@@ -8365,7 +8365,7 @@
         <v>77-81</v>
       </c>
       <c r="G170" t="str">
-        <v>38-41</v>
+        <v>57-62</v>
       </c>
       <c r="H170" s="1">
         <v>0.14</v>
@@ -8383,10 +8383,10 @@
         <v>Yes</v>
       </c>
       <c r="M170" t="str">
-        <v/>
+        <v>Cerulean Gym, Rock Tunnel</v>
       </c>
       <c r="N170" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Crobat","count":1}]}</v>
       </c>
       <c r="O170" t="str">
         <v/>
@@ -8394,10 +8394,10 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="B171" t="str">
-        <v/>
+        <v>Challenge 38</v>
       </c>
       <c r="C171" t="str">
         <v>Mount Moon</v>
@@ -8412,7 +8412,7 @@
         <v>78-82</v>
       </c>
       <c r="G171" t="str">
-        <v>38-41</v>
+        <v>57-62</v>
       </c>
       <c r="H171" s="1">
         <v>0.14</v>
@@ -8430,10 +8430,10 @@
         <v>Yes</v>
       </c>
       <c r="M171" t="str">
-        <v/>
+        <v>Cerulean Gym, Rock Tunnel</v>
       </c>
       <c r="N171" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Crobat","count":1}]}</v>
       </c>
       <c r="O171" t="str">
         <v/>
@@ -8441,10 +8441,10 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="B172" t="str">
-        <v/>
+        <v>Challenge 38</v>
       </c>
       <c r="C172" t="str">
         <v>Mount Moon</v>
@@ -8459,13 +8459,13 @@
         <v>76-82</v>
       </c>
       <c r="G172" t="str">
-        <v>38-41</v>
+        <v>57-62</v>
       </c>
       <c r="H172" s="1">
         <v>0.09</v>
       </c>
-      <c r="I172" t="str">
-        <v/>
+      <c r="I172" s="1">
+        <v>0.15</v>
       </c>
       <c r="J172" t="str">
         <v>Yes</v>
@@ -8477,10 +8477,10 @@
         <v>Yes</v>
       </c>
       <c r="M172" t="str">
-        <v/>
+        <v>Cerulean Gym, Rock Tunnel</v>
       </c>
       <c r="N172" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Crobat","count":1}]}</v>
       </c>
       <c r="O172" t="str">
         <v/>
@@ -8506,7 +8506,7 @@
         <v>79-83</v>
       </c>
       <c r="G173" t="str">
-        <v>38-41</v>
+        <v>57-62</v>
       </c>
       <c r="H173" s="1">
         <v>0.3</v>
@@ -8535,7 +8535,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v/>
+        <v>Challenge 38</v>
       </c>
       <c r="B174" t="str">
         <v/>
@@ -8553,7 +8553,7 @@
         <v>81-85</v>
       </c>
       <c r="G174" t="str">
-        <v>38-41</v>
+        <v>57-62</v>
       </c>
       <c r="H174" s="1">
         <v>0.25</v>
@@ -8582,7 +8582,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v/>
+        <v>Challenge 38</v>
       </c>
       <c r="B175" t="str">
         <v/>
@@ -8600,7 +8600,7 @@
         <v>81-85</v>
       </c>
       <c r="G175" t="str">
-        <v>38-41</v>
+        <v>57-62</v>
       </c>
       <c r="H175" s="1">
         <v>0.25</v>
@@ -8629,7 +8629,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v/>
+        <v>Challenge 38</v>
       </c>
       <c r="B176" t="str">
         <v/>
@@ -8647,7 +8647,7 @@
         <v>81-85</v>
       </c>
       <c r="G176" t="str">
-        <v>38-41</v>
+        <v>57-62</v>
       </c>
       <c r="H176" s="1">
         <v>0.2</v>
@@ -8694,13 +8694,13 @@
         <v>82-86</v>
       </c>
       <c r="G177" t="str">
-        <v>40-44</v>
+        <v>60-66</v>
       </c>
       <c r="H177" s="1">
         <v>0.4</v>
       </c>
-      <c r="I177" t="str">
-        <v/>
+      <c r="I177" s="1">
+        <v>0.33</v>
       </c>
       <c r="J177" t="str">
         <v>Yes</v>
@@ -8723,10 +8723,10 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v/>
+        <v>Challenge 40</v>
       </c>
       <c r="B178" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="C178" t="str">
         <v>Route 8</v>
@@ -8741,7 +8741,7 @@
         <v>83-87</v>
       </c>
       <c r="G178" t="str">
-        <v>40-44</v>
+        <v>60-66</v>
       </c>
       <c r="H178" s="1">
         <v>0.3</v>
@@ -8759,10 +8759,10 @@
         <v>Yes</v>
       </c>
       <c r="M178" t="str">
-        <v/>
+        <v>Celadon Gym, Casino, Casino Starter Trupe</v>
       </c>
       <c r="N178" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Slowpoke","count":20}}</v>
       </c>
       <c r="O178" t="str">
         <v/>
@@ -8770,10 +8770,10 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v/>
+        <v>Challenge 40</v>
       </c>
       <c r="B179" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="C179" t="str">
         <v>Route 8</v>
@@ -8788,7 +8788,7 @@
         <v>83-87</v>
       </c>
       <c r="G179" t="str">
-        <v>40-44</v>
+        <v>60-66</v>
       </c>
       <c r="H179" s="1">
         <v>0.3</v>
@@ -8806,10 +8806,10 @@
         <v>Yes</v>
       </c>
       <c r="M179" t="str">
-        <v/>
+        <v>Celadon Gym, Casino, Casino Starter Trupe</v>
       </c>
       <c r="N179" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Slowpoke","count":20}}</v>
       </c>
       <c r="O179" t="str">
         <v/>
@@ -8835,7 +8835,7 @@
         <v>82-86</v>
       </c>
       <c r="G180" t="str">
-        <v>40-44</v>
+        <v>60-66</v>
       </c>
       <c r="H180" s="1">
         <v>0.9</v>
@@ -8864,7 +8864,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v/>
+        <v>Challenge 40</v>
       </c>
       <c r="B181" t="str">
         <v/>
@@ -8882,7 +8882,7 @@
         <v>85-89</v>
       </c>
       <c r="G181" t="str">
-        <v>40-44</v>
+        <v>60-66</v>
       </c>
       <c r="H181" s="1">
         <v>0.1</v>
@@ -8929,13 +8929,13 @@
         <v>84-88</v>
       </c>
       <c r="G182" t="str">
-        <v>41-45</v>
+        <v>62-68</v>
       </c>
       <c r="H182" s="1">
         <v>0.25</v>
       </c>
-      <c r="I182" t="str">
-        <v/>
+      <c r="I182" s="1">
+        <v>0.17</v>
       </c>
       <c r="J182" t="str">
         <v>Yes</v>
@@ -8958,10 +8958,10 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="B183" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="C183" t="str">
         <v>Route 12</v>
@@ -8976,13 +8976,13 @@
         <v>84-88</v>
       </c>
       <c r="G183" t="str">
-        <v>41-45</v>
+        <v>62-68</v>
       </c>
       <c r="H183" s="1">
         <v>0.25</v>
       </c>
-      <c r="I183" t="str">
-        <v/>
+      <c r="I183" s="1">
+        <v>0.17</v>
       </c>
       <c r="J183" t="str">
         <v>Yes</v>
@@ -8994,10 +8994,10 @@
         <v>Yes</v>
       </c>
       <c r="M183" t="str">
-        <v/>
+        <v>Fuschia Gym, Kanto Safari Zone</v>
       </c>
       <c r="N183" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Snorlax","count":1}]}</v>
       </c>
       <c r="O183" t="str">
         <v/>
@@ -9005,10 +9005,10 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="B184" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="C184" t="str">
         <v>Route 12</v>
@@ -9023,7 +9023,7 @@
         <v>85-89</v>
       </c>
       <c r="G184" t="str">
-        <v>41-45</v>
+        <v>62-68</v>
       </c>
       <c r="H184" s="1">
         <v>0.2</v>
@@ -9041,10 +9041,10 @@
         <v>Yes</v>
       </c>
       <c r="M184" t="str">
-        <v/>
+        <v>Fuschia Gym, Kanto Safari Zone</v>
       </c>
       <c r="N184" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Snorlax","count":1}]}</v>
       </c>
       <c r="O184" t="str">
         <v/>
@@ -9052,10 +9052,10 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="B185" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="C185" t="str">
         <v>Route 12</v>
@@ -9070,7 +9070,7 @@
         <v>86-89</v>
       </c>
       <c r="G185" t="str">
-        <v>41-45</v>
+        <v>62-68</v>
       </c>
       <c r="H185" s="1">
         <v>0.15</v>
@@ -9088,10 +9088,10 @@
         <v>Yes</v>
       </c>
       <c r="M185" t="str">
-        <v/>
+        <v>Fuschia Gym, Kanto Safari Zone</v>
       </c>
       <c r="N185" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Snorlax","count":1}]}</v>
       </c>
       <c r="O185" t="str">
         <v/>
@@ -9099,10 +9099,10 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="B186" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="C186" t="str">
         <v>Route 12</v>
@@ -9117,13 +9117,13 @@
         <v>86-89</v>
       </c>
       <c r="G186" t="str">
-        <v>41-45</v>
+        <v>62-68</v>
       </c>
       <c r="H186" s="1">
         <v>0.1</v>
       </c>
-      <c r="I186" t="str">
-        <v/>
+      <c r="I186" s="1">
+        <v>0.17</v>
       </c>
       <c r="J186" t="str">
         <v>Yes</v>
@@ -9135,10 +9135,10 @@
         <v>Yes</v>
       </c>
       <c r="M186" t="str">
-        <v/>
+        <v>Fuschia Gym, Kanto Safari Zone</v>
       </c>
       <c r="N186" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Snorlax","count":1}]}</v>
       </c>
       <c r="O186" t="str">
         <v/>
@@ -9146,10 +9146,10 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="B187" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="C187" t="str">
         <v>Route 12</v>
@@ -9164,13 +9164,13 @@
         <v>88-89</v>
       </c>
       <c r="G187" t="str">
-        <v>41-45</v>
+        <v>62-68</v>
       </c>
       <c r="H187" s="1">
         <v>0.05</v>
       </c>
       <c r="I187" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J187" t="str">
         <v>Legacy</v>
@@ -9182,10 +9182,10 @@
         <v>Yes</v>
       </c>
       <c r="M187" t="str">
-        <v/>
+        <v>Fuschia Gym, Kanto Safari Zone</v>
       </c>
       <c r="N187" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Snorlax","count":1}]}</v>
       </c>
       <c r="O187" t="str">
         <v/>
@@ -9211,13 +9211,13 @@
         <v>86-90</v>
       </c>
       <c r="G188" t="str">
-        <v>41-45</v>
+        <v>62-68</v>
       </c>
       <c r="H188" s="1">
         <v>0.1</v>
       </c>
-      <c r="I188" t="str">
-        <v/>
+      <c r="I188" s="1">
+        <v>0.17</v>
       </c>
       <c r="J188" t="str">
         <v>Yes</v>
@@ -9240,7 +9240,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="B189" t="str">
         <v/>
@@ -9258,13 +9258,13 @@
         <v>86-90</v>
       </c>
       <c r="G189" t="str">
-        <v>41-45</v>
+        <v>62-68</v>
       </c>
       <c r="H189" s="1">
         <v>0.1</v>
       </c>
-      <c r="I189" t="str">
-        <v/>
+      <c r="I189" s="1">
+        <v>0.17</v>
       </c>
       <c r="J189" t="str">
         <v>Yes</v>
@@ -9287,7 +9287,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="B190" t="str">
         <v/>
@@ -9305,7 +9305,7 @@
         <v>87-90</v>
       </c>
       <c r="G190" t="str">
-        <v>41-45</v>
+        <v>62-68</v>
       </c>
       <c r="H190" s="1">
         <v>0.15</v>
@@ -9334,7 +9334,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="B191" t="str">
         <v/>
@@ -9352,7 +9352,7 @@
         <v>87-91</v>
       </c>
       <c r="G191" t="str">
-        <v>41-45</v>
+        <v>62-68</v>
       </c>
       <c r="H191" s="1">
         <v>0.2</v>
@@ -9381,7 +9381,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="B192" t="str">
         <v/>
@@ -9399,7 +9399,7 @@
         <v>87-90</v>
       </c>
       <c r="G192" t="str">
-        <v>41-45</v>
+        <v>62-68</v>
       </c>
       <c r="H192" s="1">
         <v>0.2</v>
@@ -9428,7 +9428,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="B193" t="str">
         <v/>
@@ -9446,13 +9446,13 @@
         <v>88-91</v>
       </c>
       <c r="G193" t="str">
-        <v>41-45</v>
+        <v>62-68</v>
       </c>
       <c r="H193" s="1">
         <v>0.25</v>
       </c>
-      <c r="I193" t="str">
-        <v/>
+      <c r="I193" s="1">
+        <v>0.15</v>
       </c>
       <c r="J193" t="str">
         <v>Yes</v>
@@ -9493,13 +9493,13 @@
         <v>39-44</v>
       </c>
       <c r="G194" t="str">
-        <v>43-47</v>
+        <v>64-70</v>
       </c>
       <c r="H194" s="1">
         <v>0.25</v>
       </c>
-      <c r="I194" t="str">
-        <v/>
+      <c r="I194" s="1">
+        <v>0.17</v>
       </c>
       <c r="J194" t="str">
         <v>Legacy</v>
@@ -9522,10 +9522,10 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B195" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="C195" t="str">
         <v>Safari Zone</v>
@@ -9540,13 +9540,13 @@
         <v>39-44</v>
       </c>
       <c r="G195" t="str">
-        <v>43-47</v>
+        <v>64-70</v>
       </c>
       <c r="H195" s="1">
         <v>0.25</v>
       </c>
-      <c r="I195" t="str">
-        <v/>
+      <c r="I195" s="1">
+        <v>0.17</v>
       </c>
       <c r="J195" t="str">
         <v>Legacy</v>
@@ -9558,10 +9558,10 @@
         <v>Yes</v>
       </c>
       <c r="M195" t="str">
-        <v/>
+        <v>Olivine Gym</v>
       </c>
       <c r="N195" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Nidorino","count":1},{"species":"Nidorina","count":1}]}</v>
       </c>
       <c r="O195" t="str">
         <v/>
@@ -9569,10 +9569,10 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B196" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="C196" t="str">
         <v>Safari Zone</v>
@@ -9587,7 +9587,7 @@
         <v>40-45</v>
       </c>
       <c r="G196" t="str">
-        <v>43-47</v>
+        <v>64-70</v>
       </c>
       <c r="H196" s="1">
         <v>0.15</v>
@@ -9605,10 +9605,10 @@
         <v>Yes</v>
       </c>
       <c r="M196" t="str">
-        <v/>
+        <v>Olivine Gym</v>
       </c>
       <c r="N196" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Nidorino","count":1},{"species":"Nidorina","count":1}]}</v>
       </c>
       <c r="O196" t="str">
         <v/>
@@ -9616,10 +9616,10 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B197" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="C197" t="str">
         <v>Safari Zone</v>
@@ -9634,7 +9634,7 @@
         <v>40-45</v>
       </c>
       <c r="G197" t="str">
-        <v>43-47</v>
+        <v>64-70</v>
       </c>
       <c r="H197" s="1">
         <v>0.15</v>
@@ -9652,10 +9652,10 @@
         <v>Yes</v>
       </c>
       <c r="M197" t="str">
-        <v/>
+        <v>Olivine Gym</v>
       </c>
       <c r="N197" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Nidorino","count":1},{"species":"Nidorina","count":1}]}</v>
       </c>
       <c r="O197" t="str">
         <v/>
@@ -9663,10 +9663,10 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B198" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="C198" t="str">
         <v>Safari Zone</v>
@@ -9681,13 +9681,13 @@
         <v>39-44</v>
       </c>
       <c r="G198" t="str">
-        <v>43-47</v>
+        <v>64-70</v>
       </c>
       <c r="H198" s="1">
         <v>0.1</v>
       </c>
-      <c r="I198" t="str">
-        <v/>
+      <c r="I198" s="1">
+        <v>0.17</v>
       </c>
       <c r="J198" t="str">
         <v>Yes</v>
@@ -9699,10 +9699,10 @@
         <v>Yes</v>
       </c>
       <c r="M198" t="str">
-        <v/>
+        <v>Olivine Gym</v>
       </c>
       <c r="N198" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Nidorino","count":1},{"species":"Nidorina","count":1}]}</v>
       </c>
       <c r="O198" t="str">
         <v/>
@@ -9710,10 +9710,10 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B199" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="C199" t="str">
         <v>Safari Zone</v>
@@ -9728,7 +9728,7 @@
         <v>39-44</v>
       </c>
       <c r="G199" t="str">
-        <v>43-47</v>
+        <v>64-70</v>
       </c>
       <c r="H199" s="1">
         <v>0.1</v>
@@ -9746,10 +9746,10 @@
         <v>Yes</v>
       </c>
       <c r="M199" t="str">
-        <v/>
+        <v>Olivine Gym</v>
       </c>
       <c r="N199" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Nidorino","count":1},{"species":"Nidorina","count":1}]}</v>
       </c>
       <c r="O199" t="str">
         <v/>
@@ -9775,7 +9775,7 @@
         <v>88-92</v>
       </c>
       <c r="G200" t="str">
-        <v>43-47</v>
+        <v>64-70</v>
       </c>
       <c r="H200" s="1">
         <v>0.25</v>
@@ -9804,7 +9804,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B201" t="str">
         <v/>
@@ -9822,7 +9822,7 @@
         <v>88-92</v>
       </c>
       <c r="G201" t="str">
-        <v>43-47</v>
+        <v>64-70</v>
       </c>
       <c r="H201" s="1">
         <v>0.25</v>
@@ -9851,7 +9851,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B202" t="str">
         <v/>
@@ -9869,7 +9869,7 @@
         <v>90-93</v>
       </c>
       <c r="G202" t="str">
-        <v>43-47</v>
+        <v>64-70</v>
       </c>
       <c r="H202" s="1">
         <v>0.2</v>
@@ -9898,7 +9898,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B203" t="str">
         <v/>
@@ -9916,7 +9916,7 @@
         <v>90-93</v>
       </c>
       <c r="G203" t="str">
-        <v>43-47</v>
+        <v>64-70</v>
       </c>
       <c r="H203" s="1">
         <v>0.2</v>
@@ -9945,7 +9945,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B204" t="str">
         <v/>
@@ -9963,7 +9963,7 @@
         <v>92-93</v>
       </c>
       <c r="G204" t="str">
-        <v>43-47</v>
+        <v>64-70</v>
       </c>
       <c r="H204" s="1">
         <v>0.1</v>
@@ -10010,13 +10010,13 @@
         <v>90-94</v>
       </c>
       <c r="G205" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H205" s="1">
         <v>0.25</v>
       </c>
-      <c r="I205" t="str">
-        <v/>
+      <c r="I205" s="1">
+        <v>0.17</v>
       </c>
       <c r="J205" t="str">
         <v>Yes</v>
@@ -10039,10 +10039,10 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B206" t="str">
-        <v/>
+        <v>Challenge 46</v>
       </c>
       <c r="C206" t="str">
         <v>Sea Routes</v>
@@ -10057,13 +10057,13 @@
         <v>90-94</v>
       </c>
       <c r="G206" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H206" s="1">
         <v>0.25</v>
       </c>
-      <c r="I206" t="str">
-        <v/>
+      <c r="I206" s="1">
+        <v>0.17</v>
       </c>
       <c r="J206" t="str">
         <v>Yes</v>
@@ -10075,10 +10075,10 @@
         <v>Yes</v>
       </c>
       <c r="M206" t="str">
-        <v/>
+        <v>Cinnabar Gym, Pokemansion</v>
       </c>
       <c r="N206" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Sea Routes","count":100}}</v>
       </c>
       <c r="O206" t="str">
         <v/>
@@ -10086,10 +10086,10 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B207" t="str">
-        <v/>
+        <v>Challenge 46</v>
       </c>
       <c r="C207" t="str">
         <v>Sea Routes</v>
@@ -10104,7 +10104,7 @@
         <v>91-94</v>
       </c>
       <c r="G207" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H207" s="1">
         <v>0.15</v>
@@ -10122,10 +10122,10 @@
         <v>Yes</v>
       </c>
       <c r="M207" t="str">
-        <v/>
+        <v>Cinnabar Gym, Pokemansion</v>
       </c>
       <c r="N207" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Sea Routes","count":100}}</v>
       </c>
       <c r="O207" t="str">
         <v/>
@@ -10133,10 +10133,10 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B208" t="str">
-        <v/>
+        <v>Challenge 46</v>
       </c>
       <c r="C208" t="str">
         <v>Sea Routes</v>
@@ -10151,7 +10151,7 @@
         <v>91-94</v>
       </c>
       <c r="G208" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H208" s="1">
         <v>0.15</v>
@@ -10169,10 +10169,10 @@
         <v>Yes</v>
       </c>
       <c r="M208" t="str">
-        <v/>
+        <v>Cinnabar Gym, Pokemansion</v>
       </c>
       <c r="N208" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Sea Routes","count":100}}</v>
       </c>
       <c r="O208" t="str">
         <v/>
@@ -10180,10 +10180,10 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B209" t="str">
-        <v/>
+        <v>Challenge 46</v>
       </c>
       <c r="C209" t="str">
         <v>Sea Routes</v>
@@ -10198,13 +10198,13 @@
         <v>92-94</v>
       </c>
       <c r="G209" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H209" s="1">
         <v>0.1</v>
       </c>
-      <c r="I209" t="str">
-        <v/>
+      <c r="I209" s="1">
+        <v>0.17</v>
       </c>
       <c r="J209" t="str">
         <v>Yes</v>
@@ -10216,10 +10216,10 @@
         <v>Yes</v>
       </c>
       <c r="M209" t="str">
-        <v/>
+        <v>Cinnabar Gym, Pokemansion</v>
       </c>
       <c r="N209" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Sea Routes","count":100}}</v>
       </c>
       <c r="O209" t="str">
         <v/>
@@ -10227,10 +10227,10 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v/>
+        <v>Challenge 45</v>
       </c>
       <c r="B210" t="str">
-        <v/>
+        <v>Challenge 46</v>
       </c>
       <c r="C210" t="str">
         <v>Sea Routes</v>
@@ -10245,7 +10245,7 @@
         <v>92-94</v>
       </c>
       <c r="G210" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H210" s="1">
         <v>0.1</v>
@@ -10263,10 +10263,10 @@
         <v>Yes</v>
       </c>
       <c r="M210" t="str">
-        <v/>
+        <v>Cinnabar Gym, Pokemansion</v>
       </c>
       <c r="N210" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Sea Routes","count":100}}</v>
       </c>
       <c r="O210" t="str">
         <v/>
@@ -10292,7 +10292,7 @@
         <v>91-93</v>
       </c>
       <c r="G211" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H211" s="1">
         <v>0.3</v>
@@ -10321,7 +10321,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="B212" t="str">
         <v/>
@@ -10339,7 +10339,7 @@
         <v>91-93</v>
       </c>
       <c r="G212" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H212" s="1">
         <v>0.3</v>
@@ -10368,7 +10368,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="B213" t="str">
         <v/>
@@ -10386,7 +10386,7 @@
         <v>94-95</v>
       </c>
       <c r="G213" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H213" s="1">
         <v>0.1</v>
@@ -10415,7 +10415,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="B214" t="str">
         <v/>
@@ -10433,13 +10433,13 @@
         <v>92-94</v>
       </c>
       <c r="G214" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H214" s="1">
         <v>0.15</v>
       </c>
-      <c r="I214" t="str">
-        <v/>
+      <c r="I214" s="1">
+        <v>0.2</v>
       </c>
       <c r="J214" t="str">
         <v/>
@@ -10462,7 +10462,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="B215" t="str">
         <v/>
@@ -10480,13 +10480,13 @@
         <v>92-94</v>
       </c>
       <c r="G215" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H215" s="1">
         <v>0.15</v>
       </c>
-      <c r="I215" t="str">
-        <v/>
+      <c r="I215" s="1">
+        <v>0.2</v>
       </c>
       <c r="J215" t="str">
         <v/>
@@ -10527,13 +10527,13 @@
         <v>91-95</v>
       </c>
       <c r="G216" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H216" s="1">
         <v>0.2</v>
       </c>
-      <c r="I216" t="str">
-        <v/>
+      <c r="I216" s="1">
+        <v>0.14</v>
       </c>
       <c r="J216" t="str">
         <v>Legacy</v>
@@ -10574,13 +10574,13 @@
         <v>91-95</v>
       </c>
       <c r="G217" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H217" s="1">
         <v>0.2</v>
       </c>
-      <c r="I217" t="str">
-        <v/>
+      <c r="I217" s="1">
+        <v>0.14</v>
       </c>
       <c r="J217" t="str">
         <v>Yes</v>
@@ -10621,13 +10621,13 @@
         <v>91-95</v>
       </c>
       <c r="G218" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H218" s="1">
         <v>0.2</v>
       </c>
-      <c r="I218" t="str">
-        <v/>
+      <c r="I218" s="1">
+        <v>0.14</v>
       </c>
       <c r="J218" t="str">
         <v>Yes</v>
@@ -10668,7 +10668,7 @@
         <v>92-95</v>
       </c>
       <c r="G219" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H219" s="1">
         <v>0.15</v>
@@ -10715,7 +10715,7 @@
         <v>93-95</v>
       </c>
       <c r="G220" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H220" s="1">
         <v>0.15</v>
@@ -10762,13 +10762,13 @@
         <v>93-95</v>
       </c>
       <c r="G221" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H221" s="1">
         <v>0.05</v>
       </c>
-      <c r="I221" t="str">
-        <v/>
+      <c r="I221" s="1">
+        <v>0.14</v>
       </c>
       <c r="J221" t="str">
         <v>Yes</v>
@@ -10809,13 +10809,13 @@
         <v>93-95</v>
       </c>
       <c r="G222" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H222" s="1">
         <v>0.05</v>
       </c>
-      <c r="I222" t="str">
-        <v/>
+      <c r="I222" s="1">
+        <v>0.16</v>
       </c>
       <c r="J222" t="str">
         <v>Yes</v>
@@ -10885,10 +10885,10 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="B224" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 1</v>
       </c>
       <c r="C224" t="str">
         <v>Casino Starter Trupe</v>
@@ -10921,10 +10921,10 @@
         <v>No</v>
       </c>
       <c r="M224" t="str">
-        <v/>
+        <v>Casino Babies</v>
       </c>
       <c r="N224" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Bulbasaur","count":1},{"species":"Charmander","count":1},{"species":"Squirtle","count":1},{"species":"Chikorita","count":1},{"species":"Cyndaquil","count":1},{"species":"Totodile","count":1}]}</v>
       </c>
       <c r="O224" t="str">
         <v/>
@@ -10932,10 +10932,10 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="B225" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 1</v>
       </c>
       <c r="C225" t="str">
         <v>Casino Starter Trupe</v>
@@ -10968,10 +10968,10 @@
         <v>No</v>
       </c>
       <c r="M225" t="str">
-        <v/>
+        <v>Casino Babies</v>
       </c>
       <c r="N225" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Bulbasaur","count":1},{"species":"Charmander","count":1},{"species":"Squirtle","count":1},{"species":"Chikorita","count":1},{"species":"Cyndaquil","count":1},{"species":"Totodile","count":1}]}</v>
       </c>
       <c r="O225" t="str">
         <v/>
@@ -10979,10 +10979,10 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="B226" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 1</v>
       </c>
       <c r="C226" t="str">
         <v>Casino Starter Trupe</v>
@@ -11015,10 +11015,10 @@
         <v>No</v>
       </c>
       <c r="M226" t="str">
-        <v/>
+        <v>Casino Babies</v>
       </c>
       <c r="N226" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Bulbasaur","count":1},{"species":"Charmander","count":1},{"species":"Squirtle","count":1},{"species":"Chikorita","count":1},{"species":"Cyndaquil","count":1},{"species":"Totodile","count":1}]}</v>
       </c>
       <c r="O226" t="str">
         <v/>
@@ -11026,10 +11026,10 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="B227" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 1</v>
       </c>
       <c r="C227" t="str">
         <v>Casino Starter Trupe</v>
@@ -11062,10 +11062,10 @@
         <v>No</v>
       </c>
       <c r="M227" t="str">
-        <v/>
+        <v>Casino Babies</v>
       </c>
       <c r="N227" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Bulbasaur","count":1},{"species":"Charmander","count":1},{"species":"Squirtle","count":1},{"species":"Chikorita","count":1},{"species":"Cyndaquil","count":1},{"species":"Totodile","count":1}]}</v>
       </c>
       <c r="O227" t="str">
         <v/>
@@ -11073,10 +11073,10 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="B228" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 1</v>
       </c>
       <c r="C228" t="str">
         <v>Casino Starter Trupe</v>
@@ -11109,10 +11109,10 @@
         <v>No</v>
       </c>
       <c r="M228" t="str">
-        <v/>
+        <v>Casino Babies</v>
       </c>
       <c r="N228" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Bulbasaur","count":1},{"species":"Charmander","count":1},{"species":"Squirtle","count":1},{"species":"Chikorita","count":1},{"species":"Cyndaquil","count":1},{"species":"Totodile","count":1}]}</v>
       </c>
       <c r="O228" t="str">
         <v/>
@@ -11167,10 +11167,10 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 1</v>
       </c>
       <c r="B230" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 2</v>
       </c>
       <c r="C230" t="str">
         <v>Casino Babies</v>
@@ -11203,10 +11203,10 @@
         <v>No</v>
       </c>
       <c r="M230" t="str">
-        <v/>
+        <v>Casino Special Spot</v>
       </c>
       <c r="N230" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Raichu","count":1}]}</v>
       </c>
       <c r="O230" t="str">
         <v/>
@@ -11214,10 +11214,10 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 1</v>
       </c>
       <c r="B231" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 2</v>
       </c>
       <c r="C231" t="str">
         <v>Casino Babies</v>
@@ -11250,10 +11250,10 @@
         <v>No</v>
       </c>
       <c r="M231" t="str">
-        <v/>
+        <v>Casino Special Spot</v>
       </c>
       <c r="N231" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Raichu","count":1}]}</v>
       </c>
       <c r="O231" t="str">
         <v/>
@@ -11261,10 +11261,10 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 1</v>
       </c>
       <c r="B232" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 2</v>
       </c>
       <c r="C232" t="str">
         <v>Casino Babies</v>
@@ -11297,10 +11297,10 @@
         <v>No</v>
       </c>
       <c r="M232" t="str">
-        <v/>
+        <v>Casino Special Spot</v>
       </c>
       <c r="N232" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Raichu","count":1}]}</v>
       </c>
       <c r="O232" t="str">
         <v/>
@@ -11308,10 +11308,10 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 1</v>
       </c>
       <c r="B233" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 2</v>
       </c>
       <c r="C233" t="str">
         <v>Casino Babies</v>
@@ -11344,10 +11344,10 @@
         <v>No</v>
       </c>
       <c r="M233" t="str">
-        <v/>
+        <v>Casino Special Spot</v>
       </c>
       <c r="N233" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Raichu","count":1}]}</v>
       </c>
       <c r="O233" t="str">
         <v/>
@@ -11355,10 +11355,10 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 1</v>
       </c>
       <c r="B234" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 2</v>
       </c>
       <c r="C234" t="str">
         <v>Casino Babies</v>
@@ -11391,10 +11391,10 @@
         <v>No</v>
       </c>
       <c r="M234" t="str">
-        <v/>
+        <v>Casino Special Spot</v>
       </c>
       <c r="N234" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Raichu","count":1}]}</v>
       </c>
       <c r="O234" t="str">
         <v/>
@@ -11402,10 +11402,10 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 1</v>
       </c>
       <c r="B235" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 2</v>
       </c>
       <c r="C235" t="str">
         <v>Casino Babies</v>
@@ -11438,10 +11438,10 @@
         <v>No</v>
       </c>
       <c r="M235" t="str">
-        <v/>
+        <v>Casino Special Spot</v>
       </c>
       <c r="N235" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Raichu","count":1}]}</v>
       </c>
       <c r="O235" t="str">
         <v/>
@@ -11449,10 +11449,10 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 1</v>
       </c>
       <c r="B236" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 2</v>
       </c>
       <c r="C236" t="str">
         <v>Casino Babies</v>
@@ -11485,10 +11485,10 @@
         <v>No</v>
       </c>
       <c r="M236" t="str">
-        <v/>
+        <v>Casino Special Spot</v>
       </c>
       <c r="N236" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Raichu","count":1}]}</v>
       </c>
       <c r="O236" t="str">
         <v/>
@@ -11543,10 +11543,10 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 2</v>
       </c>
       <c r="B238" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="C238" t="str">
         <v>Casino Special Spot</v>
@@ -11579,10 +11579,10 @@
         <v>No</v>
       </c>
       <c r="M238" t="str">
-        <v/>
+        <v>Casino Eeveelution, Dojo</v>
       </c>
       <c r="N238" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Porygon2","count":1}]}</v>
       </c>
       <c r="O238" t="str">
         <v/>
@@ -11590,10 +11590,10 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 2</v>
       </c>
       <c r="B239" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="C239" t="str">
         <v>Casino Special Spot</v>
@@ -11626,10 +11626,10 @@
         <v>No</v>
       </c>
       <c r="M239" t="str">
-        <v/>
+        <v>Casino Eeveelution, Dojo</v>
       </c>
       <c r="N239" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Porygon2","count":1}]}</v>
       </c>
       <c r="O239" t="str">
         <v/>
@@ -11637,10 +11637,10 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 2</v>
       </c>
       <c r="B240" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="C240" t="str">
         <v>Casino Special Spot</v>
@@ -11673,10 +11673,10 @@
         <v>No</v>
       </c>
       <c r="M240" t="str">
-        <v/>
+        <v>Casino Eeveelution, Dojo</v>
       </c>
       <c r="N240" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Porygon2","count":1}]}</v>
       </c>
       <c r="O240" t="str">
         <v/>
@@ -11702,13 +11702,13 @@
         <v>85-90</v>
       </c>
       <c r="G241" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H241" s="1">
         <v>0.2</v>
       </c>
-      <c r="I241" t="str">
-        <v/>
+      <c r="I241" s="1">
+        <v>0.11</v>
       </c>
       <c r="J241" t="str">
         <v>Yes</v>
@@ -11731,7 +11731,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B242" t="str">
         <v/>
@@ -11749,7 +11749,7 @@
         <v>86-91</v>
       </c>
       <c r="G242" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H242" s="1">
         <v>0.1</v>
@@ -11778,7 +11778,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B243" t="str">
         <v/>
@@ -11796,7 +11796,7 @@
         <v>86-91</v>
       </c>
       <c r="G243" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H243" s="1">
         <v>0.1</v>
@@ -11825,7 +11825,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B244" t="str">
         <v/>
@@ -11843,7 +11843,7 @@
         <v>86-91</v>
       </c>
       <c r="G244" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H244" s="1">
         <v>0.1</v>
@@ -11872,7 +11872,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B245" t="str">
         <v/>
@@ -11890,7 +11890,7 @@
         <v>86-91</v>
       </c>
       <c r="G245" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H245" s="1">
         <v>0.1</v>
@@ -11919,7 +11919,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B246" t="str">
         <v/>
@@ -11937,7 +11937,7 @@
         <v>86-91</v>
       </c>
       <c r="G246" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H246" s="1">
         <v>0.1</v>
@@ -11966,7 +11966,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B247" t="str">
         <v/>
@@ -11984,7 +11984,7 @@
         <v>86-91</v>
       </c>
       <c r="G247" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H247" s="1">
         <v>0.1</v>
@@ -12013,7 +12013,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B248" t="str">
         <v/>
@@ -12031,7 +12031,7 @@
         <v>86-91</v>
       </c>
       <c r="G248" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H248" s="1">
         <v>0.1</v>
@@ -12060,7 +12060,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B249" t="str">
         <v/>
@@ -12078,7 +12078,7 @@
         <v>86-91</v>
       </c>
       <c r="G249" t="str">
-        <v>44-48</v>
+        <v>67-73</v>
       </c>
       <c r="H249" s="1">
         <v>0.1</v>
@@ -12154,10 +12154,10 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B251" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 4</v>
       </c>
       <c r="C251" t="str">
         <v>Dojo</v>
@@ -12190,10 +12190,10 @@
         <v>Yes</v>
       </c>
       <c r="M251" t="str">
-        <v/>
+        <v>Casino Late Trupe</v>
       </c>
       <c r="N251" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Hitmonlee","count":1},{"species":"Hitmonchan","count":1},{"species":"Hitmontop","count":1}]}</v>
       </c>
       <c r="O251" t="str">
         <v/>
@@ -12201,10 +12201,10 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B252" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 4</v>
       </c>
       <c r="C252" t="str">
         <v>Dojo</v>
@@ -12237,10 +12237,10 @@
         <v>Yes</v>
       </c>
       <c r="M252" t="str">
-        <v/>
+        <v>Casino Late Trupe</v>
       </c>
       <c r="N252" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Hitmonlee","count":1},{"species":"Hitmonchan","count":1},{"species":"Hitmontop","count":1}]}</v>
       </c>
       <c r="O252" t="str">
         <v/>
@@ -12248,10 +12248,10 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 3</v>
       </c>
       <c r="B253" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 4</v>
       </c>
       <c r="C253" t="str">
         <v>Dojo</v>
@@ -12284,10 +12284,10 @@
         <v>Yes</v>
       </c>
       <c r="M253" t="str">
-        <v/>
+        <v>Casino Late Trupe</v>
       </c>
       <c r="N253" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Hitmonlee","count":1},{"species":"Hitmonchan","count":1},{"species":"Hitmontop","count":1}]}</v>
       </c>
       <c r="O253" t="str">
         <v/>
@@ -12318,8 +12318,8 @@
       <c r="H254" s="1">
         <v>0.17</v>
       </c>
-      <c r="I254" t="str">
-        <v/>
+      <c r="I254" s="1">
+        <v>0.17</v>
       </c>
       <c r="J254" t="str">
         <v>Yes</v>
@@ -12342,10 +12342,10 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 4</v>
       </c>
       <c r="B255" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 5</v>
       </c>
       <c r="C255" t="str">
         <v>Casino Late Trupe</v>
@@ -12365,8 +12365,8 @@
       <c r="H255" s="1">
         <v>0.17</v>
       </c>
-      <c r="I255" t="str">
-        <v/>
+      <c r="I255" s="1">
+        <v>0.17</v>
       </c>
       <c r="J255" t="str">
         <v>Yes</v>
@@ -12378,10 +12378,10 @@
         <v>No</v>
       </c>
       <c r="M255" t="str">
-        <v/>
+        <v>Legendaries Nest</v>
       </c>
       <c r="N255" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Venusaur","count":1},{"species":"Charizard","count":1},{"species":"Blastoise","count":1}]}</v>
       </c>
       <c r="O255" t="str">
         <v/>
@@ -12389,10 +12389,10 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 4</v>
       </c>
       <c r="B256" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 5</v>
       </c>
       <c r="C256" t="str">
         <v>Casino Late Trupe</v>
@@ -12412,8 +12412,8 @@
       <c r="H256" s="1">
         <v>0.17</v>
       </c>
-      <c r="I256" t="str">
-        <v/>
+      <c r="I256" s="1">
+        <v>0.17</v>
       </c>
       <c r="J256" t="str">
         <v>Yes</v>
@@ -12425,10 +12425,10 @@
         <v>No</v>
       </c>
       <c r="M256" t="str">
-        <v/>
+        <v>Legendaries Nest</v>
       </c>
       <c r="N256" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Venusaur","count":1},{"species":"Charizard","count":1},{"species":"Blastoise","count":1}]}</v>
       </c>
       <c r="O256" t="str">
         <v/>
@@ -12436,10 +12436,10 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 4</v>
       </c>
       <c r="B257" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 5</v>
       </c>
       <c r="C257" t="str">
         <v>Casino Late Trupe</v>
@@ -12459,8 +12459,8 @@
       <c r="H257" s="1">
         <v>0.17</v>
       </c>
-      <c r="I257" t="str">
-        <v/>
+      <c r="I257" s="1">
+        <v>0.17</v>
       </c>
       <c r="J257" t="str">
         <v>Yes</v>
@@ -12472,10 +12472,10 @@
         <v>No</v>
       </c>
       <c r="M257" t="str">
-        <v/>
+        <v>Legendaries Nest</v>
       </c>
       <c r="N257" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Venusaur","count":1},{"species":"Charizard","count":1},{"species":"Blastoise","count":1}]}</v>
       </c>
       <c r="O257" t="str">
         <v/>
@@ -12483,10 +12483,10 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 4</v>
       </c>
       <c r="B258" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 5</v>
       </c>
       <c r="C258" t="str">
         <v>Casino Late Trupe</v>
@@ -12506,8 +12506,8 @@
       <c r="H258" s="1">
         <v>0.17</v>
       </c>
-      <c r="I258" t="str">
-        <v/>
+      <c r="I258" s="1">
+        <v>0.17</v>
       </c>
       <c r="J258" t="str">
         <v>Yes</v>
@@ -12519,10 +12519,10 @@
         <v>No</v>
       </c>
       <c r="M258" t="str">
-        <v/>
+        <v>Legendaries Nest</v>
       </c>
       <c r="N258" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Venusaur","count":1},{"species":"Charizard","count":1},{"species":"Blastoise","count":1}]}</v>
       </c>
       <c r="O258" t="str">
         <v/>
@@ -12530,10 +12530,10 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 4</v>
       </c>
       <c r="B259" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 5</v>
       </c>
       <c r="C259" t="str">
         <v>Casino Late Trupe</v>
@@ -12553,8 +12553,8 @@
       <c r="H259" s="1">
         <v>0.17</v>
       </c>
-      <c r="I259" t="str">
-        <v/>
+      <c r="I259" s="1">
+        <v>0.15</v>
       </c>
       <c r="J259" t="str">
         <v>Yes</v>
@@ -12566,10 +12566,10 @@
         <v>No</v>
       </c>
       <c r="M259" t="str">
-        <v/>
+        <v>Legendaries Nest</v>
       </c>
       <c r="N259" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Venusaur","count":1},{"species":"Charizard","count":1},{"species":"Blastoise","count":1}]}</v>
       </c>
       <c r="O259" t="str">
         <v/>
@@ -12624,10 +12624,10 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 5</v>
       </c>
       <c r="B261" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 6</v>
       </c>
       <c r="C261" t="str">
         <v>Legendaries Nest</v>
@@ -12660,10 +12660,10 @@
         <v>Yes</v>
       </c>
       <c r="M261" t="str">
-        <v/>
+        <v>Keys to Temporal Sanctuary Challenge</v>
       </c>
       <c r="N261" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Articuno","count":1},{"species":"Zapdos","count":1},{"species":"Moltres","count":1}]}</v>
       </c>
       <c r="O261" t="str">
         <v/>
@@ -12671,10 +12671,10 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 5</v>
       </c>
       <c r="B262" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 6</v>
       </c>
       <c r="C262" t="str">
         <v>Legendaries Nest</v>
@@ -12707,10 +12707,10 @@
         <v>Yes</v>
       </c>
       <c r="M262" t="str">
-        <v/>
+        <v>Keys to Temporal Sanctuary Challenge</v>
       </c>
       <c r="N262" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Articuno","count":1},{"species":"Zapdos","count":1},{"species":"Moltres","count":1}]}</v>
       </c>
       <c r="O262" t="str">
         <v/>
@@ -12718,10 +12718,10 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 5</v>
       </c>
       <c r="B263" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 6</v>
       </c>
       <c r="C263" t="str">
         <v>Legendaries Nest</v>
@@ -12754,10 +12754,10 @@
         <v>Yes</v>
       </c>
       <c r="M263" t="str">
-        <v/>
+        <v>Keys to Temporal Sanctuary Challenge</v>
       </c>
       <c r="N263" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Articuno","count":1},{"species":"Zapdos","count":1},{"species":"Moltres","count":1}]}</v>
       </c>
       <c r="O263" t="str">
         <v/>
@@ -12765,10 +12765,10 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 5</v>
       </c>
       <c r="B264" t="str">
-        <v/>
+        <v>Kanto Extra Challenge 6</v>
       </c>
       <c r="C264" t="str">
         <v>Legendaries Nest</v>
@@ -12801,10 +12801,10 @@
         <v>Yes</v>
       </c>
       <c r="M264" t="str">
-        <v/>
+        <v>Keys to Temporal Sanctuary Challenge</v>
       </c>
       <c r="N264" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Articuno","count":1},{"species":"Zapdos","count":1},{"species":"Moltres","count":1}]}</v>
       </c>
       <c r="O264" t="str">
         <v/>
@@ -12859,10 +12859,10 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v/>
+        <v>Keys to Temporal Sanctuary Challenge</v>
       </c>
       <c r="B266" t="str">
-        <v/>
+        <v>Temporal Sanctuary Challenge</v>
       </c>
       <c r="C266" t="str">
         <v>Temporal Sanctuary Spot</v>
@@ -12898,7 +12898,7 @@
         <v/>
       </c>
       <c r="N266" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Raikou","count":1},{"species":"Entei","count":1},{"species":"Suicune","count":1}]}</v>
       </c>
       <c r="O266" t="str">
         <v/>
@@ -12906,10 +12906,10 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v/>
+        <v>Keys to Temporal Sanctuary Challenge</v>
       </c>
       <c r="B267" t="str">
-        <v/>
+        <v>Temporal Sanctuary Challenge</v>
       </c>
       <c r="C267" t="str">
         <v>Temporal Sanctuary Spot</v>
@@ -12945,7 +12945,7 @@
         <v/>
       </c>
       <c r="N267" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Raikou","count":1},{"species":"Entei","count":1},{"species":"Suicune","count":1}]}</v>
       </c>
       <c r="O267" t="str">
         <v/>
@@ -12953,10 +12953,10 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v/>
+        <v>Keys to Temporal Sanctuary Challenge</v>
       </c>
       <c r="B268" t="str">
-        <v/>
+        <v>Temporal Sanctuary Challenge</v>
       </c>
       <c r="C268" t="str">
         <v>Temporal Sanctuary Spot</v>
@@ -12992,7 +12992,7 @@
         <v/>
       </c>
       <c r="N268" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Raikou","count":1},{"species":"Entei","count":1},{"species":"Suicune","count":1}]}</v>
       </c>
       <c r="O268" t="str">
         <v/>
@@ -13000,10 +13000,10 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v/>
+        <v>Keys to Temporal Sanctuary Challenge</v>
       </c>
       <c r="B269" t="str">
-        <v/>
+        <v>Temporal Sanctuary Challenge</v>
       </c>
       <c r="C269" t="str">
         <v>Temporal Sanctuary Spot</v>
@@ -13039,7 +13039,7 @@
         <v/>
       </c>
       <c r="N269" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Raikou","count":1},{"species":"Entei","count":1},{"species":"Suicune","count":1}]}</v>
       </c>
       <c r="O269" t="str">
         <v/>
@@ -13047,10 +13047,10 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v/>
+        <v>Keys to Temporal Sanctuary Challenge</v>
       </c>
       <c r="B270" t="str">
-        <v/>
+        <v>Temporal Sanctuary Challenge</v>
       </c>
       <c r="C270" t="str">
         <v>Temporal Sanctuary Spot</v>
@@ -13086,7 +13086,7 @@
         <v/>
       </c>
       <c r="N270" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Raikou","count":1},{"species":"Entei","count":1},{"species":"Suicune","count":1}]}</v>
       </c>
       <c r="O270" t="str">
         <v/>
@@ -13112,7 +13112,7 @@
         <v>91-95</v>
       </c>
       <c r="G271" t="str">
-        <v>46-50</v>
+        <v>69-75</v>
       </c>
       <c r="H271" s="1">
         <v>0.25</v>
@@ -13141,7 +13141,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v/>
+        <v>Challenge 47</v>
       </c>
       <c r="B272" t="str">
         <v/>
@@ -13159,7 +13159,7 @@
         <v>91-95</v>
       </c>
       <c r="G272" t="str">
-        <v>46-50</v>
+        <v>69-75</v>
       </c>
       <c r="H272" s="1">
         <v>0.25</v>
@@ -13188,7 +13188,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v/>
+        <v>Challenge 47</v>
       </c>
       <c r="B273" t="str">
         <v/>
@@ -13206,7 +13206,7 @@
         <v>91-95</v>
       </c>
       <c r="G273" t="str">
-        <v>46-50</v>
+        <v>69-75</v>
       </c>
       <c r="H273" s="1">
         <v>0.25</v>
@@ -13235,7 +13235,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v/>
+        <v>Challenge 47</v>
       </c>
       <c r="B274" t="str">
         <v/>
@@ -13253,7 +13253,7 @@
         <v>91-95</v>
       </c>
       <c r="G274" t="str">
-        <v>46-50</v>
+        <v>69-75</v>
       </c>
       <c r="H274" s="1">
         <v>0.25</v>
@@ -13280,16 +13280,909 @@
         <v/>
       </c>
     </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>Challenge 3</v>
+      </c>
+      <c r="B275" t="str">
+        <v>Challenge 4</v>
+      </c>
+      <c r="C275" t="str">
+        <v>Violet Gym</v>
+      </c>
+      <c r="D275" t="str">
+        <v/>
+      </c>
+      <c r="E275" t="str">
+        <v/>
+      </c>
+      <c r="F275" t="str">
+        <v/>
+      </c>
+      <c r="G275" t="str">
+        <v/>
+      </c>
+      <c r="H275" t="str">
+        <v/>
+      </c>
+      <c r="I275" t="str">
+        <v/>
+      </c>
+      <c r="J275" t="str">
+        <v/>
+      </c>
+      <c r="K275" t="str">
+        <v/>
+      </c>
+      <c r="L275" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M275" t="str">
+        <v>Ruins of Alph</v>
+      </c>
+      <c r="N275" t="str">
+        <v>{"earnBadge":{"name":"Zephyr Badge","leader":"Falkner","badgeCount":1}}</v>
+      </c>
+      <c r="O275" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>Challenge 8</v>
+      </c>
+      <c r="B276" t="str">
+        <v>Challenge 9</v>
+      </c>
+      <c r="C276" t="str">
+        <v>Azalea Gym</v>
+      </c>
+      <c r="D276" t="str">
+        <v/>
+      </c>
+      <c r="E276" t="str">
+        <v/>
+      </c>
+      <c r="F276" t="str">
+        <v/>
+      </c>
+      <c r="G276" t="str">
+        <v/>
+      </c>
+      <c r="H276" t="str">
+        <v/>
+      </c>
+      <c r="I276" t="str">
+        <v/>
+      </c>
+      <c r="J276" t="str">
+        <v/>
+      </c>
+      <c r="K276" t="str">
+        <v/>
+      </c>
+      <c r="L276" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M276" t="str">
+        <v>Ilex Forest</v>
+      </c>
+      <c r="N276" t="str">
+        <v>{"earnBadge":{"name":"Hive Badge","leader":"Bugsy","badgeCount":2}}</v>
+      </c>
+      <c r="O276" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>Challenge 11</v>
+      </c>
+      <c r="B277" t="str">
+        <v>Challenge 12</v>
+      </c>
+      <c r="C277" t="str">
+        <v>Goldenrod Gym</v>
+      </c>
+      <c r="D277" t="str">
+        <v/>
+      </c>
+      <c r="E277" t="str">
+        <v/>
+      </c>
+      <c r="F277" t="str">
+        <v/>
+      </c>
+      <c r="G277" t="str">
+        <v/>
+      </c>
+      <c r="H277" t="str">
+        <v/>
+      </c>
+      <c r="I277" t="str">
+        <v/>
+      </c>
+      <c r="J277" t="str">
+        <v/>
+      </c>
+      <c r="K277" t="str">
+        <v/>
+      </c>
+      <c r="L277" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M277" t="str">
+        <v>Route 35, Extra Challenge (Roaming)</v>
+      </c>
+      <c r="N277" t="str">
+        <v>{"earnBadge":{"name":"Plain Badge","leader":"Whitney","badgeCount":3}}</v>
+      </c>
+      <c r="O277" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>Challenge 17</v>
+      </c>
+      <c r="B278" t="str">
+        <v>Challenge 18</v>
+      </c>
+      <c r="C278" t="str">
+        <v>Ecruteak Gym</v>
+      </c>
+      <c r="D278" t="str">
+        <v/>
+      </c>
+      <c r="E278" t="str">
+        <v/>
+      </c>
+      <c r="F278" t="str">
+        <v/>
+      </c>
+      <c r="G278" t="str">
+        <v/>
+      </c>
+      <c r="H278" t="str">
+        <v/>
+      </c>
+      <c r="I278" t="str">
+        <v/>
+      </c>
+      <c r="J278" t="str">
+        <v/>
+      </c>
+      <c r="K278" t="str">
+        <v/>
+      </c>
+      <c r="L278" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M278" t="str">
+        <v>Route 38</v>
+      </c>
+      <c r="N278" t="str">
+        <v>{"earnBadge":{"name":"Fog Badge","leader":"Morty","badgeCount":4}}</v>
+      </c>
+      <c r="O278" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>Challenge 21</v>
+      </c>
+      <c r="B279" t="str">
+        <v>Challenge 22</v>
+      </c>
+      <c r="C279" t="str">
+        <v>Cianwood Gym</v>
+      </c>
+      <c r="D279" t="str">
+        <v/>
+      </c>
+      <c r="E279" t="str">
+        <v/>
+      </c>
+      <c r="F279" t="str">
+        <v/>
+      </c>
+      <c r="G279" t="str">
+        <v/>
+      </c>
+      <c r="H279" t="str">
+        <v/>
+      </c>
+      <c r="I279" t="str">
+        <v/>
+      </c>
+      <c r="J279" t="str">
+        <v/>
+      </c>
+      <c r="K279" t="str">
+        <v/>
+      </c>
+      <c r="L279" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M279" t="str">
+        <v>Route 47</v>
+      </c>
+      <c r="N279" t="str">
+        <v>{"earnBadge":{"name":"Storm Badge","leader":"Chuck","badgeCount":5}}</v>
+      </c>
+      <c r="O279" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>Challenge 24</v>
+      </c>
+      <c r="B280" t="str">
+        <v>Challenge 25</v>
+      </c>
+      <c r="C280" t="str">
+        <v>Olivine Gym</v>
+      </c>
+      <c r="D280" t="str">
+        <v/>
+      </c>
+      <c r="E280" t="str">
+        <v/>
+      </c>
+      <c r="F280" t="str">
+        <v/>
+      </c>
+      <c r="G280" t="str">
+        <v/>
+      </c>
+      <c r="H280" t="str">
+        <v/>
+      </c>
+      <c r="I280" t="str">
+        <v/>
+      </c>
+      <c r="J280" t="str">
+        <v/>
+      </c>
+      <c r="K280" t="str">
+        <v/>
+      </c>
+      <c r="L280" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M280" t="str">
+        <v>Mount Mortar</v>
+      </c>
+      <c r="N280" t="str">
+        <v>{"earnBadge":{"name":"Mineral Badge","leader":"Jasmine","badgeCount":6}}</v>
+      </c>
+      <c r="O280" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>Challenge 26</v>
+      </c>
+      <c r="B281" t="str">
+        <v>Challenge 27</v>
+      </c>
+      <c r="C281" t="str">
+        <v>Mahogany Gym</v>
+      </c>
+      <c r="D281" t="str">
+        <v/>
+      </c>
+      <c r="E281" t="str">
+        <v/>
+      </c>
+      <c r="F281" t="str">
+        <v/>
+      </c>
+      <c r="G281" t="str">
+        <v/>
+      </c>
+      <c r="H281" t="str">
+        <v/>
+      </c>
+      <c r="I281" t="str">
+        <v/>
+      </c>
+      <c r="J281" t="str">
+        <v/>
+      </c>
+      <c r="K281" t="str">
+        <v/>
+      </c>
+      <c r="L281" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M281" t="str">
+        <v>Standard Fishing Spot</v>
+      </c>
+      <c r="N281" t="str">
+        <v>{"earnBadge":{"name":"Glacier Badge","leader":"Pryce","badgeCount":7}}</v>
+      </c>
+      <c r="O281" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>Challenge 30</v>
+      </c>
+      <c r="B282" t="str">
+        <v>Challenge 31</v>
+      </c>
+      <c r="C282" t="str">
+        <v>Blackthorn Gym</v>
+      </c>
+      <c r="D282" t="str">
+        <v/>
+      </c>
+      <c r="E282" t="str">
+        <v/>
+      </c>
+      <c r="F282" t="str">
+        <v/>
+      </c>
+      <c r="G282" t="str">
+        <v/>
+      </c>
+      <c r="H282" t="str">
+        <v/>
+      </c>
+      <c r="I282" t="str">
+        <v/>
+      </c>
+      <c r="J282" t="str">
+        <v/>
+      </c>
+      <c r="K282" t="str">
+        <v/>
+      </c>
+      <c r="L282" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M282" t="str">
+        <v>Big Fishing Spot</v>
+      </c>
+      <c r="N282" t="str">
+        <v>{"earnBadge":{"name":"Rising Badge","leader":"Clair","badgeCount":8}}</v>
+      </c>
+      <c r="O282" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>Challenge 34</v>
+      </c>
+      <c r="B283" t="str">
+        <v>Challenge 35</v>
+      </c>
+      <c r="C283" t="str">
+        <v>Johto Pokemon League</v>
+      </c>
+      <c r="D283" t="str">
+        <v/>
+      </c>
+      <c r="E283" t="str">
+        <v/>
+      </c>
+      <c r="F283" t="str">
+        <v/>
+      </c>
+      <c r="G283" t="str">
+        <v/>
+      </c>
+      <c r="H283" t="str">
+        <v/>
+      </c>
+      <c r="I283" t="str">
+        <v/>
+      </c>
+      <c r="J283" t="str">
+        <v/>
+      </c>
+      <c r="K283" t="str">
+        <v/>
+      </c>
+      <c r="L283" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M283" t="str">
+        <v>Viridian Forest</v>
+      </c>
+      <c r="N283" t="str">
+        <v>{"defeatJohtoChampion":true}</v>
+      </c>
+      <c r="O283" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>Challenge 36</v>
+      </c>
+      <c r="B284" t="str">
+        <v>Challenge 37</v>
+      </c>
+      <c r="C284" t="str">
+        <v>Pewter Gym</v>
+      </c>
+      <c r="D284" t="str">
+        <v/>
+      </c>
+      <c r="E284" t="str">
+        <v/>
+      </c>
+      <c r="F284" t="str">
+        <v/>
+      </c>
+      <c r="G284" t="str">
+        <v/>
+      </c>
+      <c r="H284" t="str">
+        <v/>
+      </c>
+      <c r="I284" t="str">
+        <v/>
+      </c>
+      <c r="J284" t="str">
+        <v/>
+      </c>
+      <c r="K284" t="str">
+        <v/>
+      </c>
+      <c r="L284" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M284" t="str">
+        <v>Mount Moon</v>
+      </c>
+      <c r="N284" t="str">
+        <v>{"earnBadge":{"name":"Badge 9","leader":"Brock","badgeCount":9}}</v>
+      </c>
+      <c r="O284" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>Challenge 38</v>
+      </c>
+      <c r="B285" t="str">
+        <v>Challenge 39</v>
+      </c>
+      <c r="C285" t="str">
+        <v>Cerulean Gym</v>
+      </c>
+      <c r="D285" t="str">
+        <v/>
+      </c>
+      <c r="E285" t="str">
+        <v/>
+      </c>
+      <c r="F285" t="str">
+        <v/>
+      </c>
+      <c r="G285" t="str">
+        <v/>
+      </c>
+      <c r="H285" t="str">
+        <v/>
+      </c>
+      <c r="I285" t="str">
+        <v/>
+      </c>
+      <c r="J285" t="str">
+        <v/>
+      </c>
+      <c r="K285" t="str">
+        <v/>
+      </c>
+      <c r="L285" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M285" t="str">
+        <v>Vermilion Gym</v>
+      </c>
+      <c r="N285" t="str">
+        <v>{"earnBadge":{"name":"Badge 10","leader":"Misty","badgeCount":10}}</v>
+      </c>
+      <c r="O285" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>Challenge 39</v>
+      </c>
+      <c r="B286" t="str">
+        <v>Challenge 40</v>
+      </c>
+      <c r="C286" t="str">
+        <v>Vermilion Gym</v>
+      </c>
+      <c r="D286" t="str">
+        <v/>
+      </c>
+      <c r="E286" t="str">
+        <v/>
+      </c>
+      <c r="F286" t="str">
+        <v/>
+      </c>
+      <c r="G286" t="str">
+        <v/>
+      </c>
+      <c r="H286" t="str">
+        <v/>
+      </c>
+      <c r="I286" t="str">
+        <v/>
+      </c>
+      <c r="J286" t="str">
+        <v/>
+      </c>
+      <c r="K286" t="str">
+        <v/>
+      </c>
+      <c r="L286" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M286" t="str">
+        <v>Route 8, Diglett Cave</v>
+      </c>
+      <c r="N286" t="str">
+        <v>{"earnBadge":{"name":"Badge 11","leader":"Lt. Surge","badgeCount":11}}</v>
+      </c>
+      <c r="O286" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>Challenge 41</v>
+      </c>
+      <c r="B287" t="str">
+        <v>Challenge 42</v>
+      </c>
+      <c r="C287" t="str">
+        <v>Celadon Gym</v>
+      </c>
+      <c r="D287" t="str">
+        <v/>
+      </c>
+      <c r="E287" t="str">
+        <v/>
+      </c>
+      <c r="F287" t="str">
+        <v/>
+      </c>
+      <c r="G287" t="str">
+        <v/>
+      </c>
+      <c r="H287" t="str">
+        <v/>
+      </c>
+      <c r="I287" t="str">
+        <v/>
+      </c>
+      <c r="J287" t="str">
+        <v/>
+      </c>
+      <c r="K287" t="str">
+        <v/>
+      </c>
+      <c r="L287" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M287" t="str">
+        <v>Saffron Gym</v>
+      </c>
+      <c r="N287" t="str">
+        <v>{"earnBadge":{"name":"Badge 12","leader":"Erika","badgeCount":12}}</v>
+      </c>
+      <c r="O287" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>Challenge 42</v>
+      </c>
+      <c r="B288" t="str">
+        <v>Challenge 43</v>
+      </c>
+      <c r="C288" t="str">
+        <v>Saffron Gym</v>
+      </c>
+      <c r="D288" t="str">
+        <v/>
+      </c>
+      <c r="E288" t="str">
+        <v/>
+      </c>
+      <c r="F288" t="str">
+        <v/>
+      </c>
+      <c r="G288" t="str">
+        <v/>
+      </c>
+      <c r="H288" t="str">
+        <v/>
+      </c>
+      <c r="I288" t="str">
+        <v/>
+      </c>
+      <c r="J288" t="str">
+        <v/>
+      </c>
+      <c r="K288" t="str">
+        <v/>
+      </c>
+      <c r="L288" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M288" t="str">
+        <v>Route 12</v>
+      </c>
+      <c r="N288" t="str">
+        <v>{"earnBadge":{"name":"Badge 13","leader":"Sabrina","badgeCount":13}}</v>
+      </c>
+      <c r="O288" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>Challenge 44</v>
+      </c>
+      <c r="B289" t="str">
+        <v>Challenge 45</v>
+      </c>
+      <c r="C289" t="str">
+        <v>Fuschia Gym</v>
+      </c>
+      <c r="D289" t="str">
+        <v/>
+      </c>
+      <c r="E289" t="str">
+        <v/>
+      </c>
+      <c r="F289" t="str">
+        <v/>
+      </c>
+      <c r="G289" t="str">
+        <v/>
+      </c>
+      <c r="H289" t="str">
+        <v/>
+      </c>
+      <c r="I289" t="str">
+        <v/>
+      </c>
+      <c r="J289" t="str">
+        <v/>
+      </c>
+      <c r="K289" t="str">
+        <v/>
+      </c>
+      <c r="L289" t="str">
+        <v>No</v>
+      </c>
+      <c r="M289" t="str">
+        <v>Cycling Road, Sea Routes</v>
+      </c>
+      <c r="N289" t="str">
+        <v>{"earnBadge":{"name":"Badge 14","leader":"Koga","badgeCount":14}}</v>
+      </c>
+      <c r="O289" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>Challenge 46</v>
+      </c>
+      <c r="B290" t="str">
+        <v>Challenge 47</v>
+      </c>
+      <c r="C290" t="str">
+        <v>Cinnabar Gym</v>
+      </c>
+      <c r="D290" t="str">
+        <v/>
+      </c>
+      <c r="E290" t="str">
+        <v/>
+      </c>
+      <c r="F290" t="str">
+        <v/>
+      </c>
+      <c r="G290" t="str">
+        <v/>
+      </c>
+      <c r="H290" t="str">
+        <v/>
+      </c>
+      <c r="I290" t="str">
+        <v/>
+      </c>
+      <c r="J290" t="str">
+        <v/>
+      </c>
+      <c r="K290" t="str">
+        <v/>
+      </c>
+      <c r="L290" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M290" t="str">
+        <v>Viridian Gym, Trade With Friends Hub, Battle Stadium</v>
+      </c>
+      <c r="N290" t="str">
+        <v>{"earnBadge":{"name":"Badge 15","leader":"Blaine","badgeCount":15}}</v>
+      </c>
+      <c r="O290" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>Challenge 47</v>
+      </c>
+      <c r="B291" t="str">
+        <v>Challenge 48</v>
+      </c>
+      <c r="C291" t="str">
+        <v>Viridian Gym</v>
+      </c>
+      <c r="D291" t="str">
+        <v/>
+      </c>
+      <c r="E291" t="str">
+        <v/>
+      </c>
+      <c r="F291" t="str">
+        <v/>
+      </c>
+      <c r="G291" t="str">
+        <v/>
+      </c>
+      <c r="H291" t="str">
+        <v/>
+      </c>
+      <c r="I291" t="str">
+        <v/>
+      </c>
+      <c r="J291" t="str">
+        <v/>
+      </c>
+      <c r="K291" t="str">
+        <v/>
+      </c>
+      <c r="L291" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M291" t="str">
+        <v>Red</v>
+      </c>
+      <c r="N291" t="str">
+        <v>{"earnBadge":{"name":"Badge 16","leader":"Giovanni","badgeCount":16}}</v>
+      </c>
+      <c r="O291" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>Challenge 48</v>
+      </c>
+      <c r="B292" t="str">
+        <v>Challenge 49</v>
+      </c>
+      <c r="C292" t="str">
+        <v>Red</v>
+      </c>
+      <c r="D292" t="str">
+        <v/>
+      </c>
+      <c r="E292" t="str">
+        <v/>
+      </c>
+      <c r="F292" t="str">
+        <v/>
+      </c>
+      <c r="G292" t="str">
+        <v/>
+      </c>
+      <c r="H292" t="str">
+        <v/>
+      </c>
+      <c r="I292" t="str">
+        <v/>
+      </c>
+      <c r="J292" t="str">
+        <v/>
+      </c>
+      <c r="K292" t="str">
+        <v/>
+      </c>
+      <c r="L292" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M292" t="str">
+        <v>Travel to a new Region, Keys to Temporal Sanctuary Challenge</v>
+      </c>
+      <c r="N292" t="str">
+        <v>{"defeatRed":true}</v>
+      </c>
+      <c r="O292" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>Challenge 49</v>
+      </c>
+      <c r="B293" t="str">
+        <v>Keys to Temporal Sanctuary Challenge</v>
+      </c>
+      <c r="C293" t="str">
+        <v>Keys to Temporal Sanctuary Challenge</v>
+      </c>
+      <c r="D293" t="str">
+        <v/>
+      </c>
+      <c r="E293" t="str">
+        <v/>
+      </c>
+      <c r="F293" t="str">
+        <v/>
+      </c>
+      <c r="G293" t="str">
+        <v/>
+      </c>
+      <c r="H293" t="str">
+        <v/>
+      </c>
+      <c r="I293" t="str">
+        <v/>
+      </c>
+      <c r="J293" t="str">
+        <v/>
+      </c>
+      <c r="K293" t="str">
+        <v/>
+      </c>
+      <c r="L293" t="str">
+        <v>No</v>
+      </c>
+      <c r="M293" t="str">
+        <v>Temporal Sanctuary Spot</v>
+      </c>
+      <c r="N293" t="str">
+        <v>{"completeChallenges":["Johto Extra Challenge 5","Extra Challenge (Roaming)","Kanto Extra Challenge 6","Challenge 49"]}</v>
+      </c>
+      <c r="O293" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O274"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O293"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F64"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -14191,9 +15084,389 @@
         <v/>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Challenge 4</v>
+      </c>
+      <c r="B46" t="str">
+        <v>{"earnBadge":{"name":"Zephyr Badge","leader":"Falkner","badgeCount":1}}</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Ruins of Alph</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Challenge 9</v>
+      </c>
+      <c r="B47" t="str">
+        <v>{"earnBadge":{"name":"Hive Badge","leader":"Bugsy","badgeCount":2}}</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Ilex Forest</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Challenge 12</v>
+      </c>
+      <c r="B48" t="str">
+        <v>{"earnBadge":{"name":"Plain Badge","leader":"Whitney","badgeCount":3}}</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Route 35, Extra Challenge (Roaming)</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Challenge 18</v>
+      </c>
+      <c r="B49" t="str">
+        <v>{"earnBadge":{"name":"Fog Badge","leader":"Morty","badgeCount":4}}</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Route 38</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Challenge 22</v>
+      </c>
+      <c r="B50" t="str">
+        <v>{"earnBadge":{"name":"Storm Badge","leader":"Chuck","badgeCount":5}}</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Route 47</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Challenge 25</v>
+      </c>
+      <c r="B51" t="str">
+        <v>{"earnBadge":{"name":"Mineral Badge","leader":"Jasmine","badgeCount":6}}</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Mount Mortar</v>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Challenge 27</v>
+      </c>
+      <c r="B52" t="str">
+        <v>{"earnBadge":{"name":"Glacier Badge","leader":"Pryce","badgeCount":7}}</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Standard Fishing Spot</v>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Challenge 31</v>
+      </c>
+      <c r="B53" t="str">
+        <v>{"earnBadge":{"name":"Rising Badge","leader":"Clair","badgeCount":8}}</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Big Fishing Spot</v>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Challenge 35</v>
+      </c>
+      <c r="B54" t="str">
+        <v>{"defeatJohtoChampion":true}</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Win Pokemon League</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Viridian Forest</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Challenge 37</v>
+      </c>
+      <c r="B55" t="str">
+        <v>{"earnBadge":{"name":"Badge 9","leader":"Brock","badgeCount":9}}</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Mount Moon</v>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Challenge 39</v>
+      </c>
+      <c r="B56" t="str">
+        <v>{"earnBadge":{"name":"Badge 10","leader":"Misty","badgeCount":10}}</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Vermilion Gym</v>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Challenge 40</v>
+      </c>
+      <c r="B57" t="str">
+        <v>{"earnBadge":{"name":"Badge 11","leader":"Lt. Surge","badgeCount":11}}</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Route 8, Diglett Cave</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Challenge 42</v>
+      </c>
+      <c r="B58" t="str">
+        <v>{"earnBadge":{"name":"Badge 12","leader":"Erika","badgeCount":12}}</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Saffron Gym</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Challenge 43</v>
+      </c>
+      <c r="B59" t="str">
+        <v>{"earnBadge":{"name":"Badge 13","leader":"Sabrina","badgeCount":13}}</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Route 12</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Challenge 45</v>
+      </c>
+      <c r="B60" t="str">
+        <v>{"earnBadge":{"name":"Badge 14","leader":"Koga","badgeCount":14}}</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Cycling Road, Sea Routes</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Challenge 47</v>
+      </c>
+      <c r="B61" t="str">
+        <v>{"earnBadge":{"name":"Badge 15","leader":"Blaine","badgeCount":15}}</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Viridian Gym, Trade With Friends Hub, Battle Stadium</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Challenge 48</v>
+      </c>
+      <c r="B62" t="str">
+        <v>{"earnBadge":{"name":"Badge 16","leader":"Giovanni","badgeCount":16}}</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Red</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Challenge 49</v>
+      </c>
+      <c r="B63" t="str">
+        <v>{"defeatRed":true}</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Defeat 250 pokemon</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Travel to a new Region, Keys to Temporal Sanctuary Challenge</v>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Keys to Temporal Sanctuary Challenge</v>
+      </c>
+      <c r="B64" t="str">
+        <v>{"completeChallenges":["Johto Extra Challenge 5","Extra Challenge (Roaming)","Kanto Extra Challenge 6","Challenge 49"]}</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Defeat 250 pokemon</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Temporal Sanctuary Spot</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F64"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/2_Johto_Data.xlsx
+++ b/2_Johto_Data.xlsx
@@ -3477,7 +3477,7 @@
         <v>8-12</v>
       </c>
       <c r="G66" t="str">
-        <v>6-8</v>
+        <v>7-9</v>
       </c>
       <c r="H66" s="1">
         <v>0.25</v>
@@ -3524,7 +3524,7 @@
         <v>8-12</v>
       </c>
       <c r="G67" t="str">
-        <v>6-8</v>
+        <v>7-9</v>
       </c>
       <c r="H67" s="1">
         <v>0.15</v>
@@ -3571,7 +3571,7 @@
         <v>8-12</v>
       </c>
       <c r="G68" t="str">
-        <v>6-8</v>
+        <v>7-9</v>
       </c>
       <c r="H68" s="1">
         <v>0.15</v>
@@ -3618,7 +3618,7 @@
         <v>8-12</v>
       </c>
       <c r="G69" t="str">
-        <v>6-8</v>
+        <v>7-9</v>
       </c>
       <c r="H69" s="1">
         <v>0.15</v>
@@ -3665,7 +3665,7 @@
         <v>8-12</v>
       </c>
       <c r="G70" t="str">
-        <v>6-8</v>
+        <v>7-9</v>
       </c>
       <c r="H70" s="1">
         <v>0.1</v>
@@ -3712,7 +3712,7 @@
         <v>8-12</v>
       </c>
       <c r="G71" t="str">
-        <v>6-8</v>
+        <v>7-9</v>
       </c>
       <c r="H71" s="1">
         <v>0.1</v>
@@ -3759,7 +3759,7 @@
         <v>8-12</v>
       </c>
       <c r="G72" t="str">
-        <v>6-8</v>
+        <v>7-9</v>
       </c>
       <c r="H72" s="1">
         <v>0.1</v>
@@ -4135,7 +4135,7 @@
         <v>13-17</v>
       </c>
       <c r="G80" t="str">
-        <v>13-16</v>
+        <v>14-17</v>
       </c>
       <c r="H80" s="1">
         <v>0.3</v>
@@ -4182,7 +4182,7 @@
         <v>12-16</v>
       </c>
       <c r="G81" t="str">
-        <v>13-16</v>
+        <v>14-17</v>
       </c>
       <c r="H81" s="1">
         <v>0.2</v>
@@ -4229,7 +4229,7 @@
         <v>12-16</v>
       </c>
       <c r="G82" t="str">
-        <v>13-16</v>
+        <v>14-17</v>
       </c>
       <c r="H82" s="1">
         <v>0.2</v>
@@ -4276,7 +4276,7 @@
         <v>13-17</v>
       </c>
       <c r="G83" t="str">
-        <v>13-16</v>
+        <v>14-17</v>
       </c>
       <c r="H83" s="1">
         <v>0.15</v>
@@ -4323,7 +4323,7 @@
         <v>13-17</v>
       </c>
       <c r="G84" t="str">
-        <v>13-16</v>
+        <v>14-17</v>
       </c>
       <c r="H84" s="1">
         <v>0.15</v>
@@ -4605,7 +4605,7 @@
         <v>20-25</v>
       </c>
       <c r="G90" t="str">
-        <v>18-21</v>
+        <v>19-22</v>
       </c>
       <c r="H90" s="1">
         <v>0.35</v>
@@ -4652,7 +4652,7 @@
         <v>20-25</v>
       </c>
       <c r="G91" t="str">
-        <v>18-21</v>
+        <v>19-22</v>
       </c>
       <c r="H91" s="1">
         <v>0.25</v>
@@ -4699,7 +4699,7 @@
         <v>19-24</v>
       </c>
       <c r="G92" t="str">
-        <v>18-21</v>
+        <v>19-22</v>
       </c>
       <c r="H92" s="1">
         <v>0.2</v>
@@ -4746,7 +4746,7 @@
         <v>19-24</v>
       </c>
       <c r="G93" t="str">
-        <v>18-21</v>
+        <v>19-22</v>
       </c>
       <c r="H93" s="1">
         <v>0.2</v>
@@ -4793,7 +4793,7 @@
         <v>20-25</v>
       </c>
       <c r="G94" t="str">
-        <v>20-23</v>
+        <v>21-24</v>
       </c>
       <c r="H94" s="1">
         <v>0.23</v>
@@ -4840,7 +4840,7 @@
         <v>20-25</v>
       </c>
       <c r="G95" t="str">
-        <v>20-23</v>
+        <v>21-24</v>
       </c>
       <c r="H95" s="1">
         <v>0.23</v>
@@ -4887,7 +4887,7 @@
         <v>20-25</v>
       </c>
       <c r="G96" t="str">
-        <v>20-23</v>
+        <v>21-24</v>
       </c>
       <c r="H96" s="1">
         <v>0.23</v>
@@ -4934,7 +4934,7 @@
         <v>24-28</v>
       </c>
       <c r="G97" t="str">
-        <v>20-23</v>
+        <v>21-24</v>
       </c>
       <c r="H97" s="1">
         <v>0.09</v>
@@ -4981,7 +4981,7 @@
         <v>24-28</v>
       </c>
       <c r="G98" t="str">
-        <v>20-23</v>
+        <v>21-24</v>
       </c>
       <c r="H98" s="1">
         <v>0.09</v>
@@ -5028,7 +5028,7 @@
         <v>22-27</v>
       </c>
       <c r="G99" t="str">
-        <v>20-23</v>
+        <v>21-24</v>
       </c>
       <c r="H99" s="1">
         <v>0.13</v>
@@ -5310,7 +5310,7 @@
         <v>26-31</v>
       </c>
       <c r="G105" t="str">
-        <v>25-28</v>
+        <v>26-29</v>
       </c>
       <c r="H105" s="1">
         <v>0.28</v>
@@ -5357,7 +5357,7 @@
         <v>26-31</v>
       </c>
       <c r="G106" t="str">
-        <v>25-28</v>
+        <v>26-29</v>
       </c>
       <c r="H106" s="1">
         <v>0.29</v>
@@ -5404,7 +5404,7 @@
         <v>27-32</v>
       </c>
       <c r="G107" t="str">
-        <v>25-28</v>
+        <v>26-29</v>
       </c>
       <c r="H107" s="1">
         <v>0.19</v>
@@ -5451,7 +5451,7 @@
         <v>27-32</v>
       </c>
       <c r="G108" t="str">
-        <v>25-28</v>
+        <v>26-29</v>
       </c>
       <c r="H108" s="1">
         <v>0.19</v>
@@ -5498,7 +5498,7 @@
         <v>26-32</v>
       </c>
       <c r="G109" t="str">
-        <v>25-28</v>
+        <v>26-29</v>
       </c>
       <c r="H109" s="1">
         <v>0.05</v>
@@ -5545,7 +5545,7 @@
         <v>28-33</v>
       </c>
       <c r="G110" t="str">
-        <v>27-30</v>
+        <v>28-31</v>
       </c>
       <c r="H110" s="1">
         <v>0.25</v>
@@ -5592,7 +5592,7 @@
         <v>27-32</v>
       </c>
       <c r="G111" t="str">
-        <v>27-30</v>
+        <v>28-31</v>
       </c>
       <c r="H111" s="1">
         <v>0.25</v>
@@ -5639,7 +5639,7 @@
         <v>27-32</v>
       </c>
       <c r="G112" t="str">
-        <v>27-30</v>
+        <v>28-31</v>
       </c>
       <c r="H112" s="1">
         <v>0.15</v>
@@ -5686,7 +5686,7 @@
         <v>28-33</v>
       </c>
       <c r="G113" t="str">
-        <v>27-30</v>
+        <v>28-31</v>
       </c>
       <c r="H113" s="1">
         <v>0.15</v>
@@ -5733,7 +5733,7 @@
         <v>32-36</v>
       </c>
       <c r="G114" t="str">
-        <v>27-30</v>
+        <v>28-31</v>
       </c>
       <c r="H114" s="1">
         <v>0.1</v>
@@ -5780,7 +5780,7 @@
         <v>32-37</v>
       </c>
       <c r="G115" t="str">
-        <v>27-30</v>
+        <v>28-31</v>
       </c>
       <c r="H115" s="1">
         <v>0.1</v>
@@ -5874,7 +5874,7 @@
         <v>31-36</v>
       </c>
       <c r="G117" t="str">
-        <v>30-33</v>
+        <v>31-34</v>
       </c>
       <c r="H117" s="1">
         <v>0.3</v>
@@ -5921,7 +5921,7 @@
         <v>31-36</v>
       </c>
       <c r="G118" t="str">
-        <v>30-33</v>
+        <v>31-34</v>
       </c>
       <c r="H118" s="1">
         <v>0.25</v>
@@ -5968,7 +5968,7 @@
         <v>30-35</v>
       </c>
       <c r="G119" t="str">
-        <v>30-33</v>
+        <v>31-34</v>
       </c>
       <c r="H119" s="1">
         <v>0.15</v>
@@ -6015,7 +6015,7 @@
         <v>31-36</v>
       </c>
       <c r="G120" t="str">
-        <v>30-33</v>
+        <v>31-34</v>
       </c>
       <c r="H120" s="1">
         <v>0.2</v>
@@ -6062,7 +6062,7 @@
         <v>32-37</v>
       </c>
       <c r="G121" t="str">
-        <v>30-33</v>
+        <v>31-34</v>
       </c>
       <c r="H121" s="1">
         <v>0.1</v>
@@ -6109,7 +6109,7 @@
         <v>33-38</v>
       </c>
       <c r="G122" t="str">
-        <v>32-35</v>
+        <v>33-36</v>
       </c>
       <c r="H122" s="1">
         <v>0.25</v>
@@ -6156,7 +6156,7 @@
         <v>34-39</v>
       </c>
       <c r="G123" t="str">
-        <v>32-35</v>
+        <v>33-36</v>
       </c>
       <c r="H123" s="1">
         <v>0.25</v>
@@ -6203,7 +6203,7 @@
         <v>34-39</v>
       </c>
       <c r="G124" t="str">
-        <v>32-35</v>
+        <v>33-36</v>
       </c>
       <c r="H124" s="1">
         <v>0.15</v>
@@ -6250,7 +6250,7 @@
         <v>33-38</v>
       </c>
       <c r="G125" t="str">
-        <v>32-35</v>
+        <v>33-36</v>
       </c>
       <c r="H125" s="1">
         <v>0.15</v>
@@ -6297,7 +6297,7 @@
         <v>35-40</v>
       </c>
       <c r="G126" t="str">
-        <v>32-35</v>
+        <v>33-36</v>
       </c>
       <c r="H126" s="1">
         <v>0.1</v>
@@ -6344,7 +6344,7 @@
         <v>35-40</v>
       </c>
       <c r="G127" t="str">
-        <v>32-35</v>
+        <v>33-36</v>
       </c>
       <c r="H127" s="1">
         <v>0.1</v>
@@ -6391,7 +6391,7 @@
         <v>36-41</v>
       </c>
       <c r="G128" t="str">
-        <v>34-37</v>
+        <v>35-38</v>
       </c>
       <c r="H128" s="1">
         <v>0.2</v>
@@ -6438,7 +6438,7 @@
         <v>36-41</v>
       </c>
       <c r="G129" t="str">
-        <v>34-37</v>
+        <v>35-38</v>
       </c>
       <c r="H129" s="1">
         <v>0.15</v>
@@ -6485,7 +6485,7 @@
         <v>36-41</v>
       </c>
       <c r="G130" t="str">
-        <v>34-37</v>
+        <v>35-38</v>
       </c>
       <c r="H130" s="1">
         <v>0.15</v>
@@ -6532,7 +6532,7 @@
         <v>36-41</v>
       </c>
       <c r="G131" t="str">
-        <v>34-37</v>
+        <v>35-38</v>
       </c>
       <c r="H131" s="1">
         <v>0.15</v>
@@ -6579,7 +6579,7 @@
         <v>36-41</v>
       </c>
       <c r="G132" t="str">
-        <v>34-37</v>
+        <v>35-38</v>
       </c>
       <c r="H132" s="1">
         <v>0.15</v>
@@ -6626,7 +6626,7 @@
         <v>37-42</v>
       </c>
       <c r="G133" t="str">
-        <v>34-37</v>
+        <v>35-38</v>
       </c>
       <c r="H133" s="1">
         <v>0.1</v>
@@ -6673,7 +6673,7 @@
         <v>37-42</v>
       </c>
       <c r="G134" t="str">
-        <v>34-37</v>
+        <v>35-38</v>
       </c>
       <c r="H134" s="1">
         <v>0.1</v>
@@ -6767,7 +6767,7 @@
         <v>38-43</v>
       </c>
       <c r="G136" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H136" s="1">
         <v>0.25</v>
@@ -6814,7 +6814,7 @@
         <v>38-43</v>
       </c>
       <c r="G137" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H137" s="1">
         <v>0.25</v>
@@ -6861,7 +6861,7 @@
         <v>38-43</v>
       </c>
       <c r="G138" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H138" s="1">
         <v>0.15</v>
@@ -6908,7 +6908,7 @@
         <v>38-43</v>
       </c>
       <c r="G139" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H139" s="1">
         <v>0.15</v>
@@ -6955,7 +6955,7 @@
         <v>38-43</v>
       </c>
       <c r="G140" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H140" s="1">
         <v>0.1</v>
@@ -7002,7 +7002,7 @@
         <v>38-43</v>
       </c>
       <c r="G141" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H141" s="1">
         <v>0.1</v>
@@ -7049,7 +7049,7 @@
         <v>39-44</v>
       </c>
       <c r="G142" t="str">
-        <v>64-70</v>
+        <v>66-72</v>
       </c>
       <c r="H142" s="1">
         <v>0.25</v>
@@ -7096,7 +7096,7 @@
         <v>39-44</v>
       </c>
       <c r="G143" t="str">
-        <v>64-70</v>
+        <v>66-72</v>
       </c>
       <c r="H143" s="1">
         <v>0.25</v>
@@ -7143,7 +7143,7 @@
         <v>40-45</v>
       </c>
       <c r="G144" t="str">
-        <v>64-70</v>
+        <v>66-72</v>
       </c>
       <c r="H144" s="1">
         <v>0.15</v>
@@ -7190,7 +7190,7 @@
         <v>40-45</v>
       </c>
       <c r="G145" t="str">
-        <v>64-70</v>
+        <v>66-72</v>
       </c>
       <c r="H145" s="1">
         <v>0.15</v>
@@ -7237,7 +7237,7 @@
         <v>39-44</v>
       </c>
       <c r="G146" t="str">
-        <v>64-70</v>
+        <v>66-72</v>
       </c>
       <c r="H146" s="1">
         <v>0.1</v>
@@ -7284,7 +7284,7 @@
         <v>39-44</v>
       </c>
       <c r="G147" t="str">
-        <v>64-70</v>
+        <v>66-72</v>
       </c>
       <c r="H147" s="1">
         <v>0.1</v>
@@ -7378,7 +7378,7 @@
         <v>40-45</v>
       </c>
       <c r="G149" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H149" s="1">
         <v>0.2</v>
@@ -7425,7 +7425,7 @@
         <v>40-45</v>
       </c>
       <c r="G150" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H150" s="1">
         <v>0.2</v>
@@ -7472,7 +7472,7 @@
         <v>42-47</v>
       </c>
       <c r="G151" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H151" s="1">
         <v>0.15</v>
@@ -7519,7 +7519,7 @@
         <v>42-47</v>
       </c>
       <c r="G152" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H152" s="1">
         <v>0.15</v>
@@ -7566,7 +7566,7 @@
         <v>42-47</v>
       </c>
       <c r="G153" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H153" s="1">
         <v>0.1</v>
@@ -7613,7 +7613,7 @@
         <v>42-47</v>
       </c>
       <c r="G154" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H154" s="1">
         <v>0.1</v>
@@ -7660,7 +7660,7 @@
         <v>43-48</v>
       </c>
       <c r="G155" t="str">
-        <v>39-42</v>
+        <v>40-44</v>
       </c>
       <c r="H155" s="1">
         <v>0.1</v>
@@ -7754,7 +7754,7 @@
         <v>48-54</v>
       </c>
       <c r="G157" t="str">
-        <v>41-45</v>
+        <v>42-46</v>
       </c>
       <c r="H157" s="1">
         <v>0.35</v>
@@ -7801,7 +7801,7 @@
         <v>48-54</v>
       </c>
       <c r="G158" t="str">
-        <v>41-45</v>
+        <v>42-46</v>
       </c>
       <c r="H158" s="1">
         <v>0.3</v>
@@ -7848,7 +7848,7 @@
         <v>49-55</v>
       </c>
       <c r="G159" t="str">
-        <v>41-45</v>
+        <v>42-46</v>
       </c>
       <c r="H159" s="1">
         <v>0.25</v>
@@ -7895,7 +7895,7 @@
         <v>50-56</v>
       </c>
       <c r="G160" t="str">
-        <v>41-45</v>
+        <v>42-46</v>
       </c>
       <c r="H160" s="1">
         <v>0.1</v>
@@ -7942,7 +7942,7 @@
         <v>52-57</v>
       </c>
       <c r="G161" t="str">
-        <v>43-47</v>
+        <v>45-49</v>
       </c>
       <c r="H161" s="1">
         <v>0.25</v>
@@ -7989,7 +7989,7 @@
         <v>50-55</v>
       </c>
       <c r="G162" t="str">
-        <v>43-47</v>
+        <v>45-49</v>
       </c>
       <c r="H162" s="1">
         <v>0.25</v>
@@ -8036,7 +8036,7 @@
         <v>52-57</v>
       </c>
       <c r="G163" t="str">
-        <v>43-47</v>
+        <v>45-49</v>
       </c>
       <c r="H163" s="1">
         <v>0.15</v>
@@ -8083,7 +8083,7 @@
         <v>54-59</v>
       </c>
       <c r="G164" t="str">
-        <v>43-47</v>
+        <v>45-49</v>
       </c>
       <c r="H164" s="1">
         <v>0.15</v>
@@ -8130,7 +8130,7 @@
         <v>53-58</v>
       </c>
       <c r="G165" t="str">
-        <v>43-47</v>
+        <v>45-49</v>
       </c>
       <c r="H165" s="1">
         <v>0.1</v>
@@ -8177,7 +8177,7 @@
         <v>54-60</v>
       </c>
       <c r="G166" t="str">
-        <v>43-47</v>
+        <v>45-49</v>
       </c>
       <c r="H166" s="1">
         <v>0.1</v>
@@ -8224,7 +8224,7 @@
         <v>58-64</v>
       </c>
       <c r="G167" t="str">
-        <v>46-50</v>
+        <v>47-51</v>
       </c>
       <c r="H167" s="1">
         <v>0.19</v>
@@ -8271,7 +8271,7 @@
         <v>58-64</v>
       </c>
       <c r="G168" t="str">
-        <v>46-50</v>
+        <v>47-51</v>
       </c>
       <c r="H168" s="1">
         <v>0.19</v>
@@ -8318,7 +8318,7 @@
         <v>57-63</v>
       </c>
       <c r="G169" t="str">
-        <v>46-50</v>
+        <v>47-51</v>
       </c>
       <c r="H169" s="1">
         <v>0.15</v>
@@ -8365,7 +8365,7 @@
         <v>58-64</v>
       </c>
       <c r="G170" t="str">
-        <v>46-50</v>
+        <v>47-51</v>
       </c>
       <c r="H170" s="1">
         <v>0.23</v>
@@ -8412,7 +8412,7 @@
         <v>57-64</v>
       </c>
       <c r="G171" t="str">
-        <v>46-50</v>
+        <v>47-51</v>
       </c>
       <c r="H171" s="1">
         <v>0.07</v>
@@ -8459,7 +8459,7 @@
         <v>57-64</v>
       </c>
       <c r="G172" t="str">
-        <v>46-50</v>
+        <v>47-51</v>
       </c>
       <c r="H172" s="1">
         <v>0.08</v>
@@ -8506,7 +8506,7 @@
         <v>57-64</v>
       </c>
       <c r="G173" t="str">
-        <v>46-50</v>
+        <v>47-51</v>
       </c>
       <c r="H173" s="1">
         <v>0.09</v>
@@ -8600,7 +8600,7 @@
         <v>62-68</v>
       </c>
       <c r="G175" t="str">
-        <v>48-52</v>
+        <v>50-55</v>
       </c>
       <c r="H175" s="1">
         <v>0.3</v>
@@ -8647,7 +8647,7 @@
         <v>63-69</v>
       </c>
       <c r="G176" t="str">
-        <v>48-52</v>
+        <v>50-55</v>
       </c>
       <c r="H176" s="1">
         <v>0.25</v>
@@ -8694,7 +8694,7 @@
         <v>62-68</v>
       </c>
       <c r="G177" t="str">
-        <v>48-52</v>
+        <v>50-55</v>
       </c>
       <c r="H177" s="1">
         <v>0.2</v>
@@ -8741,7 +8741,7 @@
         <v>64-70</v>
       </c>
       <c r="G178" t="str">
-        <v>48-52</v>
+        <v>50-55</v>
       </c>
       <c r="H178" s="1">
         <v>0.1</v>
@@ -8788,7 +8788,7 @@
         <v>64-70</v>
       </c>
       <c r="G179" t="str">
-        <v>48-52</v>
+        <v>50-55</v>
       </c>
       <c r="H179" s="1">
         <v>0.1</v>
@@ -8835,7 +8835,7 @@
         <v>65-71</v>
       </c>
       <c r="G180" t="str">
-        <v>48-52</v>
+        <v>50-55</v>
       </c>
       <c r="H180" s="1">
         <v>0.05</v>
@@ -8882,7 +8882,7 @@
         <v>64-70</v>
       </c>
       <c r="G181" t="str">
-        <v>50-55</v>
+        <v>52-57</v>
       </c>
       <c r="H181" s="1">
         <v>0.25</v>
@@ -8929,7 +8929,7 @@
         <v>63-69</v>
       </c>
       <c r="G182" t="str">
-        <v>50-55</v>
+        <v>52-57</v>
       </c>
       <c r="H182" s="1">
         <v>0.15</v>
@@ -8976,7 +8976,7 @@
         <v>64-70</v>
       </c>
       <c r="G183" t="str">
-        <v>50-55</v>
+        <v>52-57</v>
       </c>
       <c r="H183" s="1">
         <v>0.15</v>
@@ -9023,7 +9023,7 @@
         <v>68-74</v>
       </c>
       <c r="G184" t="str">
-        <v>50-55</v>
+        <v>52-57</v>
       </c>
       <c r="H184" s="1">
         <v>0.1</v>
@@ -9070,7 +9070,7 @@
         <v>65-71</v>
       </c>
       <c r="G185" t="str">
-        <v>50-55</v>
+        <v>52-57</v>
       </c>
       <c r="H185" s="1">
         <v>0.1</v>
@@ -9117,7 +9117,7 @@
         <v>64-70</v>
       </c>
       <c r="G186" t="str">
-        <v>50-55</v>
+        <v>52-57</v>
       </c>
       <c r="H186" s="1">
         <v>0.25</v>
@@ -9164,7 +9164,7 @@
         <v>68-74</v>
       </c>
       <c r="G187" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="H187" s="1">
         <v>0.4</v>
@@ -9211,7 +9211,7 @@
         <v>66-72</v>
       </c>
       <c r="G188" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="H188" s="1">
         <v>0.35</v>
@@ -9258,7 +9258,7 @@
         <v>70-76</v>
       </c>
       <c r="G189" t="str">
-        <v>53-58</v>
+        <v>54-59</v>
       </c>
       <c r="H189" s="1">
         <v>0.25</v>
@@ -9352,7 +9352,7 @@
         <v>72-76</v>
       </c>
       <c r="G191" t="str">
-        <v>55-60</v>
+        <v>57-62</v>
       </c>
       <c r="H191" s="1">
         <v>0.23</v>
@@ -9399,7 +9399,7 @@
         <v>72-76</v>
       </c>
       <c r="G192" t="str">
-        <v>55-60</v>
+        <v>57-62</v>
       </c>
       <c r="H192" s="1">
         <v>0.24</v>
@@ -9446,7 +9446,7 @@
         <v>74-78</v>
       </c>
       <c r="G193" t="str">
-        <v>55-60</v>
+        <v>57-62</v>
       </c>
       <c r="H193" s="1">
         <v>0.14</v>
@@ -9493,7 +9493,7 @@
         <v>74-78</v>
       </c>
       <c r="G194" t="str">
-        <v>55-60</v>
+        <v>57-62</v>
       </c>
       <c r="H194" s="1">
         <v>0.14</v>
@@ -9540,7 +9540,7 @@
         <v>75-78</v>
       </c>
       <c r="G195" t="str">
-        <v>55-60</v>
+        <v>57-62</v>
       </c>
       <c r="H195" s="1">
         <v>0.1</v>
@@ -9587,7 +9587,7 @@
         <v>75-78</v>
       </c>
       <c r="G196" t="str">
-        <v>55-60</v>
+        <v>57-62</v>
       </c>
       <c r="H196" s="1">
         <v>0.1</v>
@@ -9634,7 +9634,7 @@
         <v>72-78</v>
       </c>
       <c r="G197" t="str">
-        <v>55-60</v>
+        <v>57-62</v>
       </c>
       <c r="H197" s="1">
         <v>0.05</v>
@@ -9728,7 +9728,7 @@
         <v>76-80</v>
       </c>
       <c r="G199" t="str">
-        <v>57-62</v>
+        <v>59-64</v>
       </c>
       <c r="H199" s="1">
         <v>0.22</v>
@@ -9775,7 +9775,7 @@
         <v>76-81</v>
       </c>
       <c r="G200" t="str">
-        <v>57-62</v>
+        <v>59-64</v>
       </c>
       <c r="H200" s="1">
         <v>0.23</v>
@@ -9822,7 +9822,7 @@
         <v>78-82</v>
       </c>
       <c r="G201" t="str">
-        <v>57-62</v>
+        <v>59-64</v>
       </c>
       <c r="H201" s="1">
         <v>0.18</v>
@@ -9869,7 +9869,7 @@
         <v>77-81</v>
       </c>
       <c r="G202" t="str">
-        <v>57-62</v>
+        <v>59-64</v>
       </c>
       <c r="H202" s="1">
         <v>0.14</v>
@@ -9916,7 +9916,7 @@
         <v>78-82</v>
       </c>
       <c r="G203" t="str">
-        <v>57-62</v>
+        <v>59-64</v>
       </c>
       <c r="H203" s="1">
         <v>0.14</v>
@@ -9963,7 +9963,7 @@
         <v>76-82</v>
       </c>
       <c r="G204" t="str">
-        <v>57-62</v>
+        <v>59-64</v>
       </c>
       <c r="H204" s="1">
         <v>0.09</v>
@@ -10104,7 +10104,7 @@
         <v>82-86</v>
       </c>
       <c r="G207" t="str">
-        <v>60-66</v>
+        <v>62-68</v>
       </c>
       <c r="H207" s="1">
         <v>0.4</v>
@@ -10151,7 +10151,7 @@
         <v>83-87</v>
       </c>
       <c r="G208" t="str">
-        <v>60-66</v>
+        <v>62-68</v>
       </c>
       <c r="H208" s="1">
         <v>0.3</v>
@@ -10198,7 +10198,7 @@
         <v>83-87</v>
       </c>
       <c r="G209" t="str">
-        <v>60-66</v>
+        <v>62-68</v>
       </c>
       <c r="H209" s="1">
         <v>0.3</v>
@@ -10339,7 +10339,7 @@
         <v>84-88</v>
       </c>
       <c r="G212" t="str">
-        <v>62-68</v>
+        <v>64-70</v>
       </c>
       <c r="H212" s="1">
         <v>0.25</v>
@@ -10386,7 +10386,7 @@
         <v>84-88</v>
       </c>
       <c r="G213" t="str">
-        <v>62-68</v>
+        <v>64-70</v>
       </c>
       <c r="H213" s="1">
         <v>0.25</v>
@@ -10433,7 +10433,7 @@
         <v>85-89</v>
       </c>
       <c r="G214" t="str">
-        <v>62-68</v>
+        <v>64-70</v>
       </c>
       <c r="H214" s="1">
         <v>0.2</v>
@@ -10480,7 +10480,7 @@
         <v>86-89</v>
       </c>
       <c r="G215" t="str">
-        <v>62-68</v>
+        <v>64-70</v>
       </c>
       <c r="H215" s="1">
         <v>0.15</v>
@@ -10527,7 +10527,7 @@
         <v>86-89</v>
       </c>
       <c r="G216" t="str">
-        <v>62-68</v>
+        <v>64-70</v>
       </c>
       <c r="H216" s="1">
         <v>0.1</v>
@@ -10574,7 +10574,7 @@
         <v>88-89</v>
       </c>
       <c r="G217" t="str">
-        <v>62-68</v>
+        <v>64-70</v>
       </c>
       <c r="H217" s="1">
         <v>0.05</v>
@@ -10668,7 +10668,7 @@
         <v>90-94</v>
       </c>
       <c r="G219" t="str">
-        <v>67-73</v>
+        <v>69-75</v>
       </c>
       <c r="H219" s="1">
         <v>0.25</v>
@@ -10715,7 +10715,7 @@
         <v>90-94</v>
       </c>
       <c r="G220" t="str">
-        <v>67-73</v>
+        <v>69-75</v>
       </c>
       <c r="H220" s="1">
         <v>0.25</v>
@@ -10762,7 +10762,7 @@
         <v>91-94</v>
       </c>
       <c r="G221" t="str">
-        <v>67-73</v>
+        <v>69-75</v>
       </c>
       <c r="H221" s="1">
         <v>0.15</v>
@@ -10809,7 +10809,7 @@
         <v>91-94</v>
       </c>
       <c r="G222" t="str">
-        <v>67-73</v>
+        <v>69-75</v>
       </c>
       <c r="H222" s="1">
         <v>0.15</v>
@@ -10856,7 +10856,7 @@
         <v>92-94</v>
       </c>
       <c r="G223" t="str">
-        <v>67-73</v>
+        <v>69-75</v>
       </c>
       <c r="H223" s="1">
         <v>0.1</v>
@@ -10903,7 +10903,7 @@
         <v>92-94</v>
       </c>
       <c r="G224" t="str">
-        <v>67-73</v>
+        <v>69-75</v>
       </c>
       <c r="H224" s="1">
         <v>0.1</v>
